--- a/EEE2000-metadata_mapping.xlsx
+++ b/EEE2000-metadata_mapping.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10905"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\amw23\Documents\GitHub\cci_data_bridge_inputs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rhys.r.evans/Documents/CEDA/CCI/cci_data_bridge_inputs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{594DCA07-06B5-4D5C-ABFA-EF38438BEDEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B9F3D91-8869-9442-A948-917318D39AD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1125" yWindow="1125" windowWidth="28800" windowHeight="15285" xr2:uid="{B9DA58AC-C110-4CBA-A19B-6F37B44EEA38}"/>
+    <workbookView xWindow="8740" yWindow="1280" windowWidth="28800" windowHeight="15280" xr2:uid="{B9DA58AC-C110-4CBA-A19B-6F37B44EEA38}"/>
   </bookViews>
   <sheets>
     <sheet name="Mapping" sheetId="2" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1679" uniqueCount="451">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1722" uniqueCount="460">
   <si>
     <t>Dataset 1</t>
   </si>
@@ -1729,6 +1729,33 @@
   </si>
   <si>
     <t>esacci.GHG.satellite-orbit-frequency.L2.CH4.TANSO-FTS-2.GOSAT-2.SRPR.v2-0-2.r1</t>
+  </si>
+  <si>
+    <t>https://www.globalcarbonproject.org/reccap/overview.htm</t>
+  </si>
+  <si>
+    <t>RECCAP-2</t>
+  </si>
+  <si>
+    <t>Uses</t>
+  </si>
+  <si>
+    <t>IsUsedBy</t>
+  </si>
+  <si>
+    <t>https://catalogue.ceda.ac.uk/uuid/1d01d0efb6c24c218489605b5aa44cf5</t>
+  </si>
+  <si>
+    <t>This dataset has been used within RECCAP-2</t>
+  </si>
+  <si>
+    <t>This dataset is an output of RECCAP-2</t>
+  </si>
+  <si>
+    <t>Indicates A uses B</t>
+  </si>
+  <si>
+    <t>Indicates A is used by B</t>
   </si>
 </sst>
 </file>
@@ -2281,25 +2308,25 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9CC0B67C-1229-4907-A814-DF79422D0B81}">
-  <dimension ref="A1:M169"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:M170"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="36.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19.42578125" customWidth="1"/>
-    <col min="3" max="3" width="30.140625" customWidth="1"/>
-    <col min="4" max="4" width="38.5703125" customWidth="1"/>
-    <col min="5" max="5" width="23.42578125" customWidth="1"/>
-    <col min="6" max="6" width="23.5703125" style="6" customWidth="1"/>
-    <col min="7" max="7" width="30.42578125" style="9" customWidth="1"/>
-    <col min="8" max="8" width="30.42578125" style="12" customWidth="1"/>
-    <col min="9" max="9" width="42.85546875" style="4" customWidth="1"/>
-    <col min="10" max="10" width="19.42578125" style="4" customWidth="1"/>
-    <col min="11" max="11" width="19.42578125" customWidth="1"/>
-    <col min="12" max="12" width="23.42578125" style="6" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="47.140625" style="8" customWidth="1"/>
+    <col min="1" max="1" width="36.83203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.5" customWidth="1"/>
+    <col min="3" max="3" width="30.1640625" customWidth="1"/>
+    <col min="4" max="4" width="38.5" customWidth="1"/>
+    <col min="5" max="5" width="23.5" customWidth="1"/>
+    <col min="6" max="6" width="23.5" style="6" customWidth="1"/>
+    <col min="7" max="7" width="30.5" style="9" customWidth="1"/>
+    <col min="8" max="8" width="30.5" style="12" customWidth="1"/>
+    <col min="9" max="9" width="42.83203125" style="4" customWidth="1"/>
+    <col min="10" max="10" width="19.5" style="4" customWidth="1"/>
+    <col min="11" max="11" width="19.5" customWidth="1"/>
+    <col min="12" max="12" width="23.5" style="6" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="47.1640625" style="8" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" ht="16" x14ac:dyDescent="0.2">
       <c r="A1" s="27" t="s">
         <v>0</v>
       </c>
@@ -2321,7 +2348,7 @@
       <c r="K1" s="3"/>
       <c r="M1" s="17"/>
     </row>
-    <row r="2" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>4</v>
       </c>
@@ -2358,7 +2385,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:13" ht="90" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:13" ht="80" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>13</v>
       </c>
@@ -2399,7 +2426,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="4" spans="1:13" ht="90" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:13" ht="96" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>13</v>
       </c>
@@ -2440,11 +2467,11 @@
         <v>229</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B5" s="19"/>
       <c r="C5" s="19"/>
     </row>
-    <row r="6" spans="1:13" ht="105" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:13" ht="80" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>25</v>
       </c>
@@ -2485,7 +2512,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="7" spans="1:13" ht="90" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:13" ht="80" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>33</v>
       </c>
@@ -2526,7 +2553,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="8" spans="1:13" ht="90" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:13" ht="80" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>35</v>
       </c>
@@ -2567,11 +2594,11 @@
         <v>201</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B9" s="19"/>
       <c r="C9" s="19"/>
     </row>
-    <row r="10" spans="1:13" ht="60" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:13" ht="48" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>38</v>
       </c>
@@ -2612,7 +2639,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="11" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:13" ht="32" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>42</v>
       </c>
@@ -2653,7 +2680,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="12" spans="1:13" ht="120" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:13" ht="96" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>42</v>
       </c>
@@ -2694,7 +2721,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="13" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:13" ht="48" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>42</v>
       </c>
@@ -2735,7 +2762,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="14" spans="1:13" ht="90" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:13" ht="64" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>42</v>
       </c>
@@ -2776,7 +2803,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="15" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:13" ht="48" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>42</v>
       </c>
@@ -2817,7 +2844,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="16" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:13" ht="48" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>42</v>
       </c>
@@ -2858,7 +2885,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="17" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:13" ht="48" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>42</v>
       </c>
@@ -2899,7 +2926,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="18" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:13" ht="48" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>42</v>
       </c>
@@ -2940,7 +2967,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="19" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:13" ht="48" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>42</v>
       </c>
@@ -2981,7 +3008,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="20" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:13" ht="48" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>42</v>
       </c>
@@ -3022,7 +3049,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="21" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:13" ht="48" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>42</v>
       </c>
@@ -3063,7 +3090,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="22" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:13" ht="48" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>42</v>
       </c>
@@ -3104,7 +3131,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="23" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:13" ht="48" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>42</v>
       </c>
@@ -3145,7 +3172,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="24" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:13" ht="48" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>42</v>
       </c>
@@ -3186,7 +3213,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="25" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:13" ht="48" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>42</v>
       </c>
@@ -3227,7 +3254,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="26" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:13" ht="48" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>42</v>
       </c>
@@ -3268,7 +3295,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="27" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:13" ht="48" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>42</v>
       </c>
@@ -3309,7 +3336,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="28" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:13" ht="48" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>42</v>
       </c>
@@ -3350,7 +3377,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="29" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:13" ht="48" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>42</v>
       </c>
@@ -3391,7 +3418,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="30" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:13" ht="48" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>42</v>
       </c>
@@ -3432,7 +3459,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="31" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:13" ht="48" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>42</v>
       </c>
@@ -3473,7 +3500,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="32" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:13" ht="48" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>42</v>
       </c>
@@ -3514,11 +3541,11 @@
         <v>233</v>
       </c>
     </row>
-    <row r="33" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B33" s="19"/>
       <c r="C33" s="19"/>
     </row>
-    <row r="34" spans="1:13" ht="90" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:13" ht="64" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>69</v>
       </c>
@@ -3559,7 +3586,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="35" spans="1:13" ht="90" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:13" ht="64" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>69</v>
       </c>
@@ -3600,11 +3627,11 @@
         <v>220</v>
       </c>
     </row>
-    <row r="36" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B36" s="19"/>
       <c r="C36" s="19"/>
     </row>
-    <row r="37" spans="1:13" ht="75" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:13" ht="80" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>74</v>
       </c>
@@ -3645,7 +3672,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="38" spans="1:13" ht="75" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:13" ht="80" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>74</v>
       </c>
@@ -3686,7 +3713,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="39" spans="1:13" ht="90" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:13" ht="80" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>74</v>
       </c>
@@ -3727,7 +3754,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="40" spans="1:13" ht="90" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:13" ht="80" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>74</v>
       </c>
@@ -3768,7 +3795,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="41" spans="1:13" ht="60" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:13" ht="64" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>74</v>
       </c>
@@ -3809,7 +3836,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="42" spans="1:13" ht="75" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:13" ht="64" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>74</v>
       </c>
@@ -3850,7 +3877,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="43" spans="1:13" ht="75" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:13" ht="80" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>74</v>
       </c>
@@ -3891,7 +3918,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="44" spans="1:13" ht="75" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:13" ht="80" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>85</v>
       </c>
@@ -3932,7 +3959,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="45" spans="1:13" ht="75" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:13" ht="80" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>85</v>
       </c>
@@ -3973,7 +4000,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="46" spans="1:13" ht="90" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:13" ht="80" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
         <v>85</v>
       </c>
@@ -4014,7 +4041,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="47" spans="1:13" ht="90" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:13" ht="80" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
         <v>85</v>
       </c>
@@ -4055,7 +4082,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="48" spans="1:13" ht="90" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:13" ht="80" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
         <v>85</v>
       </c>
@@ -4096,7 +4123,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="49" spans="1:13" ht="90" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:13" ht="80" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
         <v>85</v>
       </c>
@@ -4137,7 +4164,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="50" spans="1:13" ht="75" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:13" ht="80" x14ac:dyDescent="0.2">
       <c r="A50" s="10" t="s">
         <v>85</v>
       </c>
@@ -4178,7 +4205,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="51" spans="1:13" ht="75" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:13" ht="80" x14ac:dyDescent="0.2">
       <c r="A51" s="10"/>
       <c r="B51" s="19">
         <v>43501</v>
@@ -4217,7 +4244,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="52" spans="1:13" ht="75" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:13" ht="80" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
         <v>85</v>
       </c>
@@ -4258,7 +4285,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="53" spans="1:13" ht="75" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:13" ht="80" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
         <v>85</v>
       </c>
@@ -4299,7 +4326,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="54" spans="1:13" ht="90" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:13" ht="96" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
         <v>85</v>
       </c>
@@ -4340,7 +4367,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="55" spans="1:13" ht="75" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:13" ht="64" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
         <v>85</v>
       </c>
@@ -4381,12 +4408,12 @@
         <v>236</v>
       </c>
     </row>
-    <row r="56" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A56" s="10"/>
       <c r="B56" s="20"/>
       <c r="C56" s="20"/>
     </row>
-    <row r="57" spans="1:13" ht="60" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:13" ht="64" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
         <v>100</v>
       </c>
@@ -4427,7 +4454,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="58" spans="1:13" ht="60" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:13" ht="64" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
         <v>100</v>
       </c>
@@ -4468,7 +4495,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="59" spans="1:13" ht="60" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:13" ht="64" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
         <v>100</v>
       </c>
@@ -4509,7 +4536,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="60" spans="1:13" ht="60" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:13" ht="64" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
         <v>100</v>
       </c>
@@ -4550,7 +4577,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="61" spans="1:13" ht="90" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:13" ht="96" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
         <v>100</v>
       </c>
@@ -4591,7 +4618,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="62" spans="1:13" ht="105" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:13" ht="96" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
         <v>100</v>
       </c>
@@ -4632,7 +4659,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="63" spans="1:13" ht="90" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:13" ht="96" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
         <v>100</v>
       </c>
@@ -4673,7 +4700,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="64" spans="1:13" ht="105" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:13" ht="96" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
         <v>100</v>
       </c>
@@ -4714,7 +4741,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="65" spans="1:13" ht="60" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:13" ht="64" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
         <v>100</v>
       </c>
@@ -4755,7 +4782,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="66" spans="1:13" ht="60" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:13" ht="64" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
         <v>100</v>
       </c>
@@ -4796,7 +4823,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="67" spans="1:13" ht="60" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:13" ht="64" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
         <v>100</v>
       </c>
@@ -4837,7 +4864,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="68" spans="1:13" ht="60" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:13" ht="64" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
         <v>100</v>
       </c>
@@ -4878,7 +4905,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="69" spans="1:13" ht="60" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:13" ht="64" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
         <v>100</v>
       </c>
@@ -4919,7 +4946,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="70" spans="1:13" ht="60" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:13" ht="64" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
         <v>100</v>
       </c>
@@ -4960,7 +4987,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="71" spans="1:13" ht="60" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:13" ht="64" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
         <v>100</v>
       </c>
@@ -5001,7 +5028,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="72" spans="1:13" ht="60" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:13" ht="64" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
         <v>100</v>
       </c>
@@ -5042,7 +5069,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="73" spans="1:13" ht="60" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:13" ht="64" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
         <v>100</v>
       </c>
@@ -5083,11 +5110,11 @@
         <v>238</v>
       </c>
     </row>
-    <row r="74" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B74" s="19"/>
       <c r="C74" s="19"/>
     </row>
-    <row r="75" spans="1:13" ht="90" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:13" ht="64" x14ac:dyDescent="0.2">
       <c r="A75" s="24" t="s">
         <v>131</v>
       </c>
@@ -5128,7 +5155,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="76" spans="1:13" ht="75" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:13" ht="48" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
         <v>131</v>
       </c>
@@ -5169,7 +5196,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="77" spans="1:13" ht="60" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:13" ht="48" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
         <v>131</v>
       </c>
@@ -5210,7 +5237,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="78" spans="1:13" ht="75" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:13" ht="64" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
         <v>131</v>
       </c>
@@ -5251,7 +5278,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="79" spans="1:13" ht="60" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:13" ht="48" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
         <v>131</v>
       </c>
@@ -5292,7 +5319,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="80" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:13" ht="48" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
         <v>131</v>
       </c>
@@ -5333,12 +5360,12 @@
         <v>244</v>
       </c>
     </row>
-    <row r="81" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B81" s="19"/>
       <c r="C81" s="19"/>
       <c r="H81" s="11"/>
     </row>
-    <row r="82" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:13" ht="48" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
         <v>134</v>
       </c>
@@ -5379,7 +5406,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="83" spans="1:13" ht="90" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:13" ht="80" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
         <v>134</v>
       </c>
@@ -5420,7 +5447,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="84" spans="1:13" ht="105" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:13" ht="96" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
         <v>134</v>
       </c>
@@ -5461,7 +5488,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="85" spans="1:13" ht="105" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:13" ht="96" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
         <v>134</v>
       </c>
@@ -5502,7 +5529,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="86" spans="1:13" ht="75" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:13" ht="80" x14ac:dyDescent="0.2">
       <c r="A86" s="24" t="s">
         <v>396</v>
       </c>
@@ -5543,7 +5570,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="87" spans="1:13" ht="120" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:13" ht="112" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
         <v>140</v>
       </c>
@@ -5584,11 +5611,11 @@
         <v>178</v>
       </c>
     </row>
-    <row r="88" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B88" s="19"/>
       <c r="C88" s="19"/>
     </row>
-    <row r="89" spans="1:13" ht="90" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:13" ht="80" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
         <v>131</v>
       </c>
@@ -5629,7 +5656,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="90" spans="1:13" ht="90" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:13" ht="80" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
         <v>131</v>
       </c>
@@ -5670,7 +5697,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="91" spans="1:13" ht="90" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:13" ht="80" x14ac:dyDescent="0.2">
       <c r="A91" t="s">
         <v>131</v>
       </c>
@@ -5711,7 +5738,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="92" spans="1:13" ht="90" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:13" ht="80" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
         <v>131</v>
       </c>
@@ -5752,7 +5779,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="93" spans="1:13" ht="90" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:13" ht="80" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
         <v>131</v>
       </c>
@@ -5793,7 +5820,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="94" spans="1:13" ht="90" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:13" ht="80" x14ac:dyDescent="0.2">
       <c r="A94" t="s">
         <v>131</v>
       </c>
@@ -5834,10 +5861,10 @@
         <v>277</v>
       </c>
     </row>
-    <row r="95" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:13" x14ac:dyDescent="0.2">
       <c r="G95" s="8"/>
     </row>
-    <row r="96" spans="1:13" ht="60" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:13" ht="48" x14ac:dyDescent="0.2">
       <c r="A96" t="s">
         <v>286</v>
       </c>
@@ -5878,11 +5905,11 @@
         <v>395</v>
       </c>
     </row>
-    <row r="97" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B97" s="19"/>
       <c r="C97" s="19"/>
     </row>
-    <row r="98" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:13" ht="48" x14ac:dyDescent="0.2">
       <c r="A98" t="s">
         <v>289</v>
       </c>
@@ -5923,7 +5950,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="100" spans="1:13" ht="90" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:13" ht="80" x14ac:dyDescent="0.2">
       <c r="A100" t="s">
         <v>301</v>
       </c>
@@ -5964,7 +5991,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="101" spans="1:13" ht="75" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:13" ht="64" x14ac:dyDescent="0.2">
       <c r="A101" t="s">
         <v>301</v>
       </c>
@@ -6005,7 +6032,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="102" spans="1:13" ht="195" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:13" ht="176" x14ac:dyDescent="0.2">
       <c r="A102" t="s">
         <v>302</v>
       </c>
@@ -6046,11 +6073,11 @@
         <v>400</v>
       </c>
     </row>
-    <row r="103" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B103" s="19"/>
       <c r="C103" s="19"/>
     </row>
-    <row r="104" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:13" ht="48" x14ac:dyDescent="0.2">
       <c r="A104" t="s">
         <v>315</v>
       </c>
@@ -6091,7 +6118,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="105" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:13" ht="48" x14ac:dyDescent="0.2">
       <c r="A105" t="s">
         <v>315</v>
       </c>
@@ -6132,7 +6159,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="106" spans="1:13" ht="60" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:13" ht="48" x14ac:dyDescent="0.2">
       <c r="A106" t="s">
         <v>315</v>
       </c>
@@ -6173,7 +6200,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="107" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:13" ht="48" x14ac:dyDescent="0.2">
       <c r="A107" t="s">
         <v>405</v>
       </c>
@@ -6214,7 +6241,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="108" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:13" ht="32" x14ac:dyDescent="0.2">
       <c r="A108" s="4" t="s">
         <v>330</v>
       </c>
@@ -6255,7 +6282,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="109" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:13" ht="48" x14ac:dyDescent="0.2">
       <c r="A109" t="s">
         <v>405</v>
       </c>
@@ -6296,7 +6323,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="110" spans="1:13" ht="75" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:13" ht="80" x14ac:dyDescent="0.2">
       <c r="A110" t="s">
         <v>405</v>
       </c>
@@ -6337,7 +6364,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="111" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:13" ht="32" x14ac:dyDescent="0.2">
       <c r="A111" t="s">
         <v>331</v>
       </c>
@@ -6378,7 +6405,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="112" spans="1:13" ht="75" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:13" ht="80" x14ac:dyDescent="0.2">
       <c r="A112" t="s">
         <v>405</v>
       </c>
@@ -6419,7 +6446,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="113" spans="1:13" ht="75" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:13" ht="80" x14ac:dyDescent="0.2">
       <c r="A113" t="s">
         <v>405</v>
       </c>
@@ -6460,11 +6487,11 @@
         <v>408</v>
       </c>
     </row>
-    <row r="114" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B114" s="19"/>
       <c r="C114" s="19"/>
     </row>
-    <row r="115" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:13" ht="32" x14ac:dyDescent="0.2">
       <c r="A115" t="s">
         <v>343</v>
       </c>
@@ -6505,7 +6532,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="116" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:13" ht="16" x14ac:dyDescent="0.2">
       <c r="A116" t="s">
         <v>342</v>
       </c>
@@ -6546,7 +6573,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="117" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:13" ht="32" x14ac:dyDescent="0.2">
       <c r="A117" t="s">
         <v>342</v>
       </c>
@@ -6587,11 +6614,11 @@
         <v>346</v>
       </c>
     </row>
-    <row r="118" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B118" s="19"/>
       <c r="C118" s="19"/>
     </row>
-    <row r="119" spans="1:13" ht="75" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:13" ht="80" x14ac:dyDescent="0.2">
       <c r="A119" s="24" t="s">
         <v>349</v>
       </c>
@@ -6632,7 +6659,7 @@
         <v>415</v>
       </c>
     </row>
-    <row r="120" spans="1:13" ht="75" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:13" ht="80" x14ac:dyDescent="0.2">
       <c r="A120" t="s">
         <v>349</v>
       </c>
@@ -6673,7 +6700,7 @@
         <v>416</v>
       </c>
     </row>
-    <row r="121" spans="1:13" ht="75" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:13" ht="80" x14ac:dyDescent="0.2">
       <c r="A121" t="s">
         <v>349</v>
       </c>
@@ -6714,7 +6741,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="122" spans="1:13" ht="75" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:13" ht="80" x14ac:dyDescent="0.2">
       <c r="A122" t="s">
         <v>349</v>
       </c>
@@ -6755,7 +6782,7 @@
         <v>418</v>
       </c>
     </row>
-    <row r="123" spans="1:13" ht="75" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:13" ht="80" x14ac:dyDescent="0.2">
       <c r="A123" t="s">
         <v>349</v>
       </c>
@@ -6796,7 +6823,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="124" spans="1:13" ht="75" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:13" ht="80" x14ac:dyDescent="0.2">
       <c r="A124" t="s">
         <v>349</v>
       </c>
@@ -6837,7 +6864,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="125" spans="1:13" ht="90" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:13" ht="80" x14ac:dyDescent="0.2">
       <c r="A125" t="s">
         <v>349</v>
       </c>
@@ -6878,7 +6905,7 @@
         <v>415</v>
       </c>
     </row>
-    <row r="126" spans="1:13" ht="90" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:13" ht="80" x14ac:dyDescent="0.2">
       <c r="A126" t="s">
         <v>349</v>
       </c>
@@ -6919,7 +6946,7 @@
         <v>416</v>
       </c>
     </row>
-    <row r="127" spans="1:13" ht="90" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:13" ht="80" x14ac:dyDescent="0.2">
       <c r="A127" t="s">
         <v>349</v>
       </c>
@@ -6960,7 +6987,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="128" spans="1:13" ht="90" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:13" ht="80" x14ac:dyDescent="0.2">
       <c r="A128" t="s">
         <v>349</v>
       </c>
@@ -7001,7 +7028,7 @@
         <v>418</v>
       </c>
     </row>
-    <row r="129" spans="1:13" ht="90" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:13" ht="80" x14ac:dyDescent="0.2">
       <c r="A129" t="s">
         <v>349</v>
       </c>
@@ -7042,7 +7069,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="130" spans="1:13" ht="90" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:13" ht="80" x14ac:dyDescent="0.2">
       <c r="A130" t="s">
         <v>349</v>
       </c>
@@ -7083,7 +7110,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="131" spans="1:13" ht="105" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:13" ht="80" x14ac:dyDescent="0.2">
       <c r="A131" t="s">
         <v>349</v>
       </c>
@@ -7124,7 +7151,7 @@
         <v>415</v>
       </c>
     </row>
-    <row r="132" spans="1:13" ht="105" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:13" ht="80" x14ac:dyDescent="0.2">
       <c r="A132" t="s">
         <v>349</v>
       </c>
@@ -7165,7 +7192,7 @@
         <v>416</v>
       </c>
     </row>
-    <row r="133" spans="1:13" ht="105" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:13" ht="80" x14ac:dyDescent="0.2">
       <c r="A133" t="s">
         <v>349</v>
       </c>
@@ -7206,7 +7233,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="134" spans="1:13" ht="105" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:13" ht="80" x14ac:dyDescent="0.2">
       <c r="A134" t="s">
         <v>349</v>
       </c>
@@ -7247,7 +7274,7 @@
         <v>418</v>
       </c>
     </row>
-    <row r="135" spans="1:13" ht="105" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:13" ht="80" x14ac:dyDescent="0.2">
       <c r="A135" t="s">
         <v>349</v>
       </c>
@@ -7288,7 +7315,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="136" spans="1:13" ht="105" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:13" ht="80" x14ac:dyDescent="0.2">
       <c r="A136" t="s">
         <v>349</v>
       </c>
@@ -7329,7 +7356,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="137" spans="1:13" ht="75" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:13" ht="80" x14ac:dyDescent="0.2">
       <c r="A137" s="26" t="s">
         <v>349</v>
       </c>
@@ -7370,7 +7397,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="138" spans="1:13" ht="75" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:13" ht="80" x14ac:dyDescent="0.2">
       <c r="A138" s="23" t="s">
         <v>349</v>
       </c>
@@ -7411,7 +7438,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="139" spans="1:13" ht="75" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:13" ht="80" x14ac:dyDescent="0.2">
       <c r="A139" s="23" t="s">
         <v>349</v>
       </c>
@@ -7452,7 +7479,7 @@
         <v>438</v>
       </c>
     </row>
-    <row r="140" spans="1:13" ht="75" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:13" ht="80" x14ac:dyDescent="0.2">
       <c r="A140" s="23" t="s">
         <v>349</v>
       </c>
@@ -7493,7 +7520,7 @@
         <v>439</v>
       </c>
     </row>
-    <row r="141" spans="1:13" ht="75" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:13" ht="80" x14ac:dyDescent="0.2">
       <c r="A141" s="23" t="s">
         <v>349</v>
       </c>
@@ -7534,7 +7561,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="142" spans="1:13" ht="75" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:13" ht="80" x14ac:dyDescent="0.2">
       <c r="A142" s="23" t="s">
         <v>349</v>
       </c>
@@ -7575,7 +7602,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="143" spans="1:13" ht="90" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:13" ht="80" x14ac:dyDescent="0.2">
       <c r="A143" s="23" t="s">
         <v>349</v>
       </c>
@@ -7616,7 +7643,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="144" spans="1:13" ht="90" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:13" ht="80" x14ac:dyDescent="0.2">
       <c r="A144" s="23" t="s">
         <v>349</v>
       </c>
@@ -7657,7 +7684,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="145" spans="1:13" ht="90" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:13" ht="80" x14ac:dyDescent="0.2">
       <c r="A145" s="23" t="s">
         <v>349</v>
       </c>
@@ -7698,7 +7725,7 @@
         <v>438</v>
       </c>
     </row>
-    <row r="146" spans="1:13" ht="90" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:13" ht="80" x14ac:dyDescent="0.2">
       <c r="A146" s="23" t="s">
         <v>349</v>
       </c>
@@ -7739,7 +7766,7 @@
         <v>439</v>
       </c>
     </row>
-    <row r="147" spans="1:13" ht="90" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:13" ht="80" x14ac:dyDescent="0.2">
       <c r="A147" s="23" t="s">
         <v>349</v>
       </c>
@@ -7780,7 +7807,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="148" spans="1:13" ht="90" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:13" ht="80" x14ac:dyDescent="0.2">
       <c r="A148" s="23" t="s">
         <v>349</v>
       </c>
@@ -7821,7 +7848,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="149" spans="1:13" ht="105" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:13" ht="80" x14ac:dyDescent="0.2">
       <c r="A149" s="23" t="s">
         <v>349</v>
       </c>
@@ -7862,7 +7889,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="150" spans="1:13" ht="105" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:13" ht="80" x14ac:dyDescent="0.2">
       <c r="A150" s="23" t="s">
         <v>349</v>
       </c>
@@ -7903,7 +7930,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="151" spans="1:13" ht="105" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:13" ht="80" x14ac:dyDescent="0.2">
       <c r="A151" s="23" t="s">
         <v>349</v>
       </c>
@@ -7944,7 +7971,7 @@
         <v>438</v>
       </c>
     </row>
-    <row r="152" spans="1:13" ht="105" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:13" ht="80" x14ac:dyDescent="0.2">
       <c r="A152" s="23" t="s">
         <v>349</v>
       </c>
@@ -7985,7 +8012,7 @@
         <v>439</v>
       </c>
     </row>
-    <row r="153" spans="1:13" ht="105" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:13" ht="80" x14ac:dyDescent="0.2">
       <c r="A153" s="23" t="s">
         <v>349</v>
       </c>
@@ -8026,7 +8053,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="154" spans="1:13" ht="105" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:13" ht="80" x14ac:dyDescent="0.2">
       <c r="A154" s="23" t="s">
         <v>349</v>
       </c>
@@ -8067,12 +8094,12 @@
         <v>441</v>
       </c>
     </row>
-    <row r="155" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A155" s="23"/>
       <c r="B155" s="19"/>
       <c r="C155" s="19"/>
     </row>
-    <row r="156" spans="1:13" ht="90" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:13" ht="80" x14ac:dyDescent="0.2">
       <c r="A156" t="s">
         <v>358</v>
       </c>
@@ -8113,7 +8140,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="157" spans="1:13" ht="105" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:13" ht="96" x14ac:dyDescent="0.2">
       <c r="A157" t="s">
         <v>358</v>
       </c>
@@ -8154,7 +8181,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="158" spans="1:13" ht="105" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:13" ht="96" x14ac:dyDescent="0.2">
       <c r="A158" t="s">
         <v>358</v>
       </c>
@@ -8195,7 +8222,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="159" spans="1:13" ht="105" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:13" ht="96" x14ac:dyDescent="0.2">
       <c r="A159" t="s">
         <v>358</v>
       </c>
@@ -8236,7 +8263,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="160" spans="1:13" ht="105" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:13" ht="96" x14ac:dyDescent="0.2">
       <c r="A160" t="s">
         <v>358</v>
       </c>
@@ -8277,7 +8304,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="161" spans="1:13" ht="105" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:13" ht="96" x14ac:dyDescent="0.2">
       <c r="A161" t="s">
         <v>358</v>
       </c>
@@ -8318,7 +8345,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="162" spans="1:13" ht="105" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:13" ht="96" x14ac:dyDescent="0.2">
       <c r="A162" t="s">
         <v>358</v>
       </c>
@@ -8359,7 +8386,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="163" spans="1:13" ht="105" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:13" ht="96" x14ac:dyDescent="0.2">
       <c r="A163" t="s">
         <v>358</v>
       </c>
@@ -8400,7 +8427,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="164" spans="1:13" ht="105" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:13" ht="112" x14ac:dyDescent="0.2">
       <c r="A164" t="s">
         <v>358</v>
       </c>
@@ -8441,12 +8468,12 @@
         <v>362</v>
       </c>
     </row>
-    <row r="165" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B165" s="19"/>
       <c r="C165" s="19"/>
       <c r="D165" s="4"/>
     </row>
-    <row r="166" spans="1:13" ht="90" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:13" ht="80" x14ac:dyDescent="0.2">
       <c r="A166" t="s">
         <v>379</v>
       </c>
@@ -8487,14 +8514,133 @@
         <v>381</v>
       </c>
     </row>
-    <row r="167" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="B167" s="19"/>
+      <c r="C167" s="19"/>
       <c r="D167" s="4"/>
     </row>
-    <row r="168" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="D168" s="4"/>
-    </row>
-    <row r="169" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="D169" s="4"/>
+    <row r="168" spans="1:13" ht="32" x14ac:dyDescent="0.2">
+      <c r="A168" s="10" t="s">
+        <v>451</v>
+      </c>
+      <c r="B168" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C168" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D168" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="E168" t="s">
+        <v>452</v>
+      </c>
+      <c r="F168" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="G168" s="9" t="s">
+        <v>453</v>
+      </c>
+      <c r="H168" s="12" t="s">
+        <v>454</v>
+      </c>
+      <c r="I168" s="16" t="s">
+        <v>255</v>
+      </c>
+      <c r="J168" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="K168" t="s">
+        <v>19</v>
+      </c>
+      <c r="L168" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="M168" s="8" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="169" spans="1:13" ht="32" x14ac:dyDescent="0.2">
+      <c r="A169" s="10" t="s">
+        <v>451</v>
+      </c>
+      <c r="B169" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C169" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D169" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="E169" t="s">
+        <v>452</v>
+      </c>
+      <c r="F169" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="G169" s="9" t="s">
+        <v>453</v>
+      </c>
+      <c r="H169" s="12" t="s">
+        <v>454</v>
+      </c>
+      <c r="I169" s="16" t="s">
+        <v>256</v>
+      </c>
+      <c r="J169" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="K169" t="s">
+        <v>19</v>
+      </c>
+      <c r="L169" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="M169" s="8" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="170" spans="1:13" ht="32" x14ac:dyDescent="0.2">
+      <c r="A170" s="10" t="s">
+        <v>451</v>
+      </c>
+      <c r="B170" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C170" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D170" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="E170" t="s">
+        <v>452</v>
+      </c>
+      <c r="F170" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="G170" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="H170" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="I170" s="16" t="s">
+        <v>455</v>
+      </c>
+      <c r="J170" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="K170" t="s">
+        <v>19</v>
+      </c>
+      <c r="L170" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="M170" s="8" t="s">
+        <v>457</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="L1:L94" xr:uid="{9CC0B67C-1229-4907-A814-DF79422D0B81}"/>
@@ -8549,27 +8695,32 @@
     <hyperlink ref="I50" r:id="rId42" xr:uid="{3A575A66-D033-48DC-ACC1-168DCA595CA5}"/>
     <hyperlink ref="I51" r:id="rId43" xr:uid="{BBD156C6-CFBB-4FC6-8700-511F389C8B83}"/>
     <hyperlink ref="I49" r:id="rId44" xr:uid="{68A955C5-13B0-4EBF-ADD6-2A9995A030AA}"/>
+    <hyperlink ref="I169" r:id="rId45" display="https://www.globalcarbonproject.org/reccap/overview.html" xr:uid="{6F2B1F2A-0F2E-2044-B3AA-CEC6EF3CC6AF}"/>
+    <hyperlink ref="I170" r:id="rId46" display="https://catalogue.ceda.ac.uk/uuid/46d136149d0a4f1cb8de7efbe8abf4b2" xr:uid="{D22E6E30-CA76-8F48-8172-301B8722BBD5}"/>
+    <hyperlink ref="A168" r:id="rId47" xr:uid="{A60828CC-03A1-ED42-BFCE-F732CB8FB216}"/>
+    <hyperlink ref="A169" r:id="rId48" xr:uid="{33E99A1E-F7B4-8845-B087-E9DD5C656628}"/>
+    <hyperlink ref="A170" r:id="rId49" xr:uid="{F32F598F-0B48-8643-A59D-0D70FAEA38AB}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId45"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId50"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E0B35E6D-763F-4C40-91D2-473BE7766F62}">
-  <dimension ref="A1:B20"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:B22"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="20.42578125" customWidth="1"/>
-    <col min="2" max="2" width="105.140625" customWidth="1"/>
+    <col min="1" max="1" width="20.5" customWidth="1"/>
+    <col min="2" max="2" width="105.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>145</v>
       </c>
@@ -8577,7 +8728,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>24</v>
       </c>
@@ -8585,7 +8736,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>23</v>
       </c>
@@ -8593,7 +8744,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>149</v>
       </c>
@@ -8601,7 +8752,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>151</v>
       </c>
@@ -8609,7 +8760,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>80</v>
       </c>
@@ -8617,7 +8768,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>81</v>
       </c>
@@ -8625,7 +8776,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>155</v>
       </c>
@@ -8633,7 +8784,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>157</v>
       </c>
@@ -8641,7 +8792,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>44</v>
       </c>
@@ -8649,7 +8800,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>43</v>
       </c>
@@ -8657,7 +8808,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>21</v>
       </c>
@@ -8665,7 +8816,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>76</v>
       </c>
@@ -8673,7 +8824,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>40</v>
       </c>
@@ -8681,7 +8832,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>164</v>
       </c>
@@ -8689,7 +8840,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>166</v>
       </c>
@@ -8697,7 +8848,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>168</v>
       </c>
@@ -8705,12 +8856,28 @@
         <v>169</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>170</v>
       </c>
       <c r="B20" t="s">
         <v>171</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A21" t="s">
+        <v>454</v>
+      </c>
+      <c r="B21" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A22" t="s">
+        <v>453</v>
+      </c>
+      <c r="B22" t="s">
+        <v>458</v>
       </c>
     </row>
   </sheetData>
@@ -8957,6 +9124,15 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="80b53ead-ac38-442a-b597-5a0e2e0802cd">
@@ -8965,15 +9141,6 @@
     <TaxCatchAll xmlns="5ec1cc48-4270-4222-9ed5-54ce9e59d47b" xsi:nil="true"/>
   </documentManagement>
 </p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -8996,6 +9163,14 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3B1B5D08-A2EB-4F47-BA81-DA28AA2A09F4}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{66AF2240-620B-4312-9739-CAF731E4A98F}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
@@ -9004,12 +9179,4 @@
     <ds:schemaRef ds:uri="5ec1cc48-4270-4222-9ed5-54ce9e59d47b"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3B1B5D08-A2EB-4F47-BA81-DA28AA2A09F4}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/EEE2000-metadata_mapping.xlsx
+++ b/EEE2000-metadata_mapping.xlsx
@@ -1,23 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\amw23\Documents\GitHub\cci_data_bridge_inputs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://stfc365-my.sharepoint.com/personal/alison_waterfall_stfc_ac_uk/Documents/Documents/GitHub/cci_data_bridge_inputs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{594DCA07-06B5-4D5C-ABFA-EF38438BEDEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="88" documentId="13_ncr:1_{594DCA07-06B5-4D5C-ABFA-EF38438BEDEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A3641DD4-BC02-4A09-9CC2-CFA66B2655FE}"/>
   <bookViews>
-    <workbookView xWindow="1125" yWindow="1125" windowWidth="28800" windowHeight="15285" xr2:uid="{B9DA58AC-C110-4CBA-A19B-6F37B44EEA38}"/>
+    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{B9DA58AC-C110-4CBA-A19B-6F37B44EEA38}"/>
   </bookViews>
   <sheets>
     <sheet name="Mapping" sheetId="2" r:id="rId1"/>
     <sheet name="Relationship definitions" sheetId="1" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Mapping!$L$1:$L$94</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Mapping!$L$1:$L$95</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1679" uniqueCount="451">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1703" uniqueCount="458">
   <si>
     <t>Dataset 1</t>
   </si>
@@ -1292,9 +1292,6 @@
     <t>The C3S CDR dataset corresonds to an earlier version of the CCI dataset and has a different format</t>
   </si>
   <si>
-    <t>The C3S ICDR dataset continues the CDR dataset forward in time to the present.  It is based on an earlier version that the current CCI dataset and has a different format.</t>
-  </si>
-  <si>
     <t>IsSupplementTo,
 IsVariantFormOf,
 IsPreviousVersionOf</t>
@@ -1308,13 +1305,6 @@
     <t>https://doi.org/10.24381/cds.4ebfe4eb</t>
   </si>
   <si>
-    <t>processing_level=level_3,
-variable=atmospheric_mole_content_of_ozone,
-vertical_aggregation=total_column,
-sensor=merged_uv,
-version=v2000</t>
-  </si>
-  <si>
     <t>Ozone</t>
   </si>
   <si>
@@ -1322,13 +1312,6 @@
   </si>
   <si>
     <t>The C3S dataset is a newer version of the CCI dataset.</t>
-  </si>
-  <si>
-    <t>variable=mole_concentration_of_ozone_in_air,
-processing_level=level_3,
-vertical_aggregation=vertical_profiles_from_limb_sensors,
-sensor=ace,
-version=v0002</t>
   </si>
   <si>
     <t>variable=mole_concentration_of_ozone_in_air,
@@ -1348,13 +1331,6 @@
     <t>variable=mole_concentration_of_ozone_in_air,
 processing_level=level_3,
 vertical_aggregation=vertical_profiles_from_limb_sensors,
-sensor=osiris,
-version=v0002</t>
-  </si>
-  <si>
-    <t>variable=mole_concentration_of_ozone_in_air,
-processing_level=level_3,
-vertical_aggregation=vertical_profiles_from_limb_sensors,
 sensor=sciamachy,
 version=v0001</t>
   </si>
@@ -1729,6 +1705,55 @@
   </si>
   <si>
     <t>esacci.GHG.satellite-orbit-frequency.L2.CH4.TANSO-FTS-2.GOSAT-2.SRPR.v2-0-2.r1</t>
+  </si>
+  <si>
+    <t>The C3S ICDR dataset continues the C3S CDR dataset forward in time to the present.  It is based on an earlier version that the current CCI dataset and has a different format.</t>
+  </si>
+  <si>
+    <t>version=v3,
+sensor=ssmis
+origin=EUMETSAT OSI SAF,
+temporal_aggregation=daily
+cdr_type=icdr</t>
+  </si>
+  <si>
+    <t>domain=greenland_ice_sheet</t>
+  </si>
+  <si>
+    <t>31/09/2022</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.24381/cds.0b96b839</t>
+  </si>
+  <si>
+    <t>domain=antarctic_ice_sheet</t>
+  </si>
+  <si>
+    <t>https://catalogue.ceda.ac.uk/uuid/00fe090efc58446e8980992a617f632f</t>
+  </si>
+  <si>
+    <t>The C3S data follows on from the CCI dataset; it is an newer version of the algorithm</t>
+  </si>
+  <si>
+    <t>processing_level=level_3,
+variable=atmospheric_mole_content_of_ozone,
+vertical_aggregation=total_column,
+sensor=merged_uv,
+version=[v2000,v2100]</t>
+  </si>
+  <si>
+    <t>variable=mole_concentration_of_ozone_in_air,
+processing_level=level_3,
+vertical_aggregation=vertical_profiles_from_limb_sensors,
+sensor=ace,
+version=v0003</t>
+  </si>
+  <si>
+    <t>variable=mole_concentration_of_ozone_in_air,
+processing_level=level_3,
+vertical_aggregation=vertical_profiles_from_limb_sensors,
+sensor=osiris,
+version=v0003</t>
   </si>
 </sst>
 </file>
@@ -2281,7 +2306,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9CC0B67C-1229-4907-A814-DF79422D0B81}">
-  <dimension ref="A1:M169"/>
+  <dimension ref="A1:M171"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="36.85546875" bestFit="1" customWidth="1"/>
@@ -3779,7 +3804,7 @@
         <v>44926</v>
       </c>
       <c r="D41" s="4" t="s">
-        <v>391</v>
+        <v>387</v>
       </c>
       <c r="E41" t="s">
         <v>15</v>
@@ -3820,7 +3845,7 @@
         <v>44561</v>
       </c>
       <c r="D42" s="4" t="s">
-        <v>392</v>
+        <v>388</v>
       </c>
       <c r="E42" t="s">
         <v>15</v>
@@ -3861,7 +3886,7 @@
         <v>45291</v>
       </c>
       <c r="D43" s="4" t="s">
-        <v>393</v>
+        <v>389</v>
       </c>
       <c r="E43" t="s">
         <v>15</v>
@@ -4148,7 +4173,7 @@
         <v>45291</v>
       </c>
       <c r="D50" s="4" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="E50" t="s">
         <v>15</v>
@@ -4175,11 +4200,13 @@
         <v>75</v>
       </c>
       <c r="M50" s="8" t="s">
-        <v>446</v>
+        <v>442</v>
       </c>
     </row>
     <row r="51" spans="1:13" ht="75" x14ac:dyDescent="0.25">
-      <c r="A51" s="10"/>
+      <c r="A51" s="10" t="s">
+        <v>85</v>
+      </c>
       <c r="B51" s="19">
         <v>43501</v>
       </c>
@@ -4187,7 +4214,7 @@
         <v>45291</v>
       </c>
       <c r="D51" s="4" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="E51" t="s">
         <v>15</v>
@@ -4202,10 +4229,10 @@
         <v>17</v>
       </c>
       <c r="I51" s="16" t="s">
-        <v>449</v>
+        <v>445</v>
       </c>
       <c r="J51" s="4" t="s">
-        <v>450</v>
+        <v>446</v>
       </c>
       <c r="K51" t="s">
         <v>19</v>
@@ -4214,7 +4241,7 @@
         <v>75</v>
       </c>
       <c r="M51" s="8" t="s">
-        <v>446</v>
+        <v>442</v>
       </c>
     </row>
     <row r="52" spans="1:13" ht="75" x14ac:dyDescent="0.25">
@@ -4228,7 +4255,7 @@
         <v>45291</v>
       </c>
       <c r="D52" s="4" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="E52" t="s">
         <v>15</v>
@@ -4255,7 +4282,7 @@
         <v>75</v>
       </c>
       <c r="M52" s="8" t="s">
-        <v>447</v>
+        <v>443</v>
       </c>
     </row>
     <row r="53" spans="1:13" ht="75" x14ac:dyDescent="0.25">
@@ -4269,7 +4296,7 @@
         <v>45291</v>
       </c>
       <c r="D53" s="4" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="E53" t="s">
         <v>15</v>
@@ -4284,10 +4311,10 @@
         <v>17</v>
       </c>
       <c r="I53" s="16" t="s">
-        <v>444</v>
+        <v>440</v>
       </c>
       <c r="J53" s="4" t="s">
-        <v>445</v>
+        <v>441</v>
       </c>
       <c r="K53" t="s">
         <v>19</v>
@@ -4296,7 +4323,7 @@
         <v>75</v>
       </c>
       <c r="M53" s="8" t="s">
-        <v>448</v>
+        <v>444</v>
       </c>
     </row>
     <row r="54" spans="1:13" ht="90" x14ac:dyDescent="0.25">
@@ -4310,7 +4337,7 @@
         <v>44926</v>
       </c>
       <c r="D54" s="4" t="s">
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="E54" t="s">
         <v>15</v>
@@ -4351,7 +4378,7 @@
         <v>44926</v>
       </c>
       <c r="D55" s="4" t="s">
-        <v>404</v>
+        <v>400</v>
       </c>
       <c r="E55" t="s">
         <v>15</v>
@@ -4397,7 +4424,7 @@
         <v>41007</v>
       </c>
       <c r="D57" s="4" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="E57" t="s">
         <v>15</v>
@@ -4412,10 +4439,10 @@
         <v>81</v>
       </c>
       <c r="I57" s="4" t="s">
-        <v>385</v>
+        <v>381</v>
       </c>
       <c r="J57" s="4" t="s">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="K57" t="s">
         <v>19</v>
@@ -4438,7 +4465,7 @@
         <v>41007</v>
       </c>
       <c r="D58" s="4" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="E58" t="s">
         <v>15</v>
@@ -4479,7 +4506,7 @@
         <v>37729</v>
       </c>
       <c r="D59" s="4" t="s">
-        <v>388</v>
+        <v>384</v>
       </c>
       <c r="E59" t="s">
         <v>15</v>
@@ -4520,7 +4547,7 @@
         <v>37729</v>
       </c>
       <c r="D60" s="4" t="s">
-        <v>389</v>
+        <v>385</v>
       </c>
       <c r="E60" t="s">
         <v>15</v>
@@ -5053,7 +5080,7 @@
         <v>41002</v>
       </c>
       <c r="D73" s="4" t="s">
-        <v>390</v>
+        <v>386</v>
       </c>
       <c r="E73" t="s">
         <v>15</v>
@@ -5504,16 +5531,16 @@
     </row>
     <row r="86" spans="1:13" ht="75" x14ac:dyDescent="0.25">
       <c r="A86" s="24" t="s">
-        <v>396</v>
+        <v>392</v>
       </c>
       <c r="B86" s="19">
         <v>33604</v>
       </c>
       <c r="C86" s="19">
-        <v>44652</v>
+        <v>45291</v>
       </c>
       <c r="D86" s="4" t="s">
-        <v>397</v>
+        <v>393</v>
       </c>
       <c r="E86" t="s">
         <v>15</v>
@@ -5540,7 +5567,7 @@
         <v>135</v>
       </c>
       <c r="M86" s="8" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
     </row>
     <row r="87" spans="1:13" ht="120" x14ac:dyDescent="0.25">
@@ -5550,11 +5577,11 @@
       <c r="B87" s="19">
         <v>43009</v>
       </c>
-      <c r="C87" s="19">
-        <v>44469</v>
+      <c r="C87" s="19" t="s">
+        <v>450</v>
       </c>
       <c r="D87" s="4" t="s">
-        <v>14</v>
+        <v>449</v>
       </c>
       <c r="E87" t="s">
         <v>15</v>
@@ -5584,50 +5611,47 @@
         <v>178</v>
       </c>
     </row>
-    <row r="88" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="B88" s="19"/>
-      <c r="C88" s="19"/>
-    </row>
-    <row r="89" spans="1:13" ht="90" x14ac:dyDescent="0.25">
-      <c r="A89" t="s">
-        <v>131</v>
-      </c>
-      <c r="B89" s="19">
-        <v>35677</v>
-      </c>
-      <c r="C89" s="19">
-        <v>45657</v>
-      </c>
-      <c r="D89" s="4" t="s">
-        <v>172</v>
-      </c>
-      <c r="E89" t="s">
-        <v>15</v>
-      </c>
-      <c r="F89" s="6" t="s">
-        <v>132</v>
-      </c>
-      <c r="G89" s="8" t="s">
-        <v>283</v>
-      </c>
-      <c r="H89" s="11" t="s">
-        <v>284</v>
-      </c>
-      <c r="I89" s="25" t="s">
-        <v>222</v>
-      </c>
-      <c r="J89" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="K89" t="s">
-        <v>19</v>
-      </c>
-      <c r="L89" s="6" t="s">
-        <v>132</v>
-      </c>
-      <c r="M89" s="8" t="s">
-        <v>276</v>
-      </c>
+    <row r="88" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>451</v>
+      </c>
+      <c r="B88" s="19">
+        <v>43009</v>
+      </c>
+      <c r="C88" s="19" t="s">
+        <v>450</v>
+      </c>
+      <c r="D88" s="4" t="s">
+        <v>452</v>
+      </c>
+      <c r="E88" t="s">
+        <v>15</v>
+      </c>
+      <c r="F88" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="G88" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="H88" s="11" t="s">
+        <v>142</v>
+      </c>
+      <c r="I88" s="10" t="s">
+        <v>453</v>
+      </c>
+      <c r="K88" t="s">
+        <v>19</v>
+      </c>
+      <c r="L88" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="M88" s="8" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="89" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="B89" s="19"/>
+      <c r="C89" s="19"/>
     </row>
     <row r="90" spans="1:13" ht="90" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
@@ -5640,7 +5664,7 @@
         <v>45657</v>
       </c>
       <c r="D90" s="4" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E90" t="s">
         <v>15</v>
@@ -5649,13 +5673,13 @@
         <v>132</v>
       </c>
       <c r="G90" s="8" t="s">
-        <v>313</v>
+        <v>283</v>
       </c>
       <c r="H90" s="11" t="s">
-        <v>314</v>
+        <v>284</v>
       </c>
       <c r="I90" s="25" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="J90" s="4" t="s">
         <v>14</v>
@@ -5667,7 +5691,7 @@
         <v>132</v>
       </c>
       <c r="M90" s="8" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="91" spans="1:13" ht="90" x14ac:dyDescent="0.25">
@@ -5681,7 +5705,7 @@
         <v>45657</v>
       </c>
       <c r="D91" s="4" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E91" t="s">
         <v>15</v>
@@ -5695,8 +5719,8 @@
       <c r="H91" s="11" t="s">
         <v>314</v>
       </c>
-      <c r="I91" s="4" t="s">
-        <v>221</v>
+      <c r="I91" s="25" t="s">
+        <v>225</v>
       </c>
       <c r="J91" s="4" t="s">
         <v>14</v>
@@ -5722,7 +5746,7 @@
         <v>45657</v>
       </c>
       <c r="D92" s="4" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E92" t="s">
         <v>15</v>
@@ -5736,8 +5760,8 @@
       <c r="H92" s="11" t="s">
         <v>314</v>
       </c>
-      <c r="I92" s="25" t="s">
-        <v>226</v>
+      <c r="I92" s="4" t="s">
+        <v>221</v>
       </c>
       <c r="J92" s="4" t="s">
         <v>14</v>
@@ -5749,7 +5773,7 @@
         <v>132</v>
       </c>
       <c r="M92" s="8" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="93" spans="1:13" ht="90" x14ac:dyDescent="0.25">
@@ -5763,7 +5787,7 @@
         <v>45657</v>
       </c>
       <c r="D93" s="4" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="E93" t="s">
         <v>15</v>
@@ -5777,8 +5801,8 @@
       <c r="H93" s="11" t="s">
         <v>314</v>
       </c>
-      <c r="I93" s="4" t="s">
-        <v>223</v>
+      <c r="I93" s="25" t="s">
+        <v>226</v>
       </c>
       <c r="J93" s="4" t="s">
         <v>14</v>
@@ -5790,7 +5814,7 @@
         <v>132</v>
       </c>
       <c r="M93" s="8" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="94" spans="1:13" ht="90" x14ac:dyDescent="0.25">
@@ -5804,7 +5828,7 @@
         <v>45657</v>
       </c>
       <c r="D94" s="4" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="E94" t="s">
         <v>15</v>
@@ -5818,8 +5842,8 @@
       <c r="H94" s="11" t="s">
         <v>314</v>
       </c>
-      <c r="I94" s="25" t="s">
-        <v>224</v>
+      <c r="I94" s="4" t="s">
+        <v>223</v>
       </c>
       <c r="J94" s="4" t="s">
         <v>14</v>
@@ -5831,151 +5855,151 @@
         <v>132</v>
       </c>
       <c r="M94" s="8" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="95" spans="1:13" ht="90" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>131</v>
+      </c>
+      <c r="B95" s="19">
+        <v>35677</v>
+      </c>
+      <c r="C95" s="19">
+        <v>45657</v>
+      </c>
+      <c r="D95" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="E95" t="s">
+        <v>15</v>
+      </c>
+      <c r="F95" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="G95" s="8" t="s">
+        <v>313</v>
+      </c>
+      <c r="H95" s="11" t="s">
+        <v>314</v>
+      </c>
+      <c r="I95" s="25" t="s">
+        <v>224</v>
+      </c>
+      <c r="J95" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="K95" t="s">
+        <v>19</v>
+      </c>
+      <c r="L95" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="M95" s="8" t="s">
         <v>277</v>
       </c>
     </row>
-    <row r="95" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="G95" s="8"/>
-    </row>
-    <row r="96" spans="1:13" ht="60" x14ac:dyDescent="0.25">
-      <c r="A96" t="s">
+    <row r="96" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="G96" s="8"/>
+    </row>
+    <row r="97" spans="1:13" ht="60" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
         <v>286</v>
       </c>
-      <c r="B96" s="19">
+      <c r="B97" s="19">
         <v>36526</v>
       </c>
-      <c r="C96" s="19">
+      <c r="C97" s="19">
         <v>36891</v>
       </c>
-      <c r="D96" s="4" t="s">
-        <v>394</v>
-      </c>
-      <c r="E96" t="s">
-        <v>15</v>
-      </c>
-      <c r="F96" s="6" t="s">
+      <c r="D97" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="E97" t="s">
+        <v>15</v>
+      </c>
+      <c r="F97" s="6" t="s">
         <v>287</v>
       </c>
-      <c r="G96" s="8" t="s">
+      <c r="G97" s="8" t="s">
         <v>128</v>
       </c>
-      <c r="H96" s="11" t="s">
+      <c r="H97" s="11" t="s">
         <v>129</v>
       </c>
-      <c r="I96" s="4" t="s">
+      <c r="I97" s="4" t="s">
         <v>288</v>
       </c>
-      <c r="J96" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="K96" t="s">
-        <v>19</v>
-      </c>
-      <c r="L96" s="6" t="s">
+      <c r="J97" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="K97" t="s">
+        <v>19</v>
+      </c>
+      <c r="L97" s="6" t="s">
         <v>287</v>
       </c>
-      <c r="M96" s="8" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="97" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="B97" s="19"/>
-      <c r="C97" s="19"/>
-    </row>
-    <row r="98" spans="1:13" ht="45" x14ac:dyDescent="0.25">
-      <c r="A98" t="s">
+      <c r="M97" s="8" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="98" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="B98" s="19"/>
+      <c r="C98" s="19"/>
+    </row>
+    <row r="99" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
         <v>289</v>
       </c>
-      <c r="B98" s="19">
+      <c r="B99" s="19">
         <v>34335</v>
       </c>
-      <c r="C98" s="19">
+      <c r="C99" s="19">
         <v>45169</v>
       </c>
-      <c r="D98" s="4" t="s">
+      <c r="D99" s="4" t="s">
         <v>290</v>
       </c>
-      <c r="E98" t="s">
-        <v>15</v>
-      </c>
-      <c r="F98" s="6" t="s">
+      <c r="E99" t="s">
+        <v>15</v>
+      </c>
+      <c r="F99" s="6" t="s">
         <v>291</v>
       </c>
-      <c r="G98" s="8" t="s">
+      <c r="G99" s="8" t="s">
         <v>292</v>
       </c>
-      <c r="H98" s="11" t="s">
+      <c r="H99" s="11" t="s">
         <v>293</v>
       </c>
-      <c r="I98" s="4" t="s">
+      <c r="I99" s="4" t="s">
         <v>294</v>
       </c>
-      <c r="J98" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="K98" t="s">
-        <v>19</v>
-      </c>
-      <c r="L98" s="6" t="s">
+      <c r="J99" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="K99" t="s">
+        <v>19</v>
+      </c>
+      <c r="L99" s="6" t="s">
         <v>291</v>
       </c>
-      <c r="M98" s="8" t="s">
+      <c r="M99" s="8" t="s">
         <v>295</v>
       </c>
     </row>
-    <row r="100" spans="1:13" ht="90" x14ac:dyDescent="0.25">
-      <c r="A100" t="s">
-        <v>301</v>
-      </c>
-      <c r="B100" s="19">
-        <v>34851</v>
-      </c>
-      <c r="C100" s="19">
-        <v>44196</v>
-      </c>
-      <c r="D100" t="s">
-        <v>303</v>
-      </c>
-      <c r="E100" t="s">
-        <v>15</v>
-      </c>
-      <c r="F100" s="6" t="s">
-        <v>304</v>
-      </c>
-      <c r="G100" s="8" t="s">
-        <v>307</v>
-      </c>
-      <c r="H100" s="11" t="s">
-        <v>306</v>
-      </c>
-      <c r="I100" s="4" t="s">
-        <v>305</v>
-      </c>
-      <c r="J100" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="K100" t="s">
-        <v>19</v>
-      </c>
-      <c r="L100" s="6" t="s">
-        <v>304</v>
-      </c>
-      <c r="M100" s="8" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="101" spans="1:13" ht="75" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:13" ht="90" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>301</v>
       </c>
       <c r="B101" s="19">
-        <v>44197</v>
+        <v>34851</v>
       </c>
       <c r="C101" s="19">
-        <v>45291</v>
+        <v>44196</v>
       </c>
       <c r="D101" t="s">
-        <v>308</v>
+        <v>303</v>
       </c>
       <c r="E101" t="s">
         <v>15</v>
@@ -5984,12 +6008,12 @@
         <v>304</v>
       </c>
       <c r="G101" s="8" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="H101" s="11" t="s">
-        <v>312</v>
-      </c>
-      <c r="I101" s="16" t="s">
+        <v>306</v>
+      </c>
+      <c r="I101" s="4" t="s">
         <v>305</v>
       </c>
       <c r="J101" s="4" t="s">
@@ -6002,21 +6026,21 @@
         <v>304</v>
       </c>
       <c r="M101" s="8" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="102" spans="1:13" ht="195" x14ac:dyDescent="0.25">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="102" spans="1:13" ht="75" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B102" s="19">
-        <v>33873</v>
+        <v>44197</v>
       </c>
       <c r="C102" s="19">
-        <v>45291</v>
+        <v>45657</v>
       </c>
       <c r="D102" t="s">
-        <v>399</v>
+        <v>308</v>
       </c>
       <c r="E102" t="s">
         <v>15</v>
@@ -6025,10 +6049,10 @@
         <v>304</v>
       </c>
       <c r="G102" s="8" t="s">
-        <v>17</v>
+        <v>311</v>
       </c>
       <c r="H102" s="11" t="s">
-        <v>32</v>
+        <v>312</v>
       </c>
       <c r="I102" s="16" t="s">
         <v>305</v>
@@ -6043,66 +6067,66 @@
         <v>304</v>
       </c>
       <c r="M102" s="8" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="103" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="B103" s="19"/>
-      <c r="C103" s="19"/>
-    </row>
-    <row r="104" spans="1:13" ht="45" x14ac:dyDescent="0.25">
-      <c r="A104" t="s">
-        <v>315</v>
-      </c>
-      <c r="B104" s="19">
-        <v>37530</v>
-      </c>
-      <c r="C104" s="19">
-        <v>40482</v>
-      </c>
-      <c r="D104" s="4" t="s">
-        <v>316</v>
-      </c>
-      <c r="E104" t="s">
-        <v>15</v>
-      </c>
-      <c r="F104" s="6" t="s">
-        <v>320</v>
-      </c>
-      <c r="G104" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="H104" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="I104" s="16" t="s">
-        <v>319</v>
-      </c>
-      <c r="J104" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="K104" t="s">
-        <v>19</v>
-      </c>
-      <c r="L104" s="6" t="s">
-        <v>320</v>
-      </c>
-      <c r="M104" s="8" t="s">
-        <v>336</v>
-      </c>
+        <v>310</v>
+      </c>
+    </row>
+    <row r="103" spans="1:13" ht="195" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>302</v>
+      </c>
+      <c r="B103" s="19">
+        <v>33873</v>
+      </c>
+      <c r="C103" s="19">
+        <v>45657</v>
+      </c>
+      <c r="D103" t="s">
+        <v>395</v>
+      </c>
+      <c r="E103" t="s">
+        <v>15</v>
+      </c>
+      <c r="F103" s="6" t="s">
+        <v>304</v>
+      </c>
+      <c r="G103" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="H103" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="I103" s="16" t="s">
+        <v>305</v>
+      </c>
+      <c r="J103" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="K103" t="s">
+        <v>19</v>
+      </c>
+      <c r="L103" s="6" t="s">
+        <v>304</v>
+      </c>
+      <c r="M103" s="8" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="104" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="B104" s="19"/>
+      <c r="C104" s="19"/>
     </row>
     <row r="105" spans="1:13" ht="45" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>315</v>
       </c>
       <c r="B105" s="19">
-        <v>40483</v>
+        <v>37530</v>
       </c>
       <c r="C105" s="19">
-        <v>43951</v>
+        <v>40482</v>
       </c>
       <c r="D105" s="4" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="E105" t="s">
         <v>15</v>
@@ -6110,14 +6134,14 @@
       <c r="F105" s="6" t="s">
         <v>320</v>
       </c>
-      <c r="G105" s="8" t="s">
+      <c r="G105" s="9" t="s">
         <v>21</v>
       </c>
       <c r="H105" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="I105" s="4" t="s">
-        <v>318</v>
+      <c r="I105" s="16" t="s">
+        <v>319</v>
       </c>
       <c r="J105" s="4" t="s">
         <v>14</v>
@@ -6132,18 +6156,18 @@
         <v>336</v>
       </c>
     </row>
-    <row r="106" spans="1:13" ht="60" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:13" ht="45" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>315</v>
       </c>
       <c r="B106" s="19">
-        <v>44105</v>
+        <v>40483</v>
       </c>
       <c r="C106" s="19">
-        <v>45657</v>
+        <v>43951</v>
       </c>
       <c r="D106" s="4" t="s">
-        <v>333</v>
+        <v>317</v>
       </c>
       <c r="E106" t="s">
         <v>15</v>
@@ -6152,10 +6176,10 @@
         <v>320</v>
       </c>
       <c r="G106" s="8" t="s">
-        <v>334</v>
-      </c>
-      <c r="H106" s="11" t="s">
-        <v>335</v>
+        <v>21</v>
+      </c>
+      <c r="H106" s="12" t="s">
+        <v>21</v>
       </c>
       <c r="I106" s="4" t="s">
         <v>318</v>
@@ -6170,21 +6194,21 @@
         <v>320</v>
       </c>
       <c r="M106" s="8" t="s">
-        <v>337</v>
-      </c>
-    </row>
-    <row r="107" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="107" spans="1:13" ht="60" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>405</v>
+        <v>315</v>
       </c>
       <c r="B107" s="19">
-        <v>37408</v>
+        <v>44105</v>
       </c>
       <c r="C107" s="19">
-        <v>44196</v>
+        <v>45657</v>
       </c>
       <c r="D107" s="4" t="s">
-        <v>321</v>
+        <v>333</v>
       </c>
       <c r="E107" t="s">
         <v>15</v>
@@ -6193,13 +6217,13 @@
         <v>320</v>
       </c>
       <c r="G107" s="8" t="s">
-        <v>80</v>
+        <v>334</v>
       </c>
       <c r="H107" s="11" t="s">
-        <v>81</v>
+        <v>335</v>
       </c>
       <c r="I107" s="4" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="J107" s="4" t="s">
         <v>14</v>
@@ -6211,12 +6235,12 @@
         <v>320</v>
       </c>
       <c r="M107" s="8" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="108" spans="1:13" ht="30" x14ac:dyDescent="0.25">
-      <c r="A108" s="4" t="s">
-        <v>330</v>
+        <v>337</v>
+      </c>
+    </row>
+    <row r="108" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
+        <v>401</v>
       </c>
       <c r="B108" s="19">
         <v>37408</v>
@@ -6225,10 +6249,10 @@
         <v>44196</v>
       </c>
       <c r="D108" s="4" t="s">
-        <v>14</v>
+        <v>321</v>
       </c>
       <c r="E108" t="s">
-        <v>328</v>
+        <v>15</v>
       </c>
       <c r="F108" s="6" t="s">
         <v>320</v>
@@ -6239,7 +6263,7 @@
       <c r="H108" s="11" t="s">
         <v>81</v>
       </c>
-      <c r="I108" s="16" t="s">
+      <c r="I108" s="4" t="s">
         <v>322</v>
       </c>
       <c r="J108" s="4" t="s">
@@ -6252,62 +6276,62 @@
         <v>320</v>
       </c>
       <c r="M108" s="8" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="109" spans="1:13" ht="45" x14ac:dyDescent="0.25">
-      <c r="A109" t="s">
-        <v>405</v>
+        <v>323</v>
+      </c>
+    </row>
+    <row r="109" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+      <c r="A109" s="4" t="s">
+        <v>330</v>
       </c>
       <c r="B109" s="19">
-        <v>37409</v>
+        <v>37408</v>
       </c>
       <c r="C109" s="19">
         <v>44196</v>
       </c>
       <c r="D109" s="4" t="s">
-        <v>321</v>
+        <v>14</v>
       </c>
       <c r="E109" t="s">
-        <v>15</v>
+        <v>328</v>
       </c>
       <c r="F109" s="6" t="s">
         <v>320</v>
       </c>
-      <c r="G109" s="9" t="s">
-        <v>40</v>
+      <c r="G109" s="8" t="s">
+        <v>80</v>
       </c>
       <c r="H109" s="11" t="s">
-        <v>40</v>
-      </c>
-      <c r="I109" s="4" t="s">
-        <v>330</v>
+        <v>81</v>
+      </c>
+      <c r="I109" s="16" t="s">
+        <v>322</v>
       </c>
       <c r="J109" s="4" t="s">
         <v>14</v>
       </c>
       <c r="K109" t="s">
-        <v>328</v>
+        <v>19</v>
       </c>
       <c r="L109" s="6" t="s">
         <v>320</v>
       </c>
       <c r="M109" s="8" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="110" spans="1:13" ht="75" x14ac:dyDescent="0.25">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="110" spans="1:13" ht="45" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>405</v>
+        <v>401</v>
       </c>
       <c r="B110" s="19">
-        <v>28788</v>
+        <v>37409</v>
       </c>
       <c r="C110" s="19">
         <v>44196</v>
       </c>
       <c r="D110" s="4" t="s">
-        <v>327</v>
+        <v>321</v>
       </c>
       <c r="E110" t="s">
         <v>15</v>
@@ -6316,42 +6340,42 @@
         <v>320</v>
       </c>
       <c r="G110" s="9" t="s">
-        <v>157</v>
-      </c>
-      <c r="H110" s="12" t="s">
-        <v>155</v>
+        <v>40</v>
+      </c>
+      <c r="H110" s="11" t="s">
+        <v>40</v>
       </c>
       <c r="I110" s="4" t="s">
-        <v>325</v>
+        <v>330</v>
       </c>
       <c r="J110" s="4" t="s">
         <v>14</v>
       </c>
       <c r="K110" t="s">
-        <v>19</v>
+        <v>328</v>
       </c>
       <c r="L110" s="6" t="s">
         <v>320</v>
       </c>
       <c r="M110" s="8" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="111" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="111" spans="1:13" ht="75" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>331</v>
+        <v>401</v>
       </c>
       <c r="B111" s="19">
-        <v>28789</v>
+        <v>28788</v>
       </c>
       <c r="C111" s="19">
-        <v>44197</v>
+        <v>44196</v>
       </c>
       <c r="D111" s="4" t="s">
-        <v>14</v>
+        <v>327</v>
       </c>
       <c r="E111" t="s">
-        <v>328</v>
+        <v>15</v>
       </c>
       <c r="F111" s="6" t="s">
         <v>320</v>
@@ -6375,59 +6399,59 @@
         <v>320</v>
       </c>
       <c r="M111" s="8" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="112" spans="1:13" ht="75" x14ac:dyDescent="0.25">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="112" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>405</v>
+        <v>331</v>
       </c>
       <c r="B112" s="19">
-        <v>28788</v>
+        <v>28789</v>
       </c>
       <c r="C112" s="19">
-        <v>44196</v>
+        <v>44197</v>
       </c>
       <c r="D112" s="4" t="s">
-        <v>327</v>
+        <v>14</v>
       </c>
       <c r="E112" t="s">
-        <v>15</v>
+        <v>328</v>
       </c>
       <c r="F112" s="6" t="s">
         <v>320</v>
       </c>
       <c r="G112" s="9" t="s">
-        <v>40</v>
+        <v>157</v>
       </c>
       <c r="H112" s="12" t="s">
-        <v>40</v>
-      </c>
-      <c r="I112" t="s">
-        <v>331</v>
+        <v>155</v>
+      </c>
+      <c r="I112" s="4" t="s">
+        <v>325</v>
       </c>
       <c r="J112" s="4" t="s">
         <v>14</v>
       </c>
       <c r="K112" t="s">
-        <v>328</v>
+        <v>19</v>
       </c>
       <c r="L112" s="6" t="s">
         <v>320</v>
       </c>
       <c r="M112" s="8" t="s">
-        <v>324</v>
+        <v>329</v>
       </c>
     </row>
     <row r="113" spans="1:13" ht="75" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>405</v>
+        <v>401</v>
       </c>
       <c r="B113" s="19">
-        <v>44197</v>
+        <v>28788</v>
       </c>
       <c r="C113" s="19">
-        <v>45728</v>
+        <v>44196</v>
       </c>
       <c r="D113" s="4" t="s">
         <v>327</v>
@@ -6438,59 +6462,96 @@
       <c r="F113" s="6" t="s">
         <v>320</v>
       </c>
-      <c r="G113" s="8" t="s">
-        <v>406</v>
-      </c>
-      <c r="H113" s="11" t="s">
-        <v>407</v>
-      </c>
-      <c r="I113" s="4" t="s">
-        <v>325</v>
+      <c r="G113" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="H113" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="I113" t="s">
+        <v>331</v>
       </c>
       <c r="J113" s="4" t="s">
         <v>14</v>
       </c>
       <c r="K113" t="s">
-        <v>19</v>
+        <v>328</v>
       </c>
       <c r="L113" s="6" t="s">
         <v>320</v>
       </c>
       <c r="M113" s="8" t="s">
-        <v>408</v>
-      </c>
-    </row>
-    <row r="114" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="B114" s="19"/>
-      <c r="C114" s="19"/>
-    </row>
-    <row r="115" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="114" spans="1:13" ht="75" x14ac:dyDescent="0.25">
+      <c r="A114" t="s">
+        <v>401</v>
+      </c>
+      <c r="B114" s="19">
+        <v>28788</v>
+      </c>
+      <c r="C114" s="19">
+        <v>44196</v>
+      </c>
+      <c r="D114" s="4" t="s">
+        <v>327</v>
+      </c>
+      <c r="E114" t="s">
+        <v>15</v>
+      </c>
+      <c r="F114" s="6" t="s">
+        <v>320</v>
+      </c>
+      <c r="G114" s="8" t="s">
+        <v>157</v>
+      </c>
+      <c r="H114" s="11" t="s">
+        <v>155</v>
+      </c>
+      <c r="I114" s="16" t="s">
+        <v>325</v>
+      </c>
+      <c r="J114" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="K114" t="s">
+        <v>19</v>
+      </c>
+      <c r="L114" s="6" t="s">
+        <v>320</v>
+      </c>
+      <c r="M114" s="8" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="115" spans="1:13" ht="75" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>343</v>
+        <v>401</v>
       </c>
       <c r="B115" s="19">
-        <v>37438</v>
+        <v>44197</v>
       </c>
       <c r="C115" s="19">
-        <v>43100</v>
+        <v>45908</v>
       </c>
       <c r="D115" s="4" t="s">
-        <v>14</v>
+        <v>448</v>
       </c>
       <c r="E115" t="s">
-        <v>338</v>
+        <v>15</v>
       </c>
       <c r="F115" s="6" t="s">
-        <v>340</v>
-      </c>
-      <c r="G115" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="H115" s="12" t="s">
-        <v>40</v>
-      </c>
-      <c r="I115" s="4" t="s">
-        <v>339</v>
+        <v>320</v>
+      </c>
+      <c r="G115" s="8" t="s">
+        <v>402</v>
+      </c>
+      <c r="H115" s="11" t="s">
+        <v>403</v>
+      </c>
+      <c r="I115" s="16" t="s">
+        <v>325</v>
       </c>
       <c r="J115" s="4" t="s">
         <v>14</v>
@@ -6499,76 +6560,39 @@
         <v>19</v>
       </c>
       <c r="L115" s="6" t="s">
-        <v>340</v>
+        <v>320</v>
       </c>
       <c r="M115" s="8" t="s">
-        <v>341</v>
+        <v>404</v>
       </c>
     </row>
     <row r="116" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A116" t="s">
-        <v>342</v>
-      </c>
-      <c r="B116" s="19">
-        <v>37439</v>
-      </c>
-      <c r="C116" s="19">
-        <v>43100</v>
-      </c>
-      <c r="D116" s="4" t="s">
-        <v>345</v>
-      </c>
-      <c r="E116" t="s">
-        <v>15</v>
-      </c>
-      <c r="F116" s="6" t="s">
-        <v>340</v>
-      </c>
-      <c r="G116" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="H116" s="11" t="s">
-        <v>40</v>
-      </c>
-      <c r="I116" t="s">
-        <v>343</v>
-      </c>
-      <c r="J116" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="K116" t="s">
-        <v>338</v>
-      </c>
-      <c r="L116" s="6" t="s">
-        <v>340</v>
-      </c>
-      <c r="M116" s="8" t="s">
-        <v>344</v>
-      </c>
+      <c r="B116" s="19"/>
+      <c r="C116" s="19"/>
     </row>
     <row r="117" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B117" s="19">
-        <v>37439</v>
+        <v>37438</v>
       </c>
       <c r="C117" s="19">
         <v>43100</v>
       </c>
       <c r="D117" s="4" t="s">
-        <v>345</v>
+        <v>14</v>
       </c>
       <c r="E117" t="s">
-        <v>15</v>
+        <v>338</v>
       </c>
       <c r="F117" s="6" t="s">
         <v>340</v>
       </c>
-      <c r="G117" s="8" t="s">
+      <c r="G117" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="H117" s="11" t="s">
+      <c r="H117" s="12" t="s">
         <v>40</v>
       </c>
       <c r="I117" s="4" t="s">
@@ -6584,97 +6608,97 @@
         <v>340</v>
       </c>
       <c r="M117" s="8" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="118" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A118" t="s">
+        <v>342</v>
+      </c>
+      <c r="B118" s="19">
+        <v>37439</v>
+      </c>
+      <c r="C118" s="19">
+        <v>43100</v>
+      </c>
+      <c r="D118" s="4" t="s">
+        <v>345</v>
+      </c>
+      <c r="E118" t="s">
+        <v>15</v>
+      </c>
+      <c r="F118" s="6" t="s">
+        <v>340</v>
+      </c>
+      <c r="G118" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="H118" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="I118" t="s">
+        <v>343</v>
+      </c>
+      <c r="J118" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="K118" t="s">
+        <v>338</v>
+      </c>
+      <c r="L118" s="6" t="s">
+        <v>340</v>
+      </c>
+      <c r="M118" s="8" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="119" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+      <c r="A119" t="s">
+        <v>342</v>
+      </c>
+      <c r="B119" s="19">
+        <v>37439</v>
+      </c>
+      <c r="C119" s="19">
+        <v>43100</v>
+      </c>
+      <c r="D119" s="4" t="s">
+        <v>345</v>
+      </c>
+      <c r="E119" t="s">
+        <v>15</v>
+      </c>
+      <c r="F119" s="6" t="s">
+        <v>340</v>
+      </c>
+      <c r="G119" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="H119" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="I119" s="4" t="s">
+        <v>339</v>
+      </c>
+      <c r="J119" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="K119" t="s">
+        <v>19</v>
+      </c>
+      <c r="L119" s="6" t="s">
+        <v>340</v>
+      </c>
+      <c r="M119" s="8" t="s">
         <v>346</v>
       </c>
     </row>
-    <row r="118" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="B118" s="19"/>
-      <c r="C118" s="19"/>
-    </row>
-    <row r="119" spans="1:13" ht="75" x14ac:dyDescent="0.25">
-      <c r="A119" s="24" t="s">
-        <v>349</v>
-      </c>
-      <c r="B119" s="19">
-        <v>33455</v>
-      </c>
-      <c r="C119" s="19">
-        <v>45291</v>
-      </c>
-      <c r="D119" s="4" t="s">
-        <v>409</v>
-      </c>
-      <c r="E119" t="s">
-        <v>15</v>
-      </c>
-      <c r="F119" s="6" t="s">
-        <v>347</v>
-      </c>
-      <c r="G119" s="8" t="s">
-        <v>334</v>
-      </c>
-      <c r="H119" s="11" t="s">
-        <v>335</v>
-      </c>
-      <c r="I119" s="4" t="s">
-        <v>348</v>
-      </c>
-      <c r="J119" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="K119" t="s">
-        <v>19</v>
-      </c>
-      <c r="L119" s="6" t="s">
-        <v>347</v>
-      </c>
-      <c r="M119" s="8" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="120" spans="1:13" ht="75" x14ac:dyDescent="0.25">
-      <c r="A120" t="s">
-        <v>349</v>
-      </c>
-      <c r="B120" s="19">
-        <v>45292</v>
-      </c>
-      <c r="C120" s="19">
-        <v>45747</v>
-      </c>
-      <c r="D120" s="4" t="s">
-        <v>410</v>
-      </c>
-      <c r="E120" t="s">
-        <v>15</v>
-      </c>
-      <c r="F120" s="6" t="s">
-        <v>347</v>
-      </c>
-      <c r="G120" s="8" t="s">
-        <v>334</v>
-      </c>
-      <c r="H120" s="11" t="s">
-        <v>335</v>
-      </c>
-      <c r="I120" s="16" t="s">
-        <v>348</v>
-      </c>
-      <c r="J120" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="K120" t="s">
-        <v>19</v>
-      </c>
-      <c r="L120" s="6" t="s">
-        <v>347</v>
-      </c>
-      <c r="M120" s="8" t="s">
-        <v>416</v>
-      </c>
+    <row r="120" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="B120" s="19"/>
+      <c r="C120" s="19"/>
     </row>
     <row r="121" spans="1:13" ht="75" x14ac:dyDescent="0.25">
-      <c r="A121" t="s">
+      <c r="A121" s="24" t="s">
         <v>349</v>
       </c>
       <c r="B121" s="19">
@@ -6684,7 +6708,7 @@
         <v>45291</v>
       </c>
       <c r="D121" s="4" t="s">
-        <v>411</v>
+        <v>405</v>
       </c>
       <c r="E121" t="s">
         <v>15</v>
@@ -6693,12 +6717,12 @@
         <v>347</v>
       </c>
       <c r="G121" s="8" t="s">
-        <v>421</v>
+        <v>334</v>
       </c>
       <c r="H121" s="11" t="s">
-        <v>422</v>
-      </c>
-      <c r="I121" s="16" t="s">
+        <v>335</v>
+      </c>
+      <c r="I121" s="4" t="s">
         <v>348</v>
       </c>
       <c r="J121" s="4" t="s">
@@ -6711,7 +6735,7 @@
         <v>347</v>
       </c>
       <c r="M121" s="8" t="s">
-        <v>417</v>
+        <v>411</v>
       </c>
     </row>
     <row r="122" spans="1:13" ht="75" x14ac:dyDescent="0.25">
@@ -6725,7 +6749,7 @@
         <v>45747</v>
       </c>
       <c r="D122" s="4" t="s">
-        <v>412</v>
+        <v>406</v>
       </c>
       <c r="E122" t="s">
         <v>15</v>
@@ -6734,10 +6758,10 @@
         <v>347</v>
       </c>
       <c r="G122" s="8" t="s">
-        <v>423</v>
+        <v>334</v>
       </c>
       <c r="H122" s="11" t="s">
-        <v>424</v>
+        <v>335</v>
       </c>
       <c r="I122" s="16" t="s">
         <v>348</v>
@@ -6752,7 +6776,7 @@
         <v>347</v>
       </c>
       <c r="M122" s="8" t="s">
-        <v>418</v>
+        <v>412</v>
       </c>
     </row>
     <row r="123" spans="1:13" ht="75" x14ac:dyDescent="0.25">
@@ -6766,7 +6790,7 @@
         <v>45291</v>
       </c>
       <c r="D123" s="4" t="s">
-        <v>413</v>
+        <v>407</v>
       </c>
       <c r="E123" t="s">
         <v>15</v>
@@ -6775,10 +6799,10 @@
         <v>347</v>
       </c>
       <c r="G123" s="8" t="s">
-        <v>423</v>
+        <v>417</v>
       </c>
       <c r="H123" s="11" t="s">
-        <v>424</v>
+        <v>418</v>
       </c>
       <c r="I123" s="16" t="s">
         <v>348</v>
@@ -6793,7 +6817,7 @@
         <v>347</v>
       </c>
       <c r="M123" s="8" t="s">
-        <v>419</v>
+        <v>413</v>
       </c>
     </row>
     <row r="124" spans="1:13" ht="75" x14ac:dyDescent="0.25">
@@ -6807,7 +6831,7 @@
         <v>45747</v>
       </c>
       <c r="D124" s="4" t="s">
-        <v>414</v>
+        <v>408</v>
       </c>
       <c r="E124" t="s">
         <v>15</v>
@@ -6816,10 +6840,10 @@
         <v>347</v>
       </c>
       <c r="G124" s="8" t="s">
-        <v>423</v>
+        <v>419</v>
       </c>
       <c r="H124" s="11" t="s">
-        <v>424</v>
+        <v>420</v>
       </c>
       <c r="I124" s="16" t="s">
         <v>348</v>
@@ -6834,10 +6858,10 @@
         <v>347</v>
       </c>
       <c r="M124" s="8" t="s">
-        <v>420</v>
-      </c>
-    </row>
-    <row r="125" spans="1:13" ht="90" x14ac:dyDescent="0.25">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="125" spans="1:13" ht="75" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>349</v>
       </c>
@@ -6848,7 +6872,7 @@
         <v>45291</v>
       </c>
       <c r="D125" s="4" t="s">
-        <v>425</v>
+        <v>409</v>
       </c>
       <c r="E125" t="s">
         <v>15</v>
@@ -6857,13 +6881,13 @@
         <v>347</v>
       </c>
       <c r="G125" s="8" t="s">
-        <v>334</v>
+        <v>419</v>
       </c>
       <c r="H125" s="11" t="s">
-        <v>335</v>
-      </c>
-      <c r="I125" s="10" t="s">
-        <v>382</v>
+        <v>420</v>
+      </c>
+      <c r="I125" s="16" t="s">
+        <v>348</v>
       </c>
       <c r="J125" s="4" t="s">
         <v>14</v>
@@ -6878,7 +6902,7 @@
         <v>415</v>
       </c>
     </row>
-    <row r="126" spans="1:13" ht="90" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:13" ht="75" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>349</v>
       </c>
@@ -6889,7 +6913,7 @@
         <v>45747</v>
       </c>
       <c r="D126" s="4" t="s">
-        <v>426</v>
+        <v>410</v>
       </c>
       <c r="E126" t="s">
         <v>15</v>
@@ -6898,13 +6922,13 @@
         <v>347</v>
       </c>
       <c r="G126" s="8" t="s">
-        <v>334</v>
+        <v>419</v>
       </c>
       <c r="H126" s="11" t="s">
-        <v>335</v>
-      </c>
-      <c r="I126" s="10" t="s">
-        <v>382</v>
+        <v>420</v>
+      </c>
+      <c r="I126" s="16" t="s">
+        <v>348</v>
       </c>
       <c r="J126" s="4" t="s">
         <v>14</v>
@@ -6930,7 +6954,7 @@
         <v>45291</v>
       </c>
       <c r="D127" s="4" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="E127" t="s">
         <v>15</v>
@@ -6939,13 +6963,13 @@
         <v>347</v>
       </c>
       <c r="G127" s="8" t="s">
-        <v>423</v>
+        <v>334</v>
       </c>
       <c r="H127" s="11" t="s">
-        <v>424</v>
+        <v>335</v>
       </c>
       <c r="I127" s="10" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="J127" s="4" t="s">
         <v>14</v>
@@ -6957,7 +6981,7 @@
         <v>347</v>
       </c>
       <c r="M127" s="8" t="s">
-        <v>417</v>
+        <v>411</v>
       </c>
     </row>
     <row r="128" spans="1:13" ht="90" x14ac:dyDescent="0.25">
@@ -6971,7 +6995,7 @@
         <v>45747</v>
       </c>
       <c r="D128" s="4" t="s">
-        <v>428</v>
+        <v>422</v>
       </c>
       <c r="E128" t="s">
         <v>15</v>
@@ -6980,13 +7004,13 @@
         <v>347</v>
       </c>
       <c r="G128" s="8" t="s">
-        <v>423</v>
+        <v>334</v>
       </c>
       <c r="H128" s="11" t="s">
-        <v>424</v>
+        <v>335</v>
       </c>
       <c r="I128" s="10" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="J128" s="4" t="s">
         <v>14</v>
@@ -6998,7 +7022,7 @@
         <v>347</v>
       </c>
       <c r="M128" s="8" t="s">
-        <v>418</v>
+        <v>412</v>
       </c>
     </row>
     <row r="129" spans="1:13" ht="90" x14ac:dyDescent="0.25">
@@ -7012,7 +7036,7 @@
         <v>45291</v>
       </c>
       <c r="D129" s="4" t="s">
-        <v>429</v>
+        <v>423</v>
       </c>
       <c r="E129" t="s">
         <v>15</v>
@@ -7021,13 +7045,13 @@
         <v>347</v>
       </c>
       <c r="G129" s="8" t="s">
-        <v>423</v>
+        <v>419</v>
       </c>
       <c r="H129" s="11" t="s">
-        <v>424</v>
+        <v>420</v>
       </c>
       <c r="I129" s="10" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="J129" s="4" t="s">
         <v>14</v>
@@ -7039,7 +7063,7 @@
         <v>347</v>
       </c>
       <c r="M129" s="8" t="s">
-        <v>419</v>
+        <v>413</v>
       </c>
     </row>
     <row r="130" spans="1:13" ht="90" x14ac:dyDescent="0.25">
@@ -7053,7 +7077,7 @@
         <v>45747</v>
       </c>
       <c r="D130" s="4" t="s">
-        <v>430</v>
+        <v>424</v>
       </c>
       <c r="E130" t="s">
         <v>15</v>
@@ -7062,13 +7086,13 @@
         <v>347</v>
       </c>
       <c r="G130" s="8" t="s">
-        <v>423</v>
+        <v>419</v>
       </c>
       <c r="H130" s="11" t="s">
-        <v>424</v>
+        <v>420</v>
       </c>
       <c r="I130" s="10" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="J130" s="4" t="s">
         <v>14</v>
@@ -7080,10 +7104,10 @@
         <v>347</v>
       </c>
       <c r="M130" s="8" t="s">
-        <v>420</v>
-      </c>
-    </row>
-    <row r="131" spans="1:13" ht="105" x14ac:dyDescent="0.25">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="131" spans="1:13" ht="90" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
         <v>349</v>
       </c>
@@ -7091,10 +7115,10 @@
         <v>33455</v>
       </c>
       <c r="C131" s="19">
-        <v>45657</v>
+        <v>45291</v>
       </c>
       <c r="D131" s="4" t="s">
-        <v>436</v>
+        <v>425</v>
       </c>
       <c r="E131" t="s">
         <v>15</v>
@@ -7103,13 +7127,13 @@
         <v>347</v>
       </c>
       <c r="G131" s="8" t="s">
-        <v>334</v>
+        <v>419</v>
       </c>
       <c r="H131" s="11" t="s">
-        <v>335</v>
-      </c>
-      <c r="I131" s="4" t="s">
-        <v>383</v>
+        <v>420</v>
+      </c>
+      <c r="I131" s="10" t="s">
+        <v>378</v>
       </c>
       <c r="J131" s="4" t="s">
         <v>14</v>
@@ -7124,7 +7148,7 @@
         <v>415</v>
       </c>
     </row>
-    <row r="132" spans="1:13" ht="105" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:13" ht="90" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
         <v>349</v>
       </c>
@@ -7135,7 +7159,7 @@
         <v>45747</v>
       </c>
       <c r="D132" s="4" t="s">
-        <v>435</v>
+        <v>426</v>
       </c>
       <c r="E132" t="s">
         <v>15</v>
@@ -7144,13 +7168,13 @@
         <v>347</v>
       </c>
       <c r="G132" s="8" t="s">
-        <v>334</v>
+        <v>419</v>
       </c>
       <c r="H132" s="11" t="s">
-        <v>335</v>
-      </c>
-      <c r="I132" s="4" t="s">
-        <v>383</v>
+        <v>420</v>
+      </c>
+      <c r="I132" s="10" t="s">
+        <v>378</v>
       </c>
       <c r="J132" s="4" t="s">
         <v>14</v>
@@ -7173,10 +7197,10 @@
         <v>33455</v>
       </c>
       <c r="C133" s="19">
-        <v>45291</v>
+        <v>45657</v>
       </c>
       <c r="D133" s="4" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="E133" t="s">
         <v>15</v>
@@ -7185,13 +7209,13 @@
         <v>347</v>
       </c>
       <c r="G133" s="8" t="s">
-        <v>423</v>
+        <v>334</v>
       </c>
       <c r="H133" s="11" t="s">
-        <v>424</v>
+        <v>335</v>
       </c>
       <c r="I133" s="4" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="J133" s="4" t="s">
         <v>14</v>
@@ -7203,7 +7227,7 @@
         <v>347</v>
       </c>
       <c r="M133" s="8" t="s">
-        <v>417</v>
+        <v>411</v>
       </c>
     </row>
     <row r="134" spans="1:13" ht="105" x14ac:dyDescent="0.25">
@@ -7217,7 +7241,7 @@
         <v>45747</v>
       </c>
       <c r="D134" s="4" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="E134" t="s">
         <v>15</v>
@@ -7226,13 +7250,13 @@
         <v>347</v>
       </c>
       <c r="G134" s="8" t="s">
-        <v>423</v>
+        <v>334</v>
       </c>
       <c r="H134" s="11" t="s">
-        <v>424</v>
+        <v>335</v>
       </c>
       <c r="I134" s="4" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="J134" s="4" t="s">
         <v>14</v>
@@ -7244,7 +7268,7 @@
         <v>347</v>
       </c>
       <c r="M134" s="8" t="s">
-        <v>418</v>
+        <v>412</v>
       </c>
     </row>
     <row r="135" spans="1:13" ht="105" x14ac:dyDescent="0.25">
@@ -7258,7 +7282,7 @@
         <v>45291</v>
       </c>
       <c r="D135" s="4" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="E135" t="s">
         <v>15</v>
@@ -7267,13 +7291,13 @@
         <v>347</v>
       </c>
       <c r="G135" s="8" t="s">
-        <v>423</v>
+        <v>419</v>
       </c>
       <c r="H135" s="11" t="s">
-        <v>424</v>
+        <v>420</v>
       </c>
       <c r="I135" s="4" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="J135" s="4" t="s">
         <v>14</v>
@@ -7285,7 +7309,7 @@
         <v>347</v>
       </c>
       <c r="M135" s="8" t="s">
-        <v>419</v>
+        <v>413</v>
       </c>
     </row>
     <row r="136" spans="1:13" ht="105" x14ac:dyDescent="0.25">
@@ -7299,7 +7323,7 @@
         <v>45747</v>
       </c>
       <c r="D136" s="4" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="E136" t="s">
         <v>15</v>
@@ -7308,13 +7332,13 @@
         <v>347</v>
       </c>
       <c r="G136" s="8" t="s">
-        <v>423</v>
+        <v>419</v>
       </c>
       <c r="H136" s="11" t="s">
-        <v>424</v>
+        <v>420</v>
       </c>
       <c r="I136" s="4" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="J136" s="4" t="s">
         <v>14</v>
@@ -7326,11 +7350,11 @@
         <v>347</v>
       </c>
       <c r="M136" s="8" t="s">
-        <v>420</v>
-      </c>
-    </row>
-    <row r="137" spans="1:13" ht="75" x14ac:dyDescent="0.25">
-      <c r="A137" s="26" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="137" spans="1:13" ht="105" x14ac:dyDescent="0.25">
+      <c r="A137" t="s">
         <v>349</v>
       </c>
       <c r="B137" s="19">
@@ -7340,7 +7364,7 @@
         <v>45291</v>
       </c>
       <c r="D137" s="4" t="s">
-        <v>409</v>
+        <v>428</v>
       </c>
       <c r="E137" t="s">
         <v>15</v>
@@ -7349,13 +7373,13 @@
         <v>347</v>
       </c>
       <c r="G137" s="8" t="s">
-        <v>350</v>
+        <v>419</v>
       </c>
       <c r="H137" s="11" t="s">
-        <v>351</v>
-      </c>
-      <c r="I137" s="10" t="s">
-        <v>437</v>
+        <v>420</v>
+      </c>
+      <c r="I137" s="4" t="s">
+        <v>379</v>
       </c>
       <c r="J137" s="4" t="s">
         <v>14</v>
@@ -7367,11 +7391,11 @@
         <v>347</v>
       </c>
       <c r="M137" s="8" t="s">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="138" spans="1:13" ht="75" x14ac:dyDescent="0.25">
-      <c r="A138" s="23" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="138" spans="1:13" ht="105" x14ac:dyDescent="0.25">
+      <c r="A138" t="s">
         <v>349</v>
       </c>
       <c r="B138" s="19">
@@ -7381,7 +7405,7 @@
         <v>45747</v>
       </c>
       <c r="D138" s="4" t="s">
-        <v>410</v>
+        <v>427</v>
       </c>
       <c r="E138" t="s">
         <v>15</v>
@@ -7390,13 +7414,13 @@
         <v>347</v>
       </c>
       <c r="G138" s="8" t="s">
-        <v>352</v>
+        <v>419</v>
       </c>
       <c r="H138" s="11" t="s">
-        <v>353</v>
-      </c>
-      <c r="I138" s="10" t="s">
-        <v>437</v>
+        <v>420</v>
+      </c>
+      <c r="I138" s="4" t="s">
+        <v>379</v>
       </c>
       <c r="J138" s="4" t="s">
         <v>14</v>
@@ -7408,11 +7432,11 @@
         <v>347</v>
       </c>
       <c r="M138" s="8" t="s">
-        <v>355</v>
+        <v>416</v>
       </c>
     </row>
     <row r="139" spans="1:13" ht="75" x14ac:dyDescent="0.25">
-      <c r="A139" s="23" t="s">
+      <c r="A139" s="26" t="s">
         <v>349</v>
       </c>
       <c r="B139" s="19">
@@ -7422,7 +7446,7 @@
         <v>45291</v>
       </c>
       <c r="D139" s="4" t="s">
-        <v>411</v>
+        <v>405</v>
       </c>
       <c r="E139" t="s">
         <v>15</v>
@@ -7431,13 +7455,13 @@
         <v>347</v>
       </c>
       <c r="G139" s="8" t="s">
-        <v>356</v>
+        <v>350</v>
       </c>
       <c r="H139" s="11" t="s">
-        <v>357</v>
+        <v>351</v>
       </c>
       <c r="I139" s="10" t="s">
-        <v>437</v>
+        <v>433</v>
       </c>
       <c r="J139" s="4" t="s">
         <v>14</v>
@@ -7449,7 +7473,7 @@
         <v>347</v>
       </c>
       <c r="M139" s="8" t="s">
-        <v>438</v>
+        <v>354</v>
       </c>
     </row>
     <row r="140" spans="1:13" ht="75" x14ac:dyDescent="0.25">
@@ -7460,10 +7484,10 @@
         <v>45292</v>
       </c>
       <c r="C140" s="19">
-        <v>45747</v>
+        <v>45858</v>
       </c>
       <c r="D140" s="4" t="s">
-        <v>412</v>
+        <v>406</v>
       </c>
       <c r="E140" t="s">
         <v>15</v>
@@ -7472,13 +7496,13 @@
         <v>347</v>
       </c>
       <c r="G140" s="8" t="s">
-        <v>356</v>
+        <v>352</v>
       </c>
       <c r="H140" s="11" t="s">
-        <v>357</v>
+        <v>353</v>
       </c>
       <c r="I140" s="10" t="s">
-        <v>437</v>
+        <v>433</v>
       </c>
       <c r="J140" s="4" t="s">
         <v>14</v>
@@ -7490,7 +7514,7 @@
         <v>347</v>
       </c>
       <c r="M140" s="8" t="s">
-        <v>439</v>
+        <v>447</v>
       </c>
     </row>
     <row r="141" spans="1:13" ht="75" x14ac:dyDescent="0.25">
@@ -7504,7 +7528,7 @@
         <v>45291</v>
       </c>
       <c r="D141" s="4" t="s">
-        <v>413</v>
+        <v>407</v>
       </c>
       <c r="E141" t="s">
         <v>15</v>
@@ -7513,13 +7537,13 @@
         <v>347</v>
       </c>
       <c r="G141" s="8" t="s">
+        <v>355</v>
+      </c>
+      <c r="H141" s="11" t="s">
         <v>356</v>
       </c>
-      <c r="H141" s="11" t="s">
-        <v>357</v>
-      </c>
       <c r="I141" s="10" t="s">
-        <v>437</v>
+        <v>433</v>
       </c>
       <c r="J141" s="4" t="s">
         <v>14</v>
@@ -7531,7 +7555,7 @@
         <v>347</v>
       </c>
       <c r="M141" s="8" t="s">
-        <v>440</v>
+        <v>434</v>
       </c>
     </row>
     <row r="142" spans="1:13" ht="75" x14ac:dyDescent="0.25">
@@ -7542,10 +7566,10 @@
         <v>45292</v>
       </c>
       <c r="C142" s="19">
-        <v>45747</v>
+        <v>45858</v>
       </c>
       <c r="D142" s="4" t="s">
-        <v>414</v>
+        <v>408</v>
       </c>
       <c r="E142" t="s">
         <v>15</v>
@@ -7554,13 +7578,13 @@
         <v>347</v>
       </c>
       <c r="G142" s="8" t="s">
+        <v>355</v>
+      </c>
+      <c r="H142" s="11" t="s">
         <v>356</v>
       </c>
-      <c r="H142" s="11" t="s">
-        <v>357</v>
-      </c>
       <c r="I142" s="10" t="s">
-        <v>437</v>
+        <v>433</v>
       </c>
       <c r="J142" s="4" t="s">
         <v>14</v>
@@ -7572,10 +7596,10 @@
         <v>347</v>
       </c>
       <c r="M142" s="8" t="s">
-        <v>441</v>
-      </c>
-    </row>
-    <row r="143" spans="1:13" ht="90" x14ac:dyDescent="0.25">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="143" spans="1:13" ht="75" x14ac:dyDescent="0.25">
       <c r="A143" s="23" t="s">
         <v>349</v>
       </c>
@@ -7586,7 +7610,7 @@
         <v>45291</v>
       </c>
       <c r="D143" s="4" t="s">
-        <v>425</v>
+        <v>409</v>
       </c>
       <c r="E143" t="s">
         <v>15</v>
@@ -7595,13 +7619,13 @@
         <v>347</v>
       </c>
       <c r="G143" s="8" t="s">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c r="H143" s="11" t="s">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="I143" s="10" t="s">
-        <v>442</v>
+        <v>433</v>
       </c>
       <c r="J143" s="4" t="s">
         <v>14</v>
@@ -7613,10 +7637,10 @@
         <v>347</v>
       </c>
       <c r="M143" s="8" t="s">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="144" spans="1:13" ht="90" x14ac:dyDescent="0.25">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="144" spans="1:13" ht="75" x14ac:dyDescent="0.25">
       <c r="A144" s="23" t="s">
         <v>349</v>
       </c>
@@ -7624,10 +7648,10 @@
         <v>45292</v>
       </c>
       <c r="C144" s="19">
-        <v>45747</v>
+        <v>45858</v>
       </c>
       <c r="D144" s="4" t="s">
-        <v>426</v>
+        <v>410</v>
       </c>
       <c r="E144" t="s">
         <v>15</v>
@@ -7636,13 +7660,13 @@
         <v>347</v>
       </c>
       <c r="G144" s="8" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="H144" s="11" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="I144" s="10" t="s">
-        <v>442</v>
+        <v>433</v>
       </c>
       <c r="J144" s="4" t="s">
         <v>14</v>
@@ -7654,7 +7678,7 @@
         <v>347</v>
       </c>
       <c r="M144" s="8" t="s">
-        <v>355</v>
+        <v>437</v>
       </c>
     </row>
     <row r="145" spans="1:13" ht="90" x14ac:dyDescent="0.25">
@@ -7668,7 +7692,7 @@
         <v>45291</v>
       </c>
       <c r="D145" s="4" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="E145" t="s">
         <v>15</v>
@@ -7677,13 +7701,13 @@
         <v>347</v>
       </c>
       <c r="G145" s="8" t="s">
-        <v>356</v>
+        <v>350</v>
       </c>
       <c r="H145" s="11" t="s">
-        <v>357</v>
+        <v>351</v>
       </c>
       <c r="I145" s="10" t="s">
-        <v>442</v>
+        <v>438</v>
       </c>
       <c r="J145" s="4" t="s">
         <v>14</v>
@@ -7695,7 +7719,7 @@
         <v>347</v>
       </c>
       <c r="M145" s="8" t="s">
-        <v>438</v>
+        <v>354</v>
       </c>
     </row>
     <row r="146" spans="1:13" ht="90" x14ac:dyDescent="0.25">
@@ -7706,10 +7730,10 @@
         <v>45292</v>
       </c>
       <c r="C146" s="19">
-        <v>45747</v>
+        <v>45920</v>
       </c>
       <c r="D146" s="4" t="s">
-        <v>428</v>
+        <v>422</v>
       </c>
       <c r="E146" t="s">
         <v>15</v>
@@ -7718,13 +7742,13 @@
         <v>347</v>
       </c>
       <c r="G146" s="8" t="s">
-        <v>356</v>
+        <v>352</v>
       </c>
       <c r="H146" s="11" t="s">
-        <v>357</v>
+        <v>353</v>
       </c>
       <c r="I146" s="10" t="s">
-        <v>442</v>
+        <v>438</v>
       </c>
       <c r="J146" s="4" t="s">
         <v>14</v>
@@ -7736,7 +7760,7 @@
         <v>347</v>
       </c>
       <c r="M146" s="8" t="s">
-        <v>439</v>
+        <v>447</v>
       </c>
     </row>
     <row r="147" spans="1:13" ht="90" x14ac:dyDescent="0.25">
@@ -7750,7 +7774,7 @@
         <v>45291</v>
       </c>
       <c r="D147" s="4" t="s">
-        <v>429</v>
+        <v>423</v>
       </c>
       <c r="E147" t="s">
         <v>15</v>
@@ -7759,13 +7783,13 @@
         <v>347</v>
       </c>
       <c r="G147" s="8" t="s">
+        <v>355</v>
+      </c>
+      <c r="H147" s="11" t="s">
         <v>356</v>
       </c>
-      <c r="H147" s="11" t="s">
-        <v>357</v>
-      </c>
       <c r="I147" s="10" t="s">
-        <v>442</v>
+        <v>438</v>
       </c>
       <c r="J147" s="4" t="s">
         <v>14</v>
@@ -7777,7 +7801,7 @@
         <v>347</v>
       </c>
       <c r="M147" s="8" t="s">
-        <v>440</v>
+        <v>434</v>
       </c>
     </row>
     <row r="148" spans="1:13" ht="90" x14ac:dyDescent="0.25">
@@ -7788,10 +7812,10 @@
         <v>45292</v>
       </c>
       <c r="C148" s="19">
-        <v>45747</v>
+        <v>45920</v>
       </c>
       <c r="D148" s="4" t="s">
-        <v>430</v>
+        <v>424</v>
       </c>
       <c r="E148" t="s">
         <v>15</v>
@@ -7800,13 +7824,13 @@
         <v>347</v>
       </c>
       <c r="G148" s="8" t="s">
+        <v>355</v>
+      </c>
+      <c r="H148" s="11" t="s">
         <v>356</v>
       </c>
-      <c r="H148" s="11" t="s">
-        <v>357</v>
-      </c>
       <c r="I148" s="10" t="s">
-        <v>442</v>
+        <v>438</v>
       </c>
       <c r="J148" s="4" t="s">
         <v>14</v>
@@ -7818,10 +7842,10 @@
         <v>347</v>
       </c>
       <c r="M148" s="8" t="s">
-        <v>441</v>
-      </c>
-    </row>
-    <row r="149" spans="1:13" ht="105" x14ac:dyDescent="0.25">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="149" spans="1:13" ht="90" x14ac:dyDescent="0.25">
       <c r="A149" s="23" t="s">
         <v>349</v>
       </c>
@@ -7832,7 +7856,7 @@
         <v>45291</v>
       </c>
       <c r="D149" s="4" t="s">
-        <v>436</v>
+        <v>425</v>
       </c>
       <c r="E149" t="s">
         <v>15</v>
@@ -7841,13 +7865,13 @@
         <v>347</v>
       </c>
       <c r="G149" s="8" t="s">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c r="H149" s="11" t="s">
-        <v>351</v>
-      </c>
-      <c r="I149" s="16" t="s">
-        <v>443</v>
+        <v>356</v>
+      </c>
+      <c r="I149" s="10" t="s">
+        <v>438</v>
       </c>
       <c r="J149" s="4" t="s">
         <v>14</v>
@@ -7859,10 +7883,10 @@
         <v>347</v>
       </c>
       <c r="M149" s="8" t="s">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="150" spans="1:13" ht="105" x14ac:dyDescent="0.25">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="150" spans="1:13" ht="90" x14ac:dyDescent="0.25">
       <c r="A150" s="23" t="s">
         <v>349</v>
       </c>
@@ -7870,10 +7894,10 @@
         <v>45292</v>
       </c>
       <c r="C150" s="19">
-        <v>45747</v>
+        <v>45920</v>
       </c>
       <c r="D150" s="4" t="s">
-        <v>435</v>
+        <v>426</v>
       </c>
       <c r="E150" t="s">
         <v>15</v>
@@ -7882,13 +7906,13 @@
         <v>347</v>
       </c>
       <c r="G150" s="8" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="H150" s="11" t="s">
-        <v>353</v>
-      </c>
-      <c r="I150" s="16" t="s">
-        <v>443</v>
+        <v>356</v>
+      </c>
+      <c r="I150" s="10" t="s">
+        <v>438</v>
       </c>
       <c r="J150" s="4" t="s">
         <v>14</v>
@@ -7900,7 +7924,7 @@
         <v>347</v>
       </c>
       <c r="M150" s="8" t="s">
-        <v>355</v>
+        <v>437</v>
       </c>
     </row>
     <row r="151" spans="1:13" ht="105" x14ac:dyDescent="0.25">
@@ -7914,7 +7938,7 @@
         <v>45291</v>
       </c>
       <c r="D151" s="4" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="E151" t="s">
         <v>15</v>
@@ -7923,13 +7947,13 @@
         <v>347</v>
       </c>
       <c r="G151" s="8" t="s">
-        <v>356</v>
+        <v>350</v>
       </c>
       <c r="H151" s="11" t="s">
-        <v>357</v>
+        <v>351</v>
       </c>
       <c r="I151" s="16" t="s">
-        <v>443</v>
+        <v>439</v>
       </c>
       <c r="J151" s="4" t="s">
         <v>14</v>
@@ -7941,7 +7965,7 @@
         <v>347</v>
       </c>
       <c r="M151" s="8" t="s">
-        <v>438</v>
+        <v>354</v>
       </c>
     </row>
     <row r="152" spans="1:13" ht="105" x14ac:dyDescent="0.25">
@@ -7952,10 +7976,10 @@
         <v>45292</v>
       </c>
       <c r="C152" s="19">
-        <v>45747</v>
+        <v>45858</v>
       </c>
       <c r="D152" s="4" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="E152" t="s">
         <v>15</v>
@@ -7964,13 +7988,13 @@
         <v>347</v>
       </c>
       <c r="G152" s="8" t="s">
-        <v>356</v>
+        <v>352</v>
       </c>
       <c r="H152" s="11" t="s">
-        <v>357</v>
+        <v>353</v>
       </c>
       <c r="I152" s="16" t="s">
-        <v>443</v>
+        <v>439</v>
       </c>
       <c r="J152" s="4" t="s">
         <v>14</v>
@@ -7982,7 +8006,7 @@
         <v>347</v>
       </c>
       <c r="M152" s="8" t="s">
-        <v>439</v>
+        <v>447</v>
       </c>
     </row>
     <row r="153" spans="1:13" ht="105" x14ac:dyDescent="0.25">
@@ -7996,7 +8020,7 @@
         <v>45291</v>
       </c>
       <c r="D153" s="4" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="E153" t="s">
         <v>15</v>
@@ -8005,13 +8029,13 @@
         <v>347</v>
       </c>
       <c r="G153" s="8" t="s">
+        <v>355</v>
+      </c>
+      <c r="H153" s="11" t="s">
         <v>356</v>
       </c>
-      <c r="H153" s="11" t="s">
-        <v>357</v>
-      </c>
       <c r="I153" s="16" t="s">
-        <v>443</v>
+        <v>439</v>
       </c>
       <c r="J153" s="4" t="s">
         <v>14</v>
@@ -8023,7 +8047,7 @@
         <v>347</v>
       </c>
       <c r="M153" s="8" t="s">
-        <v>440</v>
+        <v>434</v>
       </c>
     </row>
     <row r="154" spans="1:13" ht="105" x14ac:dyDescent="0.25">
@@ -8034,10 +8058,10 @@
         <v>45292</v>
       </c>
       <c r="C154" s="19">
-        <v>45747</v>
+        <v>45858</v>
       </c>
       <c r="D154" s="4" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="E154" t="s">
         <v>15</v>
@@ -8046,13 +8070,13 @@
         <v>347</v>
       </c>
       <c r="G154" s="8" t="s">
+        <v>355</v>
+      </c>
+      <c r="H154" s="11" t="s">
         <v>356</v>
       </c>
-      <c r="H154" s="11" t="s">
-        <v>357</v>
-      </c>
       <c r="I154" s="16" t="s">
-        <v>443</v>
+        <v>439</v>
       </c>
       <c r="J154" s="4" t="s">
         <v>14</v>
@@ -8064,114 +8088,114 @@
         <v>347</v>
       </c>
       <c r="M154" s="8" t="s">
-        <v>441</v>
-      </c>
-    </row>
-    <row r="155" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A155" s="23"/>
-      <c r="B155" s="19"/>
-      <c r="C155" s="19"/>
-    </row>
-    <row r="156" spans="1:13" ht="90" x14ac:dyDescent="0.25">
-      <c r="A156" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="155" spans="1:13" ht="105" x14ac:dyDescent="0.25">
+      <c r="A155" s="23" t="s">
+        <v>349</v>
+      </c>
+      <c r="B155" s="19">
+        <v>33455</v>
+      </c>
+      <c r="C155" s="19">
+        <v>45291</v>
+      </c>
+      <c r="D155" s="4" t="s">
+        <v>428</v>
+      </c>
+      <c r="E155" t="s">
+        <v>15</v>
+      </c>
+      <c r="F155" s="6" t="s">
+        <v>347</v>
+      </c>
+      <c r="G155" s="8" t="s">
+        <v>355</v>
+      </c>
+      <c r="H155" s="11" t="s">
+        <v>356</v>
+      </c>
+      <c r="I155" s="16" t="s">
+        <v>439</v>
+      </c>
+      <c r="J155" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="K155" t="s">
+        <v>19</v>
+      </c>
+      <c r="L155" s="6" t="s">
+        <v>347</v>
+      </c>
+      <c r="M155" s="8" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="156" spans="1:13" ht="105" x14ac:dyDescent="0.25">
+      <c r="A156" s="23" t="s">
+        <v>349</v>
+      </c>
+      <c r="B156" s="19">
+        <v>45292</v>
+      </c>
+      <c r="C156" s="19">
+        <v>45858</v>
+      </c>
+      <c r="D156" s="4" t="s">
+        <v>427</v>
+      </c>
+      <c r="E156" t="s">
+        <v>15</v>
+      </c>
+      <c r="F156" s="6" t="s">
+        <v>347</v>
+      </c>
+      <c r="G156" s="8" t="s">
+        <v>355</v>
+      </c>
+      <c r="H156" s="11" t="s">
+        <v>356</v>
+      </c>
+      <c r="I156" s="16" t="s">
+        <v>439</v>
+      </c>
+      <c r="J156" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="K156" t="s">
+        <v>19</v>
+      </c>
+      <c r="L156" s="6" t="s">
+        <v>347</v>
+      </c>
+      <c r="M156" s="8" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="157" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A157" s="23"/>
+      <c r="B157" s="19"/>
+      <c r="C157" s="19"/>
+    </row>
+    <row r="158" spans="1:13" ht="90" x14ac:dyDescent="0.25">
+      <c r="A158" t="s">
+        <v>357</v>
+      </c>
+      <c r="B158" s="19">
+        <v>34881</v>
+      </c>
+      <c r="C158" s="19">
+        <v>45230</v>
+      </c>
+      <c r="D158" s="4" t="s">
+        <v>455</v>
+      </c>
+      <c r="E158" t="s">
+        <v>15</v>
+      </c>
+      <c r="F158" s="6" t="s">
         <v>358</v>
-      </c>
-      <c r="B156" s="19">
-        <v>34881</v>
-      </c>
-      <c r="C156" s="19">
-        <v>45046</v>
-      </c>
-      <c r="D156" s="4" t="s">
-        <v>359</v>
-      </c>
-      <c r="E156" t="s">
-        <v>15</v>
-      </c>
-      <c r="F156" s="6" t="s">
-        <v>360</v>
-      </c>
-      <c r="G156" s="8" t="s">
-        <v>351</v>
-      </c>
-      <c r="H156" s="11" t="s">
-        <v>350</v>
-      </c>
-      <c r="I156" s="16" t="s">
-        <v>361</v>
-      </c>
-      <c r="J156" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="K156" t="s">
-        <v>19</v>
-      </c>
-      <c r="L156" s="6" t="s">
-        <v>360</v>
-      </c>
-      <c r="M156" s="8" t="s">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="157" spans="1:13" ht="105" x14ac:dyDescent="0.25">
-      <c r="A157" t="s">
-        <v>358</v>
-      </c>
-      <c r="B157" s="19">
-        <v>38018</v>
-      </c>
-      <c r="C157" s="19">
-        <v>44926</v>
-      </c>
-      <c r="D157" s="4" t="s">
-        <v>363</v>
-      </c>
-      <c r="E157" t="s">
-        <v>15</v>
-      </c>
-      <c r="F157" s="6" t="s">
-        <v>360</v>
-      </c>
-      <c r="G157" s="8" t="s">
-        <v>351</v>
-      </c>
-      <c r="H157" s="11" t="s">
-        <v>350</v>
-      </c>
-      <c r="I157" s="4" t="s">
-        <v>371</v>
-      </c>
-      <c r="J157" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="K157" t="s">
-        <v>19</v>
-      </c>
-      <c r="L157" s="6" t="s">
-        <v>360</v>
-      </c>
-      <c r="M157" s="8" t="s">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="158" spans="1:13" ht="105" x14ac:dyDescent="0.25">
-      <c r="A158" t="s">
-        <v>358</v>
-      </c>
-      <c r="B158" s="19">
-        <v>37469</v>
-      </c>
-      <c r="C158" s="19">
-        <v>40908</v>
-      </c>
-      <c r="D158" s="4" t="s">
-        <v>364</v>
-      </c>
-      <c r="E158" t="s">
-        <v>15</v>
-      </c>
-      <c r="F158" s="6" t="s">
-        <v>360</v>
       </c>
       <c r="G158" s="8" t="s">
         <v>351</v>
@@ -8180,7 +8204,7 @@
         <v>350</v>
       </c>
       <c r="I158" s="16" t="s">
-        <v>372</v>
+        <v>359</v>
       </c>
       <c r="J158" s="4" t="s">
         <v>14</v>
@@ -8189,30 +8213,30 @@
         <v>19</v>
       </c>
       <c r="L158" s="6" t="s">
+        <v>358</v>
+      </c>
+      <c r="M158" s="8" t="s">
         <v>360</v>
-      </c>
-      <c r="M158" s="8" t="s">
-        <v>362</v>
       </c>
     </row>
     <row r="159" spans="1:13" ht="105" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
+        <v>357</v>
+      </c>
+      <c r="B159" s="19">
+        <v>38018</v>
+      </c>
+      <c r="C159" s="19">
+        <v>45626</v>
+      </c>
+      <c r="D159" s="4" t="s">
+        <v>456</v>
+      </c>
+      <c r="E159" t="s">
+        <v>15</v>
+      </c>
+      <c r="F159" s="6" t="s">
         <v>358</v>
-      </c>
-      <c r="B159" s="19">
-        <v>37438</v>
-      </c>
-      <c r="C159" s="19">
-        <v>40908</v>
-      </c>
-      <c r="D159" s="4" t="s">
-        <v>365</v>
-      </c>
-      <c r="E159" t="s">
-        <v>15</v>
-      </c>
-      <c r="F159" s="6" t="s">
-        <v>360</v>
       </c>
       <c r="G159" s="8" t="s">
         <v>351</v>
@@ -8220,8 +8244,8 @@
       <c r="H159" s="11" t="s">
         <v>350</v>
       </c>
-      <c r="I159" s="16" t="s">
-        <v>377</v>
+      <c r="I159" s="4" t="s">
+        <v>367</v>
       </c>
       <c r="J159" s="4" t="s">
         <v>14</v>
@@ -8230,30 +8254,30 @@
         <v>19</v>
       </c>
       <c r="L159" s="6" t="s">
+        <v>358</v>
+      </c>
+      <c r="M159" s="8" t="s">
         <v>360</v>
-      </c>
-      <c r="M159" s="8" t="s">
-        <v>362</v>
       </c>
     </row>
     <row r="160" spans="1:13" ht="105" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
+        <v>357</v>
+      </c>
+      <c r="B160" s="19">
+        <v>37469</v>
+      </c>
+      <c r="C160" s="19">
+        <v>40908</v>
+      </c>
+      <c r="D160" s="4" t="s">
+        <v>361</v>
+      </c>
+      <c r="E160" t="s">
+        <v>15</v>
+      </c>
+      <c r="F160" s="6" t="s">
         <v>358</v>
-      </c>
-      <c r="B160" s="19">
-        <v>37196</v>
-      </c>
-      <c r="C160" s="19">
-        <v>44926</v>
-      </c>
-      <c r="D160" s="4" t="s">
-        <v>366</v>
-      </c>
-      <c r="E160" t="s">
-        <v>15</v>
-      </c>
-      <c r="F160" s="6" t="s">
-        <v>360</v>
       </c>
       <c r="G160" s="8" t="s">
         <v>351</v>
@@ -8262,7 +8286,7 @@
         <v>350</v>
       </c>
       <c r="I160" s="16" t="s">
-        <v>376</v>
+        <v>368</v>
       </c>
       <c r="J160" s="4" t="s">
         <v>14</v>
@@ -8271,30 +8295,30 @@
         <v>19</v>
       </c>
       <c r="L160" s="6" t="s">
+        <v>358</v>
+      </c>
+      <c r="M160" s="8" t="s">
         <v>360</v>
-      </c>
-      <c r="M160" s="8" t="s">
-        <v>362</v>
       </c>
     </row>
     <row r="161" spans="1:13" ht="105" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="B161" s="19">
-        <v>37469</v>
+        <v>37438</v>
       </c>
       <c r="C161" s="19">
         <v>40908</v>
       </c>
       <c r="D161" s="4" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="E161" t="s">
         <v>15</v>
       </c>
       <c r="F161" s="6" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="G161" s="8" t="s">
         <v>351</v>
@@ -8302,8 +8326,8 @@
       <c r="H161" s="11" t="s">
         <v>350</v>
       </c>
-      <c r="I161" s="4" t="s">
-        <v>370</v>
+      <c r="I161" s="16" t="s">
+        <v>373</v>
       </c>
       <c r="J161" s="4" t="s">
         <v>14</v>
@@ -8312,30 +8336,30 @@
         <v>19</v>
       </c>
       <c r="L161" s="6" t="s">
+        <v>358</v>
+      </c>
+      <c r="M161" s="8" t="s">
         <v>360</v>
-      </c>
-      <c r="M161" s="8" t="s">
-        <v>362</v>
       </c>
     </row>
     <row r="162" spans="1:13" ht="105" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
+        <v>357</v>
+      </c>
+      <c r="B162" s="19">
+        <v>37196</v>
+      </c>
+      <c r="C162" s="19">
+        <v>45657</v>
+      </c>
+      <c r="D162" s="4" t="s">
+        <v>457</v>
+      </c>
+      <c r="E162" t="s">
+        <v>15</v>
+      </c>
+      <c r="F162" s="6" t="s">
         <v>358</v>
-      </c>
-      <c r="B162" s="19">
-        <v>37073</v>
-      </c>
-      <c r="C162" s="19">
-        <v>41882</v>
-      </c>
-      <c r="D162" s="4" t="s">
-        <v>368</v>
-      </c>
-      <c r="E162" t="s">
-        <v>15</v>
-      </c>
-      <c r="F162" s="6" t="s">
-        <v>360</v>
       </c>
       <c r="G162" s="8" t="s">
         <v>351</v>
@@ -8344,7 +8368,7 @@
         <v>350</v>
       </c>
       <c r="I162" s="16" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="J162" s="4" t="s">
         <v>14</v>
@@ -8353,30 +8377,30 @@
         <v>19</v>
       </c>
       <c r="L162" s="6" t="s">
+        <v>358</v>
+      </c>
+      <c r="M162" s="8" t="s">
         <v>360</v>
-      </c>
-      <c r="M162" s="8" t="s">
-        <v>362</v>
       </c>
     </row>
     <row r="163" spans="1:13" ht="105" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
+        <v>357</v>
+      </c>
+      <c r="B163" s="19">
+        <v>37469</v>
+      </c>
+      <c r="C163" s="19">
+        <v>40908</v>
+      </c>
+      <c r="D163" s="4" t="s">
+        <v>363</v>
+      </c>
+      <c r="E163" t="s">
+        <v>15</v>
+      </c>
+      <c r="F163" s="6" t="s">
         <v>358</v>
-      </c>
-      <c r="B163" s="19">
-        <v>37074</v>
-      </c>
-      <c r="C163" s="19">
-        <v>41882</v>
-      </c>
-      <c r="D163" s="4" t="s">
-        <v>368</v>
-      </c>
-      <c r="E163" t="s">
-        <v>15</v>
-      </c>
-      <c r="F163" s="6" t="s">
-        <v>360</v>
       </c>
       <c r="G163" s="8" t="s">
         <v>351</v>
@@ -8385,7 +8409,7 @@
         <v>350</v>
       </c>
       <c r="I163" s="4" t="s">
-        <v>375</v>
+        <v>366</v>
       </c>
       <c r="J163" s="4" t="s">
         <v>14</v>
@@ -8394,30 +8418,30 @@
         <v>19</v>
       </c>
       <c r="L163" s="6" t="s">
+        <v>358</v>
+      </c>
+      <c r="M163" s="8" t="s">
         <v>360</v>
-      </c>
-      <c r="M163" s="8" t="s">
-        <v>362</v>
       </c>
     </row>
     <row r="164" spans="1:13" ht="105" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
+        <v>357</v>
+      </c>
+      <c r="B164" s="19">
+        <v>37073</v>
+      </c>
+      <c r="C164" s="19">
+        <v>41882</v>
+      </c>
+      <c r="D164" s="4" t="s">
+        <v>364</v>
+      </c>
+      <c r="E164" t="s">
+        <v>15</v>
+      </c>
+      <c r="F164" s="6" t="s">
         <v>358</v>
-      </c>
-      <c r="B164" s="19">
-        <v>34881</v>
-      </c>
-      <c r="C164" s="19">
-        <v>44500</v>
-      </c>
-      <c r="D164" s="4" t="s">
-        <v>369</v>
-      </c>
-      <c r="E164" t="s">
-        <v>15</v>
-      </c>
-      <c r="F164" s="6" t="s">
-        <v>360</v>
       </c>
       <c r="G164" s="8" t="s">
         <v>351</v>
@@ -8426,7 +8450,7 @@
         <v>350</v>
       </c>
       <c r="I164" s="16" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="J164" s="4" t="s">
         <v>14</v>
@@ -8435,69 +8459,151 @@
         <v>19</v>
       </c>
       <c r="L164" s="6" t="s">
+        <v>358</v>
+      </c>
+      <c r="M164" s="8" t="s">
         <v>360</v>
       </c>
-      <c r="M164" s="8" t="s">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="165" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="B165" s="19"/>
-      <c r="C165" s="19"/>
-      <c r="D165" s="4"/>
-    </row>
-    <row r="166" spans="1:13" ht="90" x14ac:dyDescent="0.25">
+    </row>
+    <row r="165" spans="1:13" ht="105" x14ac:dyDescent="0.25">
+      <c r="A165" t="s">
+        <v>357</v>
+      </c>
+      <c r="B165" s="19">
+        <v>37074</v>
+      </c>
+      <c r="C165" s="19">
+        <v>41882</v>
+      </c>
+      <c r="D165" s="4" t="s">
+        <v>364</v>
+      </c>
+      <c r="E165" t="s">
+        <v>15</v>
+      </c>
+      <c r="F165" s="6" t="s">
+        <v>358</v>
+      </c>
+      <c r="G165" s="8" t="s">
+        <v>351</v>
+      </c>
+      <c r="H165" s="11" t="s">
+        <v>350</v>
+      </c>
+      <c r="I165" s="4" t="s">
+        <v>371</v>
+      </c>
+      <c r="J165" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="K165" t="s">
+        <v>19</v>
+      </c>
+      <c r="L165" s="6" t="s">
+        <v>358</v>
+      </c>
+      <c r="M165" s="8" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="166" spans="1:13" ht="105" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
-        <v>379</v>
+        <v>357</v>
       </c>
       <c r="B166" s="19">
+        <v>34881</v>
+      </c>
+      <c r="C166" s="19">
+        <v>44500</v>
+      </c>
+      <c r="D166" s="4" t="s">
+        <v>365</v>
+      </c>
+      <c r="E166" t="s">
+        <v>15</v>
+      </c>
+      <c r="F166" s="6" t="s">
+        <v>358</v>
+      </c>
+      <c r="G166" s="8" t="s">
+        <v>351</v>
+      </c>
+      <c r="H166" s="11" t="s">
+        <v>350</v>
+      </c>
+      <c r="I166" s="16" t="s">
+        <v>369</v>
+      </c>
+      <c r="J166" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="K166" t="s">
+        <v>19</v>
+      </c>
+      <c r="L166" s="6" t="s">
+        <v>358</v>
+      </c>
+      <c r="M166" s="8" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="167" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="B167" s="19"/>
+      <c r="C167" s="19"/>
+      <c r="D167" s="4"/>
+    </row>
+    <row r="168" spans="1:13" ht="90" x14ac:dyDescent="0.25">
+      <c r="A168" t="s">
+        <v>375</v>
+      </c>
+      <c r="B168" s="19">
         <v>29830</v>
       </c>
-      <c r="C166" s="22">
+      <c r="C168" s="22">
         <v>44012</v>
       </c>
-      <c r="D166" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="E166" t="s">
-        <v>15</v>
-      </c>
-      <c r="F166" s="6" t="s">
-        <v>378</v>
-      </c>
-      <c r="G166" s="9" t="s">
+      <c r="D168" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="E168" t="s">
+        <v>15</v>
+      </c>
+      <c r="F168" s="6" t="s">
+        <v>374</v>
+      </c>
+      <c r="G168" s="9" t="s">
         <v>157</v>
       </c>
-      <c r="H166" s="12" t="s">
+      <c r="H168" s="12" t="s">
         <v>155</v>
       </c>
-      <c r="I166" s="16" t="s">
-        <v>380</v>
-      </c>
-      <c r="J166" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="K166" t="s">
-        <v>19</v>
-      </c>
-      <c r="L166" s="6" t="s">
-        <v>378</v>
-      </c>
-      <c r="M166" s="8" t="s">
-        <v>381</v>
-      </c>
-    </row>
-    <row r="167" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="D167" s="4"/>
-    </row>
-    <row r="168" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="D168" s="4"/>
+      <c r="I168" s="16" t="s">
+        <v>376</v>
+      </c>
+      <c r="J168" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="K168" t="s">
+        <v>19</v>
+      </c>
+      <c r="L168" s="6" t="s">
+        <v>374</v>
+      </c>
+      <c r="M168" s="8" t="s">
+        <v>377</v>
+      </c>
     </row>
     <row r="169" spans="1:13" x14ac:dyDescent="0.25">
       <c r="D169" s="4"/>
     </row>
+    <row r="170" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="D170" s="4"/>
+    </row>
+    <row r="171" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="D171" s="4"/>
+    </row>
   </sheetData>
-  <autoFilter ref="L1:L94" xr:uid="{9CC0B67C-1229-4907-A814-DF79422D0B81}"/>
+  <autoFilter ref="L1:L95" xr:uid="{9CC0B67C-1229-4907-A814-DF79422D0B81}"/>
   <mergeCells count="3">
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="G1:G2"/>
@@ -8512,36 +8618,36 @@
     <hyperlink ref="I10" r:id="rId5" xr:uid="{DA9BF44F-39FB-4735-B0FE-FA425B039205}"/>
     <hyperlink ref="I39" r:id="rId6" display="http://catalogue.ceda.ac.uk/uuid/9255faeb392f41debf5402caa40dada8" xr:uid="{33D8A6EC-1721-4D70-A807-90A9DC0F92B0}"/>
     <hyperlink ref="I40" r:id="rId7" display="http://catalogue.ceda.ac.uk/uuid/e61704b00267405082fbd41bb710dd74" xr:uid="{06FBE9A3-0C52-45E7-A072-ADF695817CB1}"/>
-    <hyperlink ref="I104" r:id="rId8" xr:uid="{FEB01A84-4724-4528-BBE6-6A672EF16375}"/>
-    <hyperlink ref="I156" r:id="rId9" xr:uid="{BDDFA5AF-1977-44C5-BCB0-91FD1402009E}"/>
-    <hyperlink ref="I158" r:id="rId10" xr:uid="{BDEDEFCF-A555-472E-9706-1AE567A01700}"/>
-    <hyperlink ref="I164" r:id="rId11" xr:uid="{22A88BF9-38BF-4AD8-B7DD-41EB2ECEB1F1}"/>
-    <hyperlink ref="I162" r:id="rId12" xr:uid="{93ED3F05-B542-43CF-B31F-B333FB17814F}"/>
-    <hyperlink ref="I160" r:id="rId13" xr:uid="{13FC54EB-DE3C-4179-AFA4-C1747B414A0A}"/>
-    <hyperlink ref="I159" r:id="rId14" xr:uid="{87679DBA-7FAA-4B74-AAD7-6E4D869079F3}"/>
-    <hyperlink ref="I166" r:id="rId15" xr:uid="{45452A3D-3C2A-44E8-9ECB-DDB7F746AC92}"/>
-    <hyperlink ref="I108" r:id="rId16" xr:uid="{EB97B892-ADBD-4516-822D-2741BC3C4B08}"/>
-    <hyperlink ref="I101" r:id="rId17" xr:uid="{67EAA5AF-E374-4405-89CE-CA263B98F643}"/>
+    <hyperlink ref="I105" r:id="rId8" xr:uid="{FEB01A84-4724-4528-BBE6-6A672EF16375}"/>
+    <hyperlink ref="I158" r:id="rId9" xr:uid="{BDDFA5AF-1977-44C5-BCB0-91FD1402009E}"/>
+    <hyperlink ref="I160" r:id="rId10" xr:uid="{BDEDEFCF-A555-472E-9706-1AE567A01700}"/>
+    <hyperlink ref="I166" r:id="rId11" xr:uid="{22A88BF9-38BF-4AD8-B7DD-41EB2ECEB1F1}"/>
+    <hyperlink ref="I164" r:id="rId12" xr:uid="{93ED3F05-B542-43CF-B31F-B333FB17814F}"/>
+    <hyperlink ref="I162" r:id="rId13" xr:uid="{13FC54EB-DE3C-4179-AFA4-C1747B414A0A}"/>
+    <hyperlink ref="I161" r:id="rId14" xr:uid="{87679DBA-7FAA-4B74-AAD7-6E4D869079F3}"/>
+    <hyperlink ref="I168" r:id="rId15" xr:uid="{45452A3D-3C2A-44E8-9ECB-DDB7F746AC92}"/>
+    <hyperlink ref="I109" r:id="rId16" xr:uid="{EB97B892-ADBD-4516-822D-2741BC3C4B08}"/>
+    <hyperlink ref="I102" r:id="rId17" xr:uid="{67EAA5AF-E374-4405-89CE-CA263B98F643}"/>
     <hyperlink ref="I59" r:id="rId18" xr:uid="{9DFDBD58-BE75-4AF1-8D3C-C7BA3759C551}"/>
     <hyperlink ref="A86" r:id="rId19" xr:uid="{C2FD5162-7D27-4880-8670-E9B5AA79E896}"/>
-    <hyperlink ref="I102" r:id="rId20" xr:uid="{D9EAFBBC-30CE-4CBB-9B61-E5312B5D7978}"/>
+    <hyperlink ref="I103" r:id="rId20" xr:uid="{D9EAFBBC-30CE-4CBB-9B61-E5312B5D7978}"/>
     <hyperlink ref="A75" r:id="rId21" xr:uid="{56C42FE2-0E52-42F1-9F72-91EABDAA0B79}"/>
-    <hyperlink ref="I89" r:id="rId22" xr:uid="{C17C51D4-2DB4-4C84-B398-A222BE15A2D2}"/>
-    <hyperlink ref="I90" r:id="rId23" xr:uid="{49853039-DD43-458C-9646-E83CDA5009B3}"/>
-    <hyperlink ref="I92" r:id="rId24" xr:uid="{A461AB9D-DCE9-47B7-AFDF-072C882E560B}"/>
-    <hyperlink ref="A137" r:id="rId25" xr:uid="{764A734A-9BBE-4D9D-9E4F-3CBDC6EC4B43}"/>
-    <hyperlink ref="I120" r:id="rId26" xr:uid="{79F79372-DA60-45C9-8476-0E6623AE0228}"/>
-    <hyperlink ref="I121" r:id="rId27" xr:uid="{A1AC6C46-7083-4197-B7C9-720740137FA4}"/>
-    <hyperlink ref="I122" r:id="rId28" xr:uid="{301ACED6-77BF-4670-BCBF-39C2246D20E4}"/>
-    <hyperlink ref="I123" r:id="rId29" xr:uid="{6BF57B1F-EEF6-4AB6-8570-D906D8A223CC}"/>
-    <hyperlink ref="I124" r:id="rId30" xr:uid="{44AB65B1-2B6D-49C5-A05F-005957AC1F38}"/>
-    <hyperlink ref="A119" r:id="rId31" xr:uid="{1FC09F18-7F33-469D-95F0-F7DABFC86A96}"/>
-    <hyperlink ref="I137" r:id="rId32" xr:uid="{5095AF32-192A-4076-A8AF-CE1D247DB6A5}"/>
-    <hyperlink ref="I138:I142" r:id="rId33" display="https://catalogue.ceda.ac.uk/uuid/5b1caf9095d7412282f5ba6b558034e3" xr:uid="{B35FBFC2-0376-40A1-B664-07999671DEF8}"/>
-    <hyperlink ref="I143" r:id="rId34" xr:uid="{A7C80B86-4D84-411E-BD1F-E13CB8BFECC9}"/>
-    <hyperlink ref="I144:I148" r:id="rId35" display="https://catalogue.ceda.ac.uk/uuid/ca55ac11fc814b0d95e68a34a10539c1/" xr:uid="{DE9C7552-3EA5-4AE9-AD19-F83AEA58D256}"/>
-    <hyperlink ref="I149" r:id="rId36" xr:uid="{7BFF8381-27B0-403D-8E67-52613688F84C}"/>
-    <hyperlink ref="I150:I154" r:id="rId37" display="https://catalogue.ceda.ac.uk/uuid/0e346e1e1e164ac99c60098848537a29/" xr:uid="{5FF851C7-5210-4528-B845-74A68B103347}"/>
+    <hyperlink ref="I90" r:id="rId22" xr:uid="{C17C51D4-2DB4-4C84-B398-A222BE15A2D2}"/>
+    <hyperlink ref="I91" r:id="rId23" xr:uid="{49853039-DD43-458C-9646-E83CDA5009B3}"/>
+    <hyperlink ref="I93" r:id="rId24" xr:uid="{A461AB9D-DCE9-47B7-AFDF-072C882E560B}"/>
+    <hyperlink ref="A139" r:id="rId25" xr:uid="{764A734A-9BBE-4D9D-9E4F-3CBDC6EC4B43}"/>
+    <hyperlink ref="I122" r:id="rId26" xr:uid="{79F79372-DA60-45C9-8476-0E6623AE0228}"/>
+    <hyperlink ref="I123" r:id="rId27" xr:uid="{A1AC6C46-7083-4197-B7C9-720740137FA4}"/>
+    <hyperlink ref="I124" r:id="rId28" xr:uid="{301ACED6-77BF-4670-BCBF-39C2246D20E4}"/>
+    <hyperlink ref="I125" r:id="rId29" xr:uid="{6BF57B1F-EEF6-4AB6-8570-D906D8A223CC}"/>
+    <hyperlink ref="I126" r:id="rId30" xr:uid="{44AB65B1-2B6D-49C5-A05F-005957AC1F38}"/>
+    <hyperlink ref="A121" r:id="rId31" xr:uid="{1FC09F18-7F33-469D-95F0-F7DABFC86A96}"/>
+    <hyperlink ref="I139" r:id="rId32" xr:uid="{5095AF32-192A-4076-A8AF-CE1D247DB6A5}"/>
+    <hyperlink ref="I140:I144" r:id="rId33" display="https://catalogue.ceda.ac.uk/uuid/5b1caf9095d7412282f5ba6b558034e3" xr:uid="{B35FBFC2-0376-40A1-B664-07999671DEF8}"/>
+    <hyperlink ref="I145" r:id="rId34" xr:uid="{A7C80B86-4D84-411E-BD1F-E13CB8BFECC9}"/>
+    <hyperlink ref="I146:I150" r:id="rId35" display="https://catalogue.ceda.ac.uk/uuid/ca55ac11fc814b0d95e68a34a10539c1/" xr:uid="{DE9C7552-3EA5-4AE9-AD19-F83AEA58D256}"/>
+    <hyperlink ref="I151" r:id="rId36" xr:uid="{7BFF8381-27B0-403D-8E67-52613688F84C}"/>
+    <hyperlink ref="I152:I156" r:id="rId37" display="https://catalogue.ceda.ac.uk/uuid/0e346e1e1e164ac99c60098848537a29/" xr:uid="{5FF851C7-5210-4528-B845-74A68B103347}"/>
     <hyperlink ref="I55" r:id="rId38" xr:uid="{F3A4F5EB-1458-422C-B686-7B85B60E1E35}"/>
     <hyperlink ref="I52" r:id="rId39" xr:uid="{D7526FD0-12AA-46DB-9924-01FF520728CA}"/>
     <hyperlink ref="I53" r:id="rId40" xr:uid="{AA56F239-B336-441F-A02B-2D4AD30560E0}"/>
@@ -8549,9 +8655,12 @@
     <hyperlink ref="I50" r:id="rId42" xr:uid="{3A575A66-D033-48DC-ACC1-168DCA595CA5}"/>
     <hyperlink ref="I51" r:id="rId43" xr:uid="{BBD156C6-CFBB-4FC6-8700-511F389C8B83}"/>
     <hyperlink ref="I49" r:id="rId44" xr:uid="{68A955C5-13B0-4EBF-ADD6-2A9995A030AA}"/>
+    <hyperlink ref="I114" r:id="rId45" xr:uid="{C40CE111-C25B-476A-8D6E-375085EFB8CB}"/>
+    <hyperlink ref="I115" r:id="rId46" xr:uid="{872FF38D-1259-4EDA-8BB1-45E37D744D78}"/>
+    <hyperlink ref="A51" r:id="rId47" xr:uid="{BBE9C4C4-879F-48B4-A6AB-61F81B88DECF}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId45"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId48"/>
 </worksheet>
 </file>
 
@@ -8720,6 +8829,17 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="80b53ead-ac38-442a-b597-5a0e2e0802cd">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="5ec1cc48-4270-4222-9ed5-54ce9e59d47b" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010050398B8EA2737947995C227484EA02C8" ma:contentTypeVersion="17" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="bc9a2575e6c24a964f45b6e1606b04fd">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="80b53ead-ac38-442a-b597-5a0e2e0802cd" xmlns:ns3="5ec1cc48-4270-4222-9ed5-54ce9e59d47b" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="662112485a0135ca1785eae0908ad389" ns2:_="" ns3:_="">
     <xsd:import namespace="80b53ead-ac38-442a-b597-5a0e2e0802cd"/>
@@ -8956,17 +9076,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="80b53ead-ac38-442a-b597-5a0e2e0802cd">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="5ec1cc48-4270-4222-9ed5-54ce9e59d47b" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -8977,6 +9086,17 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{66AF2240-620B-4312-9739-CAF731E4A98F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="80b53ead-ac38-442a-b597-5a0e2e0802cd"/>
+    <ds:schemaRef ds:uri="5ec1cc48-4270-4222-9ed5-54ce9e59d47b"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{72DD370E-74FD-4D33-B5A7-49A7FE6518F7}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -8995,17 +9115,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{66AF2240-620B-4312-9739-CAF731E4A98F}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="80b53ead-ac38-442a-b597-5a0e2e0802cd"/>
-    <ds:schemaRef ds:uri="5ec1cc48-4270-4222-9ed5-54ce9e59d47b"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3B1B5D08-A2EB-4F47-BA81-DA28AA2A09F4}">
   <ds:schemaRefs>

--- a/EEE2000-metadata_mapping.xlsx
+++ b/EEE2000-metadata_mapping.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10921"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://stfc365-my.sharepoint.com/personal/alison_waterfall_stfc_ac_uk/Documents/Documents/GitHub/cci_data_bridge_inputs/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/daniel.westwood/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="88" documentId="13_ncr:1_{594DCA07-06B5-4D5C-ABFA-EF38438BEDEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A3641DD4-BC02-4A09-9CC2-CFA66B2655FE}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{490DC5BD-4D72-6741-AD08-CF08C3F8DF75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{B9DA58AC-C110-4CBA-A19B-6F37B44EEA38}"/>
+    <workbookView xWindow="-20" yWindow="760" windowWidth="30240" windowHeight="17100" xr2:uid="{B9DA58AC-C110-4CBA-A19B-6F37B44EEA38}"/>
   </bookViews>
   <sheets>
     <sheet name="Mapping" sheetId="2" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1703" uniqueCount="458">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1702" uniqueCount="457">
   <si>
     <t>Dataset 1</t>
   </si>
@@ -1718,9 +1718,6 @@
   </si>
   <si>
     <t>domain=greenland_ice_sheet</t>
-  </si>
-  <si>
-    <t>31/09/2022</t>
   </si>
   <si>
     <t>https://doi.org/10.24381/cds.0b96b839</t>
@@ -2307,24 +2304,24 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9CC0B67C-1229-4907-A814-DF79422D0B81}">
   <dimension ref="A1:M171"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="36.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19.42578125" customWidth="1"/>
-    <col min="3" max="3" width="30.140625" customWidth="1"/>
-    <col min="4" max="4" width="38.5703125" customWidth="1"/>
-    <col min="5" max="5" width="23.42578125" customWidth="1"/>
-    <col min="6" max="6" width="23.5703125" style="6" customWidth="1"/>
-    <col min="7" max="7" width="30.42578125" style="9" customWidth="1"/>
-    <col min="8" max="8" width="30.42578125" style="12" customWidth="1"/>
-    <col min="9" max="9" width="42.85546875" style="4" customWidth="1"/>
-    <col min="10" max="10" width="19.42578125" style="4" customWidth="1"/>
-    <col min="11" max="11" width="19.42578125" customWidth="1"/>
-    <col min="12" max="12" width="23.42578125" style="6" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="47.140625" style="8" customWidth="1"/>
+    <col min="1" max="1" width="36.83203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.5" customWidth="1"/>
+    <col min="3" max="3" width="30.1640625" customWidth="1"/>
+    <col min="4" max="4" width="38.5" customWidth="1"/>
+    <col min="5" max="5" width="23.5" customWidth="1"/>
+    <col min="6" max="6" width="23.5" style="6" customWidth="1"/>
+    <col min="7" max="7" width="30.5" style="9" customWidth="1"/>
+    <col min="8" max="8" width="30.5" style="12" customWidth="1"/>
+    <col min="9" max="9" width="42.83203125" style="4" customWidth="1"/>
+    <col min="10" max="10" width="19.5" style="4" customWidth="1"/>
+    <col min="11" max="11" width="19.5" customWidth="1"/>
+    <col min="12" max="12" width="23.5" style="6" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="47.1640625" style="8" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" ht="16" x14ac:dyDescent="0.2">
       <c r="A1" s="27" t="s">
         <v>0</v>
       </c>
@@ -2346,7 +2343,7 @@
       <c r="K1" s="3"/>
       <c r="M1" s="17"/>
     </row>
-    <row r="2" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>4</v>
       </c>
@@ -2383,7 +2380,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:13" ht="90" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:13" ht="80" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>13</v>
       </c>
@@ -2424,7 +2421,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="4" spans="1:13" ht="90" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:13" ht="96" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>13</v>
       </c>
@@ -2465,11 +2462,11 @@
         <v>229</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B5" s="19"/>
       <c r="C5" s="19"/>
     </row>
-    <row r="6" spans="1:13" ht="105" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:13" ht="80" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>25</v>
       </c>
@@ -2510,7 +2507,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="7" spans="1:13" ht="90" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:13" ht="80" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>33</v>
       </c>
@@ -2551,7 +2548,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="8" spans="1:13" ht="90" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:13" ht="80" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>35</v>
       </c>
@@ -2592,11 +2589,11 @@
         <v>201</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B9" s="19"/>
       <c r="C9" s="19"/>
     </row>
-    <row r="10" spans="1:13" ht="60" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:13" ht="48" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>38</v>
       </c>
@@ -2637,7 +2634,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="11" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:13" ht="32" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>42</v>
       </c>
@@ -2678,7 +2675,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="12" spans="1:13" ht="120" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:13" ht="96" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>42</v>
       </c>
@@ -2719,7 +2716,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="13" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:13" ht="48" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>42</v>
       </c>
@@ -2760,7 +2757,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="14" spans="1:13" ht="90" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:13" ht="64" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>42</v>
       </c>
@@ -2801,7 +2798,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="15" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:13" ht="48" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>42</v>
       </c>
@@ -2842,7 +2839,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="16" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:13" ht="48" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>42</v>
       </c>
@@ -2883,7 +2880,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="17" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:13" ht="48" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>42</v>
       </c>
@@ -2924,7 +2921,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="18" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:13" ht="48" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>42</v>
       </c>
@@ -2965,7 +2962,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="19" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:13" ht="48" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>42</v>
       </c>
@@ -3006,7 +3003,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="20" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:13" ht="48" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>42</v>
       </c>
@@ -3047,7 +3044,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="21" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:13" ht="48" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>42</v>
       </c>
@@ -3088,7 +3085,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="22" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:13" ht="48" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>42</v>
       </c>
@@ -3129,7 +3126,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="23" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:13" ht="48" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>42</v>
       </c>
@@ -3170,7 +3167,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="24" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:13" ht="48" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>42</v>
       </c>
@@ -3211,7 +3208,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="25" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:13" ht="48" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>42</v>
       </c>
@@ -3252,7 +3249,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="26" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:13" ht="48" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>42</v>
       </c>
@@ -3293,7 +3290,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="27" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:13" ht="48" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>42</v>
       </c>
@@ -3334,7 +3331,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="28" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:13" ht="48" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>42</v>
       </c>
@@ -3375,7 +3372,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="29" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:13" ht="48" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>42</v>
       </c>
@@ -3416,7 +3413,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="30" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:13" ht="48" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>42</v>
       </c>
@@ -3457,7 +3454,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="31" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:13" ht="48" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>42</v>
       </c>
@@ -3498,7 +3495,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="32" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:13" ht="48" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>42</v>
       </c>
@@ -3539,11 +3536,11 @@
         <v>233</v>
       </c>
     </row>
-    <row r="33" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B33" s="19"/>
       <c r="C33" s="19"/>
     </row>
-    <row r="34" spans="1:13" ht="90" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:13" ht="64" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>69</v>
       </c>
@@ -3584,7 +3581,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="35" spans="1:13" ht="90" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:13" ht="64" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>69</v>
       </c>
@@ -3625,11 +3622,11 @@
         <v>220</v>
       </c>
     </row>
-    <row r="36" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B36" s="19"/>
       <c r="C36" s="19"/>
     </row>
-    <row r="37" spans="1:13" ht="75" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:13" ht="80" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>74</v>
       </c>
@@ -3670,7 +3667,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="38" spans="1:13" ht="75" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:13" ht="80" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>74</v>
       </c>
@@ -3711,7 +3708,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="39" spans="1:13" ht="90" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:13" ht="80" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>74</v>
       </c>
@@ -3752,7 +3749,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="40" spans="1:13" ht="90" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:13" ht="80" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>74</v>
       </c>
@@ -3793,7 +3790,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="41" spans="1:13" ht="60" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:13" ht="64" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>74</v>
       </c>
@@ -3834,7 +3831,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="42" spans="1:13" ht="75" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:13" ht="64" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>74</v>
       </c>
@@ -3875,7 +3872,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="43" spans="1:13" ht="75" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:13" ht="80" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>74</v>
       </c>
@@ -3916,7 +3913,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="44" spans="1:13" ht="75" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:13" ht="80" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>85</v>
       </c>
@@ -3957,7 +3954,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="45" spans="1:13" ht="75" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:13" ht="80" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>85</v>
       </c>
@@ -3998,7 +3995,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="46" spans="1:13" ht="90" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:13" ht="80" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
         <v>85</v>
       </c>
@@ -4039,7 +4036,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="47" spans="1:13" ht="90" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:13" ht="80" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
         <v>85</v>
       </c>
@@ -4080,7 +4077,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="48" spans="1:13" ht="90" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:13" ht="80" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
         <v>85</v>
       </c>
@@ -4121,7 +4118,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="49" spans="1:13" ht="90" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:13" ht="80" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
         <v>85</v>
       </c>
@@ -4162,7 +4159,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="50" spans="1:13" ht="75" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:13" ht="80" x14ac:dyDescent="0.2">
       <c r="A50" s="10" t="s">
         <v>85</v>
       </c>
@@ -4203,7 +4200,7 @@
         <v>442</v>
       </c>
     </row>
-    <row r="51" spans="1:13" ht="75" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:13" ht="80" x14ac:dyDescent="0.2">
       <c r="A51" s="10" t="s">
         <v>85</v>
       </c>
@@ -4244,7 +4241,7 @@
         <v>442</v>
       </c>
     </row>
-    <row r="52" spans="1:13" ht="75" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:13" ht="80" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
         <v>85</v>
       </c>
@@ -4285,7 +4282,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="53" spans="1:13" ht="75" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:13" ht="80" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
         <v>85</v>
       </c>
@@ -4326,7 +4323,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="54" spans="1:13" ht="90" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:13" ht="96" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
         <v>85</v>
       </c>
@@ -4367,7 +4364,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="55" spans="1:13" ht="75" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:13" ht="64" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
         <v>85</v>
       </c>
@@ -4408,12 +4405,12 @@
         <v>236</v>
       </c>
     </row>
-    <row r="56" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A56" s="10"/>
       <c r="B56" s="20"/>
       <c r="C56" s="20"/>
     </row>
-    <row r="57" spans="1:13" ht="60" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:13" ht="64" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
         <v>100</v>
       </c>
@@ -4454,7 +4451,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="58" spans="1:13" ht="60" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:13" ht="64" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
         <v>100</v>
       </c>
@@ -4495,7 +4492,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="59" spans="1:13" ht="60" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:13" ht="64" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
         <v>100</v>
       </c>
@@ -4536,7 +4533,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="60" spans="1:13" ht="60" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:13" ht="64" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
         <v>100</v>
       </c>
@@ -4577,7 +4574,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="61" spans="1:13" ht="90" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:13" ht="96" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
         <v>100</v>
       </c>
@@ -4618,7 +4615,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="62" spans="1:13" ht="105" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:13" ht="96" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
         <v>100</v>
       </c>
@@ -4659,7 +4656,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="63" spans="1:13" ht="90" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:13" ht="96" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
         <v>100</v>
       </c>
@@ -4700,7 +4697,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="64" spans="1:13" ht="105" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:13" ht="96" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
         <v>100</v>
       </c>
@@ -4741,7 +4738,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="65" spans="1:13" ht="60" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:13" ht="64" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
         <v>100</v>
       </c>
@@ -4782,7 +4779,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="66" spans="1:13" ht="60" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:13" ht="64" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
         <v>100</v>
       </c>
@@ -4823,7 +4820,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="67" spans="1:13" ht="60" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:13" ht="64" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
         <v>100</v>
       </c>
@@ -4864,7 +4861,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="68" spans="1:13" ht="60" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:13" ht="64" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
         <v>100</v>
       </c>
@@ -4905,7 +4902,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="69" spans="1:13" ht="60" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:13" ht="64" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
         <v>100</v>
       </c>
@@ -4946,7 +4943,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="70" spans="1:13" ht="60" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:13" ht="64" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
         <v>100</v>
       </c>
@@ -4987,7 +4984,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="71" spans="1:13" ht="60" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:13" ht="64" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
         <v>100</v>
       </c>
@@ -5028,7 +5025,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="72" spans="1:13" ht="60" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:13" ht="64" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
         <v>100</v>
       </c>
@@ -5069,7 +5066,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="73" spans="1:13" ht="60" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:13" ht="64" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
         <v>100</v>
       </c>
@@ -5110,11 +5107,11 @@
         <v>238</v>
       </c>
     </row>
-    <row r="74" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B74" s="19"/>
       <c r="C74" s="19"/>
     </row>
-    <row r="75" spans="1:13" ht="90" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:13" ht="64" x14ac:dyDescent="0.2">
       <c r="A75" s="24" t="s">
         <v>131</v>
       </c>
@@ -5155,7 +5152,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="76" spans="1:13" ht="75" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:13" ht="48" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
         <v>131</v>
       </c>
@@ -5196,7 +5193,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="77" spans="1:13" ht="60" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:13" ht="48" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
         <v>131</v>
       </c>
@@ -5237,7 +5234,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="78" spans="1:13" ht="75" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:13" ht="64" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
         <v>131</v>
       </c>
@@ -5278,7 +5275,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="79" spans="1:13" ht="60" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:13" ht="48" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
         <v>131</v>
       </c>
@@ -5319,7 +5316,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="80" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:13" ht="48" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
         <v>131</v>
       </c>
@@ -5360,12 +5357,12 @@
         <v>244</v>
       </c>
     </row>
-    <row r="81" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B81" s="19"/>
       <c r="C81" s="19"/>
       <c r="H81" s="11"/>
     </row>
-    <row r="82" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:13" ht="48" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
         <v>134</v>
       </c>
@@ -5406,7 +5403,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="83" spans="1:13" ht="90" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:13" ht="80" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
         <v>134</v>
       </c>
@@ -5447,7 +5444,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="84" spans="1:13" ht="105" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:13" ht="96" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
         <v>134</v>
       </c>
@@ -5488,7 +5485,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="85" spans="1:13" ht="105" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:13" ht="96" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
         <v>134</v>
       </c>
@@ -5529,7 +5526,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="86" spans="1:13" ht="75" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:13" ht="80" x14ac:dyDescent="0.2">
       <c r="A86" s="24" t="s">
         <v>392</v>
       </c>
@@ -5570,15 +5567,15 @@
         <v>394</v>
       </c>
     </row>
-    <row r="87" spans="1:13" ht="120" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:13" ht="112" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
         <v>140</v>
       </c>
       <c r="B87" s="19">
         <v>43009</v>
       </c>
-      <c r="C87" s="19" t="s">
-        <v>450</v>
+      <c r="C87" s="19">
+        <v>44834</v>
       </c>
       <c r="D87" s="4" t="s">
         <v>449</v>
@@ -5611,18 +5608,18 @@
         <v>178</v>
       </c>
     </row>
-    <row r="88" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:13" ht="32" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B88" s="19">
         <v>43009</v>
       </c>
-      <c r="C88" s="19" t="s">
-        <v>450</v>
+      <c r="C88" s="19">
+        <v>44834</v>
       </c>
       <c r="D88" s="4" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="E88" t="s">
         <v>15</v>
@@ -5637,7 +5634,10 @@
         <v>142</v>
       </c>
       <c r="I88" s="10" t="s">
-        <v>453</v>
+        <v>452</v>
+      </c>
+      <c r="J88" s="4" t="s">
+        <v>28</v>
       </c>
       <c r="K88" t="s">
         <v>19</v>
@@ -5646,14 +5646,14 @@
         <v>135</v>
       </c>
       <c r="M88" s="8" t="s">
-        <v>454</v>
-      </c>
-    </row>
-    <row r="89" spans="1:13" x14ac:dyDescent="0.25">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="89" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B89" s="19"/>
       <c r="C89" s="19"/>
     </row>
-    <row r="90" spans="1:13" ht="90" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:13" ht="80" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
         <v>131</v>
       </c>
@@ -5694,7 +5694,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="91" spans="1:13" ht="90" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:13" ht="80" x14ac:dyDescent="0.2">
       <c r="A91" t="s">
         <v>131</v>
       </c>
@@ -5735,7 +5735,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="92" spans="1:13" ht="90" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:13" ht="80" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
         <v>131</v>
       </c>
@@ -5776,7 +5776,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="93" spans="1:13" ht="90" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:13" ht="80" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
         <v>131</v>
       </c>
@@ -5817,7 +5817,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="94" spans="1:13" ht="90" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:13" ht="80" x14ac:dyDescent="0.2">
       <c r="A94" t="s">
         <v>131</v>
       </c>
@@ -5858,7 +5858,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="95" spans="1:13" ht="90" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:13" ht="80" x14ac:dyDescent="0.2">
       <c r="A95" t="s">
         <v>131</v>
       </c>
@@ -5899,10 +5899,10 @@
         <v>277</v>
       </c>
     </row>
-    <row r="96" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:13" x14ac:dyDescent="0.2">
       <c r="G96" s="8"/>
     </row>
-    <row r="97" spans="1:13" ht="60" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:13" ht="48" x14ac:dyDescent="0.2">
       <c r="A97" t="s">
         <v>286</v>
       </c>
@@ -5943,11 +5943,11 @@
         <v>391</v>
       </c>
     </row>
-    <row r="98" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B98" s="19"/>
       <c r="C98" s="19"/>
     </row>
-    <row r="99" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:13" ht="48" x14ac:dyDescent="0.2">
       <c r="A99" t="s">
         <v>289</v>
       </c>
@@ -5988,7 +5988,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="101" spans="1:13" ht="90" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:13" ht="80" x14ac:dyDescent="0.2">
       <c r="A101" t="s">
         <v>301</v>
       </c>
@@ -6029,7 +6029,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="102" spans="1:13" ht="75" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:13" ht="64" x14ac:dyDescent="0.2">
       <c r="A102" t="s">
         <v>301</v>
       </c>
@@ -6070,7 +6070,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="103" spans="1:13" ht="195" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:13" ht="176" x14ac:dyDescent="0.2">
       <c r="A103" t="s">
         <v>302</v>
       </c>
@@ -6111,11 +6111,11 @@
         <v>396</v>
       </c>
     </row>
-    <row r="104" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B104" s="19"/>
       <c r="C104" s="19"/>
     </row>
-    <row r="105" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:13" ht="48" x14ac:dyDescent="0.2">
       <c r="A105" t="s">
         <v>315</v>
       </c>
@@ -6156,7 +6156,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="106" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:13" ht="48" x14ac:dyDescent="0.2">
       <c r="A106" t="s">
         <v>315</v>
       </c>
@@ -6197,7 +6197,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="107" spans="1:13" ht="60" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:13" ht="48" x14ac:dyDescent="0.2">
       <c r="A107" t="s">
         <v>315</v>
       </c>
@@ -6238,7 +6238,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="108" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:13" ht="48" x14ac:dyDescent="0.2">
       <c r="A108" t="s">
         <v>401</v>
       </c>
@@ -6279,7 +6279,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="109" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:13" ht="32" x14ac:dyDescent="0.2">
       <c r="A109" s="4" t="s">
         <v>330</v>
       </c>
@@ -6320,7 +6320,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="110" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:13" ht="48" x14ac:dyDescent="0.2">
       <c r="A110" t="s">
         <v>401</v>
       </c>
@@ -6361,7 +6361,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="111" spans="1:13" ht="75" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:13" ht="80" x14ac:dyDescent="0.2">
       <c r="A111" t="s">
         <v>401</v>
       </c>
@@ -6402,7 +6402,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="112" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:13" ht="32" x14ac:dyDescent="0.2">
       <c r="A112" t="s">
         <v>331</v>
       </c>
@@ -6443,7 +6443,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="113" spans="1:13" ht="75" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:13" ht="80" x14ac:dyDescent="0.2">
       <c r="A113" t="s">
         <v>401</v>
       </c>
@@ -6484,7 +6484,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="114" spans="1:13" ht="75" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:13" ht="80" x14ac:dyDescent="0.2">
       <c r="A114" t="s">
         <v>401</v>
       </c>
@@ -6525,7 +6525,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="115" spans="1:13" ht="75" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:13" ht="80" x14ac:dyDescent="0.2">
       <c r="A115" t="s">
         <v>401</v>
       </c>
@@ -6566,11 +6566,11 @@
         <v>404</v>
       </c>
     </row>
-    <row r="116" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B116" s="19"/>
       <c r="C116" s="19"/>
     </row>
-    <row r="117" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:13" ht="32" x14ac:dyDescent="0.2">
       <c r="A117" t="s">
         <v>343</v>
       </c>
@@ -6611,7 +6611,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="118" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:13" ht="16" x14ac:dyDescent="0.2">
       <c r="A118" t="s">
         <v>342</v>
       </c>
@@ -6652,7 +6652,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="119" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:13" ht="32" x14ac:dyDescent="0.2">
       <c r="A119" t="s">
         <v>342</v>
       </c>
@@ -6693,11 +6693,11 @@
         <v>346</v>
       </c>
     </row>
-    <row r="120" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B120" s="19"/>
       <c r="C120" s="19"/>
     </row>
-    <row r="121" spans="1:13" ht="75" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:13" ht="80" x14ac:dyDescent="0.2">
       <c r="A121" s="24" t="s">
         <v>349</v>
       </c>
@@ -6738,7 +6738,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="122" spans="1:13" ht="75" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:13" ht="80" x14ac:dyDescent="0.2">
       <c r="A122" t="s">
         <v>349</v>
       </c>
@@ -6779,7 +6779,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="123" spans="1:13" ht="75" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:13" ht="80" x14ac:dyDescent="0.2">
       <c r="A123" t="s">
         <v>349</v>
       </c>
@@ -6820,7 +6820,7 @@
         <v>413</v>
       </c>
     </row>
-    <row r="124" spans="1:13" ht="75" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:13" ht="80" x14ac:dyDescent="0.2">
       <c r="A124" t="s">
         <v>349</v>
       </c>
@@ -6861,7 +6861,7 @@
         <v>414</v>
       </c>
     </row>
-    <row r="125" spans="1:13" ht="75" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:13" ht="80" x14ac:dyDescent="0.2">
       <c r="A125" t="s">
         <v>349</v>
       </c>
@@ -6902,7 +6902,7 @@
         <v>415</v>
       </c>
     </row>
-    <row r="126" spans="1:13" ht="75" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:13" ht="80" x14ac:dyDescent="0.2">
       <c r="A126" t="s">
         <v>349</v>
       </c>
@@ -6943,7 +6943,7 @@
         <v>416</v>
       </c>
     </row>
-    <row r="127" spans="1:13" ht="90" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:13" ht="80" x14ac:dyDescent="0.2">
       <c r="A127" t="s">
         <v>349</v>
       </c>
@@ -6984,7 +6984,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="128" spans="1:13" ht="90" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:13" ht="80" x14ac:dyDescent="0.2">
       <c r="A128" t="s">
         <v>349</v>
       </c>
@@ -7025,7 +7025,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="129" spans="1:13" ht="90" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:13" ht="80" x14ac:dyDescent="0.2">
       <c r="A129" t="s">
         <v>349</v>
       </c>
@@ -7066,7 +7066,7 @@
         <v>413</v>
       </c>
     </row>
-    <row r="130" spans="1:13" ht="90" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:13" ht="80" x14ac:dyDescent="0.2">
       <c r="A130" t="s">
         <v>349</v>
       </c>
@@ -7107,7 +7107,7 @@
         <v>414</v>
       </c>
     </row>
-    <row r="131" spans="1:13" ht="90" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:13" ht="80" x14ac:dyDescent="0.2">
       <c r="A131" t="s">
         <v>349</v>
       </c>
@@ -7148,7 +7148,7 @@
         <v>415</v>
       </c>
     </row>
-    <row r="132" spans="1:13" ht="90" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:13" ht="80" x14ac:dyDescent="0.2">
       <c r="A132" t="s">
         <v>349</v>
       </c>
@@ -7189,7 +7189,7 @@
         <v>416</v>
       </c>
     </row>
-    <row r="133" spans="1:13" ht="105" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:13" ht="80" x14ac:dyDescent="0.2">
       <c r="A133" t="s">
         <v>349</v>
       </c>
@@ -7230,7 +7230,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="134" spans="1:13" ht="105" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:13" ht="80" x14ac:dyDescent="0.2">
       <c r="A134" t="s">
         <v>349</v>
       </c>
@@ -7271,7 +7271,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="135" spans="1:13" ht="105" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:13" ht="80" x14ac:dyDescent="0.2">
       <c r="A135" t="s">
         <v>349</v>
       </c>
@@ -7312,7 +7312,7 @@
         <v>413</v>
       </c>
     </row>
-    <row r="136" spans="1:13" ht="105" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:13" ht="80" x14ac:dyDescent="0.2">
       <c r="A136" t="s">
         <v>349</v>
       </c>
@@ -7353,7 +7353,7 @@
         <v>414</v>
       </c>
     </row>
-    <row r="137" spans="1:13" ht="105" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:13" ht="80" x14ac:dyDescent="0.2">
       <c r="A137" t="s">
         <v>349</v>
       </c>
@@ -7394,7 +7394,7 @@
         <v>415</v>
       </c>
     </row>
-    <row r="138" spans="1:13" ht="105" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:13" ht="80" x14ac:dyDescent="0.2">
       <c r="A138" t="s">
         <v>349</v>
       </c>
@@ -7435,7 +7435,7 @@
         <v>416</v>
       </c>
     </row>
-    <row r="139" spans="1:13" ht="75" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:13" ht="80" x14ac:dyDescent="0.2">
       <c r="A139" s="26" t="s">
         <v>349</v>
       </c>
@@ -7476,7 +7476,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="140" spans="1:13" ht="75" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:13" ht="80" x14ac:dyDescent="0.2">
       <c r="A140" s="23" t="s">
         <v>349</v>
       </c>
@@ -7517,7 +7517,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="141" spans="1:13" ht="75" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:13" ht="80" x14ac:dyDescent="0.2">
       <c r="A141" s="23" t="s">
         <v>349</v>
       </c>
@@ -7558,7 +7558,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="142" spans="1:13" ht="75" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:13" ht="80" x14ac:dyDescent="0.2">
       <c r="A142" s="23" t="s">
         <v>349</v>
       </c>
@@ -7599,7 +7599,7 @@
         <v>435</v>
       </c>
     </row>
-    <row r="143" spans="1:13" ht="75" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:13" ht="80" x14ac:dyDescent="0.2">
       <c r="A143" s="23" t="s">
         <v>349</v>
       </c>
@@ -7640,7 +7640,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="144" spans="1:13" ht="75" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:13" ht="80" x14ac:dyDescent="0.2">
       <c r="A144" s="23" t="s">
         <v>349</v>
       </c>
@@ -7681,7 +7681,7 @@
         <v>437</v>
       </c>
     </row>
-    <row r="145" spans="1:13" ht="90" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:13" ht="80" x14ac:dyDescent="0.2">
       <c r="A145" s="23" t="s">
         <v>349</v>
       </c>
@@ -7722,7 +7722,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="146" spans="1:13" ht="90" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:13" ht="80" x14ac:dyDescent="0.2">
       <c r="A146" s="23" t="s">
         <v>349</v>
       </c>
@@ -7763,7 +7763,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="147" spans="1:13" ht="90" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:13" ht="80" x14ac:dyDescent="0.2">
       <c r="A147" s="23" t="s">
         <v>349</v>
       </c>
@@ -7804,7 +7804,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="148" spans="1:13" ht="90" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:13" ht="80" x14ac:dyDescent="0.2">
       <c r="A148" s="23" t="s">
         <v>349</v>
       </c>
@@ -7845,7 +7845,7 @@
         <v>435</v>
       </c>
     </row>
-    <row r="149" spans="1:13" ht="90" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:13" ht="80" x14ac:dyDescent="0.2">
       <c r="A149" s="23" t="s">
         <v>349</v>
       </c>
@@ -7886,7 +7886,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="150" spans="1:13" ht="90" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:13" ht="80" x14ac:dyDescent="0.2">
       <c r="A150" s="23" t="s">
         <v>349</v>
       </c>
@@ -7927,7 +7927,7 @@
         <v>437</v>
       </c>
     </row>
-    <row r="151" spans="1:13" ht="105" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:13" ht="80" x14ac:dyDescent="0.2">
       <c r="A151" s="23" t="s">
         <v>349</v>
       </c>
@@ -7968,7 +7968,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="152" spans="1:13" ht="105" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:13" ht="80" x14ac:dyDescent="0.2">
       <c r="A152" s="23" t="s">
         <v>349</v>
       </c>
@@ -8009,7 +8009,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="153" spans="1:13" ht="105" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:13" ht="80" x14ac:dyDescent="0.2">
       <c r="A153" s="23" t="s">
         <v>349</v>
       </c>
@@ -8050,7 +8050,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="154" spans="1:13" ht="105" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:13" ht="80" x14ac:dyDescent="0.2">
       <c r="A154" s="23" t="s">
         <v>349</v>
       </c>
@@ -8091,7 +8091,7 @@
         <v>435</v>
       </c>
     </row>
-    <row r="155" spans="1:13" ht="105" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:13" ht="80" x14ac:dyDescent="0.2">
       <c r="A155" s="23" t="s">
         <v>349</v>
       </c>
@@ -8132,7 +8132,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="156" spans="1:13" ht="105" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:13" ht="80" x14ac:dyDescent="0.2">
       <c r="A156" s="23" t="s">
         <v>349</v>
       </c>
@@ -8173,12 +8173,12 @@
         <v>437</v>
       </c>
     </row>
-    <row r="157" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A157" s="23"/>
       <c r="B157" s="19"/>
       <c r="C157" s="19"/>
     </row>
-    <row r="158" spans="1:13" ht="90" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:13" ht="80" x14ac:dyDescent="0.2">
       <c r="A158" t="s">
         <v>357</v>
       </c>
@@ -8189,7 +8189,7 @@
         <v>45230</v>
       </c>
       <c r="D158" s="4" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="E158" t="s">
         <v>15</v>
@@ -8219,7 +8219,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="159" spans="1:13" ht="105" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:13" ht="96" x14ac:dyDescent="0.2">
       <c r="A159" t="s">
         <v>357</v>
       </c>
@@ -8230,7 +8230,7 @@
         <v>45626</v>
       </c>
       <c r="D159" s="4" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="E159" t="s">
         <v>15</v>
@@ -8260,7 +8260,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="160" spans="1:13" ht="105" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:13" ht="96" x14ac:dyDescent="0.2">
       <c r="A160" t="s">
         <v>357</v>
       </c>
@@ -8301,7 +8301,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="161" spans="1:13" ht="105" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:13" ht="96" x14ac:dyDescent="0.2">
       <c r="A161" t="s">
         <v>357</v>
       </c>
@@ -8342,7 +8342,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="162" spans="1:13" ht="105" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:13" ht="96" x14ac:dyDescent="0.2">
       <c r="A162" t="s">
         <v>357</v>
       </c>
@@ -8353,7 +8353,7 @@
         <v>45657</v>
       </c>
       <c r="D162" s="4" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="E162" t="s">
         <v>15</v>
@@ -8383,7 +8383,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="163" spans="1:13" ht="105" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:13" ht="96" x14ac:dyDescent="0.2">
       <c r="A163" t="s">
         <v>357</v>
       </c>
@@ -8424,7 +8424,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="164" spans="1:13" ht="105" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:13" ht="96" x14ac:dyDescent="0.2">
       <c r="A164" t="s">
         <v>357</v>
       </c>
@@ -8465,7 +8465,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="165" spans="1:13" ht="105" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:13" ht="96" x14ac:dyDescent="0.2">
       <c r="A165" t="s">
         <v>357</v>
       </c>
@@ -8506,7 +8506,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="166" spans="1:13" ht="105" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:13" ht="112" x14ac:dyDescent="0.2">
       <c r="A166" t="s">
         <v>357</v>
       </c>
@@ -8547,12 +8547,12 @@
         <v>360</v>
       </c>
     </row>
-    <row r="167" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B167" s="19"/>
       <c r="C167" s="19"/>
       <c r="D167" s="4"/>
     </row>
-    <row r="168" spans="1:13" ht="90" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:13" ht="80" x14ac:dyDescent="0.2">
       <c r="A168" t="s">
         <v>375</v>
       </c>
@@ -8593,13 +8593,13 @@
         <v>377</v>
       </c>
     </row>
-    <row r="169" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:13" x14ac:dyDescent="0.2">
       <c r="D169" s="4"/>
     </row>
-    <row r="170" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:13" x14ac:dyDescent="0.2">
       <c r="D170" s="4"/>
     </row>
-    <row r="171" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:13" x14ac:dyDescent="0.2">
       <c r="D171" s="4"/>
     </row>
   </sheetData>
@@ -8667,18 +8667,18 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E0B35E6D-763F-4C40-91D2-473BE7766F62}">
   <dimension ref="A1:B20"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="20.42578125" customWidth="1"/>
-    <col min="2" max="2" width="105.140625" customWidth="1"/>
+    <col min="1" max="1" width="20.5" customWidth="1"/>
+    <col min="2" max="2" width="105.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>145</v>
       </c>
@@ -8686,7 +8686,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>24</v>
       </c>
@@ -8694,7 +8694,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>23</v>
       </c>
@@ -8702,7 +8702,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>149</v>
       </c>
@@ -8710,7 +8710,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>151</v>
       </c>
@@ -8718,7 +8718,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>80</v>
       </c>
@@ -8726,7 +8726,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>81</v>
       </c>
@@ -8734,7 +8734,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>155</v>
       </c>
@@ -8742,7 +8742,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>157</v>
       </c>
@@ -8750,7 +8750,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>44</v>
       </c>
@@ -8758,7 +8758,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>43</v>
       </c>
@@ -8766,7 +8766,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>21</v>
       </c>
@@ -8774,7 +8774,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>76</v>
       </c>
@@ -8782,7 +8782,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>40</v>
       </c>
@@ -8790,7 +8790,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>164</v>
       </c>
@@ -8798,7 +8798,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>166</v>
       </c>
@@ -8806,7 +8806,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>168</v>
       </c>
@@ -8814,7 +8814,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>170</v>
       </c>
@@ -8829,17 +8829,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="80b53ead-ac38-442a-b597-5a0e2e0802cd">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="5ec1cc48-4270-4222-9ed5-54ce9e59d47b" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010050398B8EA2737947995C227484EA02C8" ma:contentTypeVersion="17" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="bc9a2575e6c24a964f45b6e1606b04fd">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="80b53ead-ac38-442a-b597-5a0e2e0802cd" xmlns:ns3="5ec1cc48-4270-4222-9ed5-54ce9e59d47b" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="662112485a0135ca1785eae0908ad389" ns2:_="" ns3:_="">
     <xsd:import namespace="80b53ead-ac38-442a-b597-5a0e2e0802cd"/>
@@ -9076,6 +9065,17 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="80b53ead-ac38-442a-b597-5a0e2e0802cd">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="5ec1cc48-4270-4222-9ed5-54ce9e59d47b" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -9086,17 +9086,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{66AF2240-620B-4312-9739-CAF731E4A98F}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="80b53ead-ac38-442a-b597-5a0e2e0802cd"/>
-    <ds:schemaRef ds:uri="5ec1cc48-4270-4222-9ed5-54ce9e59d47b"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{72DD370E-74FD-4D33-B5A7-49A7FE6518F7}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -9115,6 +9104,17 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{66AF2240-620B-4312-9739-CAF731E4A98F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="80b53ead-ac38-442a-b597-5a0e2e0802cd"/>
+    <ds:schemaRef ds:uri="5ec1cc48-4270-4222-9ed5-54ce9e59d47b"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3B1B5D08-A2EB-4F47-BA81-DA28AA2A09F4}">
   <ds:schemaRefs>

--- a/EEE2000-metadata_mapping.xlsx
+++ b/EEE2000-metadata_mapping.xlsx
@@ -1,20 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10905"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10817"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rhys.r.evans/Documents/CEDA/CCI/cci_data_bridge_inputs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B9F3D91-8869-9442-A948-917318D39AD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{404D513E-B1AD-504D-8B3E-2798B325392D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8740" yWindow="1280" windowWidth="28800" windowHeight="15280" xr2:uid="{B9DA58AC-C110-4CBA-A19B-6F37B44EEA38}"/>
+    <workbookView xWindow="3700" yWindow="780" windowWidth="32520" windowHeight="17580" activeTab="1" xr2:uid="{B9DA58AC-C110-4CBA-A19B-6F37B44EEA38}"/>
   </bookViews>
   <sheets>
     <sheet name="Mapping" sheetId="2" r:id="rId1"/>
-    <sheet name="Relationship definitions" sheetId="1" r:id="rId2"/>
+    <sheet name="AI Mapping" sheetId="3" r:id="rId2"/>
+    <sheet name="Relationship definitions" sheetId="1" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Mapping!$L$1:$L$94</definedName>
@@ -40,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1722" uniqueCount="460">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1820" uniqueCount="495">
   <si>
     <t>Dataset 1</t>
   </si>
@@ -1756,6 +1757,111 @@
   </si>
   <si>
     <t>Indicates A is used by B</t>
+  </si>
+  <si>
+    <t>Relationship (Dataset to AI Model)</t>
+  </si>
+  <si>
+    <t>Relationship (AI Model to Dataset)</t>
+  </si>
+  <si>
+    <t>Type</t>
+  </si>
+  <si>
+    <t>Category</t>
+  </si>
+  <si>
+    <t>Classification of forest change</t>
+  </si>
+  <si>
+    <t>Uncertainty estimation of bias</t>
+  </si>
+  <si>
+    <t>Harmonise Sentinel-3 and MODIS</t>
+  </si>
+  <si>
+    <t>Classification of burned area</t>
+  </si>
+  <si>
+    <t>Identify albedo/snow before LAI calculated</t>
+  </si>
+  <si>
+    <t>Cloud screening for filtering</t>
+  </si>
+  <si>
+    <t>Generate cal/val datasets</t>
+  </si>
+  <si>
+    <t>Emulate physical models</t>
+  </si>
+  <si>
+    <t>Classification of irrigation</t>
+  </si>
+  <si>
+    <t>Modelling</t>
+  </si>
+  <si>
+    <t>Accuracy</t>
+  </si>
+  <si>
+    <t>Data assimilation</t>
+  </si>
+  <si>
+    <t>Generation</t>
+  </si>
+  <si>
+    <t>Processing</t>
+  </si>
+  <si>
+    <t>Computational efficiency</t>
+  </si>
+  <si>
+    <t>Machine Learning – supervised</t>
+  </si>
+  <si>
+    <t>Machine Learning – unsupervised</t>
+  </si>
+  <si>
+    <t>Deep Learning – unspecified neural networks</t>
+  </si>
+  <si>
+    <t>Random Forest</t>
+  </si>
+  <si>
+    <t>Principle Component Analysis</t>
+  </si>
+  <si>
+    <t>Neural Network</t>
+  </si>
+  <si>
+    <t>Gaussian Process Regression</t>
+  </si>
+  <si>
+    <t>Datatset ID</t>
+  </si>
+  <si>
+    <t>Project</t>
+  </si>
+  <si>
+    <t xml:space="preserve">- </t>
+  </si>
+  <si>
+    <t>Biomass</t>
+  </si>
+  <si>
+    <t>Anthropogenic Water Use</t>
+  </si>
+  <si>
+    <t>AI</t>
+  </si>
+  <si>
+    <t>Use</t>
+  </si>
+  <si>
+    <t>User</t>
+  </si>
+  <si>
+    <t>https://catalogue.ceda.ac.uk/uuid/6429d1aafe1e43b9b414e4a5a7f8b903</t>
   </si>
 </sst>
 </file>
@@ -1765,7 +1871,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd;@"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1808,6 +1914,12 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -1835,7 +1947,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="8">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -1916,12 +2028,47 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -1975,10 +2122,23 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1992,6 +2152,18 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2327,18 +2499,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="16" x14ac:dyDescent="0.2">
-      <c r="A1" s="27" t="s">
+      <c r="A1" s="37" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="27"/>
-      <c r="C1" s="27"/>
-      <c r="D1" s="27"/>
-      <c r="E1" s="27"/>
-      <c r="F1" s="28"/>
-      <c r="G1" s="29" t="s">
+      <c r="B1" s="37"/>
+      <c r="C1" s="37"/>
+      <c r="D1" s="37"/>
+      <c r="E1" s="37"/>
+      <c r="F1" s="45"/>
+      <c r="G1" s="38" t="s">
         <v>1</v>
       </c>
-      <c r="H1" s="31" t="s">
+      <c r="H1" s="40" t="s">
         <v>2</v>
       </c>
       <c r="I1" s="14" t="s">
@@ -2367,8 +2539,8 @@
       <c r="F2" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="G2" s="30"/>
-      <c r="H2" s="32"/>
+      <c r="G2" s="39"/>
+      <c r="H2" s="41"/>
       <c r="I2" s="15" t="s">
         <v>10</v>
       </c>
@@ -8707,6 +8879,360 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C17FE217-AB61-B742-BFE0-33900D1BEC91}">
+  <dimension ref="A1:H13"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="17.1640625" customWidth="1"/>
+    <col min="2" max="2" width="53.33203125" customWidth="1"/>
+    <col min="3" max="3" width="29.1640625" customWidth="1"/>
+    <col min="4" max="4" width="30.5" customWidth="1"/>
+    <col min="5" max="6" width="17.33203125" customWidth="1"/>
+    <col min="7" max="7" width="16.5" customWidth="1"/>
+    <col min="8" max="8" width="33.5" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="37" t="s">
+        <v>493</v>
+      </c>
+      <c r="B1" s="37"/>
+      <c r="C1" s="38" t="s">
+        <v>460</v>
+      </c>
+      <c r="D1" s="40" t="s">
+        <v>461</v>
+      </c>
+      <c r="E1" s="42" t="s">
+        <v>491</v>
+      </c>
+      <c r="F1" s="43"/>
+      <c r="G1" s="44"/>
+      <c r="H1" s="27"/>
+    </row>
+    <row r="2" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="2" t="s">
+        <v>487</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>486</v>
+      </c>
+      <c r="C2" s="39"/>
+      <c r="D2" s="41"/>
+      <c r="E2" s="30" t="s">
+        <v>462</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>463</v>
+      </c>
+      <c r="G2" s="5" t="s">
+        <v>492</v>
+      </c>
+      <c r="H2" s="28" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="32" x14ac:dyDescent="0.2">
+      <c r="A3" s="29" t="s">
+        <v>489</v>
+      </c>
+      <c r="B3" s="16" t="s">
+        <v>494</v>
+      </c>
+      <c r="C3" s="9" t="s">
+        <v>453</v>
+      </c>
+      <c r="D3" s="12" t="s">
+        <v>454</v>
+      </c>
+      <c r="E3" s="33" t="s">
+        <v>482</v>
+      </c>
+      <c r="F3" s="29" t="s">
+        <v>479</v>
+      </c>
+      <c r="G3" s="31" t="s">
+        <v>473</v>
+      </c>
+      <c r="H3" s="35" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="32" x14ac:dyDescent="0.2">
+      <c r="A4" s="29" t="s">
+        <v>489</v>
+      </c>
+      <c r="B4" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" s="9" t="s">
+        <v>453</v>
+      </c>
+      <c r="D4" s="12" t="s">
+        <v>454</v>
+      </c>
+      <c r="E4" s="34" t="s">
+        <v>482</v>
+      </c>
+      <c r="F4" s="29" t="s">
+        <v>479</v>
+      </c>
+      <c r="G4" s="32" t="s">
+        <v>474</v>
+      </c>
+      <c r="H4" s="36" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="32" x14ac:dyDescent="0.2">
+      <c r="A5" s="29" t="s">
+        <v>70</v>
+      </c>
+      <c r="B5" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="C5" s="9" t="s">
+        <v>453</v>
+      </c>
+      <c r="D5" s="12" t="s">
+        <v>454</v>
+      </c>
+      <c r="E5" s="34" t="s">
+        <v>482</v>
+      </c>
+      <c r="F5" s="29" t="s">
+        <v>479</v>
+      </c>
+      <c r="G5" s="32" t="s">
+        <v>475</v>
+      </c>
+      <c r="H5" s="36" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="32" x14ac:dyDescent="0.2">
+      <c r="A6" s="29" t="s">
+        <v>70</v>
+      </c>
+      <c r="B6" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="C6" s="9" t="s">
+        <v>453</v>
+      </c>
+      <c r="D6" s="12" t="s">
+        <v>454</v>
+      </c>
+      <c r="E6" s="34" t="s">
+        <v>482</v>
+      </c>
+      <c r="F6" s="29" t="s">
+        <v>479</v>
+      </c>
+      <c r="G6" s="32" t="s">
+        <v>476</v>
+      </c>
+      <c r="H6" s="36" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="29" t="s">
+        <v>378</v>
+      </c>
+      <c r="B7" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" s="9" t="s">
+        <v>453</v>
+      </c>
+      <c r="D7" s="12" t="s">
+        <v>454</v>
+      </c>
+      <c r="E7" s="34" t="s">
+        <v>483</v>
+      </c>
+      <c r="F7" s="29" t="s">
+        <v>480</v>
+      </c>
+      <c r="G7" s="32" t="s">
+        <v>477</v>
+      </c>
+      <c r="H7" s="36" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A8" s="29" t="s">
+        <v>340</v>
+      </c>
+      <c r="B8" s="29" t="s">
+        <v>488</v>
+      </c>
+      <c r="C8" s="9" t="s">
+        <v>453</v>
+      </c>
+      <c r="D8" s="12" t="s">
+        <v>454</v>
+      </c>
+      <c r="E8" s="34" t="s">
+        <v>484</v>
+      </c>
+      <c r="F8" s="29" t="s">
+        <v>481</v>
+      </c>
+      <c r="G8" s="32" t="s">
+        <v>477</v>
+      </c>
+      <c r="H8" s="36" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A9" s="29" t="s">
+        <v>490</v>
+      </c>
+      <c r="B9" s="29" t="s">
+        <v>14</v>
+      </c>
+      <c r="C9" s="9" t="s">
+        <v>453</v>
+      </c>
+      <c r="D9" s="12" t="s">
+        <v>454</v>
+      </c>
+      <c r="E9" s="34" t="s">
+        <v>485</v>
+      </c>
+      <c r="F9" s="29" t="s">
+        <v>479</v>
+      </c>
+      <c r="G9" s="32" t="s">
+        <v>474</v>
+      </c>
+      <c r="H9" s="36" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A10" s="29" t="s">
+        <v>490</v>
+      </c>
+      <c r="B10" s="29" t="s">
+        <v>14</v>
+      </c>
+      <c r="C10" s="9" t="s">
+        <v>453</v>
+      </c>
+      <c r="D10" s="12" t="s">
+        <v>454</v>
+      </c>
+      <c r="E10" s="34" t="s">
+        <v>485</v>
+      </c>
+      <c r="F10" s="29" t="s">
+        <v>479</v>
+      </c>
+      <c r="G10" s="32" t="s">
+        <v>478</v>
+      </c>
+      <c r="H10" s="36" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A11" s="29" t="s">
+        <v>490</v>
+      </c>
+      <c r="B11" s="29" t="s">
+        <v>14</v>
+      </c>
+      <c r="C11" s="9" t="s">
+        <v>453</v>
+      </c>
+      <c r="D11" s="12" t="s">
+        <v>454</v>
+      </c>
+      <c r="E11" s="34" t="s">
+        <v>484</v>
+      </c>
+      <c r="F11" s="29" t="s">
+        <v>481</v>
+      </c>
+      <c r="G11" s="32" t="s">
+        <v>474</v>
+      </c>
+      <c r="H11" s="36" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A12" s="29" t="s">
+        <v>490</v>
+      </c>
+      <c r="B12" s="29" t="s">
+        <v>14</v>
+      </c>
+      <c r="C12" s="9" t="s">
+        <v>453</v>
+      </c>
+      <c r="D12" s="12" t="s">
+        <v>454</v>
+      </c>
+      <c r="E12" s="34" t="s">
+        <v>484</v>
+      </c>
+      <c r="F12" s="29" t="s">
+        <v>481</v>
+      </c>
+      <c r="G12" s="32" t="s">
+        <v>478</v>
+      </c>
+      <c r="H12" s="36" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A13" s="29" t="s">
+        <v>490</v>
+      </c>
+      <c r="B13" s="29" t="s">
+        <v>14</v>
+      </c>
+      <c r="C13" s="9" t="s">
+        <v>453</v>
+      </c>
+      <c r="D13" s="12" t="s">
+        <v>454</v>
+      </c>
+      <c r="E13" s="34" t="s">
+        <v>482</v>
+      </c>
+      <c r="F13" s="29" t="s">
+        <v>479</v>
+      </c>
+      <c r="G13" s="32" t="s">
+        <v>476</v>
+      </c>
+      <c r="H13" s="36" t="s">
+        <v>472</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:G1"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="B3" r:id="rId1" xr:uid="{14FB7D38-448E-AA47-96C8-218AD71E39DE}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E0B35E6D-763F-4C40-91D2-473BE7766F62}">
   <dimension ref="A1:B22"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
@@ -8887,6 +9413,26 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="80b53ead-ac38-442a-b597-5a0e2e0802cd">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="5ec1cc48-4270-4222-9ed5-54ce9e59d47b" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010050398B8EA2737947995C227484EA02C8" ma:contentTypeVersion="17" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="bc9a2575e6c24a964f45b6e1606b04fd">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="80b53ead-ac38-442a-b597-5a0e2e0802cd" xmlns:ns3="5ec1cc48-4270-4222-9ed5-54ce9e59d47b" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="662112485a0135ca1785eae0908ad389" ns2:_="" ns3:_="">
     <xsd:import namespace="80b53ead-ac38-442a-b597-5a0e2e0802cd"/>
@@ -9123,27 +9669,26 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3B1B5D08-A2EB-4F47-BA81-DA28AA2A09F4}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="80b53ead-ac38-442a-b597-5a0e2e0802cd">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="5ec1cc48-4270-4222-9ed5-54ce9e59d47b" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{66AF2240-620B-4312-9739-CAF731E4A98F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="80b53ead-ac38-442a-b597-5a0e2e0802cd"/>
+    <ds:schemaRef ds:uri="5ec1cc48-4270-4222-9ed5-54ce9e59d47b"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{72DD370E-74FD-4D33-B5A7-49A7FE6518F7}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -9160,23 +9705,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3B1B5D08-A2EB-4F47-BA81-DA28AA2A09F4}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{66AF2240-620B-4312-9739-CAF731E4A98F}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="80b53ead-ac38-442a-b597-5a0e2e0802cd"/>
-    <ds:schemaRef ds:uri="5ec1cc48-4270-4222-9ed5-54ce9e59d47b"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/EEE2000-metadata_mapping.xlsx
+++ b/EEE2000-metadata_mapping.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rhys.r.evans/Documents/CEDA/CCI/cci_data_bridge_inputs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{404D513E-B1AD-504D-8B3E-2798B325392D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D494611D-C123-164E-A765-53DDDE64F688}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3700" yWindow="780" windowWidth="32520" windowHeight="17580" activeTab="1" xr2:uid="{B9DA58AC-C110-4CBA-A19B-6F37B44EEA38}"/>
+    <workbookView xWindow="-31560" yWindow="1000" windowWidth="32520" windowHeight="17580" activeTab="1" xr2:uid="{B9DA58AC-C110-4CBA-A19B-6F37B44EEA38}"/>
   </bookViews>
   <sheets>
     <sheet name="Mapping" sheetId="2" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1820" uniqueCount="495">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1832" uniqueCount="500">
   <si>
     <t>Dataset 1</t>
   </si>
@@ -1862,6 +1862,21 @@
   </si>
   <si>
     <t>https://catalogue.ceda.ac.uk/uuid/6429d1aafe1e43b9b414e4a5a7f8b903</t>
+  </si>
+  <si>
+    <t>Data provider</t>
+  </si>
+  <si>
+    <t>https://catalogue.ceda.ac.uk/uuid/6429d1aafe1e43b9b414e4a5a7f8b904</t>
+  </si>
+  <si>
+    <t>https://catalogue.ceda.ac.uk/uuid/db75c5f51ee240ae8743355dcebbb9b9</t>
+  </si>
+  <si>
+    <t>https://catalogue.ceda.ac.uk/uuid/db75c5f51ee240ae8743355dcebbb9b10</t>
+  </si>
+  <si>
+    <t>https://catalogue.ceda.ac.uk/uuid/8d02d224437247f6a6270a575d457bd8</t>
   </si>
 </sst>
 </file>
@@ -2068,7 +2083,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -2165,6 +2180,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -8880,353 +8896,395 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C17FE217-AB61-B742-BFE0-33900D1BEC91}">
-  <dimension ref="A1:H13"/>
+  <dimension ref="A1:I13"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="17.1640625" customWidth="1"/>
-    <col min="2" max="2" width="53.33203125" customWidth="1"/>
-    <col min="3" max="3" width="29.1640625" customWidth="1"/>
-    <col min="4" max="4" width="30.5" customWidth="1"/>
-    <col min="5" max="6" width="17.33203125" customWidth="1"/>
-    <col min="7" max="7" width="16.5" customWidth="1"/>
-    <col min="8" max="8" width="33.5" customWidth="1"/>
+    <col min="1" max="1" width="16.33203125" customWidth="1"/>
+    <col min="2" max="2" width="17.1640625" customWidth="1"/>
+    <col min="3" max="3" width="53.33203125" customWidth="1"/>
+    <col min="4" max="4" width="29.1640625" customWidth="1"/>
+    <col min="5" max="5" width="30.5" customWidth="1"/>
+    <col min="6" max="7" width="17.33203125" customWidth="1"/>
+    <col min="8" max="8" width="16.5" customWidth="1"/>
+    <col min="9" max="9" width="33.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:9" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="37" t="s">
         <v>493</v>
       </c>
       <c r="B1" s="37"/>
-      <c r="C1" s="38" t="s">
+      <c r="C1" s="45"/>
+      <c r="D1" s="38" t="s">
         <v>460</v>
       </c>
-      <c r="D1" s="40" t="s">
+      <c r="E1" s="40" t="s">
         <v>461</v>
       </c>
-      <c r="E1" s="42" t="s">
+      <c r="F1" s="42" t="s">
         <v>491</v>
       </c>
-      <c r="F1" s="43"/>
-      <c r="G1" s="44"/>
-      <c r="H1" s="27"/>
-    </row>
-    <row r="2" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G1" s="43"/>
+      <c r="H1" s="44"/>
+      <c r="I1" s="27"/>
+    </row>
+    <row r="2" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
+        <v>495</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>487</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="C2" s="2" t="s">
         <v>486</v>
       </c>
-      <c r="C2" s="39"/>
-      <c r="D2" s="41"/>
-      <c r="E2" s="30" t="s">
+      <c r="D2" s="39"/>
+      <c r="E2" s="41"/>
+      <c r="F2" s="30" t="s">
         <v>462</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="G2" s="2" t="s">
         <v>463</v>
       </c>
-      <c r="G2" s="5" t="s">
+      <c r="H2" s="5" t="s">
         <v>492</v>
       </c>
-      <c r="H2" s="28" t="s">
+      <c r="I2" s="28" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="32" x14ac:dyDescent="0.2">
-      <c r="A3" s="29" t="s">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" s="29" t="s">
         <v>489</v>
       </c>
-      <c r="B3" s="16" t="s">
+      <c r="C3" s="46" t="s">
         <v>494</v>
       </c>
-      <c r="C3" s="9" t="s">
+      <c r="D3" s="9" t="s">
         <v>453</v>
       </c>
-      <c r="D3" s="12" t="s">
+      <c r="E3" s="12" t="s">
         <v>454</v>
       </c>
-      <c r="E3" s="33" t="s">
+      <c r="F3" s="33" t="s">
         <v>482</v>
       </c>
-      <c r="F3" s="29" t="s">
+      <c r="G3" s="29" t="s">
         <v>479</v>
       </c>
-      <c r="G3" s="31" t="s">
+      <c r="H3" s="31" t="s">
         <v>473</v>
       </c>
-      <c r="H3" s="35" t="s">
+      <c r="I3" s="35" t="s">
         <v>464</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="32" x14ac:dyDescent="0.2">
-      <c r="A4" s="29" t="s">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" s="29" t="s">
         <v>489</v>
       </c>
-      <c r="B4" s="16" t="s">
-        <v>18</v>
-      </c>
-      <c r="C4" s="9" t="s">
+      <c r="C4" s="46" t="s">
+        <v>496</v>
+      </c>
+      <c r="D4" s="9" t="s">
         <v>453</v>
       </c>
-      <c r="D4" s="12" t="s">
+      <c r="E4" s="12" t="s">
         <v>454</v>
       </c>
-      <c r="E4" s="34" t="s">
+      <c r="F4" s="34" t="s">
         <v>482</v>
       </c>
-      <c r="F4" s="29" t="s">
+      <c r="G4" s="29" t="s">
         <v>479</v>
       </c>
-      <c r="G4" s="32" t="s">
+      <c r="H4" s="32" t="s">
         <v>474</v>
       </c>
-      <c r="H4" s="36" t="s">
+      <c r="I4" s="36" t="s">
         <v>465</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="32" x14ac:dyDescent="0.2">
-      <c r="A5" s="29" t="s">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" s="29" t="s">
         <v>70</v>
       </c>
-      <c r="B5" s="16" t="s">
-        <v>18</v>
-      </c>
-      <c r="C5" s="9" t="s">
+      <c r="C5" s="46" t="s">
+        <v>497</v>
+      </c>
+      <c r="D5" s="9" t="s">
         <v>453</v>
       </c>
-      <c r="D5" s="12" t="s">
+      <c r="E5" s="12" t="s">
         <v>454</v>
       </c>
-      <c r="E5" s="34" t="s">
+      <c r="F5" s="34" t="s">
         <v>482</v>
       </c>
-      <c r="F5" s="29" t="s">
+      <c r="G5" s="29" t="s">
         <v>479</v>
       </c>
-      <c r="G5" s="32" t="s">
+      <c r="H5" s="32" t="s">
         <v>475</v>
       </c>
-      <c r="H5" s="36" t="s">
+      <c r="I5" s="36" t="s">
         <v>466</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="32" x14ac:dyDescent="0.2">
-      <c r="A6" s="29" t="s">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>15</v>
+      </c>
+      <c r="B6" s="29" t="s">
         <v>70</v>
       </c>
-      <c r="B6" s="16" t="s">
-        <v>18</v>
-      </c>
-      <c r="C6" s="9" t="s">
+      <c r="C6" s="46" t="s">
+        <v>498</v>
+      </c>
+      <c r="D6" s="9" t="s">
         <v>453</v>
       </c>
-      <c r="D6" s="12" t="s">
+      <c r="E6" s="12" t="s">
         <v>454</v>
       </c>
-      <c r="E6" s="34" t="s">
+      <c r="F6" s="34" t="s">
         <v>482</v>
       </c>
-      <c r="F6" s="29" t="s">
+      <c r="G6" s="29" t="s">
         <v>479</v>
       </c>
-      <c r="G6" s="32" t="s">
+      <c r="H6" s="32" t="s">
         <v>476</v>
       </c>
-      <c r="H6" s="36" t="s">
+      <c r="I6" s="36" t="s">
         <v>467</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="29" t="s">
+    <row r="7" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>15</v>
+      </c>
+      <c r="B7" s="29" t="s">
         <v>378</v>
       </c>
-      <c r="B7" s="16" t="s">
-        <v>18</v>
-      </c>
-      <c r="C7" s="9" t="s">
+      <c r="C7" s="46" t="s">
+        <v>499</v>
+      </c>
+      <c r="D7" s="9" t="s">
         <v>453</v>
       </c>
-      <c r="D7" s="12" t="s">
+      <c r="E7" s="12" t="s">
         <v>454</v>
       </c>
-      <c r="E7" s="34" t="s">
+      <c r="F7" s="34" t="s">
         <v>483</v>
       </c>
-      <c r="F7" s="29" t="s">
+      <c r="G7" s="29" t="s">
         <v>480</v>
       </c>
-      <c r="G7" s="32" t="s">
+      <c r="H7" s="32" t="s">
         <v>477</v>
       </c>
-      <c r="H7" s="36" t="s">
+      <c r="I7" s="36" t="s">
         <v>468</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A8" s="29" t="s">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>15</v>
+      </c>
+      <c r="B8" s="29" t="s">
         <v>340</v>
       </c>
-      <c r="B8" s="29" t="s">
+      <c r="C8" s="29" t="s">
         <v>488</v>
       </c>
-      <c r="C8" s="9" t="s">
+      <c r="D8" s="9" t="s">
         <v>453</v>
       </c>
-      <c r="D8" s="12" t="s">
+      <c r="E8" s="12" t="s">
         <v>454</v>
       </c>
-      <c r="E8" s="34" t="s">
+      <c r="F8" s="34" t="s">
         <v>484</v>
       </c>
-      <c r="F8" s="29" t="s">
+      <c r="G8" s="29" t="s">
         <v>481</v>
       </c>
-      <c r="G8" s="32" t="s">
+      <c r="H8" s="32" t="s">
         <v>477</v>
       </c>
-      <c r="H8" s="36" t="s">
+      <c r="I8" s="36" t="s">
         <v>469</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A9" s="29" t="s">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>15</v>
+      </c>
+      <c r="B9" s="29" t="s">
         <v>490</v>
       </c>
-      <c r="B9" s="29" t="s">
-        <v>14</v>
-      </c>
-      <c r="C9" s="9" t="s">
+      <c r="C9" s="29" t="s">
+        <v>14</v>
+      </c>
+      <c r="D9" s="9" t="s">
         <v>453</v>
       </c>
-      <c r="D9" s="12" t="s">
+      <c r="E9" s="12" t="s">
         <v>454</v>
       </c>
-      <c r="E9" s="34" t="s">
+      <c r="F9" s="34" t="s">
         <v>485</v>
       </c>
-      <c r="F9" s="29" t="s">
+      <c r="G9" s="29" t="s">
         <v>479</v>
       </c>
-      <c r="G9" s="32" t="s">
+      <c r="H9" s="32" t="s">
         <v>474</v>
       </c>
-      <c r="H9" s="36" t="s">
+      <c r="I9" s="36" t="s">
         <v>470</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A10" s="29" t="s">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>15</v>
+      </c>
+      <c r="B10" s="29" t="s">
         <v>490</v>
       </c>
-      <c r="B10" s="29" t="s">
-        <v>14</v>
-      </c>
-      <c r="C10" s="9" t="s">
+      <c r="C10" s="29" t="s">
+        <v>14</v>
+      </c>
+      <c r="D10" s="9" t="s">
         <v>453</v>
       </c>
-      <c r="D10" s="12" t="s">
+      <c r="E10" s="12" t="s">
         <v>454</v>
       </c>
-      <c r="E10" s="34" t="s">
+      <c r="F10" s="34" t="s">
         <v>485</v>
       </c>
-      <c r="F10" s="29" t="s">
+      <c r="G10" s="29" t="s">
         <v>479</v>
       </c>
-      <c r="G10" s="32" t="s">
+      <c r="H10" s="32" t="s">
         <v>478</v>
       </c>
-      <c r="H10" s="36" t="s">
+      <c r="I10" s="36" t="s">
         <v>471</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A11" s="29" t="s">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>15</v>
+      </c>
+      <c r="B11" s="29" t="s">
         <v>490</v>
       </c>
-      <c r="B11" s="29" t="s">
-        <v>14</v>
-      </c>
-      <c r="C11" s="9" t="s">
+      <c r="C11" s="29" t="s">
+        <v>14</v>
+      </c>
+      <c r="D11" s="9" t="s">
         <v>453</v>
       </c>
-      <c r="D11" s="12" t="s">
+      <c r="E11" s="12" t="s">
         <v>454</v>
       </c>
-      <c r="E11" s="34" t="s">
+      <c r="F11" s="34" t="s">
         <v>484</v>
       </c>
-      <c r="F11" s="29" t="s">
+      <c r="G11" s="29" t="s">
         <v>481</v>
       </c>
-      <c r="G11" s="32" t="s">
+      <c r="H11" s="32" t="s">
         <v>474</v>
       </c>
-      <c r="H11" s="36" t="s">
+      <c r="I11" s="36" t="s">
         <v>470</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A12" s="29" t="s">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>15</v>
+      </c>
+      <c r="B12" s="29" t="s">
         <v>490</v>
       </c>
-      <c r="B12" s="29" t="s">
-        <v>14</v>
-      </c>
-      <c r="C12" s="9" t="s">
+      <c r="C12" s="29" t="s">
+        <v>14</v>
+      </c>
+      <c r="D12" s="9" t="s">
         <v>453</v>
       </c>
-      <c r="D12" s="12" t="s">
+      <c r="E12" s="12" t="s">
         <v>454</v>
       </c>
-      <c r="E12" s="34" t="s">
+      <c r="F12" s="34" t="s">
         <v>484</v>
       </c>
-      <c r="F12" s="29" t="s">
+      <c r="G12" s="29" t="s">
         <v>481</v>
       </c>
-      <c r="G12" s="32" t="s">
+      <c r="H12" s="32" t="s">
         <v>478</v>
       </c>
-      <c r="H12" s="36" t="s">
+      <c r="I12" s="36" t="s">
         <v>471</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A13" s="29" t="s">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>15</v>
+      </c>
+      <c r="B13" s="29" t="s">
         <v>490</v>
       </c>
-      <c r="B13" s="29" t="s">
-        <v>14</v>
-      </c>
-      <c r="C13" s="9" t="s">
+      <c r="C13" s="29" t="s">
+        <v>14</v>
+      </c>
+      <c r="D13" s="9" t="s">
         <v>453</v>
       </c>
-      <c r="D13" s="12" t="s">
+      <c r="E13" s="12" t="s">
         <v>454</v>
       </c>
-      <c r="E13" s="34" t="s">
+      <c r="F13" s="34" t="s">
         <v>482</v>
       </c>
-      <c r="F13" s="29" t="s">
+      <c r="G13" s="29" t="s">
         <v>479</v>
       </c>
-      <c r="G13" s="32" t="s">
+      <c r="H13" s="32" t="s">
         <v>476</v>
       </c>
-      <c r="H13" s="36" t="s">
+      <c r="I13" s="36" t="s">
         <v>472</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="C1:C2"/>
     <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:G1"/>
+    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="A1:C1"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="B3" r:id="rId1" xr:uid="{14FB7D38-448E-AA47-96C8-218AD71E39DE}"/>
+    <hyperlink ref="C3" r:id="rId1" xr:uid="{874F85A3-4034-F342-A238-3C6C105EDDFF}"/>
+    <hyperlink ref="C4" r:id="rId2" xr:uid="{1C64C6FD-8B50-6245-997F-968B297FEEC2}"/>
+    <hyperlink ref="C5" r:id="rId3" xr:uid="{A6BA2E7F-86EA-FA49-9787-2A7E5E89DBED}"/>
+    <hyperlink ref="C6" r:id="rId4" xr:uid="{B3F451CE-B3A7-7D4C-A39F-141164669B03}"/>
+    <hyperlink ref="C7" r:id="rId5" xr:uid="{FE91FE14-86EA-D940-9810-DB116C640F48}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -9413,26 +9471,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="80b53ead-ac38-442a-b597-5a0e2e0802cd">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="5ec1cc48-4270-4222-9ed5-54ce9e59d47b" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010050398B8EA2737947995C227484EA02C8" ma:contentTypeVersion="17" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="bc9a2575e6c24a964f45b6e1606b04fd">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="80b53ead-ac38-442a-b597-5a0e2e0802cd" xmlns:ns3="5ec1cc48-4270-4222-9ed5-54ce9e59d47b" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="662112485a0135ca1785eae0908ad389" ns2:_="" ns3:_="">
     <xsd:import namespace="80b53ead-ac38-442a-b597-5a0e2e0802cd"/>
@@ -9669,10 +9707,41 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="80b53ead-ac38-442a-b597-5a0e2e0802cd">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="5ec1cc48-4270-4222-9ed5-54ce9e59d47b" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3B1B5D08-A2EB-4F47-BA81-DA28AA2A09F4}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{72DD370E-74FD-4D33-B5A7-49A7FE6518F7}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="80b53ead-ac38-442a-b597-5a0e2e0802cd"/>
+    <ds:schemaRef ds:uri="5ec1cc48-4270-4222-9ed5-54ce9e59d47b"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -9689,20 +9758,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{72DD370E-74FD-4D33-B5A7-49A7FE6518F7}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3B1B5D08-A2EB-4F47-BA81-DA28AA2A09F4}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="80b53ead-ac38-442a-b597-5a0e2e0802cd"/>
-    <ds:schemaRef ds:uri="5ec1cc48-4270-4222-9ed5-54ce9e59d47b"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/EEE2000-metadata_mapping.xlsx
+++ b/EEE2000-metadata_mapping.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rhys.r.evans/Documents/CEDA/CCI/cci_data_bridge_inputs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D494611D-C123-164E-A765-53DDDE64F688}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D78E3127-F843-E84D-AFA1-9FF9DDF6AAA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-31560" yWindow="1000" windowWidth="32520" windowHeight="17580" activeTab="1" xr2:uid="{B9DA58AC-C110-4CBA-A19B-6F37B44EEA38}"/>
+    <workbookView xWindow="-32520" yWindow="1000" windowWidth="32520" windowHeight="17580" activeTab="1" xr2:uid="{B9DA58AC-C110-4CBA-A19B-6F37B44EEA38}"/>
   </bookViews>
   <sheets>
     <sheet name="Mapping" sheetId="2" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1832" uniqueCount="500">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1832" uniqueCount="499">
   <si>
     <t>Dataset 1</t>
   </si>
@@ -1859,9 +1859,6 @@
   </si>
   <si>
     <t>User</t>
-  </si>
-  <si>
-    <t>https://catalogue.ceda.ac.uk/uuid/6429d1aafe1e43b9b414e4a5a7f8b903</t>
   </si>
   <si>
     <t>Data provider</t>
@@ -1886,7 +1883,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd;@"/>
   </numFmts>
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1933,6 +1930,12 @@
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Aptos Narrow"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF212529"/>
+      <name val="Calibri"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -2083,7 +2086,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="47">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -2153,9 +2156,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2177,10 +2178,13 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -2515,14 +2519,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="16" x14ac:dyDescent="0.2">
-      <c r="A1" s="37" t="s">
+      <c r="A1" s="45" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="37"/>
-      <c r="C1" s="37"/>
-      <c r="D1" s="37"/>
-      <c r="E1" s="37"/>
-      <c r="F1" s="45"/>
+      <c r="B1" s="45"/>
+      <c r="C1" s="45"/>
+      <c r="D1" s="45"/>
+      <c r="E1" s="45"/>
+      <c r="F1" s="46"/>
       <c r="G1" s="38" t="s">
         <v>1</v>
       </c>
@@ -8910,11 +8914,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="37" t="s">
+      <c r="A1" s="45" t="s">
         <v>493</v>
       </c>
-      <c r="B1" s="37"/>
-      <c r="C1" s="45"/>
+      <c r="B1" s="45"/>
+      <c r="C1" s="46"/>
       <c r="D1" s="38" t="s">
         <v>460</v>
       </c>
@@ -8930,7 +8934,7 @@
     </row>
     <row r="2" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>487</v>
@@ -8953,15 +8957,15 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>15</v>
+    <row r="3" spans="1:9" ht="32" x14ac:dyDescent="0.2">
+      <c r="A3" s="47" t="s">
+        <v>19</v>
       </c>
       <c r="B3" s="29" t="s">
         <v>489</v>
       </c>
-      <c r="C3" s="46" t="s">
-        <v>494</v>
+      <c r="C3" s="16" t="s">
+        <v>27</v>
       </c>
       <c r="D3" s="9" t="s">
         <v>453</v>
@@ -8989,8 +8993,8 @@
       <c r="B4" s="29" t="s">
         <v>489</v>
       </c>
-      <c r="C4" s="46" t="s">
-        <v>496</v>
+      <c r="C4" s="37" t="s">
+        <v>495</v>
       </c>
       <c r="D4" s="9" t="s">
         <v>453</v>
@@ -9018,8 +9022,8 @@
       <c r="B5" s="29" t="s">
         <v>70</v>
       </c>
-      <c r="C5" s="46" t="s">
-        <v>497</v>
+      <c r="C5" s="37" t="s">
+        <v>496</v>
       </c>
       <c r="D5" s="9" t="s">
         <v>453</v>
@@ -9047,8 +9051,8 @@
       <c r="B6" s="29" t="s">
         <v>70</v>
       </c>
-      <c r="C6" s="46" t="s">
-        <v>498</v>
+      <c r="C6" s="37" t="s">
+        <v>497</v>
       </c>
       <c r="D6" s="9" t="s">
         <v>453</v>
@@ -9076,8 +9080,8 @@
       <c r="B7" s="29" t="s">
         <v>378</v>
       </c>
-      <c r="C7" s="46" t="s">
-        <v>499</v>
+      <c r="C7" s="37" t="s">
+        <v>498</v>
       </c>
       <c r="D7" s="9" t="s">
         <v>453</v>
@@ -9280,11 +9284,11 @@
     <mergeCell ref="A1:C1"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="C3" r:id="rId1" xr:uid="{874F85A3-4034-F342-A238-3C6C105EDDFF}"/>
+    <hyperlink ref="C5" r:id="rId1" xr:uid="{A6BA2E7F-86EA-FA49-9787-2A7E5E89DBED}"/>
     <hyperlink ref="C4" r:id="rId2" xr:uid="{1C64C6FD-8B50-6245-997F-968B297FEEC2}"/>
-    <hyperlink ref="C5" r:id="rId3" xr:uid="{A6BA2E7F-86EA-FA49-9787-2A7E5E89DBED}"/>
-    <hyperlink ref="C6" r:id="rId4" xr:uid="{B3F451CE-B3A7-7D4C-A39F-141164669B03}"/>
-    <hyperlink ref="C7" r:id="rId5" xr:uid="{FE91FE14-86EA-D940-9810-DB116C640F48}"/>
+    <hyperlink ref="C6" r:id="rId3" xr:uid="{B3F451CE-B3A7-7D4C-A39F-141164669B03}"/>
+    <hyperlink ref="C7" r:id="rId4" xr:uid="{FE91FE14-86EA-D940-9810-DB116C640F48}"/>
+    <hyperlink ref="C3" r:id="rId5" xr:uid="{F1167C98-6699-1F41-9AB7-7B02A0685787}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -9471,6 +9475,26 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="80b53ead-ac38-442a-b597-5a0e2e0802cd">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="5ec1cc48-4270-4222-9ed5-54ce9e59d47b" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010050398B8EA2737947995C227484EA02C8" ma:contentTypeVersion="17" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="bc9a2575e6c24a964f45b6e1606b04fd">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="80b53ead-ac38-442a-b597-5a0e2e0802cd" xmlns:ns3="5ec1cc48-4270-4222-9ed5-54ce9e59d47b" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="662112485a0135ca1785eae0908ad389" ns2:_="" ns3:_="">
     <xsd:import namespace="80b53ead-ac38-442a-b597-5a0e2e0802cd"/>
@@ -9707,27 +9731,26 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="80b53ead-ac38-442a-b597-5a0e2e0802cd">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="5ec1cc48-4270-4222-9ed5-54ce9e59d47b" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3B1B5D08-A2EB-4F47-BA81-DA28AA2A09F4}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{66AF2240-620B-4312-9739-CAF731E4A98F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="80b53ead-ac38-442a-b597-5a0e2e0802cd"/>
+    <ds:schemaRef ds:uri="5ec1cc48-4270-4222-9ed5-54ce9e59d47b"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{72DD370E-74FD-4D33-B5A7-49A7FE6518F7}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -9744,23 +9767,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{66AF2240-620B-4312-9739-CAF731E4A98F}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="80b53ead-ac38-442a-b597-5a0e2e0802cd"/>
-    <ds:schemaRef ds:uri="5ec1cc48-4270-4222-9ed5-54ce9e59d47b"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3B1B5D08-A2EB-4F47-BA81-DA28AA2A09F4}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/EEE2000-metadata_mapping.xlsx
+++ b/EEE2000-metadata_mapping.xlsx
@@ -1,20 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10817"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10821"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rhys.r.evans/Documents/CEDA/CCI/cci_data_bridge_inputs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D78E3127-F843-E84D-AFA1-9FF9DDF6AAA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0AAB98B8-BC09-4544-B40F-5DB8A5DD5A44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-32520" yWindow="1000" windowWidth="32520" windowHeight="17580" activeTab="1" xr2:uid="{B9DA58AC-C110-4CBA-A19B-6F37B44EEA38}"/>
+    <workbookView xWindow="120" yWindow="2220" windowWidth="32520" windowHeight="17580" activeTab="1" xr2:uid="{B9DA58AC-C110-4CBA-A19B-6F37B44EEA38}"/>
   </bookViews>
   <sheets>
     <sheet name="Mapping" sheetId="2" r:id="rId1"/>
-    <sheet name="AI Mapping" sheetId="3" r:id="rId2"/>
+    <sheet name="Technique Mapping" sheetId="3" r:id="rId2"/>
     <sheet name="Relationship definitions" sheetId="1" r:id="rId3"/>
   </sheets>
   <definedNames>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1832" uniqueCount="499">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1834" uniqueCount="499">
   <si>
     <t>Dataset 1</t>
   </si>
@@ -1759,12 +1759,6 @@
     <t>Indicates A is used by B</t>
   </si>
   <si>
-    <t>Relationship (Dataset to AI Model)</t>
-  </si>
-  <si>
-    <t>Relationship (AI Model to Dataset)</t>
-  </si>
-  <si>
     <t>Type</t>
   </si>
   <si>
@@ -1795,9 +1789,6 @@
     <t>Emulate physical models</t>
   </si>
   <si>
-    <t>Classification of irrigation</t>
-  </si>
-  <si>
     <t>Modelling</t>
   </si>
   <si>
@@ -1864,16 +1855,25 @@
     <t>Data provider</t>
   </si>
   <si>
-    <t>https://catalogue.ceda.ac.uk/uuid/6429d1aafe1e43b9b414e4a5a7f8b904</t>
-  </si>
-  <si>
     <t>https://catalogue.ceda.ac.uk/uuid/db75c5f51ee240ae8743355dcebbb9b9</t>
   </si>
   <si>
-    <t>https://catalogue.ceda.ac.uk/uuid/db75c5f51ee240ae8743355dcebbb9b10</t>
-  </si>
-  <si>
     <t>https://catalogue.ceda.ac.uk/uuid/8d02d224437247f6a6270a575d457bd8</t>
+  </si>
+  <si>
+    <t>Relationship (User to Technique)</t>
+  </si>
+  <si>
+    <t>Relationship (Technique to User)</t>
+  </si>
+  <si>
+    <t>Technique</t>
+  </si>
+  <si>
+    <t>Sub Type</t>
+  </si>
+  <si>
+    <t>https://catalogue.ceda.ac.uk/uuid/6429d1aafe1e43b9b414e4a5a7f8b903</t>
   </si>
 </sst>
 </file>
@@ -1883,7 +1883,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd;@"/>
   </numFmts>
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1933,10 +1933,33 @@
       <family val="2"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FF212529"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF467886"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="5">
@@ -2047,25 +2070,23 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top/>
       <bottom/>
       <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </left>
       <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -2073,11 +2094,9 @@
         <color indexed="64"/>
       </left>
       <right style="thin">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
+      <top/>
       <bottom/>
       <diagonal/>
     </border>
@@ -2086,7 +2105,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="48">
+  <cellXfs count="54">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -2140,23 +2159,9 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2169,22 +2174,52 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -2519,18 +2554,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="16" x14ac:dyDescent="0.2">
-      <c r="A1" s="45" t="s">
+      <c r="A1" s="34" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="45"/>
-      <c r="C1" s="45"/>
-      <c r="D1" s="45"/>
-      <c r="E1" s="45"/>
-      <c r="F1" s="46"/>
-      <c r="G1" s="38" t="s">
+      <c r="B1" s="34"/>
+      <c r="C1" s="34"/>
+      <c r="D1" s="34"/>
+      <c r="E1" s="34"/>
+      <c r="F1" s="35"/>
+      <c r="G1" s="30" t="s">
         <v>1</v>
       </c>
-      <c r="H1" s="40" t="s">
+      <c r="H1" s="32" t="s">
         <v>2</v>
       </c>
       <c r="I1" s="14" t="s">
@@ -2559,8 +2594,8 @@
       <c r="F2" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="G2" s="39"/>
-      <c r="H2" s="41"/>
+      <c r="G2" s="31"/>
+      <c r="H2" s="33"/>
       <c r="I2" s="15" t="s">
         <v>10</v>
       </c>
@@ -8900,7 +8935,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C17FE217-AB61-B742-BFE0-33900D1BEC91}">
-  <dimension ref="A1:I13"/>
+  <dimension ref="A1:J12"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="16.33203125" customWidth="1"/>
@@ -8911,384 +8946,389 @@
     <col min="6" max="7" width="17.33203125" customWidth="1"/>
     <col min="8" max="8" width="16.5" customWidth="1"/>
     <col min="9" max="9" width="33.5" customWidth="1"/>
+    <col min="10" max="10" width="30.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="45" t="s">
+    <row r="1" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="47" t="s">
+        <v>490</v>
+      </c>
+      <c r="B1" s="47"/>
+      <c r="C1" s="48"/>
+      <c r="D1" s="49" t="s">
+        <v>494</v>
+      </c>
+      <c r="E1" s="50" t="s">
+        <v>495</v>
+      </c>
+      <c r="F1" s="51" t="s">
+        <v>496</v>
+      </c>
+      <c r="G1" s="52"/>
+      <c r="H1" s="52"/>
+      <c r="I1" s="53"/>
+      <c r="J1" s="36"/>
+    </row>
+    <row r="2" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="37" t="s">
+        <v>491</v>
+      </c>
+      <c r="B2" s="37" t="s">
+        <v>484</v>
+      </c>
+      <c r="C2" s="37" t="s">
+        <v>483</v>
+      </c>
+      <c r="D2" s="49"/>
+      <c r="E2" s="50"/>
+      <c r="F2" s="38" t="s">
+        <v>460</v>
+      </c>
+      <c r="G2" s="39" t="s">
+        <v>497</v>
+      </c>
+      <c r="H2" s="37" t="s">
+        <v>461</v>
+      </c>
+      <c r="I2" s="40" t="s">
+        <v>489</v>
+      </c>
+      <c r="J2" s="41" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A3" s="42" t="s">
+        <v>19</v>
+      </c>
+      <c r="B3" s="27" t="s">
+        <v>486</v>
+      </c>
+      <c r="C3" s="10" t="s">
+        <v>498</v>
+      </c>
+      <c r="D3" s="44" t="s">
+        <v>453</v>
+      </c>
+      <c r="E3" s="45" t="s">
+        <v>454</v>
+      </c>
+      <c r="F3" s="46" t="s">
+        <v>488</v>
+      </c>
+      <c r="G3" s="27" t="s">
+        <v>479</v>
+      </c>
+      <c r="H3" s="27" t="s">
+        <v>476</v>
+      </c>
+      <c r="I3" s="28" t="s">
+        <v>470</v>
+      </c>
+      <c r="J3" s="29" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A4" s="42" t="s">
+        <v>19</v>
+      </c>
+      <c r="B4" s="27" t="s">
+        <v>486</v>
+      </c>
+      <c r="C4" s="10" t="s">
+        <v>498</v>
+      </c>
+      <c r="D4" s="44" t="s">
+        <v>453</v>
+      </c>
+      <c r="E4" s="45" t="s">
+        <v>454</v>
+      </c>
+      <c r="F4" s="46" t="s">
+        <v>488</v>
+      </c>
+      <c r="G4" s="27" t="s">
+        <v>479</v>
+      </c>
+      <c r="H4" s="27" t="s">
+        <v>476</v>
+      </c>
+      <c r="I4" s="28" t="s">
+        <v>471</v>
+      </c>
+      <c r="J4" s="29" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A5" s="42" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="27" t="s">
+        <v>70</v>
+      </c>
+      <c r="C5" s="10" t="s">
+        <v>492</v>
+      </c>
+      <c r="D5" s="44" t="s">
+        <v>453</v>
+      </c>
+      <c r="E5" s="45" t="s">
+        <v>454</v>
+      </c>
+      <c r="F5" s="46" t="s">
+        <v>488</v>
+      </c>
+      <c r="G5" s="27" t="s">
+        <v>479</v>
+      </c>
+      <c r="H5" s="27" t="s">
+        <v>476</v>
+      </c>
+      <c r="I5" s="28" t="s">
+        <v>472</v>
+      </c>
+      <c r="J5" s="29" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A6" s="42" t="s">
+        <v>19</v>
+      </c>
+      <c r="B6" s="27" t="s">
+        <v>70</v>
+      </c>
+      <c r="C6" s="10" t="s">
+        <v>492</v>
+      </c>
+      <c r="D6" s="44" t="s">
+        <v>453</v>
+      </c>
+      <c r="E6" s="45" t="s">
+        <v>454</v>
+      </c>
+      <c r="F6" s="46" t="s">
+        <v>488</v>
+      </c>
+      <c r="G6" s="27" t="s">
+        <v>479</v>
+      </c>
+      <c r="H6" s="27" t="s">
+        <v>476</v>
+      </c>
+      <c r="I6" s="28" t="s">
+        <v>473</v>
+      </c>
+      <c r="J6" s="29" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="42" t="s">
+        <v>19</v>
+      </c>
+      <c r="B7" s="27" t="s">
+        <v>378</v>
+      </c>
+      <c r="C7" s="43" t="s">
         <v>493</v>
       </c>
-      <c r="B1" s="45"/>
-      <c r="C1" s="46"/>
-      <c r="D1" s="38" t="s">
-        <v>460</v>
-      </c>
-      <c r="E1" s="40" t="s">
-        <v>461</v>
-      </c>
-      <c r="F1" s="42" t="s">
-        <v>491</v>
-      </c>
-      <c r="G1" s="43"/>
-      <c r="H1" s="44"/>
-      <c r="I1" s="27"/>
-    </row>
-    <row r="2" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="2" t="s">
-        <v>494</v>
-      </c>
-      <c r="B2" s="2" t="s">
+      <c r="D7" s="44" t="s">
+        <v>453</v>
+      </c>
+      <c r="E7" s="45" t="s">
+        <v>454</v>
+      </c>
+      <c r="F7" s="46" t="s">
+        <v>488</v>
+      </c>
+      <c r="G7" s="27" t="s">
+        <v>480</v>
+      </c>
+      <c r="H7" s="27" t="s">
+        <v>477</v>
+      </c>
+      <c r="I7" s="28" t="s">
+        <v>474</v>
+      </c>
+      <c r="J7" s="29" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A8" s="42" t="s">
+        <v>19</v>
+      </c>
+      <c r="B8" s="27" t="s">
+        <v>340</v>
+      </c>
+      <c r="C8" s="27" t="s">
+        <v>485</v>
+      </c>
+      <c r="D8" s="44" t="s">
+        <v>453</v>
+      </c>
+      <c r="E8" s="45" t="s">
+        <v>454</v>
+      </c>
+      <c r="F8" s="46" t="s">
+        <v>488</v>
+      </c>
+      <c r="G8" s="27" t="s">
+        <v>481</v>
+      </c>
+      <c r="H8" s="27" t="s">
+        <v>478</v>
+      </c>
+      <c r="I8" s="28" t="s">
+        <v>474</v>
+      </c>
+      <c r="J8" s="29" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A9" s="42" t="s">
+        <v>19</v>
+      </c>
+      <c r="B9" s="27" t="s">
         <v>487</v>
       </c>
-      <c r="C2" s="2" t="s">
-        <v>486</v>
-      </c>
-      <c r="D2" s="39"/>
-      <c r="E2" s="41"/>
-      <c r="F2" s="30" t="s">
-        <v>462</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>463</v>
-      </c>
-      <c r="H2" s="5" t="s">
-        <v>492</v>
-      </c>
-      <c r="I2" s="28" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" ht="32" x14ac:dyDescent="0.2">
-      <c r="A3" s="47" t="s">
-        <v>19</v>
-      </c>
-      <c r="B3" s="29" t="s">
-        <v>489</v>
-      </c>
-      <c r="C3" s="16" t="s">
-        <v>27</v>
-      </c>
-      <c r="D3" s="9" t="s">
+      <c r="C9" s="27" t="s">
+        <v>485</v>
+      </c>
+      <c r="D9" s="44" t="s">
         <v>453</v>
       </c>
-      <c r="E3" s="12" t="s">
+      <c r="E9" s="45" t="s">
         <v>454</v>
       </c>
-      <c r="F3" s="33" t="s">
+      <c r="F9" s="46" t="s">
+        <v>488</v>
+      </c>
+      <c r="G9" s="27" t="s">
         <v>482</v>
       </c>
-      <c r="G3" s="29" t="s">
-        <v>479</v>
-      </c>
-      <c r="H3" s="31" t="s">
-        <v>473</v>
-      </c>
-      <c r="I3" s="35" t="s">
-        <v>464</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
-        <v>15</v>
-      </c>
-      <c r="B4" s="29" t="s">
-        <v>489</v>
-      </c>
-      <c r="C4" s="37" t="s">
-        <v>495</v>
-      </c>
-      <c r="D4" s="9" t="s">
+      <c r="H9" s="27" t="s">
+        <v>476</v>
+      </c>
+      <c r="I9" s="28" t="s">
+        <v>471</v>
+      </c>
+      <c r="J9" s="29" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A10" s="42" t="s">
+        <v>19</v>
+      </c>
+      <c r="B10" s="27" t="s">
+        <v>487</v>
+      </c>
+      <c r="C10" s="27" t="s">
+        <v>485</v>
+      </c>
+      <c r="D10" s="44" t="s">
         <v>453</v>
       </c>
-      <c r="E4" s="12" t="s">
+      <c r="E10" s="45" t="s">
         <v>454</v>
       </c>
-      <c r="F4" s="34" t="s">
+      <c r="F10" s="46" t="s">
+        <v>488</v>
+      </c>
+      <c r="G10" s="27" t="s">
         <v>482</v>
       </c>
-      <c r="G4" s="29" t="s">
-        <v>479</v>
-      </c>
-      <c r="H4" s="32" t="s">
-        <v>474</v>
-      </c>
-      <c r="I4" s="36" t="s">
-        <v>465</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
-        <v>15</v>
-      </c>
-      <c r="B5" s="29" t="s">
-        <v>70</v>
-      </c>
-      <c r="C5" s="37" t="s">
-        <v>496</v>
-      </c>
-      <c r="D5" s="9" t="s">
+      <c r="H10" s="27" t="s">
+        <v>476</v>
+      </c>
+      <c r="I10" s="28" t="s">
+        <v>475</v>
+      </c>
+      <c r="J10" s="29" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A11" s="42" t="s">
+        <v>19</v>
+      </c>
+      <c r="B11" s="27" t="s">
+        <v>487</v>
+      </c>
+      <c r="C11" s="27" t="s">
+        <v>485</v>
+      </c>
+      <c r="D11" s="44" t="s">
         <v>453</v>
       </c>
-      <c r="E5" s="12" t="s">
+      <c r="E11" s="45" t="s">
         <v>454</v>
       </c>
-      <c r="F5" s="34" t="s">
-        <v>482</v>
-      </c>
-      <c r="G5" s="29" t="s">
-        <v>479</v>
-      </c>
-      <c r="H5" s="32" t="s">
+      <c r="F11" s="46" t="s">
+        <v>488</v>
+      </c>
+      <c r="G11" s="27" t="s">
+        <v>481</v>
+      </c>
+      <c r="H11" s="27" t="s">
+        <v>478</v>
+      </c>
+      <c r="I11" s="28" t="s">
+        <v>471</v>
+      </c>
+      <c r="J11" s="29" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A12" s="42" t="s">
+        <v>19</v>
+      </c>
+      <c r="B12" s="27" t="s">
+        <v>487</v>
+      </c>
+      <c r="C12" s="27" t="s">
+        <v>485</v>
+      </c>
+      <c r="D12" s="44" t="s">
+        <v>453</v>
+      </c>
+      <c r="E12" s="45" t="s">
+        <v>454</v>
+      </c>
+      <c r="F12" s="46" t="s">
+        <v>488</v>
+      </c>
+      <c r="G12" s="27" t="s">
+        <v>481</v>
+      </c>
+      <c r="H12" s="27" t="s">
+        <v>478</v>
+      </c>
+      <c r="I12" s="28" t="s">
         <v>475</v>
       </c>
-      <c r="I5" s="36" t="s">
-        <v>466</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
-        <v>15</v>
-      </c>
-      <c r="B6" s="29" t="s">
-        <v>70</v>
-      </c>
-      <c r="C6" s="37" t="s">
-        <v>497</v>
-      </c>
-      <c r="D6" s="9" t="s">
-        <v>453</v>
-      </c>
-      <c r="E6" s="12" t="s">
-        <v>454</v>
-      </c>
-      <c r="F6" s="34" t="s">
-        <v>482</v>
-      </c>
-      <c r="G6" s="29" t="s">
-        <v>479</v>
-      </c>
-      <c r="H6" s="32" t="s">
-        <v>476</v>
-      </c>
-      <c r="I6" s="36" t="s">
-        <v>467</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" t="s">
-        <v>15</v>
-      </c>
-      <c r="B7" s="29" t="s">
-        <v>378</v>
-      </c>
-      <c r="C7" s="37" t="s">
-        <v>498</v>
-      </c>
-      <c r="D7" s="9" t="s">
-        <v>453</v>
-      </c>
-      <c r="E7" s="12" t="s">
-        <v>454</v>
-      </c>
-      <c r="F7" s="34" t="s">
-        <v>483</v>
-      </c>
-      <c r="G7" s="29" t="s">
-        <v>480</v>
-      </c>
-      <c r="H7" s="32" t="s">
-        <v>477</v>
-      </c>
-      <c r="I7" s="36" t="s">
-        <v>468</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A8" t="s">
-        <v>15</v>
-      </c>
-      <c r="B8" s="29" t="s">
-        <v>340</v>
-      </c>
-      <c r="C8" s="29" t="s">
-        <v>488</v>
-      </c>
-      <c r="D8" s="9" t="s">
-        <v>453</v>
-      </c>
-      <c r="E8" s="12" t="s">
-        <v>454</v>
-      </c>
-      <c r="F8" s="34" t="s">
-        <v>484</v>
-      </c>
-      <c r="G8" s="29" t="s">
-        <v>481</v>
-      </c>
-      <c r="H8" s="32" t="s">
-        <v>477</v>
-      </c>
-      <c r="I8" s="36" t="s">
+      <c r="J12" s="29" t="s">
         <v>469</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A9" t="s">
-        <v>15</v>
-      </c>
-      <c r="B9" s="29" t="s">
-        <v>490</v>
-      </c>
-      <c r="C9" s="29" t="s">
-        <v>14</v>
-      </c>
-      <c r="D9" s="9" t="s">
-        <v>453</v>
-      </c>
-      <c r="E9" s="12" t="s">
-        <v>454</v>
-      </c>
-      <c r="F9" s="34" t="s">
-        <v>485</v>
-      </c>
-      <c r="G9" s="29" t="s">
-        <v>479</v>
-      </c>
-      <c r="H9" s="32" t="s">
-        <v>474</v>
-      </c>
-      <c r="I9" s="36" t="s">
-        <v>470</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A10" t="s">
-        <v>15</v>
-      </c>
-      <c r="B10" s="29" t="s">
-        <v>490</v>
-      </c>
-      <c r="C10" s="29" t="s">
-        <v>14</v>
-      </c>
-      <c r="D10" s="9" t="s">
-        <v>453</v>
-      </c>
-      <c r="E10" s="12" t="s">
-        <v>454</v>
-      </c>
-      <c r="F10" s="34" t="s">
-        <v>485</v>
-      </c>
-      <c r="G10" s="29" t="s">
-        <v>479</v>
-      </c>
-      <c r="H10" s="32" t="s">
-        <v>478</v>
-      </c>
-      <c r="I10" s="36" t="s">
-        <v>471</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A11" t="s">
-        <v>15</v>
-      </c>
-      <c r="B11" s="29" t="s">
-        <v>490</v>
-      </c>
-      <c r="C11" s="29" t="s">
-        <v>14</v>
-      </c>
-      <c r="D11" s="9" t="s">
-        <v>453</v>
-      </c>
-      <c r="E11" s="12" t="s">
-        <v>454</v>
-      </c>
-      <c r="F11" s="34" t="s">
-        <v>484</v>
-      </c>
-      <c r="G11" s="29" t="s">
-        <v>481</v>
-      </c>
-      <c r="H11" s="32" t="s">
-        <v>474</v>
-      </c>
-      <c r="I11" s="36" t="s">
-        <v>470</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A12" t="s">
-        <v>15</v>
-      </c>
-      <c r="B12" s="29" t="s">
-        <v>490</v>
-      </c>
-      <c r="C12" s="29" t="s">
-        <v>14</v>
-      </c>
-      <c r="D12" s="9" t="s">
-        <v>453</v>
-      </c>
-      <c r="E12" s="12" t="s">
-        <v>454</v>
-      </c>
-      <c r="F12" s="34" t="s">
-        <v>484</v>
-      </c>
-      <c r="G12" s="29" t="s">
-        <v>481</v>
-      </c>
-      <c r="H12" s="32" t="s">
-        <v>478</v>
-      </c>
-      <c r="I12" s="36" t="s">
-        <v>471</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A13" t="s">
-        <v>15</v>
-      </c>
-      <c r="B13" s="29" t="s">
-        <v>490</v>
-      </c>
-      <c r="C13" s="29" t="s">
-        <v>14</v>
-      </c>
-      <c r="D13" s="9" t="s">
-        <v>453</v>
-      </c>
-      <c r="E13" s="12" t="s">
-        <v>454</v>
-      </c>
-      <c r="F13" s="34" t="s">
-        <v>482</v>
-      </c>
-      <c r="G13" s="29" t="s">
-        <v>479</v>
-      </c>
-      <c r="H13" s="32" t="s">
-        <v>476</v>
-      </c>
-      <c r="I13" s="36" t="s">
-        <v>472</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="D1:D2"/>
     <mergeCell ref="E1:E2"/>
-    <mergeCell ref="F1:H1"/>
     <mergeCell ref="A1:C1"/>
+    <mergeCell ref="F1:I1"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="C5" r:id="rId1" xr:uid="{A6BA2E7F-86EA-FA49-9787-2A7E5E89DBED}"/>
-    <hyperlink ref="C4" r:id="rId2" xr:uid="{1C64C6FD-8B50-6245-997F-968B297FEEC2}"/>
-    <hyperlink ref="C6" r:id="rId3" xr:uid="{B3F451CE-B3A7-7D4C-A39F-141164669B03}"/>
-    <hyperlink ref="C7" r:id="rId4" xr:uid="{FE91FE14-86EA-D940-9810-DB116C640F48}"/>
-    <hyperlink ref="C3" r:id="rId5" xr:uid="{F1167C98-6699-1F41-9AB7-7B02A0685787}"/>
+    <hyperlink ref="C3" r:id="rId1" xr:uid="{E7EBFD69-AB42-1D4C-B09F-BC06AC0B1941}"/>
+    <hyperlink ref="C4" r:id="rId2" xr:uid="{19F34C30-987C-8A4F-A400-AB95B6919C72}"/>
+    <hyperlink ref="C5" r:id="rId3" xr:uid="{EB4AB897-0111-9A4F-A836-A7EA2313DA8B}"/>
+    <hyperlink ref="C6" r:id="rId4" xr:uid="{849BF08E-F4EA-6945-93EA-AD080F320746}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -9475,26 +9515,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="80b53ead-ac38-442a-b597-5a0e2e0802cd">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="5ec1cc48-4270-4222-9ed5-54ce9e59d47b" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010050398B8EA2737947995C227484EA02C8" ma:contentTypeVersion="17" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="bc9a2575e6c24a964f45b6e1606b04fd">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="80b53ead-ac38-442a-b597-5a0e2e0802cd" xmlns:ns3="5ec1cc48-4270-4222-9ed5-54ce9e59d47b" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="662112485a0135ca1785eae0908ad389" ns2:_="" ns3:_="">
     <xsd:import namespace="80b53ead-ac38-442a-b597-5a0e2e0802cd"/>
@@ -9731,10 +9751,41 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="80b53ead-ac38-442a-b597-5a0e2e0802cd">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="5ec1cc48-4270-4222-9ed5-54ce9e59d47b" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3B1B5D08-A2EB-4F47-BA81-DA28AA2A09F4}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{72DD370E-74FD-4D33-B5A7-49A7FE6518F7}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="80b53ead-ac38-442a-b597-5a0e2e0802cd"/>
+    <ds:schemaRef ds:uri="5ec1cc48-4270-4222-9ed5-54ce9e59d47b"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -9751,20 +9802,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{72DD370E-74FD-4D33-B5A7-49A7FE6518F7}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3B1B5D08-A2EB-4F47-BA81-DA28AA2A09F4}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="80b53ead-ac38-442a-b597-5a0e2e0802cd"/>
-    <ds:schemaRef ds:uri="5ec1cc48-4270-4222-9ed5-54ce9e59d47b"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/EEE2000-metadata_mapping.xlsx
+++ b/EEE2000-metadata_mapping.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10821"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rhys.r.evans/Documents/CEDA/CCI/cci_data_bridge_inputs/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://stfc365-my.sharepoint.com/personal/alison_waterfall_stfc_ac_uk/Documents/Documents/GitHub/cci_data_bridge_inputs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0AAB98B8-BC09-4544-B40F-5DB8A5DD5A44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{0AAB98B8-BC09-4544-B40F-5DB8A5DD5A44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0C817DEB-570A-4AB7-A3FA-074D47EFF721}"/>
   <bookViews>
-    <workbookView xWindow="120" yWindow="2220" windowWidth="32520" windowHeight="17580" activeTab="1" xr2:uid="{B9DA58AC-C110-4CBA-A19B-6F37B44EEA38}"/>
+    <workbookView xWindow="42060" yWindow="4590" windowWidth="28800" windowHeight="15345" activeTab="1" xr2:uid="{B9DA58AC-C110-4CBA-A19B-6F37B44EEA38}"/>
   </bookViews>
   <sheets>
     <sheet name="Mapping" sheetId="2" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1834" uniqueCount="499">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2424" uniqueCount="591">
   <si>
     <t>Dataset 1</t>
   </si>
@@ -1874,6 +1874,282 @@
   </si>
   <si>
     <t>https://catalogue.ceda.ac.uk/uuid/6429d1aafe1e43b9b414e4a5a7f8b903</t>
+  </si>
+  <si>
+    <t>Light Gradient Boosting</t>
+  </si>
+  <si>
+    <t>Bias correction</t>
+  </si>
+  <si>
+    <t>Retrieval of dust</t>
+  </si>
+  <si>
+    <t>Classification of irrigation</t>
+  </si>
+  <si>
+    <t>Cloud mask</t>
+  </si>
+  <si>
+    <t>Determine cloud parameters</t>
+  </si>
+  <si>
+    <t>Convolutional Neural Network</t>
+  </si>
+  <si>
+    <t>Deep Learning – convolutional neural networks</t>
+  </si>
+  <si>
+    <t>Combining SAR and optical</t>
+  </si>
+  <si>
+    <t>Uncertainty classification probabilities</t>
+  </si>
+  <si>
+    <t>GHGs</t>
+  </si>
+  <si>
+    <t>Cloud coverage pre-filtering</t>
+  </si>
+  <si>
+    <t>Quality-filtering and predicting bias</t>
+  </si>
+  <si>
+    <t>Extreme Gradient Boosting</t>
+  </si>
+  <si>
+    <t>Quality-filtering</t>
+  </si>
+  <si>
+    <t>HRLC</t>
+  </si>
+  <si>
+    <t>K-means clustering</t>
+  </si>
+  <si>
+    <t>Binary water extraction from SAR</t>
+  </si>
+  <si>
+    <t>Weak Supervision</t>
+  </si>
+  <si>
+    <t>Pretraining classification with thematic maps</t>
+  </si>
+  <si>
+    <t>Siamese Multi-Layer Perceptron</t>
+  </si>
+  <si>
+    <t>Deep Learning – feed-forward neural networks</t>
+  </si>
+  <si>
+    <t>Decision fusion between optical and SAR</t>
+  </si>
+  <si>
+    <t>Vision Transformer</t>
+  </si>
+  <si>
+    <t>Deep Learning – transformers</t>
+  </si>
+  <si>
+    <t>Classification of land cover from optical</t>
+  </si>
+  <si>
+    <t>Encoder-Decoder Transformer</t>
+  </si>
+  <si>
+    <t>Classification of land cover from SAR</t>
+  </si>
+  <si>
+    <t>Ice Sheets (Antarctica)</t>
+  </si>
+  <si>
+    <t>Holistically-Nested Edge Detection</t>
+  </si>
+  <si>
+    <t>Delineate grounding lines of ice shelves</t>
+  </si>
+  <si>
+    <t>U-Net Convolutional Neural Network</t>
+  </si>
+  <si>
+    <t>Delineate ice shelf coastlines</t>
+  </si>
+  <si>
+    <t>Combining SAR and altimetry data</t>
+  </si>
+  <si>
+    <t>Ice Sheets (Greenland)</t>
+  </si>
+  <si>
+    <t>Classification of supraglacial lakes</t>
+  </si>
+  <si>
+    <t>Combining SAR and optical data</t>
+  </si>
+  <si>
+    <t>Back Propagation Neural Network</t>
+  </si>
+  <si>
+    <t>Gap-filling</t>
+  </si>
+  <si>
+    <t>Producing gap-filled LSWT/ LIC dataset</t>
+  </si>
+  <si>
+    <t>Multi-layer Perceptron Neural Network</t>
+  </si>
+  <si>
+    <t>Define water level relation with altimetry</t>
+  </si>
+  <si>
+    <t>First-order water detection</t>
+  </si>
+  <si>
+    <t>Resolution enhancement</t>
+  </si>
+  <si>
+    <t>Transfer to various spatial resolution data</t>
+  </si>
+  <si>
+    <t>Quantify classification uncertainty per pixel</t>
+  </si>
+  <si>
+    <t>Gradient Boosting</t>
+  </si>
+  <si>
+    <t>Reduce hyperspectral dimensionality</t>
+  </si>
+  <si>
+    <t>Encoder Transformer</t>
+  </si>
+  <si>
+    <t>Change detection benchmarking</t>
+  </si>
+  <si>
+    <t>Classify reflectance into land cover types</t>
+  </si>
+  <si>
+    <t>LST</t>
+  </si>
+  <si>
+    <t>Retrieve LST from brightness temperature</t>
+  </si>
+  <si>
+    <t>Generate fractional vegetation cover</t>
+  </si>
+  <si>
+    <t>Estimate retrieval uncertainty</t>
+  </si>
+  <si>
+    <t>Cluster retrieval errors for calibration</t>
+  </si>
+  <si>
+    <t>Downscaling microwave for merged product</t>
+  </si>
+  <si>
+    <t>Feed-forward Neural Network</t>
+  </si>
+  <si>
+    <t>Retrieve water Inherent Optical Properties</t>
+  </si>
+  <si>
+    <t>Atmospheric correction</t>
+  </si>
+  <si>
+    <t>Predict ozone profiles</t>
+  </si>
+  <si>
+    <t>Grouping of conditions for separate models</t>
+  </si>
+  <si>
+    <t>Permafrost</t>
+  </si>
+  <si>
+    <t>Generate land cover unit parameters</t>
+  </si>
+  <si>
+    <t>Processing super-resolution land cover units</t>
+  </si>
+  <si>
+    <t>Use case on drivers</t>
+  </si>
+  <si>
+    <t>Use case on drivers and impacts</t>
+  </si>
+  <si>
+    <t>Use case on impacts</t>
+  </si>
+  <si>
+    <t>Phyto</t>
+  </si>
+  <si>
+    <t>Derive phytoplankton pigments</t>
+  </si>
+  <si>
+    <t>Precursors</t>
+  </si>
+  <si>
+    <t>Convert radiance into column abundance</t>
+  </si>
+  <si>
+    <t>SAGE</t>
+  </si>
+  <si>
+    <t>Diffusion Models</t>
+  </si>
+  <si>
+    <t>Deep Learning – generative models</t>
+  </si>
+  <si>
+    <t>Enhance resolution of old microwave data</t>
+  </si>
+  <si>
+    <t>Extract waveform clusters for training</t>
+  </si>
+  <si>
+    <t>Cross-channel ice signature identification</t>
+  </si>
+  <si>
+    <t>Set waveform cutoff for radar retrieval</t>
+  </si>
+  <si>
+    <t>Graph Neural Network</t>
+  </si>
+  <si>
+    <t>Deep Learning – graph neural networks</t>
+  </si>
+  <si>
+    <t>Processing old microwave records to extend</t>
+  </si>
+  <si>
+    <t>Sea State</t>
+  </si>
+  <si>
+    <t>Support Vector Machine</t>
+  </si>
+  <si>
+    <t>Estimate significant wave height</t>
+  </si>
+  <si>
+    <t>Sea Surface Salinity</t>
+  </si>
+  <si>
+    <t>Remove radio-frequency interference</t>
+  </si>
+  <si>
+    <t>Remove geophysical effects</t>
+  </si>
+  <si>
+    <t>Attribution of SST variability modelling</t>
+  </si>
+  <si>
+    <t>Long Short Term Memory</t>
+  </si>
+  <si>
+    <t>Deep Learning – recurrent neural networks</t>
+  </si>
+  <si>
+    <t>Predicting future SST modelling</t>
   </si>
 </sst>
 </file>
@@ -1945,18 +2221,15 @@
       <color rgb="FF212529"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF467886"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF000000"/>
+      <color rgb="FF212529"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -2105,7 +2378,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="57">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -2159,27 +2432,6 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -2194,31 +2446,77 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2536,36 +2834,36 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9CC0B67C-1229-4907-A814-DF79422D0B81}">
   <dimension ref="A1:M170"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="36.83203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19.5" customWidth="1"/>
-    <col min="3" max="3" width="30.1640625" customWidth="1"/>
-    <col min="4" max="4" width="38.5" customWidth="1"/>
-    <col min="5" max="5" width="23.5" customWidth="1"/>
-    <col min="6" max="6" width="23.5" style="6" customWidth="1"/>
-    <col min="7" max="7" width="30.5" style="9" customWidth="1"/>
-    <col min="8" max="8" width="30.5" style="12" customWidth="1"/>
-    <col min="9" max="9" width="42.83203125" style="4" customWidth="1"/>
-    <col min="10" max="10" width="19.5" style="4" customWidth="1"/>
-    <col min="11" max="11" width="19.5" customWidth="1"/>
-    <col min="12" max="12" width="23.5" style="6" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="47.1640625" style="8" customWidth="1"/>
+    <col min="1" max="1" width="36.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.42578125" customWidth="1"/>
+    <col min="3" max="3" width="30.140625" customWidth="1"/>
+    <col min="4" max="4" width="38.42578125" customWidth="1"/>
+    <col min="5" max="5" width="23.42578125" customWidth="1"/>
+    <col min="6" max="6" width="23.42578125" style="6" customWidth="1"/>
+    <col min="7" max="7" width="30.42578125" style="9" customWidth="1"/>
+    <col min="8" max="8" width="30.42578125" style="12" customWidth="1"/>
+    <col min="9" max="9" width="42.85546875" style="4" customWidth="1"/>
+    <col min="10" max="10" width="19.42578125" style="4" customWidth="1"/>
+    <col min="11" max="11" width="19.42578125" customWidth="1"/>
+    <col min="12" max="12" width="23.42578125" style="6" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="47.140625" style="8" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="16" x14ac:dyDescent="0.2">
-      <c r="A1" s="34" t="s">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1" s="40" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="34"/>
-      <c r="C1" s="34"/>
-      <c r="D1" s="34"/>
-      <c r="E1" s="34"/>
-      <c r="F1" s="35"/>
-      <c r="G1" s="30" t="s">
+      <c r="B1" s="40"/>
+      <c r="C1" s="40"/>
+      <c r="D1" s="40"/>
+      <c r="E1" s="40"/>
+      <c r="F1" s="41"/>
+      <c r="G1" s="42" t="s">
         <v>1</v>
       </c>
-      <c r="H1" s="32" t="s">
+      <c r="H1" s="44" t="s">
         <v>2</v>
       </c>
       <c r="I1" s="14" t="s">
@@ -2575,7 +2873,7 @@
       <c r="K1" s="3"/>
       <c r="M1" s="17"/>
     </row>
-    <row r="2" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>4</v>
       </c>
@@ -2594,8 +2892,8 @@
       <c r="F2" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="G2" s="31"/>
-      <c r="H2" s="33"/>
+      <c r="G2" s="43"/>
+      <c r="H2" s="45"/>
       <c r="I2" s="15" t="s">
         <v>10</v>
       </c>
@@ -2612,7 +2910,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:13" ht="80" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:13" ht="90" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>13</v>
       </c>
@@ -2653,7 +2951,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="4" spans="1:13" ht="96" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:13" ht="90" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>13</v>
       </c>
@@ -2694,11 +2992,11 @@
         <v>229</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B5" s="19"/>
       <c r="C5" s="19"/>
     </row>
-    <row r="6" spans="1:13" ht="80" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:13" ht="105" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>25</v>
       </c>
@@ -2739,7 +3037,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="7" spans="1:13" ht="80" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:13" ht="90" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>33</v>
       </c>
@@ -2780,7 +3078,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="8" spans="1:13" ht="80" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:13" ht="90" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>35</v>
       </c>
@@ -2821,11 +3119,11 @@
         <v>201</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B9" s="19"/>
       <c r="C9" s="19"/>
     </row>
-    <row r="10" spans="1:13" ht="48" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:13" ht="60" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>38</v>
       </c>
@@ -2866,7 +3164,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="11" spans="1:13" ht="32" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>42</v>
       </c>
@@ -2907,7 +3205,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="12" spans="1:13" ht="96" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:13" ht="120" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>42</v>
       </c>
@@ -2948,7 +3246,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="13" spans="1:13" ht="48" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:13" ht="45" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>42</v>
       </c>
@@ -2989,7 +3287,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="14" spans="1:13" ht="64" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:13" ht="90" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>42</v>
       </c>
@@ -3030,7 +3328,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="15" spans="1:13" ht="48" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:13" ht="45" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>42</v>
       </c>
@@ -3071,7 +3369,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="16" spans="1:13" ht="48" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:13" ht="45" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>42</v>
       </c>
@@ -3112,7 +3410,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="17" spans="1:13" ht="48" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:13" ht="45" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>42</v>
       </c>
@@ -3153,7 +3451,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="18" spans="1:13" ht="48" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:13" ht="45" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>42</v>
       </c>
@@ -3194,7 +3492,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="19" spans="1:13" ht="48" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:13" ht="45" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>42</v>
       </c>
@@ -3235,7 +3533,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="20" spans="1:13" ht="48" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:13" ht="45" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>42</v>
       </c>
@@ -3276,7 +3574,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="21" spans="1:13" ht="48" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:13" ht="45" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>42</v>
       </c>
@@ -3317,7 +3615,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="22" spans="1:13" ht="48" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:13" ht="45" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>42</v>
       </c>
@@ -3358,7 +3656,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="23" spans="1:13" ht="48" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:13" ht="45" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>42</v>
       </c>
@@ -3399,7 +3697,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="24" spans="1:13" ht="48" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:13" ht="45" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>42</v>
       </c>
@@ -3440,7 +3738,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="25" spans="1:13" ht="48" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:13" ht="45" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>42</v>
       </c>
@@ -3481,7 +3779,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="26" spans="1:13" ht="48" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:13" ht="45" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>42</v>
       </c>
@@ -3522,7 +3820,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="27" spans="1:13" ht="48" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:13" ht="45" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>42</v>
       </c>
@@ -3563,7 +3861,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="28" spans="1:13" ht="48" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:13" ht="45" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>42</v>
       </c>
@@ -3604,7 +3902,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="29" spans="1:13" ht="48" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:13" ht="45" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>42</v>
       </c>
@@ -3645,7 +3943,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="30" spans="1:13" ht="48" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:13" ht="45" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>42</v>
       </c>
@@ -3686,7 +3984,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="31" spans="1:13" ht="48" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:13" ht="45" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>42</v>
       </c>
@@ -3727,7 +4025,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="32" spans="1:13" ht="48" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:13" ht="45" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>42</v>
       </c>
@@ -3768,11 +4066,11 @@
         <v>233</v>
       </c>
     </row>
-    <row r="33" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B33" s="19"/>
       <c r="C33" s="19"/>
     </row>
-    <row r="34" spans="1:13" ht="64" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:13" ht="90" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>69</v>
       </c>
@@ -3813,7 +4111,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="35" spans="1:13" ht="64" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:13" ht="90" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>69</v>
       </c>
@@ -3854,11 +4152,11 @@
         <v>220</v>
       </c>
     </row>
-    <row r="36" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B36" s="19"/>
       <c r="C36" s="19"/>
     </row>
-    <row r="37" spans="1:13" ht="80" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:13" ht="75" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>74</v>
       </c>
@@ -3899,7 +4197,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="38" spans="1:13" ht="80" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:13" ht="75" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>74</v>
       </c>
@@ -3940,7 +4238,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="39" spans="1:13" ht="80" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:13" ht="90" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>74</v>
       </c>
@@ -3981,7 +4279,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="40" spans="1:13" ht="80" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:13" ht="90" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>74</v>
       </c>
@@ -4022,7 +4320,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="41" spans="1:13" ht="64" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:13" ht="60" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>74</v>
       </c>
@@ -4063,7 +4361,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="42" spans="1:13" ht="64" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:13" ht="75" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>74</v>
       </c>
@@ -4104,7 +4402,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="43" spans="1:13" ht="80" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:13" ht="75" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>74</v>
       </c>
@@ -4145,7 +4443,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="44" spans="1:13" ht="80" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:13" ht="75" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>85</v>
       </c>
@@ -4186,7 +4484,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="45" spans="1:13" ht="80" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:13" ht="75" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>85</v>
       </c>
@@ -4227,7 +4525,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="46" spans="1:13" ht="80" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:13" ht="90" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>85</v>
       </c>
@@ -4268,7 +4566,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="47" spans="1:13" ht="80" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:13" ht="90" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>85</v>
       </c>
@@ -4309,7 +4607,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="48" spans="1:13" ht="80" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:13" ht="90" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>85</v>
       </c>
@@ -4350,7 +4648,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="49" spans="1:13" ht="80" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:13" ht="90" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>85</v>
       </c>
@@ -4391,7 +4689,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="50" spans="1:13" ht="80" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:13" ht="75" x14ac:dyDescent="0.25">
       <c r="A50" s="10" t="s">
         <v>85</v>
       </c>
@@ -4432,7 +4730,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="51" spans="1:13" ht="80" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:13" ht="75" x14ac:dyDescent="0.25">
       <c r="A51" s="10"/>
       <c r="B51" s="19">
         <v>43501</v>
@@ -4471,7 +4769,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="52" spans="1:13" ht="80" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:13" ht="75" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>85</v>
       </c>
@@ -4512,7 +4810,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="53" spans="1:13" ht="80" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:13" ht="75" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>85</v>
       </c>
@@ -4553,7 +4851,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="54" spans="1:13" ht="96" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:13" ht="90" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>85</v>
       </c>
@@ -4594,7 +4892,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="55" spans="1:13" ht="64" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:13" ht="75" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>85</v>
       </c>
@@ -4635,12 +4933,12 @@
         <v>236</v>
       </c>
     </row>
-    <row r="56" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A56" s="10"/>
       <c r="B56" s="20"/>
       <c r="C56" s="20"/>
     </row>
-    <row r="57" spans="1:13" ht="64" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:13" ht="60" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>100</v>
       </c>
@@ -4681,7 +4979,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="58" spans="1:13" ht="64" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:13" ht="60" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>100</v>
       </c>
@@ -4722,7 +5020,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="59" spans="1:13" ht="64" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:13" ht="60" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>100</v>
       </c>
@@ -4763,7 +5061,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="60" spans="1:13" ht="64" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:13" ht="60" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>100</v>
       </c>
@@ -4804,7 +5102,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="61" spans="1:13" ht="96" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:13" ht="90" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>100</v>
       </c>
@@ -4845,7 +5143,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="62" spans="1:13" ht="96" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:13" ht="105" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>100</v>
       </c>
@@ -4886,7 +5184,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="63" spans="1:13" ht="96" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:13" ht="90" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>100</v>
       </c>
@@ -4927,7 +5225,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="64" spans="1:13" ht="96" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:13" ht="105" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>100</v>
       </c>
@@ -4968,7 +5266,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="65" spans="1:13" ht="64" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:13" ht="60" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>100</v>
       </c>
@@ -5009,7 +5307,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="66" spans="1:13" ht="64" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:13" ht="60" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>100</v>
       </c>
@@ -5050,7 +5348,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="67" spans="1:13" ht="64" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:13" ht="60" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>100</v>
       </c>
@@ -5091,7 +5389,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="68" spans="1:13" ht="64" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:13" ht="60" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>100</v>
       </c>
@@ -5132,7 +5430,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="69" spans="1:13" ht="64" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:13" ht="60" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>100</v>
       </c>
@@ -5173,7 +5471,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="70" spans="1:13" ht="64" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:13" ht="60" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>100</v>
       </c>
@@ -5214,7 +5512,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="71" spans="1:13" ht="64" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:13" ht="60" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>100</v>
       </c>
@@ -5255,7 +5553,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="72" spans="1:13" ht="64" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:13" ht="60" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>100</v>
       </c>
@@ -5296,7 +5594,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="73" spans="1:13" ht="64" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:13" ht="60" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>100</v>
       </c>
@@ -5337,11 +5635,11 @@
         <v>238</v>
       </c>
     </row>
-    <row r="74" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B74" s="19"/>
       <c r="C74" s="19"/>
     </row>
-    <row r="75" spans="1:13" ht="64" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:13" ht="90" x14ac:dyDescent="0.25">
       <c r="A75" s="24" t="s">
         <v>131</v>
       </c>
@@ -5382,7 +5680,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="76" spans="1:13" ht="48" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:13" ht="75" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>131</v>
       </c>
@@ -5423,7 +5721,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="77" spans="1:13" ht="48" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:13" ht="60" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>131</v>
       </c>
@@ -5464,7 +5762,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="78" spans="1:13" ht="64" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:13" ht="75" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>131</v>
       </c>
@@ -5505,7 +5803,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="79" spans="1:13" ht="48" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:13" ht="60" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>131</v>
       </c>
@@ -5546,7 +5844,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="80" spans="1:13" ht="48" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:13" ht="45" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>131</v>
       </c>
@@ -5587,12 +5885,12 @@
         <v>244</v>
       </c>
     </row>
-    <row r="81" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B81" s="19"/>
       <c r="C81" s="19"/>
       <c r="H81" s="11"/>
     </row>
-    <row r="82" spans="1:13" ht="48" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:13" ht="45" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>134</v>
       </c>
@@ -5633,7 +5931,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="83" spans="1:13" ht="80" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:13" ht="90" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>134</v>
       </c>
@@ -5674,7 +5972,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="84" spans="1:13" ht="96" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:13" ht="105" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>134</v>
       </c>
@@ -5715,7 +6013,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="85" spans="1:13" ht="96" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:13" ht="105" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>134</v>
       </c>
@@ -5756,7 +6054,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="86" spans="1:13" ht="80" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:13" ht="75" x14ac:dyDescent="0.25">
       <c r="A86" s="24" t="s">
         <v>396</v>
       </c>
@@ -5797,7 +6095,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="87" spans="1:13" ht="112" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:13" ht="120" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>140</v>
       </c>
@@ -5838,11 +6136,11 @@
         <v>178</v>
       </c>
     </row>
-    <row r="88" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B88" s="19"/>
       <c r="C88" s="19"/>
     </row>
-    <row r="89" spans="1:13" ht="80" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:13" ht="90" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>131</v>
       </c>
@@ -5883,7 +6181,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="90" spans="1:13" ht="80" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:13" ht="90" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>131</v>
       </c>
@@ -5924,7 +6222,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="91" spans="1:13" ht="80" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:13" ht="90" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>131</v>
       </c>
@@ -5965,7 +6263,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="92" spans="1:13" ht="80" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:13" ht="90" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>131</v>
       </c>
@@ -6006,7 +6304,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="93" spans="1:13" ht="80" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:13" ht="90" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>131</v>
       </c>
@@ -6047,7 +6345,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="94" spans="1:13" ht="80" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:13" ht="90" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>131</v>
       </c>
@@ -6088,10 +6386,10 @@
         <v>277</v>
       </c>
     </row>
-    <row r="95" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:13" x14ac:dyDescent="0.25">
       <c r="G95" s="8"/>
     </row>
-    <row r="96" spans="1:13" ht="48" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:13" ht="60" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>286</v>
       </c>
@@ -6132,11 +6430,11 @@
         <v>395</v>
       </c>
     </row>
-    <row r="97" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B97" s="19"/>
       <c r="C97" s="19"/>
     </row>
-    <row r="98" spans="1:13" ht="48" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:13" ht="45" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>289</v>
       </c>
@@ -6177,7 +6475,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="100" spans="1:13" ht="80" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:13" ht="90" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>301</v>
       </c>
@@ -6218,7 +6516,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="101" spans="1:13" ht="64" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:13" ht="75" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>301</v>
       </c>
@@ -6259,7 +6557,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="102" spans="1:13" ht="176" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:13" ht="195" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>302</v>
       </c>
@@ -6300,11 +6598,11 @@
         <v>400</v>
       </c>
     </row>
-    <row r="103" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B103" s="19"/>
       <c r="C103" s="19"/>
     </row>
-    <row r="104" spans="1:13" ht="48" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:13" ht="45" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>315</v>
       </c>
@@ -6345,7 +6643,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="105" spans="1:13" ht="48" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:13" ht="45" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>315</v>
       </c>
@@ -6386,7 +6684,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="106" spans="1:13" ht="48" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:13" ht="60" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>315</v>
       </c>
@@ -6427,7 +6725,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="107" spans="1:13" ht="48" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:13" ht="45" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>405</v>
       </c>
@@ -6468,7 +6766,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="108" spans="1:13" ht="32" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A108" s="4" t="s">
         <v>330</v>
       </c>
@@ -6509,7 +6807,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="109" spans="1:13" ht="48" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:13" ht="45" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>405</v>
       </c>
@@ -6550,7 +6848,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="110" spans="1:13" ht="80" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:13" ht="75" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>405</v>
       </c>
@@ -6591,7 +6889,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="111" spans="1:13" ht="32" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>331</v>
       </c>
@@ -6632,7 +6930,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="112" spans="1:13" ht="80" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:13" ht="75" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>405</v>
       </c>
@@ -6673,7 +6971,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="113" spans="1:13" ht="80" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:13" ht="75" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>405</v>
       </c>
@@ -6714,11 +7012,11 @@
         <v>408</v>
       </c>
     </row>
-    <row r="114" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B114" s="19"/>
       <c r="C114" s="19"/>
     </row>
-    <row r="115" spans="1:13" ht="32" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>343</v>
       </c>
@@ -6759,7 +7057,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="116" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>342</v>
       </c>
@@ -6800,7 +7098,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="117" spans="1:13" ht="32" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>342</v>
       </c>
@@ -6841,11 +7139,11 @@
         <v>346</v>
       </c>
     </row>
-    <row r="118" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B118" s="19"/>
       <c r="C118" s="19"/>
     </row>
-    <row r="119" spans="1:13" ht="80" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:13" ht="75" x14ac:dyDescent="0.25">
       <c r="A119" s="24" t="s">
         <v>349</v>
       </c>
@@ -6886,7 +7184,7 @@
         <v>415</v>
       </c>
     </row>
-    <row r="120" spans="1:13" ht="80" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:13" ht="75" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>349</v>
       </c>
@@ -6927,7 +7225,7 @@
         <v>416</v>
       </c>
     </row>
-    <row r="121" spans="1:13" ht="80" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:13" ht="75" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>349</v>
       </c>
@@ -6968,7 +7266,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="122" spans="1:13" ht="80" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:13" ht="75" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
         <v>349</v>
       </c>
@@ -7009,7 +7307,7 @@
         <v>418</v>
       </c>
     </row>
-    <row r="123" spans="1:13" ht="80" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:13" ht="75" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>349</v>
       </c>
@@ -7050,7 +7348,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="124" spans="1:13" ht="80" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:13" ht="75" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>349</v>
       </c>
@@ -7091,7 +7389,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="125" spans="1:13" ht="80" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:13" ht="90" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>349</v>
       </c>
@@ -7132,7 +7430,7 @@
         <v>415</v>
       </c>
     </row>
-    <row r="126" spans="1:13" ht="80" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:13" ht="90" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>349</v>
       </c>
@@ -7173,7 +7471,7 @@
         <v>416</v>
       </c>
     </row>
-    <row r="127" spans="1:13" ht="80" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:13" ht="90" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
         <v>349</v>
       </c>
@@ -7214,7 +7512,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="128" spans="1:13" ht="80" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:13" ht="90" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>349</v>
       </c>
@@ -7255,7 +7553,7 @@
         <v>418</v>
       </c>
     </row>
-    <row r="129" spans="1:13" ht="80" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:13" ht="90" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
         <v>349</v>
       </c>
@@ -7296,7 +7594,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="130" spans="1:13" ht="80" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:13" ht="90" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
         <v>349</v>
       </c>
@@ -7337,7 +7635,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="131" spans="1:13" ht="80" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:13" ht="105" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
         <v>349</v>
       </c>
@@ -7378,7 +7676,7 @@
         <v>415</v>
       </c>
     </row>
-    <row r="132" spans="1:13" ht="80" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:13" ht="105" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
         <v>349</v>
       </c>
@@ -7419,7 +7717,7 @@
         <v>416</v>
       </c>
     </row>
-    <row r="133" spans="1:13" ht="80" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:13" ht="105" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
         <v>349</v>
       </c>
@@ -7460,7 +7758,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="134" spans="1:13" ht="80" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:13" ht="105" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
         <v>349</v>
       </c>
@@ -7501,7 +7799,7 @@
         <v>418</v>
       </c>
     </row>
-    <row r="135" spans="1:13" ht="80" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:13" ht="105" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
         <v>349</v>
       </c>
@@ -7542,7 +7840,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="136" spans="1:13" ht="80" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:13" ht="105" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
         <v>349</v>
       </c>
@@ -7583,7 +7881,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="137" spans="1:13" ht="80" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:13" ht="75" x14ac:dyDescent="0.25">
       <c r="A137" s="26" t="s">
         <v>349</v>
       </c>
@@ -7624,7 +7922,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="138" spans="1:13" ht="80" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:13" ht="75" x14ac:dyDescent="0.25">
       <c r="A138" s="23" t="s">
         <v>349</v>
       </c>
@@ -7665,7 +7963,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="139" spans="1:13" ht="80" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:13" ht="75" x14ac:dyDescent="0.25">
       <c r="A139" s="23" t="s">
         <v>349</v>
       </c>
@@ -7706,7 +8004,7 @@
         <v>438</v>
       </c>
     </row>
-    <row r="140" spans="1:13" ht="80" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:13" ht="75" x14ac:dyDescent="0.25">
       <c r="A140" s="23" t="s">
         <v>349</v>
       </c>
@@ -7747,7 +8045,7 @@
         <v>439</v>
       </c>
     </row>
-    <row r="141" spans="1:13" ht="80" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:13" ht="75" x14ac:dyDescent="0.25">
       <c r="A141" s="23" t="s">
         <v>349</v>
       </c>
@@ -7788,7 +8086,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="142" spans="1:13" ht="80" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:13" ht="75" x14ac:dyDescent="0.25">
       <c r="A142" s="23" t="s">
         <v>349</v>
       </c>
@@ -7829,7 +8127,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="143" spans="1:13" ht="80" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:13" ht="90" x14ac:dyDescent="0.25">
       <c r="A143" s="23" t="s">
         <v>349</v>
       </c>
@@ -7870,7 +8168,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="144" spans="1:13" ht="80" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:13" ht="90" x14ac:dyDescent="0.25">
       <c r="A144" s="23" t="s">
         <v>349</v>
       </c>
@@ -7911,7 +8209,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="145" spans="1:13" ht="80" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:13" ht="90" x14ac:dyDescent="0.25">
       <c r="A145" s="23" t="s">
         <v>349</v>
       </c>
@@ -7952,7 +8250,7 @@
         <v>438</v>
       </c>
     </row>
-    <row r="146" spans="1:13" ht="80" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:13" ht="90" x14ac:dyDescent="0.25">
       <c r="A146" s="23" t="s">
         <v>349</v>
       </c>
@@ -7993,7 +8291,7 @@
         <v>439</v>
       </c>
     </row>
-    <row r="147" spans="1:13" ht="80" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:13" ht="90" x14ac:dyDescent="0.25">
       <c r="A147" s="23" t="s">
         <v>349</v>
       </c>
@@ -8034,7 +8332,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="148" spans="1:13" ht="80" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:13" ht="90" x14ac:dyDescent="0.25">
       <c r="A148" s="23" t="s">
         <v>349</v>
       </c>
@@ -8075,7 +8373,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="149" spans="1:13" ht="80" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:13" ht="105" x14ac:dyDescent="0.25">
       <c r="A149" s="23" t="s">
         <v>349</v>
       </c>
@@ -8116,7 +8414,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="150" spans="1:13" ht="80" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:13" ht="105" x14ac:dyDescent="0.25">
       <c r="A150" s="23" t="s">
         <v>349</v>
       </c>
@@ -8157,7 +8455,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="151" spans="1:13" ht="80" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:13" ht="105" x14ac:dyDescent="0.25">
       <c r="A151" s="23" t="s">
         <v>349</v>
       </c>
@@ -8198,7 +8496,7 @@
         <v>438</v>
       </c>
     </row>
-    <row r="152" spans="1:13" ht="80" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:13" ht="105" x14ac:dyDescent="0.25">
       <c r="A152" s="23" t="s">
         <v>349</v>
       </c>
@@ -8239,7 +8537,7 @@
         <v>439</v>
       </c>
     </row>
-    <row r="153" spans="1:13" ht="80" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:13" ht="105" x14ac:dyDescent="0.25">
       <c r="A153" s="23" t="s">
         <v>349</v>
       </c>
@@ -8280,7 +8578,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="154" spans="1:13" ht="80" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:13" ht="105" x14ac:dyDescent="0.25">
       <c r="A154" s="23" t="s">
         <v>349</v>
       </c>
@@ -8321,12 +8619,12 @@
         <v>441</v>
       </c>
     </row>
-    <row r="155" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A155" s="23"/>
       <c r="B155" s="19"/>
       <c r="C155" s="19"/>
     </row>
-    <row r="156" spans="1:13" ht="80" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:13" ht="90" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
         <v>358</v>
       </c>
@@ -8367,7 +8665,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="157" spans="1:13" ht="96" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:13" ht="105" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
         <v>358</v>
       </c>
@@ -8408,7 +8706,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="158" spans="1:13" ht="96" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:13" ht="105" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
         <v>358</v>
       </c>
@@ -8449,7 +8747,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="159" spans="1:13" ht="96" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:13" ht="105" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
         <v>358</v>
       </c>
@@ -8490,7 +8788,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="160" spans="1:13" ht="96" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:13" ht="105" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
         <v>358</v>
       </c>
@@ -8531,7 +8829,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="161" spans="1:13" ht="96" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:13" ht="105" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
         <v>358</v>
       </c>
@@ -8572,7 +8870,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="162" spans="1:13" ht="96" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:13" ht="105" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
         <v>358</v>
       </c>
@@ -8613,7 +8911,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="163" spans="1:13" ht="96" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:13" ht="105" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
         <v>358</v>
       </c>
@@ -8654,7 +8952,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="164" spans="1:13" ht="112" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:13" ht="105" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
         <v>358</v>
       </c>
@@ -8695,12 +8993,12 @@
         <v>362</v>
       </c>
     </row>
-    <row r="165" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B165" s="19"/>
       <c r="C165" s="19"/>
       <c r="D165" s="4"/>
     </row>
-    <row r="166" spans="1:13" ht="80" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:13" ht="90" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
         <v>379</v>
       </c>
@@ -8741,12 +9039,12 @@
         <v>381</v>
       </c>
     </row>
-    <row r="167" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B167" s="19"/>
       <c r="C167" s="19"/>
       <c r="D167" s="4"/>
     </row>
-    <row r="168" spans="1:13" ht="32" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A168" s="10" t="s">
         <v>451</v>
       </c>
@@ -8787,7 +9085,7 @@
         <v>456</v>
       </c>
     </row>
-    <row r="169" spans="1:13" ht="32" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A169" s="10" t="s">
         <v>451</v>
       </c>
@@ -8828,7 +9126,7 @@
         <v>456</v>
       </c>
     </row>
-    <row r="170" spans="1:13" ht="32" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A170" s="10" t="s">
         <v>451</v>
       </c>
@@ -8935,386 +9233,2274 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C17FE217-AB61-B742-BFE0-33900D1BEC91}">
-  <dimension ref="A1:J12"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:J71"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="16.33203125" customWidth="1"/>
-    <col min="2" max="2" width="17.1640625" customWidth="1"/>
-    <col min="3" max="3" width="53.33203125" customWidth="1"/>
-    <col min="4" max="4" width="29.1640625" customWidth="1"/>
-    <col min="5" max="5" width="30.5" customWidth="1"/>
-    <col min="6" max="7" width="17.33203125" customWidth="1"/>
-    <col min="8" max="8" width="16.5" customWidth="1"/>
-    <col min="9" max="9" width="33.5" customWidth="1"/>
-    <col min="10" max="10" width="30.6640625" customWidth="1"/>
+    <col min="1" max="1" width="16.28515625" customWidth="1"/>
+    <col min="2" max="2" width="17.140625" customWidth="1"/>
+    <col min="3" max="3" width="53.28515625" customWidth="1"/>
+    <col min="4" max="4" width="29.140625" customWidth="1"/>
+    <col min="5" max="5" width="30.42578125" customWidth="1"/>
+    <col min="6" max="7" width="17.28515625" customWidth="1"/>
+    <col min="8" max="8" width="16.42578125" customWidth="1"/>
+    <col min="9" max="9" width="33.42578125" customWidth="1"/>
+    <col min="10" max="10" width="30.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="47" t="s">
+    <row r="1" spans="1:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="35" t="s">
         <v>490</v>
       </c>
-      <c r="B1" s="47"/>
-      <c r="C1" s="48"/>
-      <c r="D1" s="49" t="s">
+      <c r="B1" s="35"/>
+      <c r="C1" s="36"/>
+      <c r="D1" s="33" t="s">
         <v>494</v>
       </c>
-      <c r="E1" s="50" t="s">
+      <c r="E1" s="34" t="s">
         <v>495</v>
       </c>
-      <c r="F1" s="51" t="s">
+      <c r="F1" s="37" t="s">
         <v>496</v>
       </c>
-      <c r="G1" s="52"/>
-      <c r="H1" s="52"/>
-      <c r="I1" s="53"/>
-      <c r="J1" s="36"/>
-    </row>
-    <row r="2" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="37" t="s">
+      <c r="G1" s="38"/>
+      <c r="H1" s="38"/>
+      <c r="I1" s="39"/>
+      <c r="J1" s="27"/>
+    </row>
+    <row r="2" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="28" t="s">
         <v>491</v>
       </c>
-      <c r="B2" s="37" t="s">
+      <c r="B2" s="28" t="s">
         <v>484</v>
       </c>
-      <c r="C2" s="37" t="s">
+      <c r="C2" s="28" t="s">
         <v>483</v>
       </c>
-      <c r="D2" s="49"/>
-      <c r="E2" s="50"/>
-      <c r="F2" s="38" t="s">
+      <c r="D2" s="33"/>
+      <c r="E2" s="34"/>
+      <c r="F2" s="29" t="s">
         <v>460</v>
       </c>
-      <c r="G2" s="39" t="s">
+      <c r="G2" s="30" t="s">
         <v>497</v>
       </c>
-      <c r="H2" s="37" t="s">
+      <c r="H2" s="28" t="s">
         <v>461</v>
       </c>
-      <c r="I2" s="40" t="s">
+      <c r="I2" s="31" t="s">
         <v>489</v>
       </c>
-      <c r="J2" s="41" t="s">
+      <c r="J2" s="32" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A3" s="42" t="s">
-        <v>19</v>
-      </c>
-      <c r="B3" s="27" t="s">
+    <row r="3" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+      <c r="A3" s="46" t="s">
+        <v>19</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D3" s="21" t="s">
+        <v>453</v>
+      </c>
+      <c r="E3" s="47" t="s">
+        <v>454</v>
+      </c>
+      <c r="F3" s="48" t="s">
+        <v>488</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>499</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>476</v>
+      </c>
+      <c r="I3" s="4" t="s">
+        <v>471</v>
+      </c>
+      <c r="J3" s="4" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+      <c r="A4" s="46" t="s">
+        <v>19</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D4" s="21" t="s">
+        <v>453</v>
+      </c>
+      <c r="E4" s="47" t="s">
+        <v>454</v>
+      </c>
+      <c r="F4" s="48" t="s">
+        <v>488</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>481</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>478</v>
+      </c>
+      <c r="I4" s="4" t="s">
+        <v>473</v>
+      </c>
+      <c r="J4" s="4" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+      <c r="A5" s="46" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>487</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D5" s="21" t="s">
+        <v>453</v>
+      </c>
+      <c r="E5" s="47" t="s">
+        <v>454</v>
+      </c>
+      <c r="F5" s="48" t="s">
+        <v>488</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>482</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>476</v>
+      </c>
+      <c r="I5" s="4" t="s">
+        <v>471</v>
+      </c>
+      <c r="J5" s="4" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+      <c r="A6" s="46" t="s">
+        <v>19</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>487</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D6" s="21" t="s">
+        <v>453</v>
+      </c>
+      <c r="E6" s="47" t="s">
+        <v>454</v>
+      </c>
+      <c r="F6" s="48" t="s">
+        <v>488</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>482</v>
+      </c>
+      <c r="H6" s="4" t="s">
+        <v>476</v>
+      </c>
+      <c r="I6" s="4" t="s">
+        <v>475</v>
+      </c>
+      <c r="J6" s="4" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="46" t="s">
+        <v>19</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>487</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D7" s="21" t="s">
+        <v>453</v>
+      </c>
+      <c r="E7" s="47" t="s">
+        <v>454</v>
+      </c>
+      <c r="F7" s="48" t="s">
+        <v>488</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>481</v>
+      </c>
+      <c r="H7" s="4" t="s">
+        <v>478</v>
+      </c>
+      <c r="I7" s="4" t="s">
+        <v>471</v>
+      </c>
+      <c r="J7" s="4" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+      <c r="A8" s="46" t="s">
+        <v>19</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>487</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D8" s="21" t="s">
+        <v>453</v>
+      </c>
+      <c r="E8" s="47" t="s">
+        <v>454</v>
+      </c>
+      <c r="F8" s="48" t="s">
+        <v>488</v>
+      </c>
+      <c r="G8" s="4" t="s">
+        <v>481</v>
+      </c>
+      <c r="H8" s="4" t="s">
+        <v>478</v>
+      </c>
+      <c r="I8" s="4" t="s">
+        <v>475</v>
+      </c>
+      <c r="J8" s="4" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+      <c r="A9" s="46" t="s">
+        <v>19</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>487</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D9" s="21" t="s">
+        <v>453</v>
+      </c>
+      <c r="E9" s="47" t="s">
+        <v>454</v>
+      </c>
+      <c r="F9" s="48" t="s">
+        <v>488</v>
+      </c>
+      <c r="G9" s="4" t="s">
+        <v>479</v>
+      </c>
+      <c r="H9" s="4" t="s">
+        <v>476</v>
+      </c>
+      <c r="I9" s="4" t="s">
+        <v>473</v>
+      </c>
+      <c r="J9" s="4" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+      <c r="A10" s="46" t="s">
+        <v>19</v>
+      </c>
+      <c r="B10" s="49" t="s">
         <v>486</v>
       </c>
-      <c r="C3" s="10" t="s">
+      <c r="C10" s="16" t="s">
         <v>498</v>
       </c>
-      <c r="D3" s="44" t="s">
+      <c r="D10" s="21" t="s">
         <v>453</v>
       </c>
-      <c r="E3" s="45" t="s">
+      <c r="E10" s="47" t="s">
         <v>454</v>
       </c>
-      <c r="F3" s="46" t="s">
+      <c r="F10" s="48" t="s">
         <v>488</v>
       </c>
-      <c r="G3" s="27" t="s">
+      <c r="G10" s="49" t="s">
         <v>479</v>
       </c>
-      <c r="H3" s="27" t="s">
+      <c r="H10" s="49" t="s">
         <v>476</v>
       </c>
-      <c r="I3" s="28" t="s">
+      <c r="I10" s="50" t="s">
         <v>470</v>
       </c>
-      <c r="J3" s="29" t="s">
+      <c r="J10" s="51" t="s">
         <v>462</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A4" s="42" t="s">
-        <v>19</v>
-      </c>
-      <c r="B4" s="27" t="s">
+    <row r="11" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+      <c r="A11" s="52" t="s">
+        <v>19</v>
+      </c>
+      <c r="B11" s="49" t="s">
         <v>486</v>
       </c>
-      <c r="C4" s="10" t="s">
+      <c r="C11" s="16" t="s">
         <v>498</v>
       </c>
-      <c r="D4" s="44" t="s">
+      <c r="D11" s="21" t="s">
         <v>453</v>
       </c>
-      <c r="E4" s="45" t="s">
+      <c r="E11" s="47" t="s">
         <v>454</v>
       </c>
-      <c r="F4" s="46" t="s">
+      <c r="F11" s="48" t="s">
         <v>488</v>
       </c>
-      <c r="G4" s="27" t="s">
+      <c r="G11" s="49" t="s">
         <v>479</v>
       </c>
-      <c r="H4" s="27" t="s">
+      <c r="H11" s="49" t="s">
         <v>476</v>
       </c>
-      <c r="I4" s="28" t="s">
+      <c r="I11" s="50" t="s">
         <v>471</v>
       </c>
-      <c r="J4" s="29" t="s">
+      <c r="J11" s="51" t="s">
         <v>463</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A5" s="42" t="s">
-        <v>19</v>
-      </c>
-      <c r="B5" s="27" t="s">
+    <row r="12" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A12" s="52" t="s">
+        <v>19</v>
+      </c>
+      <c r="B12" s="49" t="s">
+        <v>26</v>
+      </c>
+      <c r="C12" s="53" t="s">
+        <v>28</v>
+      </c>
+      <c r="D12" s="21" t="s">
+        <v>453</v>
+      </c>
+      <c r="E12" s="47" t="s">
+        <v>454</v>
+      </c>
+      <c r="F12" s="48" t="s">
+        <v>488</v>
+      </c>
+      <c r="G12" t="s">
+        <v>481</v>
+      </c>
+      <c r="H12" t="s">
+        <v>478</v>
+      </c>
+      <c r="I12" t="s">
+        <v>474</v>
+      </c>
+      <c r="J12" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A13" s="52" t="s">
+        <v>19</v>
+      </c>
+      <c r="B13" s="49" t="s">
+        <v>26</v>
+      </c>
+      <c r="C13" s="53" t="s">
+        <v>14</v>
+      </c>
+      <c r="D13" s="21" t="s">
+        <v>453</v>
+      </c>
+      <c r="E13" s="47" t="s">
+        <v>454</v>
+      </c>
+      <c r="F13" s="48" t="s">
+        <v>488</v>
+      </c>
+      <c r="G13" t="s">
+        <v>481</v>
+      </c>
+      <c r="H13" t="s">
+        <v>478</v>
+      </c>
+      <c r="I13" t="s">
+        <v>473</v>
+      </c>
+      <c r="J13" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+      <c r="A14" s="52" t="s">
+        <v>19</v>
+      </c>
+      <c r="B14" s="49" t="s">
         <v>70</v>
       </c>
-      <c r="C5" s="10" t="s">
+      <c r="C14" s="54" t="s">
         <v>492</v>
       </c>
-      <c r="D5" s="44" t="s">
+      <c r="D14" s="21" t="s">
         <v>453</v>
       </c>
-      <c r="E5" s="45" t="s">
+      <c r="E14" s="47" t="s">
         <v>454</v>
       </c>
-      <c r="F5" s="46" t="s">
+      <c r="F14" s="48" t="s">
         <v>488</v>
       </c>
-      <c r="G5" s="27" t="s">
+      <c r="G14" s="49" t="s">
         <v>479</v>
       </c>
-      <c r="H5" s="27" t="s">
+      <c r="H14" s="49" t="s">
         <v>476</v>
       </c>
-      <c r="I5" s="28" t="s">
+      <c r="I14" s="50" t="s">
         <v>472</v>
       </c>
-      <c r="J5" s="29" t="s">
+      <c r="J14" s="51" t="s">
         <v>464</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A6" s="42" t="s">
-        <v>19</v>
-      </c>
-      <c r="B6" s="27" t="s">
+    <row r="15" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+      <c r="A15" s="52" t="s">
+        <v>19</v>
+      </c>
+      <c r="B15" s="49" t="s">
         <v>70</v>
       </c>
-      <c r="C6" s="10" t="s">
+      <c r="C15" s="54" t="s">
         <v>492</v>
       </c>
-      <c r="D6" s="44" t="s">
+      <c r="D15" s="21" t="s">
         <v>453</v>
       </c>
-      <c r="E6" s="45" t="s">
+      <c r="E15" s="47" t="s">
         <v>454</v>
       </c>
-      <c r="F6" s="46" t="s">
+      <c r="F15" s="48" t="s">
         <v>488</v>
       </c>
-      <c r="G6" s="27" t="s">
+      <c r="G15" s="49" t="s">
         <v>479</v>
       </c>
-      <c r="H6" s="27" t="s">
+      <c r="H15" s="49" t="s">
         <v>476</v>
       </c>
-      <c r="I6" s="28" t="s">
+      <c r="I15" s="50" t="s">
         <v>473</v>
       </c>
-      <c r="J6" s="29" t="s">
+      <c r="J15" s="51" t="s">
         <v>465</v>
       </c>
     </row>
-    <row r="7" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="42" t="s">
-        <v>19</v>
-      </c>
-      <c r="B7" s="27" t="s">
+    <row r="16" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A16" s="52" t="s">
+        <v>19</v>
+      </c>
+      <c r="B16" s="49" t="s">
+        <v>70</v>
+      </c>
+      <c r="C16" s="55" t="s">
+        <v>14</v>
+      </c>
+      <c r="D16" s="21" t="s">
+        <v>453</v>
+      </c>
+      <c r="E16" s="47" t="s">
+        <v>454</v>
+      </c>
+      <c r="F16" s="48" t="s">
+        <v>488</v>
+      </c>
+      <c r="G16" t="s">
+        <v>505</v>
+      </c>
+      <c r="H16" t="s">
+        <v>506</v>
+      </c>
+      <c r="I16" t="s">
+        <v>473</v>
+      </c>
+      <c r="J16" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A17" s="52" t="s">
+        <v>19</v>
+      </c>
+      <c r="B17" s="49" t="s">
+        <v>70</v>
+      </c>
+      <c r="C17" s="55" t="s">
+        <v>14</v>
+      </c>
+      <c r="D17" s="21" t="s">
+        <v>453</v>
+      </c>
+      <c r="E17" s="47" t="s">
+        <v>454</v>
+      </c>
+      <c r="F17" s="48" t="s">
+        <v>488</v>
+      </c>
+      <c r="G17" t="s">
+        <v>505</v>
+      </c>
+      <c r="H17" t="s">
+        <v>506</v>
+      </c>
+      <c r="I17" t="s">
+        <v>472</v>
+      </c>
+      <c r="J17" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A18" s="52" t="s">
+        <v>19</v>
+      </c>
+      <c r="B18" s="49" t="s">
+        <v>70</v>
+      </c>
+      <c r="C18" s="55" t="s">
+        <v>14</v>
+      </c>
+      <c r="D18" s="21" t="s">
+        <v>453</v>
+      </c>
+      <c r="E18" s="47" t="s">
+        <v>454</v>
+      </c>
+      <c r="F18" s="48" t="s">
+        <v>488</v>
+      </c>
+      <c r="G18" t="s">
+        <v>505</v>
+      </c>
+      <c r="H18" t="s">
+        <v>506</v>
+      </c>
+      <c r="I18" t="s">
+        <v>471</v>
+      </c>
+      <c r="J18" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A19" s="52" t="s">
+        <v>19</v>
+      </c>
+      <c r="B19" t="s">
+        <v>509</v>
+      </c>
+      <c r="C19" s="55" t="s">
+        <v>14</v>
+      </c>
+      <c r="D19" s="21" t="s">
+        <v>453</v>
+      </c>
+      <c r="E19" s="47" t="s">
+        <v>454</v>
+      </c>
+      <c r="F19" s="48" t="s">
+        <v>488</v>
+      </c>
+      <c r="G19" t="s">
+        <v>479</v>
+      </c>
+      <c r="H19" t="s">
+        <v>476</v>
+      </c>
+      <c r="I19" t="s">
+        <v>474</v>
+      </c>
+      <c r="J19" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A20" s="52" t="s">
+        <v>19</v>
+      </c>
+      <c r="B20" t="s">
+        <v>509</v>
+      </c>
+      <c r="C20" s="55" t="s">
+        <v>14</v>
+      </c>
+      <c r="D20" s="21" t="s">
+        <v>453</v>
+      </c>
+      <c r="E20" s="47" t="s">
+        <v>454</v>
+      </c>
+      <c r="F20" s="48" t="s">
+        <v>488</v>
+      </c>
+      <c r="G20" t="s">
+        <v>479</v>
+      </c>
+      <c r="H20" t="s">
+        <v>476</v>
+      </c>
+      <c r="I20" t="s">
+        <v>471</v>
+      </c>
+      <c r="J20" t="s">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A21" s="52" t="s">
+        <v>19</v>
+      </c>
+      <c r="B21" t="s">
+        <v>509</v>
+      </c>
+      <c r="C21" s="55" t="s">
+        <v>14</v>
+      </c>
+      <c r="D21" s="21" t="s">
+        <v>453</v>
+      </c>
+      <c r="E21" s="47" t="s">
+        <v>454</v>
+      </c>
+      <c r="F21" s="48" t="s">
+        <v>488</v>
+      </c>
+      <c r="G21" t="s">
+        <v>512</v>
+      </c>
+      <c r="H21" t="s">
+        <v>476</v>
+      </c>
+      <c r="I21" t="s">
+        <v>471</v>
+      </c>
+      <c r="J21" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A22" s="52" t="s">
+        <v>19</v>
+      </c>
+      <c r="B22" t="s">
+        <v>514</v>
+      </c>
+      <c r="C22" s="55" t="s">
+        <v>14</v>
+      </c>
+      <c r="D22" s="21" t="s">
+        <v>453</v>
+      </c>
+      <c r="E22" s="47" t="s">
+        <v>454</v>
+      </c>
+      <c r="F22" s="48" t="s">
+        <v>488</v>
+      </c>
+      <c r="G22" t="s">
+        <v>515</v>
+      </c>
+      <c r="H22" t="s">
+        <v>477</v>
+      </c>
+      <c r="I22" t="s">
+        <v>474</v>
+      </c>
+      <c r="J22" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A23" s="52" t="s">
+        <v>19</v>
+      </c>
+      <c r="B23" t="s">
+        <v>514</v>
+      </c>
+      <c r="C23" s="55" t="s">
+        <v>14</v>
+      </c>
+      <c r="D23" s="21" t="s">
+        <v>453</v>
+      </c>
+      <c r="E23" s="47" t="s">
+        <v>454</v>
+      </c>
+      <c r="F23" s="48" t="s">
+        <v>488</v>
+      </c>
+      <c r="G23" t="s">
+        <v>517</v>
+      </c>
+      <c r="H23" t="s">
+        <v>476</v>
+      </c>
+      <c r="I23" t="s">
+        <v>474</v>
+      </c>
+      <c r="J23" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A24" s="52" t="s">
+        <v>19</v>
+      </c>
+      <c r="B24" t="s">
+        <v>514</v>
+      </c>
+      <c r="C24" s="55" t="s">
+        <v>14</v>
+      </c>
+      <c r="D24" s="21" t="s">
+        <v>453</v>
+      </c>
+      <c r="E24" s="47" t="s">
+        <v>454</v>
+      </c>
+      <c r="F24" s="48" t="s">
+        <v>488</v>
+      </c>
+      <c r="G24" t="s">
+        <v>519</v>
+      </c>
+      <c r="H24" t="s">
+        <v>520</v>
+      </c>
+      <c r="I24" t="s">
+        <v>472</v>
+      </c>
+      <c r="J24" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A25" s="52" t="s">
+        <v>19</v>
+      </c>
+      <c r="B25" t="s">
+        <v>514</v>
+      </c>
+      <c r="C25" s="55" t="s">
+        <v>14</v>
+      </c>
+      <c r="D25" s="21" t="s">
+        <v>453</v>
+      </c>
+      <c r="E25" s="47" t="s">
+        <v>454</v>
+      </c>
+      <c r="F25" s="48" t="s">
+        <v>488</v>
+      </c>
+      <c r="G25" t="s">
+        <v>522</v>
+      </c>
+      <c r="H25" t="s">
+        <v>523</v>
+      </c>
+      <c r="I25" t="s">
+        <v>473</v>
+      </c>
+      <c r="J25" t="s">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A26" s="52" t="s">
+        <v>19</v>
+      </c>
+      <c r="B26" t="s">
+        <v>514</v>
+      </c>
+      <c r="C26" s="55" t="s">
+        <v>14</v>
+      </c>
+      <c r="D26" s="21" t="s">
+        <v>453</v>
+      </c>
+      <c r="E26" s="47" t="s">
+        <v>454</v>
+      </c>
+      <c r="F26" s="48" t="s">
+        <v>488</v>
+      </c>
+      <c r="G26" t="s">
+        <v>525</v>
+      </c>
+      <c r="H26" t="s">
+        <v>523</v>
+      </c>
+      <c r="I26" t="s">
+        <v>473</v>
+      </c>
+      <c r="J26" t="s">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A27" s="52" t="s">
+        <v>19</v>
+      </c>
+      <c r="B27" t="s">
+        <v>527</v>
+      </c>
+      <c r="C27" s="55" t="s">
+        <v>14</v>
+      </c>
+      <c r="D27" s="21" t="s">
+        <v>453</v>
+      </c>
+      <c r="E27" s="47" t="s">
+        <v>454</v>
+      </c>
+      <c r="F27" s="48" t="s">
+        <v>488</v>
+      </c>
+      <c r="G27" t="s">
+        <v>528</v>
+      </c>
+      <c r="H27" t="s">
+        <v>506</v>
+      </c>
+      <c r="I27" t="s">
+        <v>473</v>
+      </c>
+      <c r="J27" t="s">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A28" s="52" t="s">
+        <v>19</v>
+      </c>
+      <c r="B28" t="s">
+        <v>527</v>
+      </c>
+      <c r="C28" s="55" t="s">
+        <v>14</v>
+      </c>
+      <c r="D28" s="21" t="s">
+        <v>453</v>
+      </c>
+      <c r="E28" s="47" t="s">
+        <v>454</v>
+      </c>
+      <c r="F28" s="48" t="s">
+        <v>488</v>
+      </c>
+      <c r="G28" t="s">
+        <v>530</v>
+      </c>
+      <c r="H28" t="s">
+        <v>506</v>
+      </c>
+      <c r="I28" t="s">
+        <v>473</v>
+      </c>
+      <c r="J28" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A29" s="52" t="s">
+        <v>19</v>
+      </c>
+      <c r="B29" t="s">
+        <v>527</v>
+      </c>
+      <c r="C29" s="55" t="s">
+        <v>14</v>
+      </c>
+      <c r="D29" s="21" t="s">
+        <v>453</v>
+      </c>
+      <c r="E29" s="47" t="s">
+        <v>454</v>
+      </c>
+      <c r="F29" s="48" t="s">
+        <v>488</v>
+      </c>
+      <c r="G29" t="s">
+        <v>530</v>
+      </c>
+      <c r="H29" t="s">
+        <v>506</v>
+      </c>
+      <c r="I29" t="s">
+        <v>472</v>
+      </c>
+      <c r="J29" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A30" s="52" t="s">
+        <v>19</v>
+      </c>
+      <c r="B30" t="s">
+        <v>533</v>
+      </c>
+      <c r="C30" s="55" t="s">
+        <v>14</v>
+      </c>
+      <c r="D30" s="21" t="s">
+        <v>453</v>
+      </c>
+      <c r="E30" s="47" t="s">
+        <v>454</v>
+      </c>
+      <c r="F30" s="48" t="s">
+        <v>488</v>
+      </c>
+      <c r="G30" t="s">
+        <v>530</v>
+      </c>
+      <c r="H30" t="s">
+        <v>506</v>
+      </c>
+      <c r="I30" t="s">
+        <v>473</v>
+      </c>
+      <c r="J30" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A31" s="52" t="s">
+        <v>19</v>
+      </c>
+      <c r="B31" t="s">
+        <v>533</v>
+      </c>
+      <c r="C31" s="55" t="s">
+        <v>14</v>
+      </c>
+      <c r="D31" s="21" t="s">
+        <v>453</v>
+      </c>
+      <c r="E31" s="47" t="s">
+        <v>454</v>
+      </c>
+      <c r="F31" s="48" t="s">
+        <v>488</v>
+      </c>
+      <c r="G31" t="s">
+        <v>530</v>
+      </c>
+      <c r="H31" t="s">
+        <v>506</v>
+      </c>
+      <c r="I31" t="s">
+        <v>472</v>
+      </c>
+      <c r="J31" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A32" s="52" t="s">
+        <v>19</v>
+      </c>
+      <c r="B32" t="s">
+        <v>304</v>
+      </c>
+      <c r="C32" s="55" t="s">
+        <v>14</v>
+      </c>
+      <c r="D32" s="21" t="s">
+        <v>453</v>
+      </c>
+      <c r="E32" s="47" t="s">
+        <v>454</v>
+      </c>
+      <c r="F32" s="48" t="s">
+        <v>488</v>
+      </c>
+      <c r="G32" t="s">
+        <v>536</v>
+      </c>
+      <c r="H32" t="s">
+        <v>520</v>
+      </c>
+      <c r="I32" t="s">
+        <v>537</v>
+      </c>
+      <c r="J32" t="s">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A33" s="52" t="s">
+        <v>19</v>
+      </c>
+      <c r="B33" t="s">
+        <v>304</v>
+      </c>
+      <c r="C33" s="55" t="s">
+        <v>14</v>
+      </c>
+      <c r="D33" s="21" t="s">
+        <v>453</v>
+      </c>
+      <c r="E33" s="47" t="s">
+        <v>454</v>
+      </c>
+      <c r="F33" s="48" t="s">
+        <v>488</v>
+      </c>
+      <c r="G33" t="s">
+        <v>539</v>
+      </c>
+      <c r="H33" t="s">
+        <v>520</v>
+      </c>
+      <c r="I33" t="s">
+        <v>474</v>
+      </c>
+      <c r="J33" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A34" s="52" t="s">
+        <v>19</v>
+      </c>
+      <c r="B34" t="s">
+        <v>304</v>
+      </c>
+      <c r="C34" s="55" t="s">
+        <v>14</v>
+      </c>
+      <c r="D34" s="21" t="s">
+        <v>453</v>
+      </c>
+      <c r="E34" s="47" t="s">
+        <v>454</v>
+      </c>
+      <c r="F34" s="48" t="s">
+        <v>488</v>
+      </c>
+      <c r="G34" t="s">
+        <v>481</v>
+      </c>
+      <c r="H34" t="s">
+        <v>478</v>
+      </c>
+      <c r="I34" t="s">
+        <v>474</v>
+      </c>
+      <c r="J34" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A35" s="52" t="s">
+        <v>19</v>
+      </c>
+      <c r="B35" t="s">
+        <v>16</v>
+      </c>
+      <c r="C35" s="55" t="s">
+        <v>14</v>
+      </c>
+      <c r="D35" s="21" t="s">
+        <v>453</v>
+      </c>
+      <c r="E35" s="47" t="s">
+        <v>454</v>
+      </c>
+      <c r="F35" s="48" t="s">
+        <v>488</v>
+      </c>
+      <c r="G35" t="s">
+        <v>479</v>
+      </c>
+      <c r="H35" t="s">
+        <v>476</v>
+      </c>
+      <c r="I35" t="s">
+        <v>542</v>
+      </c>
+      <c r="J35" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A36" s="52" t="s">
+        <v>19</v>
+      </c>
+      <c r="B36" t="s">
+        <v>16</v>
+      </c>
+      <c r="C36" s="55" t="s">
+        <v>14</v>
+      </c>
+      <c r="D36" s="21" t="s">
+        <v>453</v>
+      </c>
+      <c r="E36" s="47" t="s">
+        <v>454</v>
+      </c>
+      <c r="F36" s="48" t="s">
+        <v>488</v>
+      </c>
+      <c r="G36" t="s">
+        <v>479</v>
+      </c>
+      <c r="H36" t="s">
+        <v>476</v>
+      </c>
+      <c r="I36" t="s">
+        <v>471</v>
+      </c>
+      <c r="J36" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A37" s="52" t="s">
+        <v>19</v>
+      </c>
+      <c r="B37" t="s">
+        <v>16</v>
+      </c>
+      <c r="C37" s="55" t="s">
+        <v>14</v>
+      </c>
+      <c r="D37" s="21" t="s">
+        <v>453</v>
+      </c>
+      <c r="E37" s="47" t="s">
+        <v>454</v>
+      </c>
+      <c r="F37" s="48" t="s">
+        <v>488</v>
+      </c>
+      <c r="G37" t="s">
+        <v>545</v>
+      </c>
+      <c r="H37" t="s">
+        <v>476</v>
+      </c>
+      <c r="I37" t="s">
+        <v>542</v>
+      </c>
+      <c r="J37" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A38" s="52" t="s">
+        <v>19</v>
+      </c>
+      <c r="B38" t="s">
+        <v>16</v>
+      </c>
+      <c r="C38" s="55" t="s">
+        <v>14</v>
+      </c>
+      <c r="D38" s="21" t="s">
+        <v>453</v>
+      </c>
+      <c r="E38" s="47" t="s">
+        <v>454</v>
+      </c>
+      <c r="F38" s="48" t="s">
+        <v>488</v>
+      </c>
+      <c r="G38" t="s">
+        <v>545</v>
+      </c>
+      <c r="H38" t="s">
+        <v>476</v>
+      </c>
+      <c r="I38" t="s">
+        <v>471</v>
+      </c>
+      <c r="J38" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A39" s="52" t="s">
+        <v>19</v>
+      </c>
+      <c r="B39" t="s">
+        <v>16</v>
+      </c>
+      <c r="C39" s="55" t="s">
+        <v>14</v>
+      </c>
+      <c r="D39" s="21" t="s">
+        <v>453</v>
+      </c>
+      <c r="E39" s="47" t="s">
+        <v>454</v>
+      </c>
+      <c r="F39" s="48" t="s">
+        <v>488</v>
+      </c>
+      <c r="G39" t="s">
+        <v>480</v>
+      </c>
+      <c r="H39" t="s">
+        <v>477</v>
+      </c>
+      <c r="I39" t="s">
+        <v>474</v>
+      </c>
+      <c r="J39" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A40" s="52" t="s">
+        <v>19</v>
+      </c>
+      <c r="B40" t="s">
+        <v>16</v>
+      </c>
+      <c r="C40" s="55" t="s">
+        <v>14</v>
+      </c>
+      <c r="D40" s="21" t="s">
+        <v>453</v>
+      </c>
+      <c r="E40" s="47" t="s">
+        <v>454</v>
+      </c>
+      <c r="F40" s="48" t="s">
+        <v>488</v>
+      </c>
+      <c r="G40" t="s">
+        <v>547</v>
+      </c>
+      <c r="H40" t="s">
+        <v>523</v>
+      </c>
+      <c r="I40" t="s">
+        <v>470</v>
+      </c>
+      <c r="J40" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A41" s="52" t="s">
+        <v>19</v>
+      </c>
+      <c r="B41" t="s">
+        <v>16</v>
+      </c>
+      <c r="C41" s="55" t="s">
+        <v>14</v>
+      </c>
+      <c r="D41" s="21" t="s">
+        <v>453</v>
+      </c>
+      <c r="E41" s="47" t="s">
+        <v>454</v>
+      </c>
+      <c r="F41" s="48" t="s">
+        <v>488</v>
+      </c>
+      <c r="G41" t="s">
+        <v>479</v>
+      </c>
+      <c r="H41" t="s">
+        <v>476</v>
+      </c>
+      <c r="I41" t="s">
+        <v>473</v>
+      </c>
+      <c r="J41" t="s">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A42" s="52" t="s">
+        <v>19</v>
+      </c>
+      <c r="B42" t="s">
+        <v>16</v>
+      </c>
+      <c r="C42" s="55" t="s">
+        <v>14</v>
+      </c>
+      <c r="D42" s="21" t="s">
+        <v>453</v>
+      </c>
+      <c r="E42" s="47" t="s">
+        <v>454</v>
+      </c>
+      <c r="F42" s="48" t="s">
+        <v>488</v>
+      </c>
+      <c r="G42" t="s">
+        <v>545</v>
+      </c>
+      <c r="H42" t="s">
+        <v>476</v>
+      </c>
+      <c r="I42" t="s">
+        <v>473</v>
+      </c>
+      <c r="J42" t="s">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A43" s="52" t="s">
+        <v>19</v>
+      </c>
+      <c r="B43" t="s">
+        <v>550</v>
+      </c>
+      <c r="C43" s="55" t="s">
+        <v>14</v>
+      </c>
+      <c r="D43" s="21" t="s">
+        <v>453</v>
+      </c>
+      <c r="E43" s="47" t="s">
+        <v>454</v>
+      </c>
+      <c r="F43" s="48" t="s">
+        <v>488</v>
+      </c>
+      <c r="G43" t="s">
+        <v>539</v>
+      </c>
+      <c r="H43" t="s">
+        <v>520</v>
+      </c>
+      <c r="I43" t="s">
+        <v>473</v>
+      </c>
+      <c r="J43" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A44" s="52" t="s">
+        <v>19</v>
+      </c>
+      <c r="B44" t="s">
+        <v>550</v>
+      </c>
+      <c r="C44" s="55" t="s">
+        <v>14</v>
+      </c>
+      <c r="D44" s="21" t="s">
+        <v>453</v>
+      </c>
+      <c r="E44" s="47" t="s">
+        <v>454</v>
+      </c>
+      <c r="F44" s="48" t="s">
+        <v>488</v>
+      </c>
+      <c r="G44" t="s">
+        <v>539</v>
+      </c>
+      <c r="H44" t="s">
+        <v>520</v>
+      </c>
+      <c r="I44" t="s">
+        <v>473</v>
+      </c>
+      <c r="J44" t="s">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A45" s="52" t="s">
+        <v>19</v>
+      </c>
+      <c r="B45" t="s">
+        <v>550</v>
+      </c>
+      <c r="C45" s="55" t="s">
+        <v>14</v>
+      </c>
+      <c r="D45" s="21" t="s">
+        <v>453</v>
+      </c>
+      <c r="E45" s="47" t="s">
+        <v>454</v>
+      </c>
+      <c r="F45" s="48" t="s">
+        <v>488</v>
+      </c>
+      <c r="G45" t="s">
+        <v>539</v>
+      </c>
+      <c r="H45" t="s">
+        <v>520</v>
+      </c>
+      <c r="I45" t="s">
+        <v>471</v>
+      </c>
+      <c r="J45" t="s">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A46" s="52" t="s">
+        <v>19</v>
+      </c>
+      <c r="B46" t="s">
+        <v>550</v>
+      </c>
+      <c r="C46" s="55" t="s">
+        <v>14</v>
+      </c>
+      <c r="D46" s="21" t="s">
+        <v>453</v>
+      </c>
+      <c r="E46" s="47" t="s">
+        <v>454</v>
+      </c>
+      <c r="F46" s="48" t="s">
+        <v>488</v>
+      </c>
+      <c r="G46" t="s">
+        <v>515</v>
+      </c>
+      <c r="H46" t="s">
+        <v>477</v>
+      </c>
+      <c r="I46" t="s">
+        <v>471</v>
+      </c>
+      <c r="J46" t="s">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A47" s="52" t="s">
+        <v>19</v>
+      </c>
+      <c r="B47" t="s">
+        <v>550</v>
+      </c>
+      <c r="C47" s="55" t="s">
+        <v>14</v>
+      </c>
+      <c r="D47" s="21" t="s">
+        <v>453</v>
+      </c>
+      <c r="E47" s="47" t="s">
+        <v>454</v>
+      </c>
+      <c r="F47" s="48" t="s">
+        <v>488</v>
+      </c>
+      <c r="G47" t="s">
+        <v>530</v>
+      </c>
+      <c r="H47" t="s">
+        <v>506</v>
+      </c>
+      <c r="I47" t="s">
+        <v>542</v>
+      </c>
+      <c r="J47" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A48" s="52" t="s">
+        <v>19</v>
+      </c>
+      <c r="B48" t="s">
+        <v>132</v>
+      </c>
+      <c r="C48" s="55" t="s">
+        <v>14</v>
+      </c>
+      <c r="D48" s="21" t="s">
+        <v>453</v>
+      </c>
+      <c r="E48" s="47" t="s">
+        <v>454</v>
+      </c>
+      <c r="F48" s="48" t="s">
+        <v>488</v>
+      </c>
+      <c r="G48" t="s">
+        <v>556</v>
+      </c>
+      <c r="H48" t="s">
+        <v>520</v>
+      </c>
+      <c r="I48" t="s">
+        <v>473</v>
+      </c>
+      <c r="J48" t="s">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A49" s="52" t="s">
+        <v>19</v>
+      </c>
+      <c r="B49" t="s">
+        <v>132</v>
+      </c>
+      <c r="C49" s="55" t="s">
+        <v>14</v>
+      </c>
+      <c r="D49" s="21" t="s">
+        <v>453</v>
+      </c>
+      <c r="E49" s="47" t="s">
+        <v>454</v>
+      </c>
+      <c r="F49" s="48" t="s">
+        <v>488</v>
+      </c>
+      <c r="G49" t="s">
+        <v>556</v>
+      </c>
+      <c r="H49" t="s">
+        <v>520</v>
+      </c>
+      <c r="I49" t="s">
+        <v>474</v>
+      </c>
+      <c r="J49" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A50" s="52" t="s">
+        <v>19</v>
+      </c>
+      <c r="B50" t="s">
+        <v>360</v>
+      </c>
+      <c r="C50" s="55" t="s">
+        <v>14</v>
+      </c>
+      <c r="D50" s="21" t="s">
+        <v>453</v>
+      </c>
+      <c r="E50" s="47" t="s">
+        <v>454</v>
+      </c>
+      <c r="F50" s="48" t="s">
+        <v>488</v>
+      </c>
+      <c r="G50" t="s">
+        <v>481</v>
+      </c>
+      <c r="H50" t="s">
+        <v>478</v>
+      </c>
+      <c r="I50" t="s">
+        <v>473</v>
+      </c>
+      <c r="J50" t="s">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A51" s="52" t="s">
+        <v>19</v>
+      </c>
+      <c r="B51" t="s">
+        <v>360</v>
+      </c>
+      <c r="C51" s="55" t="s">
+        <v>14</v>
+      </c>
+      <c r="D51" s="21" t="s">
+        <v>453</v>
+      </c>
+      <c r="E51" s="47" t="s">
+        <v>454</v>
+      </c>
+      <c r="F51" s="48" t="s">
+        <v>488</v>
+      </c>
+      <c r="G51" t="s">
+        <v>515</v>
+      </c>
+      <c r="H51" t="s">
+        <v>477</v>
+      </c>
+      <c r="I51" t="s">
+        <v>474</v>
+      </c>
+      <c r="J51" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A52" s="52" t="s">
+        <v>19</v>
+      </c>
+      <c r="B52" t="s">
+        <v>561</v>
+      </c>
+      <c r="C52" s="55" t="s">
+        <v>14</v>
+      </c>
+      <c r="D52" s="21" t="s">
+        <v>453</v>
+      </c>
+      <c r="E52" s="47" t="s">
+        <v>454</v>
+      </c>
+      <c r="F52" s="48" t="s">
+        <v>488</v>
+      </c>
+      <c r="G52" t="s">
+        <v>515</v>
+      </c>
+      <c r="H52" t="s">
+        <v>477</v>
+      </c>
+      <c r="I52" t="s">
+        <v>474</v>
+      </c>
+      <c r="J52" t="s">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="53" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A53" s="52" t="s">
+        <v>19</v>
+      </c>
+      <c r="B53" t="s">
+        <v>561</v>
+      </c>
+      <c r="C53" s="55" t="s">
+        <v>14</v>
+      </c>
+      <c r="D53" s="21" t="s">
+        <v>453</v>
+      </c>
+      <c r="E53" s="47" t="s">
+        <v>454</v>
+      </c>
+      <c r="F53" s="48" t="s">
+        <v>488</v>
+      </c>
+      <c r="G53" t="s">
+        <v>505</v>
+      </c>
+      <c r="H53" t="s">
+        <v>506</v>
+      </c>
+      <c r="I53" t="s">
+        <v>474</v>
+      </c>
+      <c r="J53" t="s">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A54" s="52" t="s">
+        <v>19</v>
+      </c>
+      <c r="B54" t="s">
+        <v>561</v>
+      </c>
+      <c r="C54" s="55" t="s">
+        <v>14</v>
+      </c>
+      <c r="D54" s="21" t="s">
+        <v>453</v>
+      </c>
+      <c r="E54" s="47" t="s">
+        <v>454</v>
+      </c>
+      <c r="F54" s="48" t="s">
+        <v>488</v>
+      </c>
+      <c r="G54" t="s">
+        <v>479</v>
+      </c>
+      <c r="H54" t="s">
+        <v>476</v>
+      </c>
+      <c r="I54" t="s">
+        <v>470</v>
+      </c>
+      <c r="J54" t="s">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="55" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A55" s="52" t="s">
+        <v>19</v>
+      </c>
+      <c r="B55" t="s">
+        <v>561</v>
+      </c>
+      <c r="C55" s="55" t="s">
+        <v>14</v>
+      </c>
+      <c r="D55" s="21" t="s">
+        <v>453</v>
+      </c>
+      <c r="E55" s="47" t="s">
+        <v>454</v>
+      </c>
+      <c r="F55" s="48" t="s">
+        <v>488</v>
+      </c>
+      <c r="G55" t="s">
+        <v>512</v>
+      </c>
+      <c r="H55" t="s">
+        <v>476</v>
+      </c>
+      <c r="I55" t="s">
+        <v>470</v>
+      </c>
+      <c r="J55" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="56" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A56" s="52" t="s">
+        <v>19</v>
+      </c>
+      <c r="B56" t="s">
+        <v>561</v>
+      </c>
+      <c r="C56" s="55" t="s">
+        <v>14</v>
+      </c>
+      <c r="D56" s="21" t="s">
+        <v>453</v>
+      </c>
+      <c r="E56" s="47" t="s">
+        <v>454</v>
+      </c>
+      <c r="F56" s="48" t="s">
+        <v>488</v>
+      </c>
+      <c r="G56" t="s">
+        <v>530</v>
+      </c>
+      <c r="H56" t="s">
+        <v>506</v>
+      </c>
+      <c r="I56" t="s">
+        <v>470</v>
+      </c>
+      <c r="J56" t="s">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="57" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A57" s="52" t="s">
+        <v>19</v>
+      </c>
+      <c r="B57" t="s">
+        <v>567</v>
+      </c>
+      <c r="C57" s="55" t="s">
+        <v>14</v>
+      </c>
+      <c r="D57" s="21" t="s">
+        <v>453</v>
+      </c>
+      <c r="E57" s="47" t="s">
+        <v>454</v>
+      </c>
+      <c r="F57" s="48" t="s">
+        <v>488</v>
+      </c>
+      <c r="G57" t="s">
+        <v>479</v>
+      </c>
+      <c r="H57" t="s">
+        <v>476</v>
+      </c>
+      <c r="I57" t="s">
+        <v>473</v>
+      </c>
+      <c r="J57" t="s">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="58" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A58" s="52" t="s">
+        <v>19</v>
+      </c>
+      <c r="B58" t="s">
+        <v>569</v>
+      </c>
+      <c r="C58" s="55" t="s">
+        <v>14</v>
+      </c>
+      <c r="D58" s="21" t="s">
+        <v>453</v>
+      </c>
+      <c r="E58" s="47" t="s">
+        <v>454</v>
+      </c>
+      <c r="F58" s="48" t="s">
+        <v>488</v>
+      </c>
+      <c r="G58" t="s">
+        <v>556</v>
+      </c>
+      <c r="H58" t="s">
+        <v>520</v>
+      </c>
+      <c r="I58" t="s">
+        <v>473</v>
+      </c>
+      <c r="J58" t="s">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="59" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A59" s="52" t="s">
+        <v>19</v>
+      </c>
+      <c r="B59" t="s">
+        <v>571</v>
+      </c>
+      <c r="C59" s="55" t="s">
+        <v>14</v>
+      </c>
+      <c r="D59" s="21" t="s">
+        <v>453</v>
+      </c>
+      <c r="E59" s="47" t="s">
+        <v>454</v>
+      </c>
+      <c r="F59" s="48" t="s">
+        <v>488</v>
+      </c>
+      <c r="G59" t="s">
+        <v>572</v>
+      </c>
+      <c r="H59" t="s">
+        <v>573</v>
+      </c>
+      <c r="I59" t="s">
+        <v>542</v>
+      </c>
+      <c r="J59" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="60" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A60" s="52" t="s">
+        <v>19</v>
+      </c>
+      <c r="B60" t="s">
+        <v>320</v>
+      </c>
+      <c r="C60" s="55" t="s">
+        <v>14</v>
+      </c>
+      <c r="D60" s="21" t="s">
+        <v>453</v>
+      </c>
+      <c r="E60" s="47" t="s">
+        <v>454</v>
+      </c>
+      <c r="F60" s="48" t="s">
+        <v>488</v>
+      </c>
+      <c r="G60" t="s">
+        <v>515</v>
+      </c>
+      <c r="H60" t="s">
+        <v>477</v>
+      </c>
+      <c r="I60" t="s">
+        <v>474</v>
+      </c>
+      <c r="J60" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="61" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A61" s="52" t="s">
+        <v>19</v>
+      </c>
+      <c r="B61" t="s">
+        <v>320</v>
+      </c>
+      <c r="C61" s="55" t="s">
+        <v>14</v>
+      </c>
+      <c r="D61" s="21" t="s">
+        <v>453</v>
+      </c>
+      <c r="E61" s="47" t="s">
+        <v>454</v>
+      </c>
+      <c r="F61" s="48" t="s">
+        <v>488</v>
+      </c>
+      <c r="G61" t="s">
+        <v>480</v>
+      </c>
+      <c r="H61" t="s">
+        <v>477</v>
+      </c>
+      <c r="I61" t="s">
+        <v>474</v>
+      </c>
+      <c r="J61" t="s">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="62" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A62" s="52" t="s">
+        <v>19</v>
+      </c>
+      <c r="B62" t="s">
+        <v>320</v>
+      </c>
+      <c r="C62" s="55" t="s">
+        <v>14</v>
+      </c>
+      <c r="D62" s="21" t="s">
+        <v>453</v>
+      </c>
+      <c r="E62" s="47" t="s">
+        <v>454</v>
+      </c>
+      <c r="F62" s="48" t="s">
+        <v>488</v>
+      </c>
+      <c r="G62" t="s">
+        <v>481</v>
+      </c>
+      <c r="H62" t="s">
+        <v>478</v>
+      </c>
+      <c r="I62" t="s">
+        <v>474</v>
+      </c>
+      <c r="J62" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="63" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A63" s="52" t="s">
+        <v>19</v>
+      </c>
+      <c r="B63" t="s">
+        <v>320</v>
+      </c>
+      <c r="C63" s="55" t="s">
+        <v>14</v>
+      </c>
+      <c r="D63" s="21" t="s">
+        <v>453</v>
+      </c>
+      <c r="E63" s="47" t="s">
+        <v>454</v>
+      </c>
+      <c r="F63" s="48" t="s">
+        <v>488</v>
+      </c>
+      <c r="G63" t="s">
+        <v>578</v>
+      </c>
+      <c r="H63" t="s">
+        <v>579</v>
+      </c>
+      <c r="I63" t="s">
+        <v>472</v>
+      </c>
+      <c r="J63" t="s">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="64" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A64" s="52" t="s">
+        <v>19</v>
+      </c>
+      <c r="B64" t="s">
+        <v>291</v>
+      </c>
+      <c r="C64" s="55" t="s">
+        <v>14</v>
+      </c>
+      <c r="D64" s="21" t="s">
+        <v>453</v>
+      </c>
+      <c r="E64" s="47" t="s">
+        <v>454</v>
+      </c>
+      <c r="F64" s="48" t="s">
+        <v>488</v>
+      </c>
+      <c r="G64" t="s">
+        <v>481</v>
+      </c>
+      <c r="H64" t="s">
+        <v>478</v>
+      </c>
+      <c r="I64" t="s">
+        <v>474</v>
+      </c>
+      <c r="J64" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="65" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A65" s="52" t="s">
+        <v>19</v>
+      </c>
+      <c r="B65" t="s">
+        <v>581</v>
+      </c>
+      <c r="C65" s="55" t="s">
+        <v>14</v>
+      </c>
+      <c r="D65" s="21" t="s">
+        <v>453</v>
+      </c>
+      <c r="E65" s="47" t="s">
+        <v>454</v>
+      </c>
+      <c r="F65" s="48" t="s">
+        <v>488</v>
+      </c>
+      <c r="G65" t="s">
+        <v>582</v>
+      </c>
+      <c r="H65" t="s">
+        <v>476</v>
+      </c>
+      <c r="I65" t="s">
+        <v>473</v>
+      </c>
+      <c r="J65" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="66" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A66" s="52" t="s">
+        <v>19</v>
+      </c>
+      <c r="B66" t="s">
+        <v>584</v>
+      </c>
+      <c r="C66" s="55" t="s">
+        <v>14</v>
+      </c>
+      <c r="D66" s="21" t="s">
+        <v>453</v>
+      </c>
+      <c r="E66" s="47" t="s">
+        <v>454</v>
+      </c>
+      <c r="F66" s="48" t="s">
+        <v>488</v>
+      </c>
+      <c r="G66" t="s">
+        <v>480</v>
+      </c>
+      <c r="H66" t="s">
+        <v>477</v>
+      </c>
+      <c r="I66" t="s">
+        <v>474</v>
+      </c>
+      <c r="J66" t="s">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="67" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A67" s="52" t="s">
+        <v>19</v>
+      </c>
+      <c r="B67" t="s">
+        <v>584</v>
+      </c>
+      <c r="C67" s="55" t="s">
+        <v>14</v>
+      </c>
+      <c r="D67" s="21" t="s">
+        <v>453</v>
+      </c>
+      <c r="E67" s="47" t="s">
+        <v>454</v>
+      </c>
+      <c r="F67" s="48" t="s">
+        <v>488</v>
+      </c>
+      <c r="G67" t="s">
+        <v>481</v>
+      </c>
+      <c r="H67" t="s">
+        <v>478</v>
+      </c>
+      <c r="I67" t="s">
+        <v>474</v>
+      </c>
+      <c r="J67" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="68" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A68" s="52" t="s">
+        <v>19</v>
+      </c>
+      <c r="B68" t="s">
+        <v>39</v>
+      </c>
+      <c r="C68" s="55" t="s">
+        <v>14</v>
+      </c>
+      <c r="D68" s="21" t="s">
+        <v>453</v>
+      </c>
+      <c r="E68" s="47" t="s">
+        <v>454</v>
+      </c>
+      <c r="F68" s="48" t="s">
+        <v>488</v>
+      </c>
+      <c r="G68" t="s">
+        <v>480</v>
+      </c>
+      <c r="H68" t="s">
+        <v>477</v>
+      </c>
+      <c r="I68" t="s">
+        <v>470</v>
+      </c>
+      <c r="J68" t="s">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="69" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A69" s="52" t="s">
+        <v>19</v>
+      </c>
+      <c r="B69" t="s">
+        <v>39</v>
+      </c>
+      <c r="C69" s="55" t="s">
+        <v>14</v>
+      </c>
+      <c r="D69" s="21" t="s">
+        <v>453</v>
+      </c>
+      <c r="E69" s="47" t="s">
+        <v>454</v>
+      </c>
+      <c r="F69" s="48" t="s">
+        <v>488</v>
+      </c>
+      <c r="G69" t="s">
+        <v>588</v>
+      </c>
+      <c r="H69" t="s">
+        <v>589</v>
+      </c>
+      <c r="I69" t="s">
+        <v>470</v>
+      </c>
+      <c r="J69" t="s">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="70" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+      <c r="A70" s="52" t="s">
+        <v>19</v>
+      </c>
+      <c r="B70" s="49" t="s">
         <v>378</v>
       </c>
-      <c r="C7" s="43" t="s">
+      <c r="C70" s="54" t="s">
         <v>493</v>
       </c>
-      <c r="D7" s="44" t="s">
+      <c r="D70" s="21" t="s">
         <v>453</v>
       </c>
-      <c r="E7" s="45" t="s">
+      <c r="E70" s="47" t="s">
         <v>454</v>
       </c>
-      <c r="F7" s="46" t="s">
+      <c r="F70" s="48" t="s">
         <v>488</v>
       </c>
-      <c r="G7" s="27" t="s">
+      <c r="G70" s="49" t="s">
         <v>480</v>
       </c>
-      <c r="H7" s="27" t="s">
+      <c r="H70" s="49" t="s">
         <v>477</v>
       </c>
-      <c r="I7" s="28" t="s">
+      <c r="I70" s="50" t="s">
         <v>474</v>
       </c>
-      <c r="J7" s="29" t="s">
+      <c r="J70" s="51" t="s">
         <v>466</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A8" s="42" t="s">
-        <v>19</v>
-      </c>
-      <c r="B8" s="27" t="s">
+    <row r="71" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+      <c r="A71" s="52" t="s">
+        <v>19</v>
+      </c>
+      <c r="B71" s="49" t="s">
         <v>340</v>
       </c>
-      <c r="C8" s="27" t="s">
+      <c r="C71" s="56" t="s">
         <v>485</v>
       </c>
-      <c r="D8" s="44" t="s">
+      <c r="D71" s="21" t="s">
         <v>453</v>
       </c>
-      <c r="E8" s="45" t="s">
+      <c r="E71" s="47" t="s">
         <v>454</v>
       </c>
-      <c r="F8" s="46" t="s">
+      <c r="F71" s="48" t="s">
         <v>488</v>
       </c>
-      <c r="G8" s="27" t="s">
+      <c r="G71" s="49" t="s">
         <v>481</v>
       </c>
-      <c r="H8" s="27" t="s">
+      <c r="H71" s="49" t="s">
         <v>478</v>
       </c>
-      <c r="I8" s="28" t="s">
+      <c r="I71" s="50" t="s">
         <v>474</v>
       </c>
-      <c r="J8" s="29" t="s">
+      <c r="J71" s="51" t="s">
         <v>467</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A9" s="42" t="s">
-        <v>19</v>
-      </c>
-      <c r="B9" s="27" t="s">
-        <v>487</v>
-      </c>
-      <c r="C9" s="27" t="s">
-        <v>485</v>
-      </c>
-      <c r="D9" s="44" t="s">
-        <v>453</v>
-      </c>
-      <c r="E9" s="45" t="s">
-        <v>454</v>
-      </c>
-      <c r="F9" s="46" t="s">
-        <v>488</v>
-      </c>
-      <c r="G9" s="27" t="s">
-        <v>482</v>
-      </c>
-      <c r="H9" s="27" t="s">
-        <v>476</v>
-      </c>
-      <c r="I9" s="28" t="s">
-        <v>471</v>
-      </c>
-      <c r="J9" s="29" t="s">
-        <v>468</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A10" s="42" t="s">
-        <v>19</v>
-      </c>
-      <c r="B10" s="27" t="s">
-        <v>487</v>
-      </c>
-      <c r="C10" s="27" t="s">
-        <v>485</v>
-      </c>
-      <c r="D10" s="44" t="s">
-        <v>453</v>
-      </c>
-      <c r="E10" s="45" t="s">
-        <v>454</v>
-      </c>
-      <c r="F10" s="46" t="s">
-        <v>488</v>
-      </c>
-      <c r="G10" s="27" t="s">
-        <v>482</v>
-      </c>
-      <c r="H10" s="27" t="s">
-        <v>476</v>
-      </c>
-      <c r="I10" s="28" t="s">
-        <v>475</v>
-      </c>
-      <c r="J10" s="29" t="s">
-        <v>469</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A11" s="42" t="s">
-        <v>19</v>
-      </c>
-      <c r="B11" s="27" t="s">
-        <v>487</v>
-      </c>
-      <c r="C11" s="27" t="s">
-        <v>485</v>
-      </c>
-      <c r="D11" s="44" t="s">
-        <v>453</v>
-      </c>
-      <c r="E11" s="45" t="s">
-        <v>454</v>
-      </c>
-      <c r="F11" s="46" t="s">
-        <v>488</v>
-      </c>
-      <c r="G11" s="27" t="s">
-        <v>481</v>
-      </c>
-      <c r="H11" s="27" t="s">
-        <v>478</v>
-      </c>
-      <c r="I11" s="28" t="s">
-        <v>471</v>
-      </c>
-      <c r="J11" s="29" t="s">
-        <v>468</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A12" s="42" t="s">
-        <v>19</v>
-      </c>
-      <c r="B12" s="27" t="s">
-        <v>487</v>
-      </c>
-      <c r="C12" s="27" t="s">
-        <v>485</v>
-      </c>
-      <c r="D12" s="44" t="s">
-        <v>453</v>
-      </c>
-      <c r="E12" s="45" t="s">
-        <v>454</v>
-      </c>
-      <c r="F12" s="46" t="s">
-        <v>488</v>
-      </c>
-      <c r="G12" s="27" t="s">
-        <v>481</v>
-      </c>
-      <c r="H12" s="27" t="s">
-        <v>478</v>
-      </c>
-      <c r="I12" s="28" t="s">
-        <v>475</v>
-      </c>
-      <c r="J12" s="29" t="s">
-        <v>469</v>
       </c>
     </row>
   </sheetData>
@@ -9325,10 +11511,11 @@
     <mergeCell ref="F1:I1"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="C3" r:id="rId1" xr:uid="{E7EBFD69-AB42-1D4C-B09F-BC06AC0B1941}"/>
-    <hyperlink ref="C4" r:id="rId2" xr:uid="{19F34C30-987C-8A4F-A400-AB95B6919C72}"/>
-    <hyperlink ref="C5" r:id="rId3" xr:uid="{EB4AB897-0111-9A4F-A836-A7EA2313DA8B}"/>
-    <hyperlink ref="C6" r:id="rId4" xr:uid="{849BF08E-F4EA-6945-93EA-AD080F320746}"/>
+    <hyperlink ref="C15" r:id="rId1" xr:uid="{294DB162-98E0-4B40-B781-02251F467A27}"/>
+    <hyperlink ref="C11" r:id="rId2" xr:uid="{8C07C59C-DA86-4C8D-9DA6-4A5AD6B80303}"/>
+    <hyperlink ref="C10" r:id="rId3" xr:uid="{B5671DF9-3065-42E2-9796-B313A496FC76}"/>
+    <hyperlink ref="C14" r:id="rId4" xr:uid="{E53E5D07-BD2D-4B6C-B0A0-EF6A87F85B42}"/>
+    <hyperlink ref="C70" r:id="rId5" xr:uid="{AC230D2C-F23B-4440-90A7-C101B0AB6EAB}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -9337,18 +11524,18 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E0B35E6D-763F-4C40-91D2-473BE7766F62}">
   <dimension ref="A1:B22"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="20.5" customWidth="1"/>
-    <col min="2" max="2" width="105.1640625" customWidth="1"/>
+    <col min="1" max="1" width="20.42578125" customWidth="1"/>
+    <col min="2" max="2" width="105.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>145</v>
       </c>
@@ -9356,7 +11543,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>24</v>
       </c>
@@ -9364,7 +11551,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>23</v>
       </c>
@@ -9372,7 +11559,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>149</v>
       </c>
@@ -9380,7 +11567,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>151</v>
       </c>
@@ -9388,7 +11575,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>80</v>
       </c>
@@ -9396,7 +11583,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>81</v>
       </c>
@@ -9404,7 +11591,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>155</v>
       </c>
@@ -9412,7 +11599,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>157</v>
       </c>
@@ -9420,7 +11607,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>44</v>
       </c>
@@ -9428,7 +11615,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>43</v>
       </c>
@@ -9436,7 +11623,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>21</v>
       </c>
@@ -9444,7 +11631,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>76</v>
       </c>
@@ -9452,7 +11639,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>40</v>
       </c>
@@ -9460,7 +11647,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>164</v>
       </c>
@@ -9468,7 +11655,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>166</v>
       </c>
@@ -9476,7 +11663,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>168</v>
       </c>
@@ -9484,7 +11671,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>170</v>
       </c>
@@ -9492,7 +11679,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>454</v>
       </c>
@@ -9500,7 +11687,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>453</v>
       </c>
@@ -9752,6 +11939,15 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="80b53ead-ac38-442a-b597-5a0e2e0802cd">
@@ -9760,15 +11956,6 @@
     <TaxCatchAll xmlns="5ec1cc48-4270-4222-9ed5-54ce9e59d47b" xsi:nil="true"/>
   </documentManagement>
 </p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -9791,6 +11978,14 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3B1B5D08-A2EB-4F47-BA81-DA28AA2A09F4}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{66AF2240-620B-4312-9739-CAF731E4A98F}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
@@ -9799,12 +11994,4 @@
     <ds:schemaRef ds:uri="5ec1cc48-4270-4222-9ed5-54ce9e59d47b"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3B1B5D08-A2EB-4F47-BA81-DA28AA2A09F4}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/EEE2000-metadata_mapping.xlsx
+++ b/EEE2000-metadata_mapping.xlsx
@@ -1,21 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10920"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://stfc365-my.sharepoint.com/personal/alison_waterfall_stfc_ac_uk/Documents/Documents/GitHub/cci_data_bridge_inputs/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rhys.r.evans/Documents/CEDA/CCI/cci_data_bridge_inputs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{0AAB98B8-BC09-4544-B40F-5DB8A5DD5A44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0C817DEB-570A-4AB7-A3FA-074D47EFF721}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA4E4495-34F6-ED4D-9D62-526DD6082160}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="42060" yWindow="4590" windowWidth="28800" windowHeight="15345" activeTab="1" xr2:uid="{B9DA58AC-C110-4CBA-A19B-6F37B44EEA38}"/>
+    <workbookView xWindow="2520" yWindow="880" windowWidth="28800" windowHeight="15340" activeTab="1" xr2:uid="{B9DA58AC-C110-4CBA-A19B-6F37B44EEA38}"/>
   </bookViews>
   <sheets>
     <sheet name="Mapping" sheetId="2" r:id="rId1"/>
-    <sheet name="Technique Mapping" sheetId="3" r:id="rId2"/>
-    <sheet name="Relationship definitions" sheetId="1" r:id="rId3"/>
+    <sheet name="Relationship definitions" sheetId="1" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Mapping!$L$1:$L$94</definedName>
@@ -41,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2424" uniqueCount="591">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1722" uniqueCount="460">
   <si>
     <t>Dataset 1</t>
   </si>
@@ -1757,399 +1756,6 @@
   </si>
   <si>
     <t>Indicates A is used by B</t>
-  </si>
-  <si>
-    <t>Type</t>
-  </si>
-  <si>
-    <t>Category</t>
-  </si>
-  <si>
-    <t>Classification of forest change</t>
-  </si>
-  <si>
-    <t>Uncertainty estimation of bias</t>
-  </si>
-  <si>
-    <t>Harmonise Sentinel-3 and MODIS</t>
-  </si>
-  <si>
-    <t>Classification of burned area</t>
-  </si>
-  <si>
-    <t>Identify albedo/snow before LAI calculated</t>
-  </si>
-  <si>
-    <t>Cloud screening for filtering</t>
-  </si>
-  <si>
-    <t>Generate cal/val datasets</t>
-  </si>
-  <si>
-    <t>Emulate physical models</t>
-  </si>
-  <si>
-    <t>Modelling</t>
-  </si>
-  <si>
-    <t>Accuracy</t>
-  </si>
-  <si>
-    <t>Data assimilation</t>
-  </si>
-  <si>
-    <t>Generation</t>
-  </si>
-  <si>
-    <t>Processing</t>
-  </si>
-  <si>
-    <t>Computational efficiency</t>
-  </si>
-  <si>
-    <t>Machine Learning – supervised</t>
-  </si>
-  <si>
-    <t>Machine Learning – unsupervised</t>
-  </si>
-  <si>
-    <t>Deep Learning – unspecified neural networks</t>
-  </si>
-  <si>
-    <t>Random Forest</t>
-  </si>
-  <si>
-    <t>Principle Component Analysis</t>
-  </si>
-  <si>
-    <t>Neural Network</t>
-  </si>
-  <si>
-    <t>Gaussian Process Regression</t>
-  </si>
-  <si>
-    <t>Datatset ID</t>
-  </si>
-  <si>
-    <t>Project</t>
-  </si>
-  <si>
-    <t xml:space="preserve">- </t>
-  </si>
-  <si>
-    <t>Biomass</t>
-  </si>
-  <si>
-    <t>Anthropogenic Water Use</t>
-  </si>
-  <si>
-    <t>AI</t>
-  </si>
-  <si>
-    <t>Use</t>
-  </si>
-  <si>
-    <t>User</t>
-  </si>
-  <si>
-    <t>Data provider</t>
-  </si>
-  <si>
-    <t>https://catalogue.ceda.ac.uk/uuid/db75c5f51ee240ae8743355dcebbb9b9</t>
-  </si>
-  <si>
-    <t>https://catalogue.ceda.ac.uk/uuid/8d02d224437247f6a6270a575d457bd8</t>
-  </si>
-  <si>
-    <t>Relationship (User to Technique)</t>
-  </si>
-  <si>
-    <t>Relationship (Technique to User)</t>
-  </si>
-  <si>
-    <t>Technique</t>
-  </si>
-  <si>
-    <t>Sub Type</t>
-  </si>
-  <si>
-    <t>https://catalogue.ceda.ac.uk/uuid/6429d1aafe1e43b9b414e4a5a7f8b903</t>
-  </si>
-  <si>
-    <t>Light Gradient Boosting</t>
-  </si>
-  <si>
-    <t>Bias correction</t>
-  </si>
-  <si>
-    <t>Retrieval of dust</t>
-  </si>
-  <si>
-    <t>Classification of irrigation</t>
-  </si>
-  <si>
-    <t>Cloud mask</t>
-  </si>
-  <si>
-    <t>Determine cloud parameters</t>
-  </si>
-  <si>
-    <t>Convolutional Neural Network</t>
-  </si>
-  <si>
-    <t>Deep Learning – convolutional neural networks</t>
-  </si>
-  <si>
-    <t>Combining SAR and optical</t>
-  </si>
-  <si>
-    <t>Uncertainty classification probabilities</t>
-  </si>
-  <si>
-    <t>GHGs</t>
-  </si>
-  <si>
-    <t>Cloud coverage pre-filtering</t>
-  </si>
-  <si>
-    <t>Quality-filtering and predicting bias</t>
-  </si>
-  <si>
-    <t>Extreme Gradient Boosting</t>
-  </si>
-  <si>
-    <t>Quality-filtering</t>
-  </si>
-  <si>
-    <t>HRLC</t>
-  </si>
-  <si>
-    <t>K-means clustering</t>
-  </si>
-  <si>
-    <t>Binary water extraction from SAR</t>
-  </si>
-  <si>
-    <t>Weak Supervision</t>
-  </si>
-  <si>
-    <t>Pretraining classification with thematic maps</t>
-  </si>
-  <si>
-    <t>Siamese Multi-Layer Perceptron</t>
-  </si>
-  <si>
-    <t>Deep Learning – feed-forward neural networks</t>
-  </si>
-  <si>
-    <t>Decision fusion between optical and SAR</t>
-  </si>
-  <si>
-    <t>Vision Transformer</t>
-  </si>
-  <si>
-    <t>Deep Learning – transformers</t>
-  </si>
-  <si>
-    <t>Classification of land cover from optical</t>
-  </si>
-  <si>
-    <t>Encoder-Decoder Transformer</t>
-  </si>
-  <si>
-    <t>Classification of land cover from SAR</t>
-  </si>
-  <si>
-    <t>Ice Sheets (Antarctica)</t>
-  </si>
-  <si>
-    <t>Holistically-Nested Edge Detection</t>
-  </si>
-  <si>
-    <t>Delineate grounding lines of ice shelves</t>
-  </si>
-  <si>
-    <t>U-Net Convolutional Neural Network</t>
-  </si>
-  <si>
-    <t>Delineate ice shelf coastlines</t>
-  </si>
-  <si>
-    <t>Combining SAR and altimetry data</t>
-  </si>
-  <si>
-    <t>Ice Sheets (Greenland)</t>
-  </si>
-  <si>
-    <t>Classification of supraglacial lakes</t>
-  </si>
-  <si>
-    <t>Combining SAR and optical data</t>
-  </si>
-  <si>
-    <t>Back Propagation Neural Network</t>
-  </si>
-  <si>
-    <t>Gap-filling</t>
-  </si>
-  <si>
-    <t>Producing gap-filled LSWT/ LIC dataset</t>
-  </si>
-  <si>
-    <t>Multi-layer Perceptron Neural Network</t>
-  </si>
-  <si>
-    <t>Define water level relation with altimetry</t>
-  </si>
-  <si>
-    <t>First-order water detection</t>
-  </si>
-  <si>
-    <t>Resolution enhancement</t>
-  </si>
-  <si>
-    <t>Transfer to various spatial resolution data</t>
-  </si>
-  <si>
-    <t>Quantify classification uncertainty per pixel</t>
-  </si>
-  <si>
-    <t>Gradient Boosting</t>
-  </si>
-  <si>
-    <t>Reduce hyperspectral dimensionality</t>
-  </si>
-  <si>
-    <t>Encoder Transformer</t>
-  </si>
-  <si>
-    <t>Change detection benchmarking</t>
-  </si>
-  <si>
-    <t>Classify reflectance into land cover types</t>
-  </si>
-  <si>
-    <t>LST</t>
-  </si>
-  <si>
-    <t>Retrieve LST from brightness temperature</t>
-  </si>
-  <si>
-    <t>Generate fractional vegetation cover</t>
-  </si>
-  <si>
-    <t>Estimate retrieval uncertainty</t>
-  </si>
-  <si>
-    <t>Cluster retrieval errors for calibration</t>
-  </si>
-  <si>
-    <t>Downscaling microwave for merged product</t>
-  </si>
-  <si>
-    <t>Feed-forward Neural Network</t>
-  </si>
-  <si>
-    <t>Retrieve water Inherent Optical Properties</t>
-  </si>
-  <si>
-    <t>Atmospheric correction</t>
-  </si>
-  <si>
-    <t>Predict ozone profiles</t>
-  </si>
-  <si>
-    <t>Grouping of conditions for separate models</t>
-  </si>
-  <si>
-    <t>Permafrost</t>
-  </si>
-  <si>
-    <t>Generate land cover unit parameters</t>
-  </si>
-  <si>
-    <t>Processing super-resolution land cover units</t>
-  </si>
-  <si>
-    <t>Use case on drivers</t>
-  </si>
-  <si>
-    <t>Use case on drivers and impacts</t>
-  </si>
-  <si>
-    <t>Use case on impacts</t>
-  </si>
-  <si>
-    <t>Phyto</t>
-  </si>
-  <si>
-    <t>Derive phytoplankton pigments</t>
-  </si>
-  <si>
-    <t>Precursors</t>
-  </si>
-  <si>
-    <t>Convert radiance into column abundance</t>
-  </si>
-  <si>
-    <t>SAGE</t>
-  </si>
-  <si>
-    <t>Diffusion Models</t>
-  </si>
-  <si>
-    <t>Deep Learning – generative models</t>
-  </si>
-  <si>
-    <t>Enhance resolution of old microwave data</t>
-  </si>
-  <si>
-    <t>Extract waveform clusters for training</t>
-  </si>
-  <si>
-    <t>Cross-channel ice signature identification</t>
-  </si>
-  <si>
-    <t>Set waveform cutoff for radar retrieval</t>
-  </si>
-  <si>
-    <t>Graph Neural Network</t>
-  </si>
-  <si>
-    <t>Deep Learning – graph neural networks</t>
-  </si>
-  <si>
-    <t>Processing old microwave records to extend</t>
-  </si>
-  <si>
-    <t>Sea State</t>
-  </si>
-  <si>
-    <t>Support Vector Machine</t>
-  </si>
-  <si>
-    <t>Estimate significant wave height</t>
-  </si>
-  <si>
-    <t>Sea Surface Salinity</t>
-  </si>
-  <si>
-    <t>Remove radio-frequency interference</t>
-  </si>
-  <si>
-    <t>Remove geophysical effects</t>
-  </si>
-  <si>
-    <t>Attribution of SST variability modelling</t>
-  </si>
-  <si>
-    <t>Long Short Term Memory</t>
-  </si>
-  <si>
-    <t>Deep Learning – recurrent neural networks</t>
-  </si>
-  <si>
-    <t>Predicting future SST modelling</t>
   </si>
 </sst>
 </file>
@@ -2159,7 +1765,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd;@"/>
   </numFmts>
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2202,38 +1808,6 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF212529"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF212529"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="10"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -2261,7 +1835,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="11">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -2342,43 +1916,12 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="57">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -2432,41 +1975,6 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2484,39 +1992,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2834,36 +2309,36 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9CC0B67C-1229-4907-A814-DF79422D0B81}">
   <dimension ref="A1:M170"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="36.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19.42578125" customWidth="1"/>
-    <col min="3" max="3" width="30.140625" customWidth="1"/>
-    <col min="4" max="4" width="38.42578125" customWidth="1"/>
-    <col min="5" max="5" width="23.42578125" customWidth="1"/>
-    <col min="6" max="6" width="23.42578125" style="6" customWidth="1"/>
-    <col min="7" max="7" width="30.42578125" style="9" customWidth="1"/>
-    <col min="8" max="8" width="30.42578125" style="12" customWidth="1"/>
-    <col min="9" max="9" width="42.85546875" style="4" customWidth="1"/>
-    <col min="10" max="10" width="19.42578125" style="4" customWidth="1"/>
-    <col min="11" max="11" width="19.42578125" customWidth="1"/>
-    <col min="12" max="12" width="23.42578125" style="6" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="47.140625" style="8" customWidth="1"/>
+    <col min="1" max="1" width="36.83203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.5" customWidth="1"/>
+    <col min="3" max="3" width="30.1640625" customWidth="1"/>
+    <col min="4" max="4" width="38.5" customWidth="1"/>
+    <col min="5" max="5" width="23.5" customWidth="1"/>
+    <col min="6" max="6" width="23.5" style="6" customWidth="1"/>
+    <col min="7" max="7" width="30.5" style="9" customWidth="1"/>
+    <col min="8" max="8" width="30.5" style="12" customWidth="1"/>
+    <col min="9" max="9" width="42.83203125" style="4" customWidth="1"/>
+    <col min="10" max="10" width="19.5" style="4" customWidth="1"/>
+    <col min="11" max="11" width="19.5" customWidth="1"/>
+    <col min="12" max="12" width="23.5" style="6" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="47.1640625" style="8" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A1" s="40" t="s">
+    <row r="1" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+      <c r="A1" s="27" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="40"/>
-      <c r="C1" s="40"/>
-      <c r="D1" s="40"/>
-      <c r="E1" s="40"/>
-      <c r="F1" s="41"/>
-      <c r="G1" s="42" t="s">
+      <c r="B1" s="27"/>
+      <c r="C1" s="27"/>
+      <c r="D1" s="27"/>
+      <c r="E1" s="27"/>
+      <c r="F1" s="28"/>
+      <c r="G1" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="H1" s="44" t="s">
+      <c r="H1" s="31" t="s">
         <v>2</v>
       </c>
       <c r="I1" s="14" t="s">
@@ -2873,7 +2348,7 @@
       <c r="K1" s="3"/>
       <c r="M1" s="17"/>
     </row>
-    <row r="2" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>4</v>
       </c>
@@ -2892,8 +2367,8 @@
       <c r="F2" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="G2" s="43"/>
-      <c r="H2" s="45"/>
+      <c r="G2" s="30"/>
+      <c r="H2" s="32"/>
       <c r="I2" s="15" t="s">
         <v>10</v>
       </c>
@@ -2910,7 +2385,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:13" ht="90" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:13" ht="80" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>13</v>
       </c>
@@ -2951,7 +2426,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="4" spans="1:13" ht="90" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:13" ht="96" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>13</v>
       </c>
@@ -2992,11 +2467,11 @@
         <v>229</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B5" s="19"/>
       <c r="C5" s="19"/>
     </row>
-    <row r="6" spans="1:13" ht="105" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:13" ht="80" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>25</v>
       </c>
@@ -3037,7 +2512,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="7" spans="1:13" ht="90" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:13" ht="80" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>33</v>
       </c>
@@ -3078,7 +2553,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="8" spans="1:13" ht="90" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:13" ht="80" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>35</v>
       </c>
@@ -3119,11 +2594,11 @@
         <v>201</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B9" s="19"/>
       <c r="C9" s="19"/>
     </row>
-    <row r="10" spans="1:13" ht="60" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:13" ht="48" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>38</v>
       </c>
@@ -3164,7 +2639,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="11" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:13" ht="32" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>42</v>
       </c>
@@ -3205,7 +2680,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="12" spans="1:13" ht="120" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:13" ht="96" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>42</v>
       </c>
@@ -3246,7 +2721,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="13" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:13" ht="48" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>42</v>
       </c>
@@ -3287,7 +2762,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="14" spans="1:13" ht="90" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:13" ht="64" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>42</v>
       </c>
@@ -3328,7 +2803,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="15" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:13" ht="48" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>42</v>
       </c>
@@ -3369,7 +2844,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="16" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:13" ht="48" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>42</v>
       </c>
@@ -3410,7 +2885,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="17" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:13" ht="48" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>42</v>
       </c>
@@ -3451,7 +2926,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="18" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:13" ht="48" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>42</v>
       </c>
@@ -3492,7 +2967,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="19" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:13" ht="48" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>42</v>
       </c>
@@ -3533,7 +3008,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="20" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:13" ht="48" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>42</v>
       </c>
@@ -3574,7 +3049,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="21" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:13" ht="48" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>42</v>
       </c>
@@ -3615,7 +3090,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="22" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:13" ht="48" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>42</v>
       </c>
@@ -3656,7 +3131,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="23" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:13" ht="48" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>42</v>
       </c>
@@ -3697,7 +3172,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="24" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:13" ht="48" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>42</v>
       </c>
@@ -3738,7 +3213,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="25" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:13" ht="48" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>42</v>
       </c>
@@ -3779,7 +3254,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="26" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:13" ht="48" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>42</v>
       </c>
@@ -3820,7 +3295,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="27" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:13" ht="48" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>42</v>
       </c>
@@ -3861,7 +3336,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="28" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:13" ht="48" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>42</v>
       </c>
@@ -3902,7 +3377,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="29" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:13" ht="48" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>42</v>
       </c>
@@ -3943,7 +3418,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="30" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:13" ht="48" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>42</v>
       </c>
@@ -3984,7 +3459,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="31" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:13" ht="48" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>42</v>
       </c>
@@ -4025,7 +3500,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="32" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:13" ht="48" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>42</v>
       </c>
@@ -4066,11 +3541,11 @@
         <v>233</v>
       </c>
     </row>
-    <row r="33" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B33" s="19"/>
       <c r="C33" s="19"/>
     </row>
-    <row r="34" spans="1:13" ht="90" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:13" ht="64" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>69</v>
       </c>
@@ -4111,7 +3586,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="35" spans="1:13" ht="90" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:13" ht="64" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>69</v>
       </c>
@@ -4152,11 +3627,11 @@
         <v>220</v>
       </c>
     </row>
-    <row r="36" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B36" s="19"/>
       <c r="C36" s="19"/>
     </row>
-    <row r="37" spans="1:13" ht="75" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:13" ht="80" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>74</v>
       </c>
@@ -4197,7 +3672,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="38" spans="1:13" ht="75" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:13" ht="80" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>74</v>
       </c>
@@ -4238,7 +3713,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="39" spans="1:13" ht="90" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:13" ht="80" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>74</v>
       </c>
@@ -4279,7 +3754,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="40" spans="1:13" ht="90" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:13" ht="80" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>74</v>
       </c>
@@ -4320,7 +3795,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="41" spans="1:13" ht="60" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:13" ht="64" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>74</v>
       </c>
@@ -4361,7 +3836,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="42" spans="1:13" ht="75" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:13" ht="64" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>74</v>
       </c>
@@ -4402,7 +3877,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="43" spans="1:13" ht="75" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:13" ht="80" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>74</v>
       </c>
@@ -4443,7 +3918,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="44" spans="1:13" ht="75" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:13" ht="80" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>85</v>
       </c>
@@ -4484,7 +3959,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="45" spans="1:13" ht="75" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:13" ht="80" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>85</v>
       </c>
@@ -4525,7 +4000,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="46" spans="1:13" ht="90" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:13" ht="80" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
         <v>85</v>
       </c>
@@ -4566,7 +4041,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="47" spans="1:13" ht="90" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:13" ht="80" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
         <v>85</v>
       </c>
@@ -4607,7 +4082,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="48" spans="1:13" ht="90" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:13" ht="80" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
         <v>85</v>
       </c>
@@ -4648,7 +4123,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="49" spans="1:13" ht="90" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:13" ht="80" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
         <v>85</v>
       </c>
@@ -4689,7 +4164,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="50" spans="1:13" ht="75" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:13" ht="80" x14ac:dyDescent="0.2">
       <c r="A50" s="10" t="s">
         <v>85</v>
       </c>
@@ -4730,7 +4205,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="51" spans="1:13" ht="75" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:13" ht="80" x14ac:dyDescent="0.2">
       <c r="A51" s="10"/>
       <c r="B51" s="19">
         <v>43501</v>
@@ -4769,7 +4244,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="52" spans="1:13" ht="75" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:13" ht="80" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
         <v>85</v>
       </c>
@@ -4810,7 +4285,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="53" spans="1:13" ht="75" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:13" ht="80" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
         <v>85</v>
       </c>
@@ -4851,7 +4326,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="54" spans="1:13" ht="90" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:13" ht="96" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
         <v>85</v>
       </c>
@@ -4892,7 +4367,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="55" spans="1:13" ht="75" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:13" ht="64" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
         <v>85</v>
       </c>
@@ -4933,12 +4408,12 @@
         <v>236</v>
       </c>
     </row>
-    <row r="56" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A56" s="10"/>
       <c r="B56" s="20"/>
       <c r="C56" s="20"/>
     </row>
-    <row r="57" spans="1:13" ht="60" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:13" ht="64" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
         <v>100</v>
       </c>
@@ -4979,7 +4454,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="58" spans="1:13" ht="60" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:13" ht="64" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
         <v>100</v>
       </c>
@@ -5020,7 +4495,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="59" spans="1:13" ht="60" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:13" ht="64" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
         <v>100</v>
       </c>
@@ -5061,7 +4536,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="60" spans="1:13" ht="60" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:13" ht="64" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
         <v>100</v>
       </c>
@@ -5102,7 +4577,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="61" spans="1:13" ht="90" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:13" ht="96" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
         <v>100</v>
       </c>
@@ -5143,7 +4618,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="62" spans="1:13" ht="105" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:13" ht="96" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
         <v>100</v>
       </c>
@@ -5184,7 +4659,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="63" spans="1:13" ht="90" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:13" ht="96" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
         <v>100</v>
       </c>
@@ -5225,7 +4700,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="64" spans="1:13" ht="105" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:13" ht="96" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
         <v>100</v>
       </c>
@@ -5266,7 +4741,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="65" spans="1:13" ht="60" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:13" ht="64" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
         <v>100</v>
       </c>
@@ -5307,7 +4782,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="66" spans="1:13" ht="60" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:13" ht="64" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
         <v>100</v>
       </c>
@@ -5348,7 +4823,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="67" spans="1:13" ht="60" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:13" ht="64" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
         <v>100</v>
       </c>
@@ -5389,7 +4864,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="68" spans="1:13" ht="60" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:13" ht="64" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
         <v>100</v>
       </c>
@@ -5430,7 +4905,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="69" spans="1:13" ht="60" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:13" ht="64" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
         <v>100</v>
       </c>
@@ -5471,7 +4946,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="70" spans="1:13" ht="60" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:13" ht="64" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
         <v>100</v>
       </c>
@@ -5512,7 +4987,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="71" spans="1:13" ht="60" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:13" ht="64" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
         <v>100</v>
       </c>
@@ -5553,7 +5028,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="72" spans="1:13" ht="60" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:13" ht="64" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
         <v>100</v>
       </c>
@@ -5594,7 +5069,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="73" spans="1:13" ht="60" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:13" ht="64" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
         <v>100</v>
       </c>
@@ -5635,11 +5110,11 @@
         <v>238</v>
       </c>
     </row>
-    <row r="74" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B74" s="19"/>
       <c r="C74" s="19"/>
     </row>
-    <row r="75" spans="1:13" ht="90" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:13" ht="64" x14ac:dyDescent="0.2">
       <c r="A75" s="24" t="s">
         <v>131</v>
       </c>
@@ -5680,7 +5155,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="76" spans="1:13" ht="75" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:13" ht="48" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
         <v>131</v>
       </c>
@@ -5721,7 +5196,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="77" spans="1:13" ht="60" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:13" ht="48" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
         <v>131</v>
       </c>
@@ -5762,7 +5237,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="78" spans="1:13" ht="75" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:13" ht="64" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
         <v>131</v>
       </c>
@@ -5803,7 +5278,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="79" spans="1:13" ht="60" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:13" ht="48" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
         <v>131</v>
       </c>
@@ -5844,7 +5319,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="80" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:13" ht="48" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
         <v>131</v>
       </c>
@@ -5885,12 +5360,12 @@
         <v>244</v>
       </c>
     </row>
-    <row r="81" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B81" s="19"/>
       <c r="C81" s="19"/>
       <c r="H81" s="11"/>
     </row>
-    <row r="82" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:13" ht="48" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
         <v>134</v>
       </c>
@@ -5931,7 +5406,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="83" spans="1:13" ht="90" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:13" ht="80" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
         <v>134</v>
       </c>
@@ -5972,7 +5447,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="84" spans="1:13" ht="105" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:13" ht="96" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
         <v>134</v>
       </c>
@@ -6013,7 +5488,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="85" spans="1:13" ht="105" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:13" ht="96" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
         <v>134</v>
       </c>
@@ -6054,7 +5529,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="86" spans="1:13" ht="75" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:13" ht="80" x14ac:dyDescent="0.2">
       <c r="A86" s="24" t="s">
         <v>396</v>
       </c>
@@ -6095,7 +5570,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="87" spans="1:13" ht="120" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:13" ht="112" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
         <v>140</v>
       </c>
@@ -6136,11 +5611,11 @@
         <v>178</v>
       </c>
     </row>
-    <row r="88" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B88" s="19"/>
       <c r="C88" s="19"/>
     </row>
-    <row r="89" spans="1:13" ht="90" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:13" ht="80" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
         <v>131</v>
       </c>
@@ -6181,7 +5656,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="90" spans="1:13" ht="90" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:13" ht="80" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
         <v>131</v>
       </c>
@@ -6222,7 +5697,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="91" spans="1:13" ht="90" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:13" ht="80" x14ac:dyDescent="0.2">
       <c r="A91" t="s">
         <v>131</v>
       </c>
@@ -6263,7 +5738,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="92" spans="1:13" ht="90" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:13" ht="80" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
         <v>131</v>
       </c>
@@ -6304,7 +5779,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="93" spans="1:13" ht="90" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:13" ht="80" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
         <v>131</v>
       </c>
@@ -6345,7 +5820,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="94" spans="1:13" ht="90" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:13" ht="80" x14ac:dyDescent="0.2">
       <c r="A94" t="s">
         <v>131</v>
       </c>
@@ -6386,10 +5861,10 @@
         <v>277</v>
       </c>
     </row>
-    <row r="95" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:13" x14ac:dyDescent="0.2">
       <c r="G95" s="8"/>
     </row>
-    <row r="96" spans="1:13" ht="60" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:13" ht="48" x14ac:dyDescent="0.2">
       <c r="A96" t="s">
         <v>286</v>
       </c>
@@ -6430,11 +5905,11 @@
         <v>395</v>
       </c>
     </row>
-    <row r="97" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B97" s="19"/>
       <c r="C97" s="19"/>
     </row>
-    <row r="98" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:13" ht="48" x14ac:dyDescent="0.2">
       <c r="A98" t="s">
         <v>289</v>
       </c>
@@ -6475,7 +5950,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="100" spans="1:13" ht="90" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:13" ht="80" x14ac:dyDescent="0.2">
       <c r="A100" t="s">
         <v>301</v>
       </c>
@@ -6516,7 +5991,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="101" spans="1:13" ht="75" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:13" ht="64" x14ac:dyDescent="0.2">
       <c r="A101" t="s">
         <v>301</v>
       </c>
@@ -6557,7 +6032,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="102" spans="1:13" ht="195" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:13" ht="176" x14ac:dyDescent="0.2">
       <c r="A102" t="s">
         <v>302</v>
       </c>
@@ -6598,11 +6073,11 @@
         <v>400</v>
       </c>
     </row>
-    <row r="103" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B103" s="19"/>
       <c r="C103" s="19"/>
     </row>
-    <row r="104" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:13" ht="48" x14ac:dyDescent="0.2">
       <c r="A104" t="s">
         <v>315</v>
       </c>
@@ -6643,7 +6118,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="105" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:13" ht="48" x14ac:dyDescent="0.2">
       <c r="A105" t="s">
         <v>315</v>
       </c>
@@ -6684,7 +6159,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="106" spans="1:13" ht="60" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:13" ht="48" x14ac:dyDescent="0.2">
       <c r="A106" t="s">
         <v>315</v>
       </c>
@@ -6725,7 +6200,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="107" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:13" ht="48" x14ac:dyDescent="0.2">
       <c r="A107" t="s">
         <v>405</v>
       </c>
@@ -6766,7 +6241,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="108" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:13" ht="32" x14ac:dyDescent="0.2">
       <c r="A108" s="4" t="s">
         <v>330</v>
       </c>
@@ -6807,7 +6282,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="109" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:13" ht="48" x14ac:dyDescent="0.2">
       <c r="A109" t="s">
         <v>405</v>
       </c>
@@ -6848,7 +6323,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="110" spans="1:13" ht="75" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:13" ht="80" x14ac:dyDescent="0.2">
       <c r="A110" t="s">
         <v>405</v>
       </c>
@@ -6889,7 +6364,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="111" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:13" ht="32" x14ac:dyDescent="0.2">
       <c r="A111" t="s">
         <v>331</v>
       </c>
@@ -6930,7 +6405,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="112" spans="1:13" ht="75" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:13" ht="80" x14ac:dyDescent="0.2">
       <c r="A112" t="s">
         <v>405</v>
       </c>
@@ -6971,7 +6446,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="113" spans="1:13" ht="75" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:13" ht="80" x14ac:dyDescent="0.2">
       <c r="A113" t="s">
         <v>405</v>
       </c>
@@ -7012,11 +6487,11 @@
         <v>408</v>
       </c>
     </row>
-    <row r="114" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B114" s="19"/>
       <c r="C114" s="19"/>
     </row>
-    <row r="115" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:13" ht="32" x14ac:dyDescent="0.2">
       <c r="A115" t="s">
         <v>343</v>
       </c>
@@ -7057,7 +6532,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="116" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:13" ht="16" x14ac:dyDescent="0.2">
       <c r="A116" t="s">
         <v>342</v>
       </c>
@@ -7098,7 +6573,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="117" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:13" ht="32" x14ac:dyDescent="0.2">
       <c r="A117" t="s">
         <v>342</v>
       </c>
@@ -7139,11 +6614,11 @@
         <v>346</v>
       </c>
     </row>
-    <row r="118" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B118" s="19"/>
       <c r="C118" s="19"/>
     </row>
-    <row r="119" spans="1:13" ht="75" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:13" ht="80" x14ac:dyDescent="0.2">
       <c r="A119" s="24" t="s">
         <v>349</v>
       </c>
@@ -7184,7 +6659,7 @@
         <v>415</v>
       </c>
     </row>
-    <row r="120" spans="1:13" ht="75" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:13" ht="80" x14ac:dyDescent="0.2">
       <c r="A120" t="s">
         <v>349</v>
       </c>
@@ -7225,7 +6700,7 @@
         <v>416</v>
       </c>
     </row>
-    <row r="121" spans="1:13" ht="75" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:13" ht="80" x14ac:dyDescent="0.2">
       <c r="A121" t="s">
         <v>349</v>
       </c>
@@ -7266,7 +6741,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="122" spans="1:13" ht="75" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:13" ht="80" x14ac:dyDescent="0.2">
       <c r="A122" t="s">
         <v>349</v>
       </c>
@@ -7307,7 +6782,7 @@
         <v>418</v>
       </c>
     </row>
-    <row r="123" spans="1:13" ht="75" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:13" ht="80" x14ac:dyDescent="0.2">
       <c r="A123" t="s">
         <v>349</v>
       </c>
@@ -7348,7 +6823,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="124" spans="1:13" ht="75" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:13" ht="80" x14ac:dyDescent="0.2">
       <c r="A124" t="s">
         <v>349</v>
       </c>
@@ -7389,7 +6864,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="125" spans="1:13" ht="90" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:13" ht="80" x14ac:dyDescent="0.2">
       <c r="A125" t="s">
         <v>349</v>
       </c>
@@ -7430,7 +6905,7 @@
         <v>415</v>
       </c>
     </row>
-    <row r="126" spans="1:13" ht="90" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:13" ht="80" x14ac:dyDescent="0.2">
       <c r="A126" t="s">
         <v>349</v>
       </c>
@@ -7471,7 +6946,7 @@
         <v>416</v>
       </c>
     </row>
-    <row r="127" spans="1:13" ht="90" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:13" ht="80" x14ac:dyDescent="0.2">
       <c r="A127" t="s">
         <v>349</v>
       </c>
@@ -7512,7 +6987,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="128" spans="1:13" ht="90" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:13" ht="80" x14ac:dyDescent="0.2">
       <c r="A128" t="s">
         <v>349</v>
       </c>
@@ -7553,7 +7028,7 @@
         <v>418</v>
       </c>
     </row>
-    <row r="129" spans="1:13" ht="90" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:13" ht="80" x14ac:dyDescent="0.2">
       <c r="A129" t="s">
         <v>349</v>
       </c>
@@ -7594,7 +7069,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="130" spans="1:13" ht="90" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:13" ht="80" x14ac:dyDescent="0.2">
       <c r="A130" t="s">
         <v>349</v>
       </c>
@@ -7635,7 +7110,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="131" spans="1:13" ht="105" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:13" ht="80" x14ac:dyDescent="0.2">
       <c r="A131" t="s">
         <v>349</v>
       </c>
@@ -7676,7 +7151,7 @@
         <v>415</v>
       </c>
     </row>
-    <row r="132" spans="1:13" ht="105" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:13" ht="80" x14ac:dyDescent="0.2">
       <c r="A132" t="s">
         <v>349</v>
       </c>
@@ -7717,7 +7192,7 @@
         <v>416</v>
       </c>
     </row>
-    <row r="133" spans="1:13" ht="105" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:13" ht="80" x14ac:dyDescent="0.2">
       <c r="A133" t="s">
         <v>349</v>
       </c>
@@ -7758,7 +7233,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="134" spans="1:13" ht="105" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:13" ht="80" x14ac:dyDescent="0.2">
       <c r="A134" t="s">
         <v>349</v>
       </c>
@@ -7799,7 +7274,7 @@
         <v>418</v>
       </c>
     </row>
-    <row r="135" spans="1:13" ht="105" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:13" ht="80" x14ac:dyDescent="0.2">
       <c r="A135" t="s">
         <v>349</v>
       </c>
@@ -7840,7 +7315,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="136" spans="1:13" ht="105" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:13" ht="80" x14ac:dyDescent="0.2">
       <c r="A136" t="s">
         <v>349</v>
       </c>
@@ -7881,7 +7356,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="137" spans="1:13" ht="75" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:13" ht="80" x14ac:dyDescent="0.2">
       <c r="A137" s="26" t="s">
         <v>349</v>
       </c>
@@ -7922,7 +7397,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="138" spans="1:13" ht="75" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:13" ht="80" x14ac:dyDescent="0.2">
       <c r="A138" s="23" t="s">
         <v>349</v>
       </c>
@@ -7963,7 +7438,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="139" spans="1:13" ht="75" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:13" ht="80" x14ac:dyDescent="0.2">
       <c r="A139" s="23" t="s">
         <v>349</v>
       </c>
@@ -8004,7 +7479,7 @@
         <v>438</v>
       </c>
     </row>
-    <row r="140" spans="1:13" ht="75" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:13" ht="80" x14ac:dyDescent="0.2">
       <c r="A140" s="23" t="s">
         <v>349</v>
       </c>
@@ -8045,7 +7520,7 @@
         <v>439</v>
       </c>
     </row>
-    <row r="141" spans="1:13" ht="75" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:13" ht="80" x14ac:dyDescent="0.2">
       <c r="A141" s="23" t="s">
         <v>349</v>
       </c>
@@ -8086,7 +7561,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="142" spans="1:13" ht="75" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:13" ht="80" x14ac:dyDescent="0.2">
       <c r="A142" s="23" t="s">
         <v>349</v>
       </c>
@@ -8127,7 +7602,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="143" spans="1:13" ht="90" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:13" ht="80" x14ac:dyDescent="0.2">
       <c r="A143" s="23" t="s">
         <v>349</v>
       </c>
@@ -8168,7 +7643,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="144" spans="1:13" ht="90" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:13" ht="80" x14ac:dyDescent="0.2">
       <c r="A144" s="23" t="s">
         <v>349</v>
       </c>
@@ -8209,7 +7684,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="145" spans="1:13" ht="90" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:13" ht="80" x14ac:dyDescent="0.2">
       <c r="A145" s="23" t="s">
         <v>349</v>
       </c>
@@ -8250,7 +7725,7 @@
         <v>438</v>
       </c>
     </row>
-    <row r="146" spans="1:13" ht="90" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:13" ht="80" x14ac:dyDescent="0.2">
       <c r="A146" s="23" t="s">
         <v>349</v>
       </c>
@@ -8291,7 +7766,7 @@
         <v>439</v>
       </c>
     </row>
-    <row r="147" spans="1:13" ht="90" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:13" ht="80" x14ac:dyDescent="0.2">
       <c r="A147" s="23" t="s">
         <v>349</v>
       </c>
@@ -8332,7 +7807,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="148" spans="1:13" ht="90" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:13" ht="80" x14ac:dyDescent="0.2">
       <c r="A148" s="23" t="s">
         <v>349</v>
       </c>
@@ -8373,7 +7848,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="149" spans="1:13" ht="105" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:13" ht="80" x14ac:dyDescent="0.2">
       <c r="A149" s="23" t="s">
         <v>349</v>
       </c>
@@ -8414,7 +7889,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="150" spans="1:13" ht="105" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:13" ht="80" x14ac:dyDescent="0.2">
       <c r="A150" s="23" t="s">
         <v>349</v>
       </c>
@@ -8455,7 +7930,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="151" spans="1:13" ht="105" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:13" ht="80" x14ac:dyDescent="0.2">
       <c r="A151" s="23" t="s">
         <v>349</v>
       </c>
@@ -8496,7 +7971,7 @@
         <v>438</v>
       </c>
     </row>
-    <row r="152" spans="1:13" ht="105" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:13" ht="80" x14ac:dyDescent="0.2">
       <c r="A152" s="23" t="s">
         <v>349</v>
       </c>
@@ -8537,7 +8012,7 @@
         <v>439</v>
       </c>
     </row>
-    <row r="153" spans="1:13" ht="105" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:13" ht="80" x14ac:dyDescent="0.2">
       <c r="A153" s="23" t="s">
         <v>349</v>
       </c>
@@ -8578,7 +8053,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="154" spans="1:13" ht="105" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:13" ht="80" x14ac:dyDescent="0.2">
       <c r="A154" s="23" t="s">
         <v>349</v>
       </c>
@@ -8619,12 +8094,12 @@
         <v>441</v>
       </c>
     </row>
-    <row r="155" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A155" s="23"/>
       <c r="B155" s="19"/>
       <c r="C155" s="19"/>
     </row>
-    <row r="156" spans="1:13" ht="90" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:13" ht="80" x14ac:dyDescent="0.2">
       <c r="A156" t="s">
         <v>358</v>
       </c>
@@ -8665,7 +8140,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="157" spans="1:13" ht="105" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:13" ht="96" x14ac:dyDescent="0.2">
       <c r="A157" t="s">
         <v>358</v>
       </c>
@@ -8706,7 +8181,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="158" spans="1:13" ht="105" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:13" ht="96" x14ac:dyDescent="0.2">
       <c r="A158" t="s">
         <v>358</v>
       </c>
@@ -8747,7 +8222,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="159" spans="1:13" ht="105" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:13" ht="96" x14ac:dyDescent="0.2">
       <c r="A159" t="s">
         <v>358</v>
       </c>
@@ -8788,7 +8263,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="160" spans="1:13" ht="105" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:13" ht="96" x14ac:dyDescent="0.2">
       <c r="A160" t="s">
         <v>358</v>
       </c>
@@ -8829,7 +8304,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="161" spans="1:13" ht="105" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:13" ht="96" x14ac:dyDescent="0.2">
       <c r="A161" t="s">
         <v>358</v>
       </c>
@@ -8870,7 +8345,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="162" spans="1:13" ht="105" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:13" ht="96" x14ac:dyDescent="0.2">
       <c r="A162" t="s">
         <v>358</v>
       </c>
@@ -8911,7 +8386,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="163" spans="1:13" ht="105" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:13" ht="96" x14ac:dyDescent="0.2">
       <c r="A163" t="s">
         <v>358</v>
       </c>
@@ -8952,7 +8427,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="164" spans="1:13" ht="105" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:13" ht="112" x14ac:dyDescent="0.2">
       <c r="A164" t="s">
         <v>358</v>
       </c>
@@ -8993,12 +8468,12 @@
         <v>362</v>
       </c>
     </row>
-    <row r="165" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B165" s="19"/>
       <c r="C165" s="19"/>
       <c r="D165" s="4"/>
     </row>
-    <row r="166" spans="1:13" ht="90" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:13" ht="80" x14ac:dyDescent="0.2">
       <c r="A166" t="s">
         <v>379</v>
       </c>
@@ -9039,12 +8514,12 @@
         <v>381</v>
       </c>
     </row>
-    <row r="167" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B167" s="19"/>
       <c r="C167" s="19"/>
       <c r="D167" s="4"/>
     </row>
-    <row r="168" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:13" ht="32" x14ac:dyDescent="0.2">
       <c r="A168" s="10" t="s">
         <v>451</v>
       </c>
@@ -9085,7 +8560,7 @@
         <v>456</v>
       </c>
     </row>
-    <row r="169" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:13" ht="32" x14ac:dyDescent="0.2">
       <c r="A169" s="10" t="s">
         <v>451</v>
       </c>
@@ -9126,7 +8601,7 @@
         <v>456</v>
       </c>
     </row>
-    <row r="170" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:13" ht="32" x14ac:dyDescent="0.2">
       <c r="A170" s="10" t="s">
         <v>451</v>
       </c>
@@ -9232,2310 +8707,20 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C17FE217-AB61-B742-BFE0-33900D1BEC91}">
-  <dimension ref="A1:J71"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E0B35E6D-763F-4C40-91D2-473BE7766F62}">
+  <dimension ref="A1:B22"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="16.28515625" customWidth="1"/>
-    <col min="2" max="2" width="17.140625" customWidth="1"/>
-    <col min="3" max="3" width="53.28515625" customWidth="1"/>
-    <col min="4" max="4" width="29.140625" customWidth="1"/>
-    <col min="5" max="5" width="30.42578125" customWidth="1"/>
-    <col min="6" max="7" width="17.28515625" customWidth="1"/>
-    <col min="8" max="8" width="16.42578125" customWidth="1"/>
-    <col min="9" max="9" width="33.42578125" customWidth="1"/>
-    <col min="10" max="10" width="30.7109375" customWidth="1"/>
+    <col min="1" max="1" width="20.5" customWidth="1"/>
+    <col min="2" max="2" width="105.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="35" t="s">
-        <v>490</v>
-      </c>
-      <c r="B1" s="35"/>
-      <c r="C1" s="36"/>
-      <c r="D1" s="33" t="s">
-        <v>494</v>
-      </c>
-      <c r="E1" s="34" t="s">
-        <v>495</v>
-      </c>
-      <c r="F1" s="37" t="s">
-        <v>496</v>
-      </c>
-      <c r="G1" s="38"/>
-      <c r="H1" s="38"/>
-      <c r="I1" s="39"/>
-      <c r="J1" s="27"/>
-    </row>
-    <row r="2" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="28" t="s">
-        <v>491</v>
-      </c>
-      <c r="B2" s="28" t="s">
-        <v>484</v>
-      </c>
-      <c r="C2" s="28" t="s">
-        <v>483</v>
-      </c>
-      <c r="D2" s="33"/>
-      <c r="E2" s="34"/>
-      <c r="F2" s="29" t="s">
-        <v>460</v>
-      </c>
-      <c r="G2" s="30" t="s">
-        <v>497</v>
-      </c>
-      <c r="H2" s="28" t="s">
-        <v>461</v>
-      </c>
-      <c r="I2" s="31" t="s">
-        <v>489</v>
-      </c>
-      <c r="J2" s="32" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" ht="45" x14ac:dyDescent="0.25">
-      <c r="A3" s="46" t="s">
-        <v>19</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="D3" s="21" t="s">
-        <v>453</v>
-      </c>
-      <c r="E3" s="47" t="s">
-        <v>454</v>
-      </c>
-      <c r="F3" s="48" t="s">
-        <v>488</v>
-      </c>
-      <c r="G3" s="4" t="s">
-        <v>499</v>
-      </c>
-      <c r="H3" s="4" t="s">
-        <v>476</v>
-      </c>
-      <c r="I3" s="4" t="s">
-        <v>471</v>
-      </c>
-      <c r="J3" s="4" t="s">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" ht="45" x14ac:dyDescent="0.25">
-      <c r="A4" s="46" t="s">
-        <v>19</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="D4" s="21" t="s">
-        <v>453</v>
-      </c>
-      <c r="E4" s="47" t="s">
-        <v>454</v>
-      </c>
-      <c r="F4" s="48" t="s">
-        <v>488</v>
-      </c>
-      <c r="G4" s="4" t="s">
-        <v>481</v>
-      </c>
-      <c r="H4" s="4" t="s">
-        <v>478</v>
-      </c>
-      <c r="I4" s="4" t="s">
-        <v>473</v>
-      </c>
-      <c r="J4" s="4" t="s">
-        <v>501</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" ht="45" x14ac:dyDescent="0.25">
-      <c r="A5" s="46" t="s">
-        <v>19</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>487</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="D5" s="21" t="s">
-        <v>453</v>
-      </c>
-      <c r="E5" s="47" t="s">
-        <v>454</v>
-      </c>
-      <c r="F5" s="48" t="s">
-        <v>488</v>
-      </c>
-      <c r="G5" s="4" t="s">
-        <v>482</v>
-      </c>
-      <c r="H5" s="4" t="s">
-        <v>476</v>
-      </c>
-      <c r="I5" s="4" t="s">
-        <v>471</v>
-      </c>
-      <c r="J5" s="4" t="s">
-        <v>468</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" ht="45" x14ac:dyDescent="0.25">
-      <c r="A6" s="46" t="s">
-        <v>19</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>487</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="D6" s="21" t="s">
-        <v>453</v>
-      </c>
-      <c r="E6" s="47" t="s">
-        <v>454</v>
-      </c>
-      <c r="F6" s="48" t="s">
-        <v>488</v>
-      </c>
-      <c r="G6" s="4" t="s">
-        <v>482</v>
-      </c>
-      <c r="H6" s="4" t="s">
-        <v>476</v>
-      </c>
-      <c r="I6" s="4" t="s">
-        <v>475</v>
-      </c>
-      <c r="J6" s="4" t="s">
-        <v>469</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="46" t="s">
-        <v>19</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>487</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="D7" s="21" t="s">
-        <v>453</v>
-      </c>
-      <c r="E7" s="47" t="s">
-        <v>454</v>
-      </c>
-      <c r="F7" s="48" t="s">
-        <v>488</v>
-      </c>
-      <c r="G7" s="4" t="s">
-        <v>481</v>
-      </c>
-      <c r="H7" s="4" t="s">
-        <v>478</v>
-      </c>
-      <c r="I7" s="4" t="s">
-        <v>471</v>
-      </c>
-      <c r="J7" s="4" t="s">
-        <v>468</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" ht="45" x14ac:dyDescent="0.25">
-      <c r="A8" s="46" t="s">
-        <v>19</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>487</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="D8" s="21" t="s">
-        <v>453</v>
-      </c>
-      <c r="E8" s="47" t="s">
-        <v>454</v>
-      </c>
-      <c r="F8" s="48" t="s">
-        <v>488</v>
-      </c>
-      <c r="G8" s="4" t="s">
-        <v>481</v>
-      </c>
-      <c r="H8" s="4" t="s">
-        <v>478</v>
-      </c>
-      <c r="I8" s="4" t="s">
-        <v>475</v>
-      </c>
-      <c r="J8" s="4" t="s">
-        <v>469</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" ht="45" x14ac:dyDescent="0.25">
-      <c r="A9" s="46" t="s">
-        <v>19</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>487</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="D9" s="21" t="s">
-        <v>453</v>
-      </c>
-      <c r="E9" s="47" t="s">
-        <v>454</v>
-      </c>
-      <c r="F9" s="48" t="s">
-        <v>488</v>
-      </c>
-      <c r="G9" s="4" t="s">
-        <v>479</v>
-      </c>
-      <c r="H9" s="4" t="s">
-        <v>476</v>
-      </c>
-      <c r="I9" s="4" t="s">
-        <v>473</v>
-      </c>
-      <c r="J9" s="4" t="s">
-        <v>502</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" ht="45" x14ac:dyDescent="0.25">
-      <c r="A10" s="46" t="s">
-        <v>19</v>
-      </c>
-      <c r="B10" s="49" t="s">
-        <v>486</v>
-      </c>
-      <c r="C10" s="16" t="s">
-        <v>498</v>
-      </c>
-      <c r="D10" s="21" t="s">
-        <v>453</v>
-      </c>
-      <c r="E10" s="47" t="s">
-        <v>454</v>
-      </c>
-      <c r="F10" s="48" t="s">
-        <v>488</v>
-      </c>
-      <c r="G10" s="49" t="s">
-        <v>479</v>
-      </c>
-      <c r="H10" s="49" t="s">
-        <v>476</v>
-      </c>
-      <c r="I10" s="50" t="s">
-        <v>470</v>
-      </c>
-      <c r="J10" s="51" t="s">
-        <v>462</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" ht="45" x14ac:dyDescent="0.25">
-      <c r="A11" s="52" t="s">
-        <v>19</v>
-      </c>
-      <c r="B11" s="49" t="s">
-        <v>486</v>
-      </c>
-      <c r="C11" s="16" t="s">
-        <v>498</v>
-      </c>
-      <c r="D11" s="21" t="s">
-        <v>453</v>
-      </c>
-      <c r="E11" s="47" t="s">
-        <v>454</v>
-      </c>
-      <c r="F11" s="48" t="s">
-        <v>488</v>
-      </c>
-      <c r="G11" s="49" t="s">
-        <v>479</v>
-      </c>
-      <c r="H11" s="49" t="s">
-        <v>476</v>
-      </c>
-      <c r="I11" s="50" t="s">
-        <v>471</v>
-      </c>
-      <c r="J11" s="51" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="A12" s="52" t="s">
-        <v>19</v>
-      </c>
-      <c r="B12" s="49" t="s">
-        <v>26</v>
-      </c>
-      <c r="C12" s="53" t="s">
-        <v>28</v>
-      </c>
-      <c r="D12" s="21" t="s">
-        <v>453</v>
-      </c>
-      <c r="E12" s="47" t="s">
-        <v>454</v>
-      </c>
-      <c r="F12" s="48" t="s">
-        <v>488</v>
-      </c>
-      <c r="G12" t="s">
-        <v>481</v>
-      </c>
-      <c r="H12" t="s">
-        <v>478</v>
-      </c>
-      <c r="I12" t="s">
-        <v>474</v>
-      </c>
-      <c r="J12" t="s">
-        <v>503</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="A13" s="52" t="s">
-        <v>19</v>
-      </c>
-      <c r="B13" s="49" t="s">
-        <v>26</v>
-      </c>
-      <c r="C13" s="53" t="s">
-        <v>14</v>
-      </c>
-      <c r="D13" s="21" t="s">
-        <v>453</v>
-      </c>
-      <c r="E13" s="47" t="s">
-        <v>454</v>
-      </c>
-      <c r="F13" s="48" t="s">
-        <v>488</v>
-      </c>
-      <c r="G13" t="s">
-        <v>481</v>
-      </c>
-      <c r="H13" t="s">
-        <v>478</v>
-      </c>
-      <c r="I13" t="s">
-        <v>473</v>
-      </c>
-      <c r="J13" t="s">
-        <v>504</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" ht="45" x14ac:dyDescent="0.25">
-      <c r="A14" s="52" t="s">
-        <v>19</v>
-      </c>
-      <c r="B14" s="49" t="s">
-        <v>70</v>
-      </c>
-      <c r="C14" s="54" t="s">
-        <v>492</v>
-      </c>
-      <c r="D14" s="21" t="s">
-        <v>453</v>
-      </c>
-      <c r="E14" s="47" t="s">
-        <v>454</v>
-      </c>
-      <c r="F14" s="48" t="s">
-        <v>488</v>
-      </c>
-      <c r="G14" s="49" t="s">
-        <v>479</v>
-      </c>
-      <c r="H14" s="49" t="s">
-        <v>476</v>
-      </c>
-      <c r="I14" s="50" t="s">
-        <v>472</v>
-      </c>
-      <c r="J14" s="51" t="s">
-        <v>464</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" ht="45" x14ac:dyDescent="0.25">
-      <c r="A15" s="52" t="s">
-        <v>19</v>
-      </c>
-      <c r="B15" s="49" t="s">
-        <v>70</v>
-      </c>
-      <c r="C15" s="54" t="s">
-        <v>492</v>
-      </c>
-      <c r="D15" s="21" t="s">
-        <v>453</v>
-      </c>
-      <c r="E15" s="47" t="s">
-        <v>454</v>
-      </c>
-      <c r="F15" s="48" t="s">
-        <v>488</v>
-      </c>
-      <c r="G15" s="49" t="s">
-        <v>479</v>
-      </c>
-      <c r="H15" s="49" t="s">
-        <v>476</v>
-      </c>
-      <c r="I15" s="50" t="s">
-        <v>473</v>
-      </c>
-      <c r="J15" s="51" t="s">
-        <v>465</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="A16" s="52" t="s">
-        <v>19</v>
-      </c>
-      <c r="B16" s="49" t="s">
-        <v>70</v>
-      </c>
-      <c r="C16" s="55" t="s">
-        <v>14</v>
-      </c>
-      <c r="D16" s="21" t="s">
-        <v>453</v>
-      </c>
-      <c r="E16" s="47" t="s">
-        <v>454</v>
-      </c>
-      <c r="F16" s="48" t="s">
-        <v>488</v>
-      </c>
-      <c r="G16" t="s">
-        <v>505</v>
-      </c>
-      <c r="H16" t="s">
-        <v>506</v>
-      </c>
-      <c r="I16" t="s">
-        <v>473</v>
-      </c>
-      <c r="J16" t="s">
-        <v>465</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="A17" s="52" t="s">
-        <v>19</v>
-      </c>
-      <c r="B17" s="49" t="s">
-        <v>70</v>
-      </c>
-      <c r="C17" s="55" t="s">
-        <v>14</v>
-      </c>
-      <c r="D17" s="21" t="s">
-        <v>453</v>
-      </c>
-      <c r="E17" s="47" t="s">
-        <v>454</v>
-      </c>
-      <c r="F17" s="48" t="s">
-        <v>488</v>
-      </c>
-      <c r="G17" t="s">
-        <v>505</v>
-      </c>
-      <c r="H17" t="s">
-        <v>506</v>
-      </c>
-      <c r="I17" t="s">
-        <v>472</v>
-      </c>
-      <c r="J17" t="s">
-        <v>507</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="A18" s="52" t="s">
-        <v>19</v>
-      </c>
-      <c r="B18" s="49" t="s">
-        <v>70</v>
-      </c>
-      <c r="C18" s="55" t="s">
-        <v>14</v>
-      </c>
-      <c r="D18" s="21" t="s">
-        <v>453</v>
-      </c>
-      <c r="E18" s="47" t="s">
-        <v>454</v>
-      </c>
-      <c r="F18" s="48" t="s">
-        <v>488</v>
-      </c>
-      <c r="G18" t="s">
-        <v>505</v>
-      </c>
-      <c r="H18" t="s">
-        <v>506</v>
-      </c>
-      <c r="I18" t="s">
-        <v>471</v>
-      </c>
-      <c r="J18" t="s">
-        <v>508</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="A19" s="52" t="s">
-        <v>19</v>
-      </c>
-      <c r="B19" t="s">
-        <v>509</v>
-      </c>
-      <c r="C19" s="55" t="s">
-        <v>14</v>
-      </c>
-      <c r="D19" s="21" t="s">
-        <v>453</v>
-      </c>
-      <c r="E19" s="47" t="s">
-        <v>454</v>
-      </c>
-      <c r="F19" s="48" t="s">
-        <v>488</v>
-      </c>
-      <c r="G19" t="s">
-        <v>479</v>
-      </c>
-      <c r="H19" t="s">
-        <v>476</v>
-      </c>
-      <c r="I19" t="s">
-        <v>474</v>
-      </c>
-      <c r="J19" t="s">
-        <v>510</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="A20" s="52" t="s">
-        <v>19</v>
-      </c>
-      <c r="B20" t="s">
-        <v>509</v>
-      </c>
-      <c r="C20" s="55" t="s">
-        <v>14</v>
-      </c>
-      <c r="D20" s="21" t="s">
-        <v>453</v>
-      </c>
-      <c r="E20" s="47" t="s">
-        <v>454</v>
-      </c>
-      <c r="F20" s="48" t="s">
-        <v>488</v>
-      </c>
-      <c r="G20" t="s">
-        <v>479</v>
-      </c>
-      <c r="H20" t="s">
-        <v>476</v>
-      </c>
-      <c r="I20" t="s">
-        <v>471</v>
-      </c>
-      <c r="J20" t="s">
-        <v>511</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="A21" s="52" t="s">
-        <v>19</v>
-      </c>
-      <c r="B21" t="s">
-        <v>509</v>
-      </c>
-      <c r="C21" s="55" t="s">
-        <v>14</v>
-      </c>
-      <c r="D21" s="21" t="s">
-        <v>453</v>
-      </c>
-      <c r="E21" s="47" t="s">
-        <v>454</v>
-      </c>
-      <c r="F21" s="48" t="s">
-        <v>488</v>
-      </c>
-      <c r="G21" t="s">
-        <v>512</v>
-      </c>
-      <c r="H21" t="s">
-        <v>476</v>
-      </c>
-      <c r="I21" t="s">
-        <v>471</v>
-      </c>
-      <c r="J21" t="s">
-        <v>513</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="A22" s="52" t="s">
-        <v>19</v>
-      </c>
-      <c r="B22" t="s">
-        <v>514</v>
-      </c>
-      <c r="C22" s="55" t="s">
-        <v>14</v>
-      </c>
-      <c r="D22" s="21" t="s">
-        <v>453</v>
-      </c>
-      <c r="E22" s="47" t="s">
-        <v>454</v>
-      </c>
-      <c r="F22" s="48" t="s">
-        <v>488</v>
-      </c>
-      <c r="G22" t="s">
-        <v>515</v>
-      </c>
-      <c r="H22" t="s">
-        <v>477</v>
-      </c>
-      <c r="I22" t="s">
-        <v>474</v>
-      </c>
-      <c r="J22" t="s">
-        <v>516</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="A23" s="52" t="s">
-        <v>19</v>
-      </c>
-      <c r="B23" t="s">
-        <v>514</v>
-      </c>
-      <c r="C23" s="55" t="s">
-        <v>14</v>
-      </c>
-      <c r="D23" s="21" t="s">
-        <v>453</v>
-      </c>
-      <c r="E23" s="47" t="s">
-        <v>454</v>
-      </c>
-      <c r="F23" s="48" t="s">
-        <v>488</v>
-      </c>
-      <c r="G23" t="s">
-        <v>517</v>
-      </c>
-      <c r="H23" t="s">
-        <v>476</v>
-      </c>
-      <c r="I23" t="s">
-        <v>474</v>
-      </c>
-      <c r="J23" t="s">
-        <v>518</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="A24" s="52" t="s">
-        <v>19</v>
-      </c>
-      <c r="B24" t="s">
-        <v>514</v>
-      </c>
-      <c r="C24" s="55" t="s">
-        <v>14</v>
-      </c>
-      <c r="D24" s="21" t="s">
-        <v>453</v>
-      </c>
-      <c r="E24" s="47" t="s">
-        <v>454</v>
-      </c>
-      <c r="F24" s="48" t="s">
-        <v>488</v>
-      </c>
-      <c r="G24" t="s">
-        <v>519</v>
-      </c>
-      <c r="H24" t="s">
-        <v>520</v>
-      </c>
-      <c r="I24" t="s">
-        <v>472</v>
-      </c>
-      <c r="J24" t="s">
-        <v>521</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="A25" s="52" t="s">
-        <v>19</v>
-      </c>
-      <c r="B25" t="s">
-        <v>514</v>
-      </c>
-      <c r="C25" s="55" t="s">
-        <v>14</v>
-      </c>
-      <c r="D25" s="21" t="s">
-        <v>453</v>
-      </c>
-      <c r="E25" s="47" t="s">
-        <v>454</v>
-      </c>
-      <c r="F25" s="48" t="s">
-        <v>488</v>
-      </c>
-      <c r="G25" t="s">
-        <v>522</v>
-      </c>
-      <c r="H25" t="s">
-        <v>523</v>
-      </c>
-      <c r="I25" t="s">
-        <v>473</v>
-      </c>
-      <c r="J25" t="s">
-        <v>524</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="A26" s="52" t="s">
-        <v>19</v>
-      </c>
-      <c r="B26" t="s">
-        <v>514</v>
-      </c>
-      <c r="C26" s="55" t="s">
-        <v>14</v>
-      </c>
-      <c r="D26" s="21" t="s">
-        <v>453</v>
-      </c>
-      <c r="E26" s="47" t="s">
-        <v>454</v>
-      </c>
-      <c r="F26" s="48" t="s">
-        <v>488</v>
-      </c>
-      <c r="G26" t="s">
-        <v>525</v>
-      </c>
-      <c r="H26" t="s">
-        <v>523</v>
-      </c>
-      <c r="I26" t="s">
-        <v>473</v>
-      </c>
-      <c r="J26" t="s">
-        <v>526</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="A27" s="52" t="s">
-        <v>19</v>
-      </c>
-      <c r="B27" t="s">
-        <v>527</v>
-      </c>
-      <c r="C27" s="55" t="s">
-        <v>14</v>
-      </c>
-      <c r="D27" s="21" t="s">
-        <v>453</v>
-      </c>
-      <c r="E27" s="47" t="s">
-        <v>454</v>
-      </c>
-      <c r="F27" s="48" t="s">
-        <v>488</v>
-      </c>
-      <c r="G27" t="s">
-        <v>528</v>
-      </c>
-      <c r="H27" t="s">
-        <v>506</v>
-      </c>
-      <c r="I27" t="s">
-        <v>473</v>
-      </c>
-      <c r="J27" t="s">
-        <v>529</v>
-      </c>
-    </row>
-    <row r="28" spans="1:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="A28" s="52" t="s">
-        <v>19</v>
-      </c>
-      <c r="B28" t="s">
-        <v>527</v>
-      </c>
-      <c r="C28" s="55" t="s">
-        <v>14</v>
-      </c>
-      <c r="D28" s="21" t="s">
-        <v>453</v>
-      </c>
-      <c r="E28" s="47" t="s">
-        <v>454</v>
-      </c>
-      <c r="F28" s="48" t="s">
-        <v>488</v>
-      </c>
-      <c r="G28" t="s">
-        <v>530</v>
-      </c>
-      <c r="H28" t="s">
-        <v>506</v>
-      </c>
-      <c r="I28" t="s">
-        <v>473</v>
-      </c>
-      <c r="J28" t="s">
-        <v>531</v>
-      </c>
-    </row>
-    <row r="29" spans="1:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="A29" s="52" t="s">
-        <v>19</v>
-      </c>
-      <c r="B29" t="s">
-        <v>527</v>
-      </c>
-      <c r="C29" s="55" t="s">
-        <v>14</v>
-      </c>
-      <c r="D29" s="21" t="s">
-        <v>453</v>
-      </c>
-      <c r="E29" s="47" t="s">
-        <v>454</v>
-      </c>
-      <c r="F29" s="48" t="s">
-        <v>488</v>
-      </c>
-      <c r="G29" t="s">
-        <v>530</v>
-      </c>
-      <c r="H29" t="s">
-        <v>506</v>
-      </c>
-      <c r="I29" t="s">
-        <v>472</v>
-      </c>
-      <c r="J29" t="s">
-        <v>532</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="A30" s="52" t="s">
-        <v>19</v>
-      </c>
-      <c r="B30" t="s">
-        <v>533</v>
-      </c>
-      <c r="C30" s="55" t="s">
-        <v>14</v>
-      </c>
-      <c r="D30" s="21" t="s">
-        <v>453</v>
-      </c>
-      <c r="E30" s="47" t="s">
-        <v>454</v>
-      </c>
-      <c r="F30" s="48" t="s">
-        <v>488</v>
-      </c>
-      <c r="G30" t="s">
-        <v>530</v>
-      </c>
-      <c r="H30" t="s">
-        <v>506</v>
-      </c>
-      <c r="I30" t="s">
-        <v>473</v>
-      </c>
-      <c r="J30" t="s">
-        <v>534</v>
-      </c>
-    </row>
-    <row r="31" spans="1:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="A31" s="52" t="s">
-        <v>19</v>
-      </c>
-      <c r="B31" t="s">
-        <v>533</v>
-      </c>
-      <c r="C31" s="55" t="s">
-        <v>14</v>
-      </c>
-      <c r="D31" s="21" t="s">
-        <v>453</v>
-      </c>
-      <c r="E31" s="47" t="s">
-        <v>454</v>
-      </c>
-      <c r="F31" s="48" t="s">
-        <v>488</v>
-      </c>
-      <c r="G31" t="s">
-        <v>530</v>
-      </c>
-      <c r="H31" t="s">
-        <v>506</v>
-      </c>
-      <c r="I31" t="s">
-        <v>472</v>
-      </c>
-      <c r="J31" t="s">
-        <v>535</v>
-      </c>
-    </row>
-    <row r="32" spans="1:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="A32" s="52" t="s">
-        <v>19</v>
-      </c>
-      <c r="B32" t="s">
-        <v>304</v>
-      </c>
-      <c r="C32" s="55" t="s">
-        <v>14</v>
-      </c>
-      <c r="D32" s="21" t="s">
-        <v>453</v>
-      </c>
-      <c r="E32" s="47" t="s">
-        <v>454</v>
-      </c>
-      <c r="F32" s="48" t="s">
-        <v>488</v>
-      </c>
-      <c r="G32" t="s">
-        <v>536</v>
-      </c>
-      <c r="H32" t="s">
-        <v>520</v>
-      </c>
-      <c r="I32" t="s">
-        <v>537</v>
-      </c>
-      <c r="J32" t="s">
-        <v>538</v>
-      </c>
-    </row>
-    <row r="33" spans="1:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="A33" s="52" t="s">
-        <v>19</v>
-      </c>
-      <c r="B33" t="s">
-        <v>304</v>
-      </c>
-      <c r="C33" s="55" t="s">
-        <v>14</v>
-      </c>
-      <c r="D33" s="21" t="s">
-        <v>453</v>
-      </c>
-      <c r="E33" s="47" t="s">
-        <v>454</v>
-      </c>
-      <c r="F33" s="48" t="s">
-        <v>488</v>
-      </c>
-      <c r="G33" t="s">
-        <v>539</v>
-      </c>
-      <c r="H33" t="s">
-        <v>520</v>
-      </c>
-      <c r="I33" t="s">
-        <v>474</v>
-      </c>
-      <c r="J33" t="s">
-        <v>540</v>
-      </c>
-    </row>
-    <row r="34" spans="1:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="A34" s="52" t="s">
-        <v>19</v>
-      </c>
-      <c r="B34" t="s">
-        <v>304</v>
-      </c>
-      <c r="C34" s="55" t="s">
-        <v>14</v>
-      </c>
-      <c r="D34" s="21" t="s">
-        <v>453</v>
-      </c>
-      <c r="E34" s="47" t="s">
-        <v>454</v>
-      </c>
-      <c r="F34" s="48" t="s">
-        <v>488</v>
-      </c>
-      <c r="G34" t="s">
-        <v>481</v>
-      </c>
-      <c r="H34" t="s">
-        <v>478</v>
-      </c>
-      <c r="I34" t="s">
-        <v>474</v>
-      </c>
-      <c r="J34" t="s">
-        <v>541</v>
-      </c>
-    </row>
-    <row r="35" spans="1:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="A35" s="52" t="s">
-        <v>19</v>
-      </c>
-      <c r="B35" t="s">
-        <v>16</v>
-      </c>
-      <c r="C35" s="55" t="s">
-        <v>14</v>
-      </c>
-      <c r="D35" s="21" t="s">
-        <v>453</v>
-      </c>
-      <c r="E35" s="47" t="s">
-        <v>454</v>
-      </c>
-      <c r="F35" s="48" t="s">
-        <v>488</v>
-      </c>
-      <c r="G35" t="s">
-        <v>479</v>
-      </c>
-      <c r="H35" t="s">
-        <v>476</v>
-      </c>
-      <c r="I35" t="s">
-        <v>542</v>
-      </c>
-      <c r="J35" t="s">
-        <v>543</v>
-      </c>
-    </row>
-    <row r="36" spans="1:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="A36" s="52" t="s">
-        <v>19</v>
-      </c>
-      <c r="B36" t="s">
-        <v>16</v>
-      </c>
-      <c r="C36" s="55" t="s">
-        <v>14</v>
-      </c>
-      <c r="D36" s="21" t="s">
-        <v>453</v>
-      </c>
-      <c r="E36" s="47" t="s">
-        <v>454</v>
-      </c>
-      <c r="F36" s="48" t="s">
-        <v>488</v>
-      </c>
-      <c r="G36" t="s">
-        <v>479</v>
-      </c>
-      <c r="H36" t="s">
-        <v>476</v>
-      </c>
-      <c r="I36" t="s">
-        <v>471</v>
-      </c>
-      <c r="J36" t="s">
-        <v>544</v>
-      </c>
-    </row>
-    <row r="37" spans="1:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="A37" s="52" t="s">
-        <v>19</v>
-      </c>
-      <c r="B37" t="s">
-        <v>16</v>
-      </c>
-      <c r="C37" s="55" t="s">
-        <v>14</v>
-      </c>
-      <c r="D37" s="21" t="s">
-        <v>453</v>
-      </c>
-      <c r="E37" s="47" t="s">
-        <v>454</v>
-      </c>
-      <c r="F37" s="48" t="s">
-        <v>488</v>
-      </c>
-      <c r="G37" t="s">
-        <v>545</v>
-      </c>
-      <c r="H37" t="s">
-        <v>476</v>
-      </c>
-      <c r="I37" t="s">
-        <v>542</v>
-      </c>
-      <c r="J37" t="s">
-        <v>543</v>
-      </c>
-    </row>
-    <row r="38" spans="1:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="A38" s="52" t="s">
-        <v>19</v>
-      </c>
-      <c r="B38" t="s">
-        <v>16</v>
-      </c>
-      <c r="C38" s="55" t="s">
-        <v>14</v>
-      </c>
-      <c r="D38" s="21" t="s">
-        <v>453</v>
-      </c>
-      <c r="E38" s="47" t="s">
-        <v>454</v>
-      </c>
-      <c r="F38" s="48" t="s">
-        <v>488</v>
-      </c>
-      <c r="G38" t="s">
-        <v>545</v>
-      </c>
-      <c r="H38" t="s">
-        <v>476</v>
-      </c>
-      <c r="I38" t="s">
-        <v>471</v>
-      </c>
-      <c r="J38" t="s">
-        <v>544</v>
-      </c>
-    </row>
-    <row r="39" spans="1:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="A39" s="52" t="s">
-        <v>19</v>
-      </c>
-      <c r="B39" t="s">
-        <v>16</v>
-      </c>
-      <c r="C39" s="55" t="s">
-        <v>14</v>
-      </c>
-      <c r="D39" s="21" t="s">
-        <v>453</v>
-      </c>
-      <c r="E39" s="47" t="s">
-        <v>454</v>
-      </c>
-      <c r="F39" s="48" t="s">
-        <v>488</v>
-      </c>
-      <c r="G39" t="s">
-        <v>480</v>
-      </c>
-      <c r="H39" t="s">
-        <v>477</v>
-      </c>
-      <c r="I39" t="s">
-        <v>474</v>
-      </c>
-      <c r="J39" t="s">
-        <v>546</v>
-      </c>
-    </row>
-    <row r="40" spans="1:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="A40" s="52" t="s">
-        <v>19</v>
-      </c>
-      <c r="B40" t="s">
-        <v>16</v>
-      </c>
-      <c r="C40" s="55" t="s">
-        <v>14</v>
-      </c>
-      <c r="D40" s="21" t="s">
-        <v>453</v>
-      </c>
-      <c r="E40" s="47" t="s">
-        <v>454</v>
-      </c>
-      <c r="F40" s="48" t="s">
-        <v>488</v>
-      </c>
-      <c r="G40" t="s">
-        <v>547</v>
-      </c>
-      <c r="H40" t="s">
-        <v>523</v>
-      </c>
-      <c r="I40" t="s">
-        <v>470</v>
-      </c>
-      <c r="J40" t="s">
-        <v>548</v>
-      </c>
-    </row>
-    <row r="41" spans="1:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="A41" s="52" t="s">
-        <v>19</v>
-      </c>
-      <c r="B41" t="s">
-        <v>16</v>
-      </c>
-      <c r="C41" s="55" t="s">
-        <v>14</v>
-      </c>
-      <c r="D41" s="21" t="s">
-        <v>453</v>
-      </c>
-      <c r="E41" s="47" t="s">
-        <v>454</v>
-      </c>
-      <c r="F41" s="48" t="s">
-        <v>488</v>
-      </c>
-      <c r="G41" t="s">
-        <v>479</v>
-      </c>
-      <c r="H41" t="s">
-        <v>476</v>
-      </c>
-      <c r="I41" t="s">
-        <v>473</v>
-      </c>
-      <c r="J41" t="s">
-        <v>549</v>
-      </c>
-    </row>
-    <row r="42" spans="1:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="A42" s="52" t="s">
-        <v>19</v>
-      </c>
-      <c r="B42" t="s">
-        <v>16</v>
-      </c>
-      <c r="C42" s="55" t="s">
-        <v>14</v>
-      </c>
-      <c r="D42" s="21" t="s">
-        <v>453</v>
-      </c>
-      <c r="E42" s="47" t="s">
-        <v>454</v>
-      </c>
-      <c r="F42" s="48" t="s">
-        <v>488</v>
-      </c>
-      <c r="G42" t="s">
-        <v>545</v>
-      </c>
-      <c r="H42" t="s">
-        <v>476</v>
-      </c>
-      <c r="I42" t="s">
-        <v>473</v>
-      </c>
-      <c r="J42" t="s">
-        <v>549</v>
-      </c>
-    </row>
-    <row r="43" spans="1:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="A43" s="52" t="s">
-        <v>19</v>
-      </c>
-      <c r="B43" t="s">
-        <v>550</v>
-      </c>
-      <c r="C43" s="55" t="s">
-        <v>14</v>
-      </c>
-      <c r="D43" s="21" t="s">
-        <v>453</v>
-      </c>
-      <c r="E43" s="47" t="s">
-        <v>454</v>
-      </c>
-      <c r="F43" s="48" t="s">
-        <v>488</v>
-      </c>
-      <c r="G43" t="s">
-        <v>539</v>
-      </c>
-      <c r="H43" t="s">
-        <v>520</v>
-      </c>
-      <c r="I43" t="s">
-        <v>473</v>
-      </c>
-      <c r="J43" t="s">
-        <v>551</v>
-      </c>
-    </row>
-    <row r="44" spans="1:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="A44" s="52" t="s">
-        <v>19</v>
-      </c>
-      <c r="B44" t="s">
-        <v>550</v>
-      </c>
-      <c r="C44" s="55" t="s">
-        <v>14</v>
-      </c>
-      <c r="D44" s="21" t="s">
-        <v>453</v>
-      </c>
-      <c r="E44" s="47" t="s">
-        <v>454</v>
-      </c>
-      <c r="F44" s="48" t="s">
-        <v>488</v>
-      </c>
-      <c r="G44" t="s">
-        <v>539</v>
-      </c>
-      <c r="H44" t="s">
-        <v>520</v>
-      </c>
-      <c r="I44" t="s">
-        <v>473</v>
-      </c>
-      <c r="J44" t="s">
-        <v>552</v>
-      </c>
-    </row>
-    <row r="45" spans="1:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="A45" s="52" t="s">
-        <v>19</v>
-      </c>
-      <c r="B45" t="s">
-        <v>550</v>
-      </c>
-      <c r="C45" s="55" t="s">
-        <v>14</v>
-      </c>
-      <c r="D45" s="21" t="s">
-        <v>453</v>
-      </c>
-      <c r="E45" s="47" t="s">
-        <v>454</v>
-      </c>
-      <c r="F45" s="48" t="s">
-        <v>488</v>
-      </c>
-      <c r="G45" t="s">
-        <v>539</v>
-      </c>
-      <c r="H45" t="s">
-        <v>520</v>
-      </c>
-      <c r="I45" t="s">
-        <v>471</v>
-      </c>
-      <c r="J45" t="s">
-        <v>553</v>
-      </c>
-    </row>
-    <row r="46" spans="1:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="A46" s="52" t="s">
-        <v>19</v>
-      </c>
-      <c r="B46" t="s">
-        <v>550</v>
-      </c>
-      <c r="C46" s="55" t="s">
-        <v>14</v>
-      </c>
-      <c r="D46" s="21" t="s">
-        <v>453</v>
-      </c>
-      <c r="E46" s="47" t="s">
-        <v>454</v>
-      </c>
-      <c r="F46" s="48" t="s">
-        <v>488</v>
-      </c>
-      <c r="G46" t="s">
-        <v>515</v>
-      </c>
-      <c r="H46" t="s">
-        <v>477</v>
-      </c>
-      <c r="I46" t="s">
-        <v>471</v>
-      </c>
-      <c r="J46" t="s">
-        <v>554</v>
-      </c>
-    </row>
-    <row r="47" spans="1:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="A47" s="52" t="s">
-        <v>19</v>
-      </c>
-      <c r="B47" t="s">
-        <v>550</v>
-      </c>
-      <c r="C47" s="55" t="s">
-        <v>14</v>
-      </c>
-      <c r="D47" s="21" t="s">
-        <v>453</v>
-      </c>
-      <c r="E47" s="47" t="s">
-        <v>454</v>
-      </c>
-      <c r="F47" s="48" t="s">
-        <v>488</v>
-      </c>
-      <c r="G47" t="s">
-        <v>530</v>
-      </c>
-      <c r="H47" t="s">
-        <v>506</v>
-      </c>
-      <c r="I47" t="s">
-        <v>542</v>
-      </c>
-      <c r="J47" t="s">
-        <v>555</v>
-      </c>
-    </row>
-    <row r="48" spans="1:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="A48" s="52" t="s">
-        <v>19</v>
-      </c>
-      <c r="B48" t="s">
-        <v>132</v>
-      </c>
-      <c r="C48" s="55" t="s">
-        <v>14</v>
-      </c>
-      <c r="D48" s="21" t="s">
-        <v>453</v>
-      </c>
-      <c r="E48" s="47" t="s">
-        <v>454</v>
-      </c>
-      <c r="F48" s="48" t="s">
-        <v>488</v>
-      </c>
-      <c r="G48" t="s">
-        <v>556</v>
-      </c>
-      <c r="H48" t="s">
-        <v>520</v>
-      </c>
-      <c r="I48" t="s">
-        <v>473</v>
-      </c>
-      <c r="J48" t="s">
-        <v>557</v>
-      </c>
-    </row>
-    <row r="49" spans="1:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="A49" s="52" t="s">
-        <v>19</v>
-      </c>
-      <c r="B49" t="s">
-        <v>132</v>
-      </c>
-      <c r="C49" s="55" t="s">
-        <v>14</v>
-      </c>
-      <c r="D49" s="21" t="s">
-        <v>453</v>
-      </c>
-      <c r="E49" s="47" t="s">
-        <v>454</v>
-      </c>
-      <c r="F49" s="48" t="s">
-        <v>488</v>
-      </c>
-      <c r="G49" t="s">
-        <v>556</v>
-      </c>
-      <c r="H49" t="s">
-        <v>520</v>
-      </c>
-      <c r="I49" t="s">
-        <v>474</v>
-      </c>
-      <c r="J49" t="s">
-        <v>558</v>
-      </c>
-    </row>
-    <row r="50" spans="1:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="A50" s="52" t="s">
-        <v>19</v>
-      </c>
-      <c r="B50" t="s">
-        <v>360</v>
-      </c>
-      <c r="C50" s="55" t="s">
-        <v>14</v>
-      </c>
-      <c r="D50" s="21" t="s">
-        <v>453</v>
-      </c>
-      <c r="E50" s="47" t="s">
-        <v>454</v>
-      </c>
-      <c r="F50" s="48" t="s">
-        <v>488</v>
-      </c>
-      <c r="G50" t="s">
-        <v>481</v>
-      </c>
-      <c r="H50" t="s">
-        <v>478</v>
-      </c>
-      <c r="I50" t="s">
-        <v>473</v>
-      </c>
-      <c r="J50" t="s">
-        <v>559</v>
-      </c>
-    </row>
-    <row r="51" spans="1:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="A51" s="52" t="s">
-        <v>19</v>
-      </c>
-      <c r="B51" t="s">
-        <v>360</v>
-      </c>
-      <c r="C51" s="55" t="s">
-        <v>14</v>
-      </c>
-      <c r="D51" s="21" t="s">
-        <v>453</v>
-      </c>
-      <c r="E51" s="47" t="s">
-        <v>454</v>
-      </c>
-      <c r="F51" s="48" t="s">
-        <v>488</v>
-      </c>
-      <c r="G51" t="s">
-        <v>515</v>
-      </c>
-      <c r="H51" t="s">
-        <v>477</v>
-      </c>
-      <c r="I51" t="s">
-        <v>474</v>
-      </c>
-      <c r="J51" t="s">
-        <v>560</v>
-      </c>
-    </row>
-    <row r="52" spans="1:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="A52" s="52" t="s">
-        <v>19</v>
-      </c>
-      <c r="B52" t="s">
-        <v>561</v>
-      </c>
-      <c r="C52" s="55" t="s">
-        <v>14</v>
-      </c>
-      <c r="D52" s="21" t="s">
-        <v>453</v>
-      </c>
-      <c r="E52" s="47" t="s">
-        <v>454</v>
-      </c>
-      <c r="F52" s="48" t="s">
-        <v>488</v>
-      </c>
-      <c r="G52" t="s">
-        <v>515</v>
-      </c>
-      <c r="H52" t="s">
-        <v>477</v>
-      </c>
-      <c r="I52" t="s">
-        <v>474</v>
-      </c>
-      <c r="J52" t="s">
-        <v>562</v>
-      </c>
-    </row>
-    <row r="53" spans="1:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="A53" s="52" t="s">
-        <v>19</v>
-      </c>
-      <c r="B53" t="s">
-        <v>561</v>
-      </c>
-      <c r="C53" s="55" t="s">
-        <v>14</v>
-      </c>
-      <c r="D53" s="21" t="s">
-        <v>453</v>
-      </c>
-      <c r="E53" s="47" t="s">
-        <v>454</v>
-      </c>
-      <c r="F53" s="48" t="s">
-        <v>488</v>
-      </c>
-      <c r="G53" t="s">
-        <v>505</v>
-      </c>
-      <c r="H53" t="s">
-        <v>506</v>
-      </c>
-      <c r="I53" t="s">
-        <v>474</v>
-      </c>
-      <c r="J53" t="s">
-        <v>563</v>
-      </c>
-    </row>
-    <row r="54" spans="1:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="A54" s="52" t="s">
-        <v>19</v>
-      </c>
-      <c r="B54" t="s">
-        <v>561</v>
-      </c>
-      <c r="C54" s="55" t="s">
-        <v>14</v>
-      </c>
-      <c r="D54" s="21" t="s">
-        <v>453</v>
-      </c>
-      <c r="E54" s="47" t="s">
-        <v>454</v>
-      </c>
-      <c r="F54" s="48" t="s">
-        <v>488</v>
-      </c>
-      <c r="G54" t="s">
-        <v>479</v>
-      </c>
-      <c r="H54" t="s">
-        <v>476</v>
-      </c>
-      <c r="I54" t="s">
-        <v>470</v>
-      </c>
-      <c r="J54" t="s">
-        <v>564</v>
-      </c>
-    </row>
-    <row r="55" spans="1:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="A55" s="52" t="s">
-        <v>19</v>
-      </c>
-      <c r="B55" t="s">
-        <v>561</v>
-      </c>
-      <c r="C55" s="55" t="s">
-        <v>14</v>
-      </c>
-      <c r="D55" s="21" t="s">
-        <v>453</v>
-      </c>
-      <c r="E55" s="47" t="s">
-        <v>454</v>
-      </c>
-      <c r="F55" s="48" t="s">
-        <v>488</v>
-      </c>
-      <c r="G55" t="s">
-        <v>512</v>
-      </c>
-      <c r="H55" t="s">
-        <v>476</v>
-      </c>
-      <c r="I55" t="s">
-        <v>470</v>
-      </c>
-      <c r="J55" t="s">
-        <v>565</v>
-      </c>
-    </row>
-    <row r="56" spans="1:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="A56" s="52" t="s">
-        <v>19</v>
-      </c>
-      <c r="B56" t="s">
-        <v>561</v>
-      </c>
-      <c r="C56" s="55" t="s">
-        <v>14</v>
-      </c>
-      <c r="D56" s="21" t="s">
-        <v>453</v>
-      </c>
-      <c r="E56" s="47" t="s">
-        <v>454</v>
-      </c>
-      <c r="F56" s="48" t="s">
-        <v>488</v>
-      </c>
-      <c r="G56" t="s">
-        <v>530</v>
-      </c>
-      <c r="H56" t="s">
-        <v>506</v>
-      </c>
-      <c r="I56" t="s">
-        <v>470</v>
-      </c>
-      <c r="J56" t="s">
-        <v>566</v>
-      </c>
-    </row>
-    <row r="57" spans="1:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="A57" s="52" t="s">
-        <v>19</v>
-      </c>
-      <c r="B57" t="s">
-        <v>567</v>
-      </c>
-      <c r="C57" s="55" t="s">
-        <v>14</v>
-      </c>
-      <c r="D57" s="21" t="s">
-        <v>453</v>
-      </c>
-      <c r="E57" s="47" t="s">
-        <v>454</v>
-      </c>
-      <c r="F57" s="48" t="s">
-        <v>488</v>
-      </c>
-      <c r="G57" t="s">
-        <v>479</v>
-      </c>
-      <c r="H57" t="s">
-        <v>476</v>
-      </c>
-      <c r="I57" t="s">
-        <v>473</v>
-      </c>
-      <c r="J57" t="s">
-        <v>568</v>
-      </c>
-    </row>
-    <row r="58" spans="1:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="A58" s="52" t="s">
-        <v>19</v>
-      </c>
-      <c r="B58" t="s">
-        <v>569</v>
-      </c>
-      <c r="C58" s="55" t="s">
-        <v>14</v>
-      </c>
-      <c r="D58" s="21" t="s">
-        <v>453</v>
-      </c>
-      <c r="E58" s="47" t="s">
-        <v>454</v>
-      </c>
-      <c r="F58" s="48" t="s">
-        <v>488</v>
-      </c>
-      <c r="G58" t="s">
-        <v>556</v>
-      </c>
-      <c r="H58" t="s">
-        <v>520</v>
-      </c>
-      <c r="I58" t="s">
-        <v>473</v>
-      </c>
-      <c r="J58" t="s">
-        <v>570</v>
-      </c>
-    </row>
-    <row r="59" spans="1:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="A59" s="52" t="s">
-        <v>19</v>
-      </c>
-      <c r="B59" t="s">
-        <v>571</v>
-      </c>
-      <c r="C59" s="55" t="s">
-        <v>14</v>
-      </c>
-      <c r="D59" s="21" t="s">
-        <v>453</v>
-      </c>
-      <c r="E59" s="47" t="s">
-        <v>454</v>
-      </c>
-      <c r="F59" s="48" t="s">
-        <v>488</v>
-      </c>
-      <c r="G59" t="s">
-        <v>572</v>
-      </c>
-      <c r="H59" t="s">
-        <v>573</v>
-      </c>
-      <c r="I59" t="s">
-        <v>542</v>
-      </c>
-      <c r="J59" t="s">
-        <v>574</v>
-      </c>
-    </row>
-    <row r="60" spans="1:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="A60" s="52" t="s">
-        <v>19</v>
-      </c>
-      <c r="B60" t="s">
-        <v>320</v>
-      </c>
-      <c r="C60" s="55" t="s">
-        <v>14</v>
-      </c>
-      <c r="D60" s="21" t="s">
-        <v>453</v>
-      </c>
-      <c r="E60" s="47" t="s">
-        <v>454</v>
-      </c>
-      <c r="F60" s="48" t="s">
-        <v>488</v>
-      </c>
-      <c r="G60" t="s">
-        <v>515</v>
-      </c>
-      <c r="H60" t="s">
-        <v>477</v>
-      </c>
-      <c r="I60" t="s">
-        <v>474</v>
-      </c>
-      <c r="J60" t="s">
-        <v>575</v>
-      </c>
-    </row>
-    <row r="61" spans="1:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="A61" s="52" t="s">
-        <v>19</v>
-      </c>
-      <c r="B61" t="s">
-        <v>320</v>
-      </c>
-      <c r="C61" s="55" t="s">
-        <v>14</v>
-      </c>
-      <c r="D61" s="21" t="s">
-        <v>453</v>
-      </c>
-      <c r="E61" s="47" t="s">
-        <v>454</v>
-      </c>
-      <c r="F61" s="48" t="s">
-        <v>488</v>
-      </c>
-      <c r="G61" t="s">
-        <v>480</v>
-      </c>
-      <c r="H61" t="s">
-        <v>477</v>
-      </c>
-      <c r="I61" t="s">
-        <v>474</v>
-      </c>
-      <c r="J61" t="s">
-        <v>576</v>
-      </c>
-    </row>
-    <row r="62" spans="1:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="A62" s="52" t="s">
-        <v>19</v>
-      </c>
-      <c r="B62" t="s">
-        <v>320</v>
-      </c>
-      <c r="C62" s="55" t="s">
-        <v>14</v>
-      </c>
-      <c r="D62" s="21" t="s">
-        <v>453</v>
-      </c>
-      <c r="E62" s="47" t="s">
-        <v>454</v>
-      </c>
-      <c r="F62" s="48" t="s">
-        <v>488</v>
-      </c>
-      <c r="G62" t="s">
-        <v>481</v>
-      </c>
-      <c r="H62" t="s">
-        <v>478</v>
-      </c>
-      <c r="I62" t="s">
-        <v>474</v>
-      </c>
-      <c r="J62" t="s">
-        <v>577</v>
-      </c>
-    </row>
-    <row r="63" spans="1:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="A63" s="52" t="s">
-        <v>19</v>
-      </c>
-      <c r="B63" t="s">
-        <v>320</v>
-      </c>
-      <c r="C63" s="55" t="s">
-        <v>14</v>
-      </c>
-      <c r="D63" s="21" t="s">
-        <v>453</v>
-      </c>
-      <c r="E63" s="47" t="s">
-        <v>454</v>
-      </c>
-      <c r="F63" s="48" t="s">
-        <v>488</v>
-      </c>
-      <c r="G63" t="s">
-        <v>578</v>
-      </c>
-      <c r="H63" t="s">
-        <v>579</v>
-      </c>
-      <c r="I63" t="s">
-        <v>472</v>
-      </c>
-      <c r="J63" t="s">
-        <v>580</v>
-      </c>
-    </row>
-    <row r="64" spans="1:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="A64" s="52" t="s">
-        <v>19</v>
-      </c>
-      <c r="B64" t="s">
-        <v>291</v>
-      </c>
-      <c r="C64" s="55" t="s">
-        <v>14</v>
-      </c>
-      <c r="D64" s="21" t="s">
-        <v>453</v>
-      </c>
-      <c r="E64" s="47" t="s">
-        <v>454</v>
-      </c>
-      <c r="F64" s="48" t="s">
-        <v>488</v>
-      </c>
-      <c r="G64" t="s">
-        <v>481</v>
-      </c>
-      <c r="H64" t="s">
-        <v>478</v>
-      </c>
-      <c r="I64" t="s">
-        <v>474</v>
-      </c>
-      <c r="J64" t="s">
-        <v>558</v>
-      </c>
-    </row>
-    <row r="65" spans="1:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="A65" s="52" t="s">
-        <v>19</v>
-      </c>
-      <c r="B65" t="s">
-        <v>581</v>
-      </c>
-      <c r="C65" s="55" t="s">
-        <v>14</v>
-      </c>
-      <c r="D65" s="21" t="s">
-        <v>453</v>
-      </c>
-      <c r="E65" s="47" t="s">
-        <v>454</v>
-      </c>
-      <c r="F65" s="48" t="s">
-        <v>488</v>
-      </c>
-      <c r="G65" t="s">
-        <v>582</v>
-      </c>
-      <c r="H65" t="s">
-        <v>476</v>
-      </c>
-      <c r="I65" t="s">
-        <v>473</v>
-      </c>
-      <c r="J65" t="s">
-        <v>583</v>
-      </c>
-    </row>
-    <row r="66" spans="1:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="A66" s="52" t="s">
-        <v>19</v>
-      </c>
-      <c r="B66" t="s">
-        <v>584</v>
-      </c>
-      <c r="C66" s="55" t="s">
-        <v>14</v>
-      </c>
-      <c r="D66" s="21" t="s">
-        <v>453</v>
-      </c>
-      <c r="E66" s="47" t="s">
-        <v>454</v>
-      </c>
-      <c r="F66" s="48" t="s">
-        <v>488</v>
-      </c>
-      <c r="G66" t="s">
-        <v>480</v>
-      </c>
-      <c r="H66" t="s">
-        <v>477</v>
-      </c>
-      <c r="I66" t="s">
-        <v>474</v>
-      </c>
-      <c r="J66" t="s">
-        <v>585</v>
-      </c>
-    </row>
-    <row r="67" spans="1:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="A67" s="52" t="s">
-        <v>19</v>
-      </c>
-      <c r="B67" t="s">
-        <v>584</v>
-      </c>
-      <c r="C67" s="55" t="s">
-        <v>14</v>
-      </c>
-      <c r="D67" s="21" t="s">
-        <v>453</v>
-      </c>
-      <c r="E67" s="47" t="s">
-        <v>454</v>
-      </c>
-      <c r="F67" s="48" t="s">
-        <v>488</v>
-      </c>
-      <c r="G67" t="s">
-        <v>481</v>
-      </c>
-      <c r="H67" t="s">
-        <v>478</v>
-      </c>
-      <c r="I67" t="s">
-        <v>474</v>
-      </c>
-      <c r="J67" t="s">
-        <v>586</v>
-      </c>
-    </row>
-    <row r="68" spans="1:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="A68" s="52" t="s">
-        <v>19</v>
-      </c>
-      <c r="B68" t="s">
-        <v>39</v>
-      </c>
-      <c r="C68" s="55" t="s">
-        <v>14</v>
-      </c>
-      <c r="D68" s="21" t="s">
-        <v>453</v>
-      </c>
-      <c r="E68" s="47" t="s">
-        <v>454</v>
-      </c>
-      <c r="F68" s="48" t="s">
-        <v>488</v>
-      </c>
-      <c r="G68" t="s">
-        <v>480</v>
-      </c>
-      <c r="H68" t="s">
-        <v>477</v>
-      </c>
-      <c r="I68" t="s">
-        <v>470</v>
-      </c>
-      <c r="J68" t="s">
-        <v>587</v>
-      </c>
-    </row>
-    <row r="69" spans="1:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="A69" s="52" t="s">
-        <v>19</v>
-      </c>
-      <c r="B69" t="s">
-        <v>39</v>
-      </c>
-      <c r="C69" s="55" t="s">
-        <v>14</v>
-      </c>
-      <c r="D69" s="21" t="s">
-        <v>453</v>
-      </c>
-      <c r="E69" s="47" t="s">
-        <v>454</v>
-      </c>
-      <c r="F69" s="48" t="s">
-        <v>488</v>
-      </c>
-      <c r="G69" t="s">
-        <v>588</v>
-      </c>
-      <c r="H69" t="s">
-        <v>589</v>
-      </c>
-      <c r="I69" t="s">
-        <v>470</v>
-      </c>
-      <c r="J69" t="s">
-        <v>590</v>
-      </c>
-    </row>
-    <row r="70" spans="1:10" ht="45" x14ac:dyDescent="0.25">
-      <c r="A70" s="52" t="s">
-        <v>19</v>
-      </c>
-      <c r="B70" s="49" t="s">
-        <v>378</v>
-      </c>
-      <c r="C70" s="54" t="s">
-        <v>493</v>
-      </c>
-      <c r="D70" s="21" t="s">
-        <v>453</v>
-      </c>
-      <c r="E70" s="47" t="s">
-        <v>454</v>
-      </c>
-      <c r="F70" s="48" t="s">
-        <v>488</v>
-      </c>
-      <c r="G70" s="49" t="s">
-        <v>480</v>
-      </c>
-      <c r="H70" s="49" t="s">
-        <v>477</v>
-      </c>
-      <c r="I70" s="50" t="s">
-        <v>474</v>
-      </c>
-      <c r="J70" s="51" t="s">
-        <v>466</v>
-      </c>
-    </row>
-    <row r="71" spans="1:10" ht="45" x14ac:dyDescent="0.25">
-      <c r="A71" s="52" t="s">
-        <v>19</v>
-      </c>
-      <c r="B71" s="49" t="s">
-        <v>340</v>
-      </c>
-      <c r="C71" s="56" t="s">
-        <v>485</v>
-      </c>
-      <c r="D71" s="21" t="s">
-        <v>453</v>
-      </c>
-      <c r="E71" s="47" t="s">
-        <v>454</v>
-      </c>
-      <c r="F71" s="48" t="s">
-        <v>488</v>
-      </c>
-      <c r="G71" s="49" t="s">
-        <v>481</v>
-      </c>
-      <c r="H71" s="49" t="s">
-        <v>478</v>
-      </c>
-      <c r="I71" s="50" t="s">
-        <v>474</v>
-      </c>
-      <c r="J71" s="51" t="s">
-        <v>467</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:E2"/>
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="F1:I1"/>
-  </mergeCells>
-  <hyperlinks>
-    <hyperlink ref="C15" r:id="rId1" xr:uid="{294DB162-98E0-4B40-B781-02251F467A27}"/>
-    <hyperlink ref="C11" r:id="rId2" xr:uid="{8C07C59C-DA86-4C8D-9DA6-4A5AD6B80303}"/>
-    <hyperlink ref="C10" r:id="rId3" xr:uid="{B5671DF9-3065-42E2-9796-B313A496FC76}"/>
-    <hyperlink ref="C14" r:id="rId4" xr:uid="{E53E5D07-BD2D-4B6C-B0A0-EF6A87F85B42}"/>
-    <hyperlink ref="C70" r:id="rId5" xr:uid="{AC230D2C-F23B-4440-90A7-C101B0AB6EAB}"/>
-  </hyperlinks>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E0B35E6D-763F-4C40-91D2-473BE7766F62}">
-  <dimension ref="A1:B22"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="20.42578125" customWidth="1"/>
-    <col min="2" max="2" width="105.140625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>145</v>
       </c>
@@ -11543,7 +8728,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>24</v>
       </c>
@@ -11551,7 +8736,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>23</v>
       </c>
@@ -11559,7 +8744,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>149</v>
       </c>
@@ -11567,7 +8752,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>151</v>
       </c>
@@ -11575,7 +8760,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>80</v>
       </c>
@@ -11583,7 +8768,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>81</v>
       </c>
@@ -11591,7 +8776,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>155</v>
       </c>
@@ -11599,7 +8784,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>157</v>
       </c>
@@ -11607,7 +8792,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>44</v>
       </c>
@@ -11615,7 +8800,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>43</v>
       </c>
@@ -11623,7 +8808,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>21</v>
       </c>
@@ -11631,7 +8816,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>76</v>
       </c>
@@ -11639,7 +8824,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>40</v>
       </c>
@@ -11647,7 +8832,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>164</v>
       </c>
@@ -11655,7 +8840,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>166</v>
       </c>
@@ -11663,7 +8848,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>168</v>
       </c>
@@ -11671,7 +8856,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>170</v>
       </c>
@@ -11679,7 +8864,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>454</v>
       </c>
@@ -11687,7 +8872,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>453</v>
       </c>
@@ -11702,6 +8887,26 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="80b53ead-ac38-442a-b597-5a0e2e0802cd">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="5ec1cc48-4270-4222-9ed5-54ce9e59d47b" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010050398B8EA2737947995C227484EA02C8" ma:contentTypeVersion="17" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="bc9a2575e6c24a964f45b6e1606b04fd">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="80b53ead-ac38-442a-b597-5a0e2e0802cd" xmlns:ns3="5ec1cc48-4270-4222-9ed5-54ce9e59d47b" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="662112485a0135ca1785eae0908ad389" ns2:_="" ns3:_="">
     <xsd:import namespace="80b53ead-ac38-442a-b597-5a0e2e0802cd"/>
@@ -11938,27 +9143,26 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{66AF2240-620B-4312-9739-CAF731E4A98F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="80b53ead-ac38-442a-b597-5a0e2e0802cd"/>
+    <ds:schemaRef ds:uri="5ec1cc48-4270-4222-9ed5-54ce9e59d47b"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="80b53ead-ac38-442a-b597-5a0e2e0802cd">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="5ec1cc48-4270-4222-9ed5-54ce9e59d47b" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3B1B5D08-A2EB-4F47-BA81-DA28AA2A09F4}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{72DD370E-74FD-4D33-B5A7-49A7FE6518F7}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -11975,23 +9179,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3B1B5D08-A2EB-4F47-BA81-DA28AA2A09F4}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{66AF2240-620B-4312-9739-CAF731E4A98F}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="80b53ead-ac38-442a-b597-5a0e2e0802cd"/>
-    <ds:schemaRef ds:uri="5ec1cc48-4270-4222-9ed5-54ce9e59d47b"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>